--- a/src/otd_apply.xlsx
+++ b/src/otd_apply.xlsx
@@ -10607,12 +10607,12 @@
     <row r="142" customHeight="true" ht="15">
       <c r="A142" t="inlineStr">
         <is>
-          <t>JDYPR26092802423752LK10M-C1</t>
+          <t>JDYPR26092809143118LK10L-T4</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>审核中</t>
+          <t>已审核</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -10627,12 +10627,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>VYWB5252LK10M-C1</t>
+          <t>SPVYMB5518LK10L-T4</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>手提电脑包</t>
+          <t>旅行背包</t>
         </is>
       </c>
       <c r="G142" s="1" t="n">
@@ -10640,12 +10640,12 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>白家瑞</t>
+          <t>汪曦</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>4001#黑色(PU)/15.6寸</t>
+          <t>41#黑色/19.5寸/四件套</t>
         </is>
       </c>
       <c r="J142" s="1" t="n">
@@ -10664,12 +10664,12 @@
       <c r="O142"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>合成革高速线（计件）</t>
+          <t>布类高速线（计件）</t>
         </is>
       </c>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>英国 德国均断货 日均偏低 实际利润变体库存不足 需要备货</t>
+          <t>二推中，目前在提升单量毛利较低，另外有1300库存属于新变体在途，这次补货实际超限1100</t>
         </is>
       </c>
       <c r="R142"/>
@@ -10682,12 +10682,12 @@
     <row r="143" customHeight="true" ht="15">
       <c r="A143" t="inlineStr">
         <is>
-          <t>JDYPR260928024237B5252LKP1M</t>
+          <t>JDYPR26092809143118LKP2L-T4</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>审核中</t>
+          <t>已审核</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -10702,29 +10702,29 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>VYWB5252LKP1M</t>
+          <t>SPVYMB5518LKP2L-T4</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>手提电脑包</t>
+          <t>旅行背包</t>
         </is>
       </c>
       <c r="G143" s="1" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>白家瑞</t>
+          <t>汪曦</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>75#米白/4001#黑色/15.6寸</t>
+          <t>94#浅卡其色/234#卡其色/41#黑色/19.5寸/四件套</t>
         </is>
       </c>
       <c r="J143" s="1" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="K143" t="inlineStr">
         <is>
@@ -10732,7 +10732,7 @@
         </is>
       </c>
       <c r="L143" s="1" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="M143"/>
       <c r="N143"/>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="Q143" t="inlineStr">
         <is>
-          <t>英国 德国均断货 日均偏低 实际利润变体库存不足 需要备货</t>
+          <t>二推中，目前在提升单量毛利较低，另外有1300库存属于新变体在途，这次补货实际超限1100</t>
         </is>
       </c>
       <c r="R143"/>
@@ -10757,12 +10757,12 @@
     <row r="144" customHeight="true" ht="15">
       <c r="A144" t="inlineStr">
         <is>
-          <t>JDYPR260928024237B5252LKP3M</t>
+          <t>JDYPR26092809143118LKP2M-T4</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>审核中</t>
+          <t>已审核</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -10777,29 +10777,29 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>VYWB5252LKP3M</t>
+          <t>SPVYMB5518LKP2M-T4</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>手提电脑包</t>
+          <t>旅行背包</t>
         </is>
       </c>
       <c r="G144" s="1" t="n">
-        <v>100</v>
+        <v>1200</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>白家瑞</t>
+          <t>汪曦</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>154#裸色/9071#裸色/15.6寸</t>
+          <t>94#浅卡其色/234#卡其色/41#黑色/18.5寸/四件套</t>
         </is>
       </c>
       <c r="J144" s="1" t="n">
-        <v>100</v>
+        <v>1200</v>
       </c>
       <c r="K144" t="inlineStr">
         <is>
@@ -10807,7 +10807,7 @@
         </is>
       </c>
       <c r="L144" s="1" t="n">
-        <v>100</v>
+        <v>1200</v>
       </c>
       <c r="M144"/>
       <c r="N144"/>
@@ -10819,7 +10819,7 @@
       </c>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>英国 德国均断货 日均偏低 实际利润变体库存不足 需要备货</t>
+          <t>二推中，目前在提升单量毛利较低，另外有1300库存属于新变体在途，这次补货实际超限1100</t>
         </is>
       </c>
       <c r="R144"/>
@@ -10832,7 +10832,7 @@
     <row r="145" customHeight="true" ht="15">
       <c r="A145" t="inlineStr">
         <is>
-          <t>JDYPR26092809143118LK10L-T4</t>
+          <t>JDYPR26092809143118LKP3L-T4</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -10852,7 +10852,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>SPVYMB5518LK10L-T4</t>
+          <t>SPVYMB5518LKP3L-T4</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -10870,7 +10870,7 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>41#黑色/19.5寸/四件套</t>
+          <t>132#嫩绿色/350#米白色/190#深灰色/19.5寸/四件套</t>
         </is>
       </c>
       <c r="J145" s="1" t="n">
@@ -10907,7 +10907,7 @@
     <row r="146" customHeight="true" ht="15">
       <c r="A146" t="inlineStr">
         <is>
-          <t>JDYPR26092809143118LKP2L-T4</t>
+          <t>JDYPR26092809143118LKP4M-T4</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -10927,7 +10927,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>SPVYMB5518LKP2L-T4</t>
+          <t>SPVYMB5518LKP4M-T4</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -10936,7 +10936,7 @@
         </is>
       </c>
       <c r="G146" s="1" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
@@ -10945,11 +10945,11 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>94#浅卡其色/234#卡其色/41#黑色/19.5寸/四件套</t>
+          <t>旅行背包/287#浅蓝色/211#湖蓝色/41#黑色/18.5寸/四件套</t>
         </is>
       </c>
       <c r="J146" s="1" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="K146" t="inlineStr">
         <is>
@@ -10957,7 +10957,7 @@
         </is>
       </c>
       <c r="L146" s="1" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="M146"/>
       <c r="N146"/>
@@ -10982,7 +10982,7 @@
     <row r="147" customHeight="true" ht="15">
       <c r="A147" t="inlineStr">
         <is>
-          <t>JDYPR26092809143118LKP2M-T4</t>
+          <t>JDYPR26092809143118LKP5M-T4</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11002,7 +11002,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>SPVYMB5518LKP2M-T4</t>
+          <t>SPVYMB5518LKP5M-T4</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -11011,7 +11011,7 @@
         </is>
       </c>
       <c r="G147" s="1" t="n">
-        <v>1200</v>
+        <v>200</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
@@ -11020,11 +11020,11 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>94#浅卡其色/234#卡其色/41#黑色/18.5寸/四件套</t>
+          <t>旅行背包/127#浅粉色/20#紫色/41#黑色/18.5寸/四件套</t>
         </is>
       </c>
       <c r="J147" s="1" t="n">
-        <v>1200</v>
+        <v>200</v>
       </c>
       <c r="K147" t="inlineStr">
         <is>
@@ -11032,7 +11032,7 @@
         </is>
       </c>
       <c r="L147" s="1" t="n">
-        <v>1200</v>
+        <v>200</v>
       </c>
       <c r="M147"/>
       <c r="N147"/>
@@ -11057,12 +11057,12 @@
     <row r="148" customHeight="true" ht="15">
       <c r="A148" t="inlineStr">
         <is>
-          <t>JDYPR26092809143118LKP3L-T4</t>
+          <t>JDYPR26100904101312LK80M-C1</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>已审核</t>
+          <t>创建</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -11072,17 +11072,17 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026/9/29</t>
+          <t>2026/10/9</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>SPVYMB5518LKP3L-T4</t>
+          <t>SPVYWB1512LK80M-C1</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>旅行背包</t>
+          <t>圆顶贝壳包</t>
         </is>
       </c>
       <c r="G148" s="1" t="n">
@@ -11090,12 +11090,12 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>汪曦</t>
+          <t>姚鲜珍</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>132#嫩绿色/350#米白色/190#深灰色/19.5寸/四件套</t>
+          <t>8089#黄棕色（压花）/中号</t>
         </is>
       </c>
       <c r="J148" s="1" t="n">
@@ -11103,7 +11103,7 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>2026/10/28 00:00:00</t>
+          <t>2026/11/8 00:00:00</t>
         </is>
       </c>
       <c r="L148" s="1" t="n">
@@ -11114,12 +11114,12 @@
       <c r="O148"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>布类高速线（计件）</t>
+          <t>合成革高速线（计件）</t>
         </is>
       </c>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>二推中，目前在提升单量毛利较低，另外有1300库存属于新变体在途，这次补货实际超限1100</t>
+          <t>常规补货</t>
         </is>
       </c>
       <c r="R148"/>
@@ -11132,12 +11132,12 @@
     <row r="149" customHeight="true" ht="15">
       <c r="A149" t="inlineStr">
         <is>
-          <t>JDYPR26092809143118LKP4M-T4</t>
+          <t>JDYPR261009041013B1512LK01M</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>已审核</t>
+          <t>创建</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -11147,17 +11147,17 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026/9/29</t>
+          <t>2026/10/9</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>SPVYMB5518LKP4M-T4</t>
+          <t>SPVYWB1512LK01M</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>旅行背包</t>
+          <t>圆顶贝壳包</t>
         </is>
       </c>
       <c r="G149" s="1" t="n">
@@ -11165,12 +11165,12 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>汪曦</t>
+          <t>姚鲜珍</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>旅行背包/287#浅蓝色/211#湖蓝色/41#黑色/18.5寸/四件套</t>
+          <t>黑色</t>
         </is>
       </c>
       <c r="J149" s="1" t="n">
@@ -11178,7 +11178,7 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>2026/10/28 00:00:00</t>
+          <t>2026/11/8 00:00:00</t>
         </is>
       </c>
       <c r="L149" s="1" t="n">
@@ -11189,12 +11189,12 @@
       <c r="O149"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>布类高速线（计件）</t>
+          <t>合成革高速线（计件）</t>
         </is>
       </c>
       <c r="Q149" t="inlineStr">
         <is>
-          <t>二推中，目前在提升单量毛利较低，另外有1300库存属于新变体在途，这次补货实际超限1100</t>
+          <t>常规补货</t>
         </is>
       </c>
       <c r="R149"/>
@@ -11207,12 +11207,12 @@
     <row r="150" customHeight="true" ht="15">
       <c r="A150" t="inlineStr">
         <is>
-          <t>JDYPR26092809143118LKP5M-T4</t>
+          <t>JDYPR261009041013B1512LK03M</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>已审核</t>
+          <t>创建</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -11222,54 +11222,54 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026/9/29</t>
+          <t>2026/10/9</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>SPVYMB5518LKP5M-T4</t>
+          <t>SPVYWB1512LK03M</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>旅行背包</t>
+          <t>圆顶贝壳包</t>
         </is>
       </c>
       <c r="G150" s="1" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>汪曦</t>
+          <t>姚鲜珍</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>旅行背包/127#浅粉色/20#紫色/41#黑色/18.5寸/四件套</t>
+          <t>米色配黑色</t>
         </is>
       </c>
       <c r="J150" s="1" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>2026/10/28 00:00:00</t>
+          <t>2026/11/8 00:00:00</t>
         </is>
       </c>
       <c r="L150" s="1" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="M150"/>
       <c r="N150"/>
       <c r="O150"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>布类高速线（计件）</t>
+          <t>合成革高速线（计件）</t>
         </is>
       </c>
       <c r="Q150" t="inlineStr">
         <is>
-          <t>二推中，目前在提升单量毛利较低，另外有1300库存属于新变体在途，这次补货实际超限1100</t>
+          <t>常规补货</t>
         </is>
       </c>
       <c r="R150"/>
@@ -11282,7 +11282,7 @@
     <row r="151" customHeight="true" ht="15">
       <c r="A151" t="inlineStr">
         <is>
-          <t>JDYPR26100904101312LK80M-C1</t>
+          <t>JDYPR261009041013B1512LK04M</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11302,7 +11302,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>SPVYWB1512LK80M-C1</t>
+          <t>SPVYWB1512LK04M</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -11320,7 +11320,7 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>8089#黄棕色（压花）/中号</t>
+          <t>米白配粉色</t>
         </is>
       </c>
       <c r="J151" s="1" t="n">
@@ -11357,7 +11357,7 @@
     <row r="152" customHeight="true" ht="15">
       <c r="A152" t="inlineStr">
         <is>
-          <t>JDYPR261009041013B1512LK01M</t>
+          <t>JDYPR261009041013B1512LK06M</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -11377,7 +11377,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>SPVYWB1512LK01M</t>
+          <t>SPVYWB1512LK06M</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -11386,7 +11386,7 @@
         </is>
       </c>
       <c r="G152" s="1" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
@@ -11395,11 +11395,11 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>黑色</t>
+          <t>深蓝</t>
         </is>
       </c>
       <c r="J152" s="1" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K152" t="inlineStr">
         <is>
@@ -11407,7 +11407,7 @@
         </is>
       </c>
       <c r="L152" s="1" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="M152"/>
       <c r="N152"/>
@@ -11432,7 +11432,7 @@
     <row r="153" customHeight="true" ht="15">
       <c r="A153" t="inlineStr">
         <is>
-          <t>JDYPR261009041013B1512LK03M</t>
+          <t>JDYPR261009041013B1512LK10L</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>SPVYWB1512LK03M</t>
+          <t>SPVYWB1512LK10L</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -11470,7 +11470,7 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>米色配黑色</t>
+          <t>11#大红色/大号</t>
         </is>
       </c>
       <c r="J153" s="1" t="n">
@@ -11507,7 +11507,7 @@
     <row r="154" customHeight="true" ht="15">
       <c r="A154" t="inlineStr">
         <is>
-          <t>JDYPR261009041013B1512LK04M</t>
+          <t>JDYPR261009041013B1512LK18M</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -11527,7 +11527,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>SPVYWB1512LK04M</t>
+          <t>SPVYWB1512LK18M</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -11545,7 +11545,7 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>米白配粉色</t>
+          <t>棕色</t>
         </is>
       </c>
       <c r="J154" s="1" t="n">
@@ -11582,7 +11582,7 @@
     <row r="155" customHeight="true" ht="15">
       <c r="A155" t="inlineStr">
         <is>
-          <t>JDYPR261009041013B1512LK06M</t>
+          <t>JDYPR261009041013B1512LK29M</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -11602,7 +11602,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>SPVYWB1512LK06M</t>
+          <t>SPVYWB1512LK29M</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -11620,7 +11620,7 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>深蓝</t>
+          <t>186#裸色</t>
         </is>
       </c>
       <c r="J155" s="1" t="n">
@@ -11657,12 +11657,12 @@
     <row r="156" customHeight="true" ht="15">
       <c r="A156" t="inlineStr">
         <is>
-          <t>JDYPR261009041013B1512LK10L</t>
+          <t>JDYPR26101007430316LK90M-X1</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>创建</t>
+          <t>已审核</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -11672,21 +11672,21 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026/10/9</t>
+          <t>2026/10/11</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>SPVYWB1512LK10L</t>
+          <t>SPVYUB4416LK90M-X1</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>圆顶贝壳包</t>
+          <t>拉杆箱</t>
         </is>
       </c>
       <c r="G156" s="1" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="H156" t="inlineStr">
         <is>
@@ -11695,31 +11695,31 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>11#大红色/大号</t>
+          <t>72#深绿色(菱形格绣线)/小号</t>
         </is>
       </c>
       <c r="J156" s="1" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>2026/11/8 00:00:00</t>
+          <t>2026/11/9 00:00:00</t>
         </is>
       </c>
       <c r="L156" s="1" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="M156"/>
       <c r="N156"/>
       <c r="O156"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>合成革高速线（计件）</t>
+          <t>拉杆箱组装线</t>
         </is>
       </c>
       <c r="Q156" t="inlineStr">
         <is>
-          <t>常规补货</t>
+          <t>常规备货（做货周期长）</t>
         </is>
       </c>
       <c r="R156"/>
@@ -11732,12 +11732,12 @@
     <row r="157" customHeight="true" ht="15">
       <c r="A157" t="inlineStr">
         <is>
-          <t>JDYPR261009041013B1512LK18M</t>
+          <t>JDYPR261010074303B4416LK10M</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>创建</t>
+          <t>已审核</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -11747,21 +11747,21 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026/10/9</t>
+          <t>2026/10/11</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>SPVYWB1512LK18M</t>
+          <t>SPVYUB4416LK10M</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>圆顶贝壳包</t>
+          <t>拉杆箱</t>
         </is>
       </c>
       <c r="G157" s="1" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H157" t="inlineStr">
         <is>
@@ -11770,31 +11770,31 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>棕色</t>
+          <t>48#黑色/小号</t>
         </is>
       </c>
       <c r="J157" s="1" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>2026/11/8 00:00:00</t>
+          <t>2026/11/9 00:00:00</t>
         </is>
       </c>
       <c r="L157" s="1" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="M157"/>
       <c r="N157"/>
       <c r="O157"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>合成革高速线（计件）</t>
+          <t>拉杆箱组装线</t>
         </is>
       </c>
       <c r="Q157" t="inlineStr">
         <is>
-          <t>常规补货</t>
+          <t>常规备货（做货周期长）</t>
         </is>
       </c>
       <c r="R157"/>
@@ -11807,12 +11807,12 @@
     <row r="158" customHeight="true" ht="15">
       <c r="A158" t="inlineStr">
         <is>
-          <t>JDYPR261009041013B1512LK29M</t>
+          <t>JDYPR261010074303B4416LKP1M</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>创建</t>
+          <t>已审核</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -11822,17 +11822,17 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026/10/9</t>
+          <t>2026/10/11</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>SPVYWB1512LK29M</t>
+          <t>SPVYUB4416LKP1M</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>圆顶贝壳包</t>
+          <t>拉杆箱</t>
         </is>
       </c>
       <c r="G158" s="1" t="n">
@@ -11845,7 +11845,7 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>186#裸色</t>
+          <t>4125-pvc-黑色/73#米白/8123D#板栗棕/小号</t>
         </is>
       </c>
       <c r="J158" s="1" t="n">
@@ -11853,7 +11853,7 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>2026/11/8 00:00:00</t>
+          <t>2026/11/9 00:00:00</t>
         </is>
       </c>
       <c r="L158" s="1" t="n">
@@ -11864,12 +11864,12 @@
       <c r="O158"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>合成革高速线（计件）</t>
+          <t>拉杆箱组装线</t>
         </is>
       </c>
       <c r="Q158" t="inlineStr">
         <is>
-          <t>常规补货</t>
+          <t>常规备货（做货周期长）</t>
         </is>
       </c>
       <c r="R158"/>
@@ -11882,7 +11882,7 @@
     <row r="159" customHeight="true" ht="15">
       <c r="A159" t="inlineStr">
         <is>
-          <t>JDYPR26101007430316LK90M-X1</t>
+          <t>JDYPR261010074303B4416LKP2M</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -11902,7 +11902,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>SPVYUB4416LK90M-X1</t>
+          <t>SPVYUB4416LKP2M</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -11911,7 +11911,7 @@
         </is>
       </c>
       <c r="G159" s="1" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="H159" t="inlineStr">
         <is>
@@ -11920,11 +11920,11 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>72#深绿色(菱形格绣线)/小号</t>
+          <t>4125-pvc-黑色/8123D#板栗棕/小号</t>
         </is>
       </c>
       <c r="J159" s="1" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="K159" t="inlineStr">
         <is>
@@ -11932,7 +11932,7 @@
         </is>
       </c>
       <c r="L159" s="1" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="M159"/>
       <c r="N159"/>
@@ -11957,7 +11957,7 @@
     <row r="160" customHeight="true" ht="15">
       <c r="A160" t="inlineStr">
         <is>
-          <t>JDYPR261010074303B4416LK10M</t>
+          <t>JDYPR261010074303B4416LKP5M</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -11977,7 +11977,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>SPVYUB4416LK10M</t>
+          <t>SPVYUB4416LKP5M</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -11986,7 +11986,7 @@
         </is>
       </c>
       <c r="G160" s="1" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H160" t="inlineStr">
         <is>
@@ -11995,11 +11995,11 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>48#黑色/小号</t>
+          <t>213#米白/284#卡其/小号</t>
         </is>
       </c>
       <c r="J160" s="1" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K160" t="inlineStr">
         <is>
@@ -12007,7 +12007,7 @@
         </is>
       </c>
       <c r="L160" s="1" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="M160"/>
       <c r="N160"/>
@@ -12032,12 +12032,12 @@
     <row r="161" customHeight="true" ht="15">
       <c r="A161" t="inlineStr">
         <is>
-          <t>JDYPR261010074303B4416LKP1M</t>
+          <t>JDYPR261010091000B5771LK10L</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>已审核</t>
+          <t>创建</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -12047,54 +12047,54 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026/10/11</t>
+          <t>2026/10/10</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>SPVYUB4416LKP1M</t>
+          <t>SPVYUB5771LK10L</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>拉杆箱</t>
+          <t>午餐包</t>
         </is>
       </c>
       <c r="G161" s="1" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>姚鲜珍</t>
+          <t>李小平</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>4125-pvc-黑色/73#米白/8123D#板栗棕/小号</t>
+          <t>1#黑色（菱形格绣线）/大号</t>
         </is>
       </c>
       <c r="J161" s="1" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>2026/11/9 00:00:00</t>
+          <t>2026/11/8 00:00:00</t>
         </is>
       </c>
       <c r="L161" s="1" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="M161"/>
       <c r="N161"/>
       <c r="O161"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>拉杆箱组装线</t>
+          <t>午餐包生产线</t>
         </is>
       </c>
       <c r="Q161" t="inlineStr">
         <is>
-          <t>常规备货（做货周期长）</t>
+          <t>午餐包首批返单，超限变体断货已久</t>
         </is>
       </c>
       <c r="R161"/>
@@ -12107,12 +12107,12 @@
     <row r="162" customHeight="true" ht="15">
       <c r="A162" t="inlineStr">
         <is>
-          <t>JDYPR261010074303B4416LKP2M</t>
+          <t>JDYPR261010091000B5771LK10M</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>已审核</t>
+          <t>创建</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -12122,54 +12122,54 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026/10/11</t>
+          <t>2026/10/10</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>SPVYUB4416LKP2M</t>
+          <t>SPVYUB5771LK10M</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>拉杆箱</t>
+          <t>午餐包</t>
         </is>
       </c>
       <c r="G162" s="1" t="n">
-        <v>250</v>
+        <v>296</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>姚鲜珍</t>
+          <t>李小平</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>4125-pvc-黑色/8123D#板栗棕/小号</t>
+          <t>1#黑色（菱形格绣线）/小号</t>
         </is>
       </c>
       <c r="J162" s="1" t="n">
-        <v>250</v>
+        <v>296</v>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>2026/11/9 00:00:00</t>
+          <t>2026/11/8 00:00:00</t>
         </is>
       </c>
       <c r="L162" s="1" t="n">
-        <v>250</v>
+        <v>296</v>
       </c>
       <c r="M162"/>
       <c r="N162"/>
       <c r="O162"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>拉杆箱组装线</t>
+          <t>午餐包生产线</t>
         </is>
       </c>
       <c r="Q162" t="inlineStr">
         <is>
-          <t>常规备货（做货周期长）</t>
+          <t>午餐包首批返单，超限变体断货已久(SPVYUB5771LK10M平衡利库调拨，修改时间2026-10-14 11:27:17，调整前申请数量：300.0；调整后申请数量：296.0;)</t>
         </is>
       </c>
       <c r="R162"/>
@@ -12182,12 +12182,12 @@
     <row r="163" customHeight="true" ht="15">
       <c r="A163" t="inlineStr">
         <is>
-          <t>JDYPR261010074303B4416LKP5M</t>
+          <t>JDYPR261010091000B5771LK20M</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>已审核</t>
+          <t>创建</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -12197,17 +12197,17 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026/10/11</t>
+          <t>2026/10/10</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>SPVYUB4416LKP5M</t>
+          <t>SPVYUB5771LK20M</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>拉杆箱</t>
+          <t>午餐包</t>
         </is>
       </c>
       <c r="G163" s="1" t="n">
@@ -12215,12 +12215,12 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>姚鲜珍</t>
+          <t>李小平</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>213#米白/284#卡其/小号</t>
+          <t>98#裸色（菱形格绣线）/小号</t>
         </is>
       </c>
       <c r="J163" s="1" t="n">
@@ -12228,7 +12228,7 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>2026/11/9 00:00:00</t>
+          <t>2026/11/8 00:00:00</t>
         </is>
       </c>
       <c r="L163" s="1" t="n">
@@ -12239,12 +12239,12 @@
       <c r="O163"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>拉杆箱组装线</t>
+          <t>午餐包生产线</t>
         </is>
       </c>
       <c r="Q163" t="inlineStr">
         <is>
-          <t>常规备货（做货周期长）</t>
+          <t>午餐包首批返单，超限变体断货已久</t>
         </is>
       </c>
       <c r="R163"/>
@@ -12257,7 +12257,7 @@
     <row r="164" customHeight="true" ht="15">
       <c r="A164" t="inlineStr">
         <is>
-          <t>JDYPR261010091000B5771LK10L</t>
+          <t>JDYPR261010091000B5771LKP1M</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -12277,7 +12277,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>SPVYUB5771LK10L</t>
+          <t>SPVYUB5771LKP1M</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -12286,7 +12286,7 @@
         </is>
       </c>
       <c r="G164" s="1" t="n">
-        <v>150</v>
+        <v>992</v>
       </c>
       <c r="H164" t="inlineStr">
         <is>
@@ -12295,11 +12295,11 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>1#黑色（菱形格绣线）/大号</t>
+          <t>78#米白色/1#黑色（菱形格绣线）/93#红棕色/小号</t>
         </is>
       </c>
       <c r="J164" s="1" t="n">
-        <v>150</v>
+        <v>992</v>
       </c>
       <c r="K164" t="inlineStr">
         <is>
@@ -12307,7 +12307,7 @@
         </is>
       </c>
       <c r="L164" s="1" t="n">
-        <v>150</v>
+        <v>992</v>
       </c>
       <c r="M164"/>
       <c r="N164"/>
@@ -12319,7 +12319,7 @@
       </c>
       <c r="Q164" t="inlineStr">
         <is>
-          <t>午餐包首批返单，超限变体断货已久</t>
+          <t>午餐包首批返单，超限变体断货已久(SPVYUB5771LKP1M平衡利库调拨，修改时间2026-10-14 11:27:14，调整前申请数量：1000.0；调整后申请数量：992.0;)</t>
         </is>
       </c>
       <c r="R164"/>
@@ -12332,7 +12332,7 @@
     <row r="165" customHeight="true" ht="15">
       <c r="A165" t="inlineStr">
         <is>
-          <t>JDYPR261010091000B5771LK10M</t>
+          <t>JDYPR261010091000B5771LKP2L</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -12352,7 +12352,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>SPVYUB5771LK10M</t>
+          <t>SPVYUB5771LKP2L</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -12361,7 +12361,7 @@
         </is>
       </c>
       <c r="G165" s="1" t="n">
-        <v>296</v>
+        <v>100</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
@@ -12370,11 +12370,11 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>1#黑色（菱形格绣线）/小号</t>
+          <t>78#米白色/48#豆绿色（菱形格绣线）/357#橄榄绿/大号</t>
         </is>
       </c>
       <c r="J165" s="1" t="n">
-        <v>296</v>
+        <v>100</v>
       </c>
       <c r="K165" t="inlineStr">
         <is>
@@ -12382,7 +12382,7 @@
         </is>
       </c>
       <c r="L165" s="1" t="n">
-        <v>296</v>
+        <v>100</v>
       </c>
       <c r="M165"/>
       <c r="N165"/>
@@ -12394,7 +12394,7 @@
       </c>
       <c r="Q165" t="inlineStr">
         <is>
-          <t>午餐包首批返单，超限变体断货已久(SPVYUB5771LK10M平衡利库调拨，修改时间2026-10-14 11:27:17，调整前申请数量：300.0；调整后申请数量：296.0;)</t>
+          <t>午餐包首批返单，超限变体断货已久</t>
         </is>
       </c>
       <c r="R165"/>
@@ -12407,7 +12407,7 @@
     <row r="166" customHeight="true" ht="15">
       <c r="A166" t="inlineStr">
         <is>
-          <t>JDYPR261010091000B5771LK20M</t>
+          <t>JDYPR261010091000B5771LKP2M</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -12427,7 +12427,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>SPVYUB5771LK20M</t>
+          <t>SPVYUB5771LKP2M</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -12436,7 +12436,7 @@
         </is>
       </c>
       <c r="G166" s="1" t="n">
-        <v>100</v>
+        <v>396</v>
       </c>
       <c r="H166" t="inlineStr">
         <is>
@@ -12445,11 +12445,11 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>98#裸色（菱形格绣线）/小号</t>
+          <t>78#米白色/48#豆绿色（菱形格绣线）/357#橄榄绿/小号</t>
         </is>
       </c>
       <c r="J166" s="1" t="n">
-        <v>100</v>
+        <v>396</v>
       </c>
       <c r="K166" t="inlineStr">
         <is>
@@ -12457,7 +12457,7 @@
         </is>
       </c>
       <c r="L166" s="1" t="n">
-        <v>100</v>
+        <v>396</v>
       </c>
       <c r="M166"/>
       <c r="N166"/>
@@ -12469,7 +12469,7 @@
       </c>
       <c r="Q166" t="inlineStr">
         <is>
-          <t>午餐包首批返单，超限变体断货已久</t>
+          <t>午餐包首批返单，超限变体断货已久(SPVYUB5771LKP2M平衡利库调拨，修改时间2026-10-14 11:27:09，调整前申请数量：400.0；调整后申请数量：396.0;)</t>
         </is>
       </c>
       <c r="R166"/>
@@ -12482,7 +12482,7 @@
     <row r="167" customHeight="true" ht="15">
       <c r="A167" t="inlineStr">
         <is>
-          <t>JDYPR261010091000B5771LKP1M</t>
+          <t>JDYPR261010091000B5771LKP3M</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -12502,7 +12502,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>SPVYUB5771LKP1M</t>
+          <t>SPVYUB5771LKP3M</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -12511,7 +12511,7 @@
         </is>
       </c>
       <c r="G167" s="1" t="n">
-        <v>992</v>
+        <v>150</v>
       </c>
       <c r="H167" t="inlineStr">
         <is>
@@ -12520,11 +12520,11 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>78#米白色/1#黑色（菱形格绣线）/93#红棕色/小号</t>
+          <t>78#米白色/104#浅卡其（菱形格绣线）/64#卡其/小号</t>
         </is>
       </c>
       <c r="J167" s="1" t="n">
-        <v>992</v>
+        <v>150</v>
       </c>
       <c r="K167" t="inlineStr">
         <is>
@@ -12532,7 +12532,7 @@
         </is>
       </c>
       <c r="L167" s="1" t="n">
-        <v>992</v>
+        <v>150</v>
       </c>
       <c r="M167"/>
       <c r="N167"/>
@@ -12544,7 +12544,7 @@
       </c>
       <c r="Q167" t="inlineStr">
         <is>
-          <t>午餐包首批返单，超限变体断货已久(SPVYUB5771LKP1M平衡利库调拨，修改时间2026-10-14 11:27:14，调整前申请数量：1000.0；调整后申请数量：992.0;)</t>
+          <t>午餐包首批返单，超限变体断货已久</t>
         </is>
       </c>
       <c r="R167"/>
@@ -12557,7 +12557,7 @@
     <row r="168" customHeight="true" ht="15">
       <c r="A168" t="inlineStr">
         <is>
-          <t>JDYPR261010091000B5771LKP2L</t>
+          <t>JDYPR261010091000B5771LKP4L</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -12577,7 +12577,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>SPVYUB5771LKP2L</t>
+          <t>SPVYUB5771LKP4L</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -12595,7 +12595,7 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>78#米白色/48#豆绿色（菱形格绣线）/357#橄榄绿/大号</t>
+          <t>78#米白色/353#紫罗兰（菱形格绣线）/66#深紫/大号</t>
         </is>
       </c>
       <c r="J168" s="1" t="n">
@@ -12632,7 +12632,7 @@
     <row r="169" customHeight="true" ht="15">
       <c r="A169" t="inlineStr">
         <is>
-          <t>JDYPR261010091000B5771LKP2M</t>
+          <t>JDYPR261010091000B5771LKP4M</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -12652,7 +12652,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>SPVYUB5771LKP2M</t>
+          <t>SPVYUB5771LKP4M</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -12661,7 +12661,7 @@
         </is>
       </c>
       <c r="G169" s="1" t="n">
-        <v>396</v>
+        <v>100</v>
       </c>
       <c r="H169" t="inlineStr">
         <is>
@@ -12670,11 +12670,11 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>78#米白色/48#豆绿色（菱形格绣线）/357#橄榄绿/小号</t>
+          <t>78#米白色/353#紫罗兰（菱形格绣线）/66#深紫/小号</t>
         </is>
       </c>
       <c r="J169" s="1" t="n">
-        <v>396</v>
+        <v>100</v>
       </c>
       <c r="K169" t="inlineStr">
         <is>
@@ -12682,7 +12682,7 @@
         </is>
       </c>
       <c r="L169" s="1" t="n">
-        <v>396</v>
+        <v>100</v>
       </c>
       <c r="M169"/>
       <c r="N169"/>
@@ -12694,7 +12694,7 @@
       </c>
       <c r="Q169" t="inlineStr">
         <is>
-          <t>午餐包首批返单，超限变体断货已久(SPVYUB5771LKP2M平衡利库调拨，修改时间2026-10-14 11:27:09，调整前申请数量：400.0；调整后申请数量：396.0;)</t>
+          <t>午餐包首批返单，超限变体断货已久</t>
         </is>
       </c>
       <c r="R169"/>
@@ -12707,7 +12707,7 @@
     <row r="170" customHeight="true" ht="15">
       <c r="A170" t="inlineStr">
         <is>
-          <t>JDYPR261010091000B5771LKP3M</t>
+          <t>JDYPR261010091000B5771LKP5L</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -12727,7 +12727,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>SPVYUB5771LKP3M</t>
+          <t>SPVYUB5771LKP5L</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -12736,7 +12736,7 @@
         </is>
       </c>
       <c r="G170" s="1" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="H170" t="inlineStr">
         <is>
@@ -12745,11 +12745,11 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>78#米白色/104#浅卡其（菱形格绣线）/64#卡其/小号</t>
+          <t>43#米白色/36#紫色（菱形格绣线）/56#粉色/大号</t>
         </is>
       </c>
       <c r="J170" s="1" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="K170" t="inlineStr">
         <is>
@@ -12757,7 +12757,7 @@
         </is>
       </c>
       <c r="L170" s="1" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="M170"/>
       <c r="N170"/>
@@ -12782,7 +12782,7 @@
     <row r="171" customHeight="true" ht="15">
       <c r="A171" t="inlineStr">
         <is>
-          <t>JDYPR261010091000B5771LKP4L</t>
+          <t>JDYPR261010091130B5771LKP5M</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -12802,7 +12802,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>SPVYUB5771LKP4L</t>
+          <t>SPVYUB5771LKP5M</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -12811,7 +12811,7 @@
         </is>
       </c>
       <c r="G171" s="1" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="H171" t="inlineStr">
         <is>
@@ -12820,11 +12820,11 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>78#米白色/353#紫罗兰（菱形格绣线）/66#深紫/大号</t>
+          <t>43#米白色/36#紫色（菱形格绣线）/56#粉色/小号</t>
         </is>
       </c>
       <c r="J171" s="1" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="K171" t="inlineStr">
         <is>
@@ -12832,7 +12832,7 @@
         </is>
       </c>
       <c r="L171" s="1" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="M171"/>
       <c r="N171"/>
@@ -12857,12 +12857,12 @@
     <row r="172" customHeight="true" ht="15">
       <c r="A172" t="inlineStr">
         <is>
-          <t>JDYPR261010091000B5771LKP4M</t>
+          <t>JDYPR261012111150B5036LK10M</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>创建</t>
+          <t>已审核</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -12872,54 +12872,54 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2026/10/10</t>
+          <t>2026/10/12</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>SPVYUB5771LKP4M</t>
+          <t>SPVYWB5036LK10M</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>午餐包</t>
+          <t>托特包</t>
         </is>
       </c>
       <c r="G172" s="1" t="n">
-        <v>100</v>
+        <v>1050</v>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>李小平</t>
+          <t>阳金灿</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>78#米白色/353#紫罗兰（菱形格绣线）/66#深紫/小号</t>
+          <t>48#黑色/15.6寸</t>
         </is>
       </c>
       <c r="J172" s="1" t="n">
-        <v>100</v>
+        <v>1050</v>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>2026/11/8 00:00:00</t>
+          <t>2026/11/11 00:00:00</t>
         </is>
       </c>
       <c r="L172" s="1" t="n">
-        <v>100</v>
+        <v>1050</v>
       </c>
       <c r="M172"/>
       <c r="N172"/>
       <c r="O172"/>
       <c r="P172" t="inlineStr">
         <is>
-          <t>午餐包生产线</t>
+          <t>丝棉包生产线</t>
         </is>
       </c>
       <c r="Q172" t="inlineStr">
         <is>
-          <t>午餐包首批返单，超限变体断货已久</t>
+          <t>新增绿色大号变体</t>
         </is>
       </c>
       <c r="R172"/>
@@ -12932,12 +12932,12 @@
     <row r="173" customHeight="true" ht="15">
       <c r="A173" t="inlineStr">
         <is>
-          <t>JDYPR261010091000B5771LKP5L</t>
+          <t>JDYPR261012111150B5036LKP2M</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>创建</t>
+          <t>已审核</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -12947,17 +12947,17 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2026/10/10</t>
+          <t>2026/10/12</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>SPVYUB5771LKP5L</t>
+          <t>SPVYWB5036LKP2M</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>午餐包</t>
+          <t>托特包</t>
         </is>
       </c>
       <c r="G173" s="1" t="n">
@@ -12965,12 +12965,12 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>李小平</t>
+          <t>阳金灿</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>43#米白色/36#紫色（菱形格绣线）/56#粉色/大号</t>
+          <t>213#米白/48#黑色/A2#板栗棕/15.6寸</t>
         </is>
       </c>
       <c r="J173" s="1" t="n">
@@ -12978,7 +12978,7 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>2026/11/8 00:00:00</t>
+          <t>2026/11/11 00:00:00</t>
         </is>
       </c>
       <c r="L173" s="1" t="n">
@@ -12989,12 +12989,12 @@
       <c r="O173"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>午餐包生产线</t>
+          <t>丝棉包生产线</t>
         </is>
       </c>
       <c r="Q173" t="inlineStr">
         <is>
-          <t>午餐包首批返单，超限变体断货已久</t>
+          <t>新增绿色大号变体(SPVYWB5036LKP2M平衡利库调拨，修改时间2026-10-14 10:40:37，调整前申请数量：100.0；调整后申请数量：91.0;)</t>
         </is>
       </c>
       <c r="R173"/>
@@ -13007,12 +13007,12 @@
     <row r="174" customHeight="true" ht="15">
       <c r="A174" t="inlineStr">
         <is>
-          <t>JDYPR261010091130B5771LKP5M</t>
+          <t>JDYPR261012111912B5036LK10L</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>创建</t>
+          <t>已审核</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -13022,54 +13022,54 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2026/10/10</t>
+          <t>2026/10/12</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>SPVYUB5771LKP5M</t>
+          <t>SPVYWB5036LK10L</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>午餐包</t>
+          <t>托特包</t>
         </is>
       </c>
       <c r="G174" s="1" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>李小平</t>
+          <t>阳金灿</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>43#米白色/36#紫色（菱形格绣线）/56#粉色/小号</t>
+          <t>48#黑色/17.3寸</t>
         </is>
       </c>
       <c r="J174" s="1" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>2026/11/8 00:00:00</t>
+          <t>2026/11/11 00:00:00</t>
         </is>
       </c>
       <c r="L174" s="1" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="M174"/>
       <c r="N174"/>
       <c r="O174"/>
       <c r="P174" t="inlineStr">
         <is>
-          <t>午餐包生产线</t>
+          <t>丝棉包生产线</t>
         </is>
       </c>
       <c r="Q174" t="inlineStr">
         <is>
-          <t>午餐包首批返单，超限变体断货已久</t>
+          <t>新增绿色大号变体</t>
         </is>
       </c>
       <c r="R174"/>
@@ -13082,7 +13082,7 @@
     <row r="175" customHeight="true" ht="15">
       <c r="A175" t="inlineStr">
         <is>
-          <t>JDYPR261012111150B5036LK10M</t>
+          <t>JDYPR261012111912B5036LK42L</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13102,7 +13102,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>SPVYWB5036LK10M</t>
+          <t>SPVYWB5036LK42L</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -13111,7 +13111,7 @@
         </is>
       </c>
       <c r="G175" s="1" t="n">
-        <v>1050</v>
+        <v>100</v>
       </c>
       <c r="H175" t="inlineStr">
         <is>
@@ -13120,11 +13120,11 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>48#黑色/15.6寸</t>
+          <t>138#裸色/17.3寸</t>
         </is>
       </c>
       <c r="J175" s="1" t="n">
-        <v>1050</v>
+        <v>100</v>
       </c>
       <c r="K175" t="inlineStr">
         <is>
@@ -13132,7 +13132,7 @@
         </is>
       </c>
       <c r="L175" s="1" t="n">
-        <v>1050</v>
+        <v>100</v>
       </c>
       <c r="M175"/>
       <c r="N175"/>
@@ -13157,7 +13157,7 @@
     <row r="176" customHeight="true" ht="15">
       <c r="A176" t="inlineStr">
         <is>
-          <t>JDYPR261012111150B5036LKP2M</t>
+          <t>JDYPR261012111912B5036LK42M</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13177,7 +13177,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>SPVYWB5036LKP2M</t>
+          <t>SPVYWB5036LK42M</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -13195,7 +13195,7 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>213#米白/48#黑色/A2#板栗棕/15.6寸</t>
+          <t>138#裸色/15.6寸</t>
         </is>
       </c>
       <c r="J176" s="1" t="n">
@@ -13219,7 +13219,7 @@
       </c>
       <c r="Q176" t="inlineStr">
         <is>
-          <t>新增绿色大号变体(SPVYWB5036LKP2M平衡利库调拨，修改时间2026-10-14 10:40:37，调整前申请数量：100.0；调整后申请数量：91.0;)</t>
+          <t>新增绿色大号变体</t>
         </is>
       </c>
       <c r="R176"/>
@@ -13232,7 +13232,7 @@
     <row r="177" customHeight="true" ht="15">
       <c r="A177" t="inlineStr">
         <is>
-          <t>JDYPR261012111912B5036LK10L</t>
+          <t>JDYPR261012111912B5036LK43M</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -13252,7 +13252,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>SPVYWB5036LK10L</t>
+          <t>SPVYWB5036LK43M</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -13270,7 +13270,7 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>48#黑色/17.3寸</t>
+          <t>284#卡其/15.6寸(偏粉)</t>
         </is>
       </c>
       <c r="J177" s="1" t="n">
@@ -13307,7 +13307,7 @@
     <row r="178" customHeight="true" ht="15">
       <c r="A178" t="inlineStr">
         <is>
-          <t>JDYPR261012111912B5036LK42L</t>
+          <t>JDYPR261012111912B5036LKP1L</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -13327,7 +13327,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>SPVYWB5036LK42L</t>
+          <t>SPVYWB5036LKP1L</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -13345,7 +13345,7 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>138#裸色/17.3寸</t>
+          <t>213#米白/170#豆绿/18#深绿/17.3寸</t>
         </is>
       </c>
       <c r="J178" s="1" t="n">
@@ -13369,7 +13369,7 @@
       </c>
       <c r="Q178" t="inlineStr">
         <is>
-          <t>新增绿色大号变体</t>
+          <t>新增绿色大号变体(SPVYWB5036LKP1L平衡利库调拨，修改时间2026-10-14 10:38:59，调整前申请数量：100.0；调整后申请数量：81.0;)</t>
         </is>
       </c>
       <c r="R178"/>
@@ -13382,7 +13382,7 @@
     <row r="179" customHeight="true" ht="15">
       <c r="A179" t="inlineStr">
         <is>
-          <t>JDYPR261012111912B5036LK42M</t>
+          <t>JDYPR261012111912B5036LKP1M</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -13402,7 +13402,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>SPVYWB5036LK42M</t>
+          <t>SPVYWB5036LKP1M</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -13420,7 +13420,7 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>138#裸色/15.6寸</t>
+          <t>213#米白/1559#豆绿/18#深绿/15.6寸</t>
         </is>
       </c>
       <c r="J179" s="1" t="n">
@@ -13444,7 +13444,7 @@
       </c>
       <c r="Q179" t="inlineStr">
         <is>
-          <t>新增绿色大号变体</t>
+          <t>新增绿色大号变体(SPVYWB5036LKP1M平衡利库调拨，修改时间2026-10-14 10:40:49，调整前申请数量：100.0；调整后申请数量：84.0;)</t>
         </is>
       </c>
       <c r="R179"/>
@@ -13457,12 +13457,12 @@
     <row r="180" customHeight="true" ht="15">
       <c r="A180" t="inlineStr">
         <is>
-          <t>JDYPR261012111912B5036LK43M</t>
+          <t>JDYPR26101303323231LK42M-M1</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>已审核</t>
+          <t>创建</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -13472,54 +13472,54 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2026/10/12</t>
+          <t>2026/10/13</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>SPVYWB5036LK43M</t>
+          <t>SPVYUB5631LK42M-M1</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>托特包</t>
+          <t>午餐包</t>
         </is>
       </c>
       <c r="G180" s="1" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>阳金灿</t>
+          <t>唐海阳</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>284#卡其/15.6寸(偏粉)</t>
+          <t>复古8089#黄棕色（压花）/复古8089#黄棕色/中号/两件套</t>
         </is>
       </c>
       <c r="J180" s="1" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>2026/11/11 00:00:00</t>
+          <t>2026/11/12 00:00:00</t>
         </is>
       </c>
       <c r="L180" s="1" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="M180"/>
       <c r="N180"/>
       <c r="O180"/>
       <c r="P180" t="inlineStr">
         <is>
-          <t>丝棉包生产线</t>
+          <t>午餐包生产线</t>
         </is>
       </c>
       <c r="Q180" t="inlineStr">
         <is>
-          <t>新增绿色大号变体</t>
+          <t>5631近期2推表现符合预期，补充活动消耗的库存，避免年底大流量结束后库存缺失导致断货</t>
         </is>
       </c>
       <c r="R180"/>
@@ -13532,12 +13532,12 @@
     <row r="181" customHeight="true" ht="15">
       <c r="A181" t="inlineStr">
         <is>
-          <t>JDYPR261012111912B5036LKP1L</t>
+          <t>JDYPR26101303340831LK40L-T2</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>已审核</t>
+          <t>创建</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -13547,54 +13547,54 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2026/10/12</t>
+          <t>2026/10/13</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>SPVYWB5036LKP1L</t>
+          <t>SPVYUB5631LK40L-T2</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>托特包</t>
+          <t>午餐包</t>
         </is>
       </c>
       <c r="G181" s="1" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>阳金灿</t>
+          <t>唐海阳</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>213#米白/170#豆绿/18#深绿/17.3寸</t>
+          <t>12#焦糖棕/大号/两件套</t>
         </is>
       </c>
       <c r="J181" s="1" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>2026/11/11 00:00:00</t>
+          <t>2026/11/12 00:00:00</t>
         </is>
       </c>
       <c r="L181" s="1" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="M181"/>
       <c r="N181"/>
       <c r="O181"/>
       <c r="P181" t="inlineStr">
         <is>
-          <t>丝棉包生产线</t>
+          <t>午餐包生产线</t>
         </is>
       </c>
       <c r="Q181" t="inlineStr">
         <is>
-          <t>新增绿色大号变体(SPVYWB5036LKP1L平衡利库调拨，修改时间2026-10-14 10:38:59，调整前申请数量：100.0；调整后申请数量：81.0;)</t>
+          <t>5631近期2推表现符合预期，补充活动消耗的库存，避免年底大流量结束后库存缺失导致断货</t>
         </is>
       </c>
       <c r="R181"/>
@@ -13607,12 +13607,12 @@
     <row r="182" customHeight="true" ht="15">
       <c r="A182" t="inlineStr">
         <is>
-          <t>JDYPR261012111912B5036LKP1M</t>
+          <t>JDYPR26101303340831LK40M-T2</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>已审核</t>
+          <t>创建</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -13622,54 +13622,54 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2026/10/12</t>
+          <t>2026/10/13</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>SPVYWB5036LKP1M</t>
+          <t>SPVYUB5631LK40M-T2</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>托特包</t>
+          <t>午餐包</t>
         </is>
       </c>
       <c r="G182" s="1" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>阳金灿</t>
+          <t>唐海阳</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>213#米白/1559#豆绿/18#深绿/15.6寸</t>
+          <t>12#焦糖棕/中号/两件套</t>
         </is>
       </c>
       <c r="J182" s="1" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>2026/11/11 00:00:00</t>
+          <t>2026/11/12 00:00:00</t>
         </is>
       </c>
       <c r="L182" s="1" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="M182"/>
       <c r="N182"/>
       <c r="O182"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>丝棉包生产线</t>
+          <t>午餐包生产线</t>
         </is>
       </c>
       <c r="Q182" t="inlineStr">
         <is>
-          <t>新增绿色大号变体(SPVYWB5036LKP1M平衡利库调拨，修改时间2026-10-14 10:40:49，调整前申请数量：100.0；调整后申请数量：84.0;)</t>
+          <t>5631近期2推表现符合预期，补充活动消耗的库存，避免年底大流量结束后库存缺失导致断货</t>
         </is>
       </c>
       <c r="R182"/>
@@ -13682,7 +13682,7 @@
     <row r="183" customHeight="true" ht="15">
       <c r="A183" t="inlineStr">
         <is>
-          <t>JDYPR26101303323231LK42M-M1</t>
+          <t>JDYPR26101303340831LK42L-M1</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -13702,7 +13702,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>SPVYUB5631LK42M-M1</t>
+          <t>SPVYUB5631LK42L-M1</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -13711,7 +13711,7 @@
         </is>
       </c>
       <c r="G183" s="1" t="n">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="H183" t="inlineStr">
         <is>
@@ -13720,11 +13720,11 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>复古8089#黄棕色（压花）/复古8089#黄棕色/中号/两件套</t>
+          <t>复古8089#黄棕色（压花）/复古8089#黄棕色/大号/两件套</t>
         </is>
       </c>
       <c r="J183" s="1" t="n">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="K183" t="inlineStr">
         <is>
@@ -13732,7 +13732,7 @@
         </is>
       </c>
       <c r="L183" s="1" t="n">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="M183"/>
       <c r="N183"/>
@@ -13757,12 +13757,12 @@
     <row r="184" customHeight="true" ht="15">
       <c r="A184" t="inlineStr">
         <is>
-          <t>JDYPR26101303340831LK40L-T2</t>
+          <t>JDYPR26101310142069LK30S-V1</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>创建</t>
+          <t>重新审核</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -13777,49 +13777,49 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>SPVYUB5631LK40L-T2</t>
+          <t>VYWB4069LK30S-V1</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>午餐包</t>
+          <t>女式挎包</t>
         </is>
       </c>
       <c r="G184" s="1" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>唐海阳</t>
+          <t>符琪</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>12#焦糖棕/大号/两件套</t>
+          <t>52#湛蓝/11寸/(更换挂饰)</t>
         </is>
       </c>
       <c r="J184" s="1" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>2026/11/12 00:00:00</t>
+          <t>2026/10/15 00:00:00</t>
         </is>
       </c>
       <c r="L184" s="1" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="M184"/>
       <c r="N184"/>
       <c r="O184"/>
       <c r="P184" t="inlineStr">
         <is>
-          <t>午餐包生产线</t>
+          <t>合成革高速线（计件）</t>
         </is>
       </c>
       <c r="Q184" t="inlineStr">
         <is>
-          <t>5631近期2推表现符合预期，补充活动消耗的库存，避免年底大流量结束后库存缺失导致断货</t>
+          <t>加急出货</t>
         </is>
       </c>
       <c r="R184"/>
@@ -13832,7 +13832,7 @@
     <row r="185" customHeight="true" ht="15">
       <c r="A185" t="inlineStr">
         <is>
-          <t>JDYPR26101303340831LK40M-T2</t>
+          <t>JDYPR261014094903B5400SU10M</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -13847,54 +13847,54 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2026/10/13</t>
+          <t>2026/10/14</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>SPVYUB5631LK40M-T2</t>
+          <t>SPVYUB5400SU10M</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>午餐包</t>
+          <t>网球包</t>
         </is>
       </c>
       <c r="G185" s="1" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>唐海阳</t>
+          <t>李小平</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>12#焦糖棕/中号/两件套</t>
+          <t>48#黑色（菱形格绣线)/48#黑色/中号</t>
         </is>
       </c>
       <c r="J185" s="1" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>2026/11/12 00:00:00</t>
+          <t>2026/11/13 00:00:00</t>
         </is>
       </c>
       <c r="L185" s="1" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="M185"/>
       <c r="N185"/>
       <c r="O185"/>
       <c r="P185" t="inlineStr">
         <is>
-          <t>午餐包生产线</t>
+          <t>丝棉包生产线</t>
         </is>
       </c>
       <c r="Q185" t="inlineStr">
         <is>
-          <t>5631近期2推表现符合预期，补充活动消耗的库存，避免年底大流量结束后库存缺失导致断货</t>
+          <t>变体近期销量不错</t>
         </is>
       </c>
       <c r="R185"/>
@@ -13907,7 +13907,7 @@
     <row r="186" customHeight="true" ht="15">
       <c r="A186" t="inlineStr">
         <is>
-          <t>JDYPR26101303340831LK42L-M1</t>
+          <t>JDYPR26101511293796LK10L-T4</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -13922,17 +13922,17 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2026/10/13</t>
+          <t>2026/10/15</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>SPVYUB5631LK42L-M1</t>
+          <t>SPVYMB4496LK10L-T4</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>午餐包</t>
+          <t>旅行背包</t>
         </is>
       </c>
       <c r="G186" s="1" t="n">
@@ -13940,12 +13940,12 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>唐海阳</t>
+          <t>吴颖</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>复古8089#黄棕色（压花）/复古8089#黄棕色/大号/两件套</t>
+          <t>48#黑色/大号/四件套</t>
         </is>
       </c>
       <c r="J186" s="1" t="n">
@@ -13953,23 +13953,27 @@
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>2026/11/12 00:00:00</t>
+          <t>2026/11/14 00:00:00</t>
         </is>
       </c>
       <c r="L186" s="1" t="n">
         <v>100</v>
       </c>
       <c r="M186"/>
-      <c r="N186"/>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>近期销量高，毛利高</t>
+        </is>
+      </c>
       <c r="O186"/>
       <c r="P186" t="inlineStr">
         <is>
-          <t>午餐包生产线</t>
+          <t>布类高速线（计件）</t>
         </is>
       </c>
       <c r="Q186" t="inlineStr">
         <is>
-          <t>5631近期2推表现符合预期，补充活动消耗的库存，避免年底大流量结束后库存缺失导致断货</t>
+          <t>旺季销量上涨</t>
         </is>
       </c>
       <c r="R186"/>
@@ -13982,12 +13986,12 @@
     <row r="187" customHeight="true" ht="15">
       <c r="A187" t="inlineStr">
         <is>
-          <t>JDYPR26101310142069LK30S-V1</t>
+          <t>JDYPR26101511293796LK10M-T4</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>重新审核</t>
+          <t>创建</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -13997,54 +14001,58 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2026/10/13</t>
+          <t>2026/10/15</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>VYWB4069LK30S-V1</t>
+          <t>SPVYMB4496LK10M-T4</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>女式挎包</t>
+          <t>旅行背包</t>
         </is>
       </c>
       <c r="G187" s="1" t="n">
-        <v>50</v>
+        <v>1250</v>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>符琪</t>
+          <t>吴颖</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>52#湛蓝/11寸/(更换挂饰)</t>
+          <t>48#黑色/中号/四件套</t>
         </is>
       </c>
       <c r="J187" s="1" t="n">
-        <v>50</v>
+        <v>1250</v>
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>2026/10/15 00:00:00</t>
+          <t>2026/11/14 00:00:00</t>
         </is>
       </c>
       <c r="L187" s="1" t="n">
-        <v>50</v>
+        <v>1250</v>
       </c>
       <c r="M187"/>
-      <c r="N187"/>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>主推</t>
+        </is>
+      </c>
       <c r="O187"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>合成革高速线（计件）</t>
+          <t>布类高速线（计件）</t>
         </is>
       </c>
       <c r="Q187" t="inlineStr">
         <is>
-          <t>加急出货</t>
+          <t>旺季销量上涨</t>
         </is>
       </c>
       <c r="R187"/>
@@ -14057,7 +14065,7 @@
     <row r="188" customHeight="true" ht="15">
       <c r="A188" t="inlineStr">
         <is>
-          <t>JDYPR261014094903B5400SU10M</t>
+          <t>JDYPR26101511293796LK50M-T4</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14072,17 +14080,17 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2026/10/14</t>
+          <t>2026/10/15</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>SPVYUB5400SU10M</t>
+          <t>SPVYMB4496LK50M-T4</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>网球包</t>
+          <t>旅行背包</t>
         </is>
       </c>
       <c r="G188" s="1" t="n">
@@ -14090,12 +14098,12 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>李小平</t>
+          <t>吴颖</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>48#黑色（菱形格绣线)/48#黑色/中号</t>
+          <t>127#浅粉中号/四件套</t>
         </is>
       </c>
       <c r="J188" s="1" t="n">
@@ -14103,23 +14111,27 @@
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>2026/11/13 00:00:00</t>
+          <t>2026/11/14 00:00:00</t>
         </is>
       </c>
       <c r="L188" s="1" t="n">
         <v>200</v>
       </c>
       <c r="M188"/>
-      <c r="N188"/>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>未断货前销量高，毛利高</t>
+        </is>
+      </c>
       <c r="O188"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>丝棉包生产线</t>
+          <t>布类高速线（计件）</t>
         </is>
       </c>
       <c r="Q188" t="inlineStr">
         <is>
-          <t>变体近期销量不错</t>
+          <t>旺季销量上涨</t>
         </is>
       </c>
       <c r="R188"/>
@@ -14132,7 +14144,7 @@
     <row r="189" customHeight="true" ht="15">
       <c r="A189" t="inlineStr">
         <is>
-          <t>JDYPR26101511293796LK10L-T4</t>
+          <t>JDYPR26101511293796LK70M-T4</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14152,7 +14164,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>SPVYMB4496LK10L-T4</t>
+          <t>SPVYMB4496LK70M-T4</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -14170,7 +14182,7 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>48#黑色/大号/四件套</t>
+          <t>191#深紫色/中号/四件套</t>
         </is>
       </c>
       <c r="J189" s="1" t="n">
@@ -14185,11 +14197,7 @@
         <v>100</v>
       </c>
       <c r="M189"/>
-      <c r="N189" t="inlineStr">
-        <is>
-          <t>近期销量高，毛利高</t>
-        </is>
-      </c>
+      <c r="N189"/>
       <c r="O189"/>
       <c r="P189" t="inlineStr">
         <is>
@@ -14211,7 +14219,7 @@
     <row r="190" customHeight="true" ht="15">
       <c r="A190" t="inlineStr">
         <is>
-          <t>JDYPR26101511293796LK10M-T4</t>
+          <t>JDYPR26101511293796LK90L-T4</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -14231,7 +14239,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>SPVYMB4496LK10M-T4</t>
+          <t>SPVYMB4496LK90L-T4</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -14240,7 +14248,7 @@
         </is>
       </c>
       <c r="G190" s="1" t="n">
-        <v>1250</v>
+        <v>100</v>
       </c>
       <c r="H190" t="inlineStr">
         <is>
@@ -14249,11 +14257,11 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>48#黑色/中号/四件套</t>
+          <t>156#绿色/大号/四件套</t>
         </is>
       </c>
       <c r="J190" s="1" t="n">
-        <v>1250</v>
+        <v>100</v>
       </c>
       <c r="K190" t="inlineStr">
         <is>
@@ -14261,12 +14269,12 @@
         </is>
       </c>
       <c r="L190" s="1" t="n">
-        <v>1250</v>
+        <v>100</v>
       </c>
       <c r="M190"/>
       <c r="N190" t="inlineStr">
         <is>
-          <t>主推</t>
+          <t>销量一直偏高，毛利高</t>
         </is>
       </c>
       <c r="O190"/>
@@ -14290,7 +14298,7 @@
     <row r="191" customHeight="true" ht="15">
       <c r="A191" t="inlineStr">
         <is>
-          <t>JDYPR26101511293796LK50M-T4</t>
+          <t>JDYPR26101511293796LK90M-T4</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -14310,7 +14318,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>SPVYMB4496LK50M-T4</t>
+          <t>SPVYMB4496LK90M-T4</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -14328,7 +14336,7 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>127#浅粉中号/四件套</t>
+          <t>156#绿色/中号/四件套</t>
         </is>
       </c>
       <c r="J191" s="1" t="n">
@@ -14369,7 +14377,7 @@
     <row r="192" customHeight="true" ht="15">
       <c r="A192" t="inlineStr">
         <is>
-          <t>JDYPR26101511293796LK70M-T4</t>
+          <t>JDYPR26101511293796LKP1M-T4</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -14389,7 +14397,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>SPVYMB4496LK70M-T4</t>
+          <t>SPVYMB4496LKP1M-T4</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -14407,7 +14415,7 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>191#深紫色/中号/四件套</t>
+          <t>146#香芋紫/213#米白/中号/四件套</t>
         </is>
       </c>
       <c r="J192" s="1" t="n">
@@ -14422,7 +14430,11 @@
         <v>100</v>
       </c>
       <c r="M192"/>
-      <c r="N192"/>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>毛利高、转好好</t>
+        </is>
+      </c>
       <c r="O192"/>
       <c r="P192" t="inlineStr">
         <is>
@@ -14444,7 +14456,7 @@
     <row r="193" customHeight="true" ht="15">
       <c r="A193" t="inlineStr">
         <is>
-          <t>JDYPR26101511293796LK90L-T4</t>
+          <t>JDYPR26101511293796LKP3L-T4</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -14464,7 +14476,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>SPVYMB4496LK90L-T4</t>
+          <t>SPVYMB4496LKP3L-T4</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -14482,7 +14494,7 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>156#绿色/大号/四件套</t>
+          <t>2508342豹纹/246#米黄色/大号/四件套</t>
         </is>
       </c>
       <c r="J193" s="1" t="n">
@@ -14499,7 +14511,7 @@
       <c r="M193"/>
       <c r="N193" t="inlineStr">
         <is>
-          <t>销量一直偏高，毛利高</t>
+          <t>豹纹新变体，站内竞品及TK表现好</t>
         </is>
       </c>
       <c r="O193"/>
@@ -14523,7 +14535,7 @@
     <row r="194" customHeight="true" ht="15">
       <c r="A194" t="inlineStr">
         <is>
-          <t>JDYPR26101511293796LK90M-T4</t>
+          <t>JDYPR26101511293796LKP3M-T4</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -14543,7 +14555,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>SPVYMB4496LK90M-T4</t>
+          <t>SPVYMB4496LKP3M-T4</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -14552,7 +14564,7 @@
         </is>
       </c>
       <c r="G194" s="1" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="H194" t="inlineStr">
         <is>
@@ -14561,11 +14573,11 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>156#绿色/中号/四件套</t>
+          <t>2508342豹纹/246#米黄色/中号/四件套</t>
         </is>
       </c>
       <c r="J194" s="1" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="K194" t="inlineStr">
         <is>
@@ -14573,12 +14585,12 @@
         </is>
       </c>
       <c r="L194" s="1" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="M194"/>
       <c r="N194" t="inlineStr">
         <is>
-          <t>未断货前销量高，毛利高</t>
+          <t>豹纹新变体，站内竞品及TK表现好</t>
         </is>
       </c>
       <c r="O194"/>
@@ -14602,7 +14614,7 @@
     <row r="195" customHeight="true" ht="15">
       <c r="A195" t="inlineStr">
         <is>
-          <t>JDYPR26101511293796LKP1M-T4</t>
+          <t>JDYPR261019045336B4561LKP6M</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -14617,17 +14629,17 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2026/10/15</t>
+          <t>2026/10/20</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>SPVYMB4496LKP1M-T4</t>
+          <t>SPVYMB4561LKP6M</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>旅行背包</t>
+          <t>电脑背包</t>
         </is>
       </c>
       <c r="G195" s="1" t="n">
@@ -14635,12 +14647,12 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>吴颖</t>
+          <t>李晓玲</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>146#香芋紫/213#米白/中号/四件套</t>
+          <t>48#绿色/77#米白色/7429D深绿灰/15.6寸</t>
         </is>
       </c>
       <c r="J195" s="1" t="n">
@@ -14648,18 +14660,14 @@
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>2026/11/14 00:00:00</t>
+          <t>2026/11/18 00:00:00</t>
         </is>
       </c>
       <c r="L195" s="1" t="n">
         <v>100</v>
       </c>
       <c r="M195"/>
-      <c r="N195" t="inlineStr">
-        <is>
-          <t>毛利高、转好好</t>
-        </is>
-      </c>
+      <c r="N195"/>
       <c r="O195"/>
       <c r="P195" t="inlineStr">
         <is>
@@ -14668,7 +14676,7 @@
       </c>
       <c r="Q195" t="inlineStr">
         <is>
-          <t>旺季销量上涨</t>
+          <t>4561 IT/ES/FR在做推广，导致整体毛利率偏低，预计10月底能恢复正常；欧洲整体销量趋势向好，目前变体较少，增加2个新变体</t>
         </is>
       </c>
       <c r="R195"/>
@@ -14681,7 +14689,7 @@
     <row r="196" customHeight="true" ht="15">
       <c r="A196" t="inlineStr">
         <is>
-          <t>JDYPR26101511293796LKP3L-T4</t>
+          <t>JDYPR261019045336B4561LKP7M</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -14696,49 +14704,45 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2026/10/15</t>
+          <t>2026/10/20</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>SPVYMB4496LKP3L-T4</t>
+          <t>SPVYMB4561LKP7M</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>旅行背包</t>
+          <t>电脑背包</t>
         </is>
       </c>
       <c r="G196" s="1" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>吴颖</t>
+          <t>李晓玲</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>2508342豹纹/246#米黄色/大号/四件套</t>
+          <t>2508342豹纹/8176#深咖啡/15.6寸</t>
         </is>
       </c>
       <c r="J196" s="1" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>2026/11/14 00:00:00</t>
+          <t>2026/11/18 00:00:00</t>
         </is>
       </c>
       <c r="L196" s="1" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="M196"/>
-      <c r="N196" t="inlineStr">
-        <is>
-          <t>豹纹新变体，站内竞品及TK表现好</t>
-        </is>
-      </c>
+      <c r="N196"/>
       <c r="O196"/>
       <c r="P196" t="inlineStr">
         <is>
@@ -14747,7 +14751,7 @@
       </c>
       <c r="Q196" t="inlineStr">
         <is>
-          <t>旺季销量上涨</t>
+          <t>4561 IT/ES/FR在做推广，导致整体毛利率偏低，预计10月底能恢复正常；欧洲整体销量趋势向好，目前变体较少，增加2个新变体</t>
         </is>
       </c>
       <c r="R196"/>
@@ -14760,7 +14764,7 @@
     <row r="197" customHeight="true" ht="15">
       <c r="A197" t="inlineStr">
         <is>
-          <t>JDYPR26101511293796LKP3M-T4</t>
+          <t>JDYPR26101905180252LK43M-C1</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -14775,58 +14779,54 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>2026/10/15</t>
+          <t>2026/10/20</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>SPVYMB4496LKP3M-T4</t>
+          <t>SPVYWB5252LK43M-C1</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>旅行背包</t>
+          <t>手提电脑包</t>
         </is>
       </c>
       <c r="G197" s="1" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>吴颖</t>
+          <t>李晓玲</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>2508342豹纹/246#米黄色/中号/四件套</t>
+          <t>复古205#深棕色/15.6寸(PU)</t>
         </is>
       </c>
       <c r="J197" s="1" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>2026/11/14 00:00:00</t>
+          <t>2026/11/18 00:00:00</t>
         </is>
       </c>
       <c r="L197" s="1" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="M197"/>
-      <c r="N197" t="inlineStr">
-        <is>
-          <t>豹纹新变体，站内竞品及TK表现好</t>
-        </is>
-      </c>
+      <c r="N197"/>
       <c r="O197"/>
       <c r="P197" t="inlineStr">
         <is>
-          <t>布类高速线（计件）</t>
+          <t>合成革高速线（计件）</t>
         </is>
       </c>
       <c r="Q197" t="inlineStr">
         <is>
-          <t>旺季销量上涨</t>
+          <t>加新变体</t>
         </is>
       </c>
       <c r="R197"/>
@@ -14839,7 +14839,7 @@
     <row r="198" customHeight="true" ht="15">
       <c r="A198" t="inlineStr">
         <is>
-          <t>JDYPR261019045336B4561LKP6M</t>
+          <t>JDYPR261019115741B4462LK10L</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -14859,12 +14859,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>SPVYMB4561LKP6M</t>
+          <t>SPVYWB4462LK10L</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>电脑背包</t>
+          <t>时尚背包</t>
         </is>
       </c>
       <c r="G198" s="1" t="n">
@@ -14872,12 +14872,12 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>李晓玲</t>
+          <t>康会杰</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>48#绿色/77#米白色/7429D深绿灰/15.6寸</t>
+          <t>48#黑色/大号</t>
         </is>
       </c>
       <c r="J198" s="1" t="n">
@@ -14885,7 +14885,7 @@
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>2026/11/18 00:00:00</t>
+          <t>2026/11/12 00:00:00</t>
         </is>
       </c>
       <c r="L198" s="1" t="n">
@@ -14896,12 +14896,12 @@
       <c r="O198"/>
       <c r="P198" t="inlineStr">
         <is>
-          <t>布类高速线（计件）</t>
+          <t>丝棉包生产线</t>
         </is>
       </c>
       <c r="Q198" t="inlineStr">
         <is>
-          <t>4561 IT/ES/FR在做推广，导致整体毛利率偏低，预计10月底能恢复正常；欧洲整体销量趋势向好，目前变体较少，增加2个新变体</t>
+          <t>时尚包类目11、12月是旺季，根据去年同期预测日均销量会上涨</t>
         </is>
       </c>
       <c r="R198"/>
@@ -14914,7 +14914,7 @@
     <row r="199" customHeight="true" ht="15">
       <c r="A199" t="inlineStr">
         <is>
-          <t>JDYPR261019045336B4561LKP7M</t>
+          <t>JDYPR261019115741B4462LK10M</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -14934,49 +14934,49 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>SPVYMB4561LKP7M</t>
+          <t>SPVYMB4462LK10M</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>电脑背包</t>
+          <t>时尚背包</t>
         </is>
       </c>
       <c r="G199" s="1" t="n">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>李晓玲</t>
+          <t>康会杰</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>2508342豹纹/8176#深咖啡/15.6寸</t>
+          <t>48#黑色/小号</t>
         </is>
       </c>
       <c r="J199" s="1" t="n">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>2026/11/18 00:00:00</t>
+          <t>2026/11/12 00:00:00</t>
         </is>
       </c>
       <c r="L199" s="1" t="n">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="M199"/>
       <c r="N199"/>
       <c r="O199"/>
       <c r="P199" t="inlineStr">
         <is>
-          <t>布类高速线（计件）</t>
+          <t>丝棉包生产线</t>
         </is>
       </c>
       <c r="Q199" t="inlineStr">
         <is>
-          <t>4561 IT/ES/FR在做推广，导致整体毛利率偏低，预计10月底能恢复正常；欧洲整体销量趋势向好，目前变体较少，增加2个新变体</t>
+          <t>时尚包类目11、12月是旺季，根据去年同期预测日均销量会上涨</t>
         </is>
       </c>
       <c r="R199"/>
@@ -14989,7 +14989,7 @@
     <row r="200" customHeight="true" ht="15">
       <c r="A200" t="inlineStr">
         <is>
-          <t>JDYPR26101905180252LK43M-C1</t>
+          <t>JDYPR261019115741B4462LK20M</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15009,49 +15009,49 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>SPVYWB5252LK43M-C1</t>
+          <t>SPVYMB4462LK20M</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>手提电脑包</t>
+          <t>时尚背包</t>
         </is>
       </c>
       <c r="G200" s="1" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>李晓玲</t>
+          <t>康会杰</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>复古205#深棕色/15.6寸(PU)</t>
+          <t>115#米灰色/小号</t>
         </is>
       </c>
       <c r="J200" s="1" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>2026/11/18 00:00:00</t>
+          <t>2026/11/12 00:00:00</t>
         </is>
       </c>
       <c r="L200" s="1" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="M200"/>
       <c r="N200"/>
       <c r="O200"/>
       <c r="P200" t="inlineStr">
         <is>
-          <t>合成革高速线（计件）</t>
+          <t>丝棉包生产线</t>
         </is>
       </c>
       <c r="Q200" t="inlineStr">
         <is>
-          <t>加新变体</t>
+          <t>时尚包类目11、12月是旺季，根据去年同期预测日均销量会上涨</t>
         </is>
       </c>
       <c r="R200"/>
@@ -15064,7 +15064,7 @@
     <row r="201" customHeight="true" ht="15">
       <c r="A201" t="inlineStr">
         <is>
-          <t>JDYPR261019115741B4462LK10L</t>
+          <t>JDYPR261019115741B4462LK40M</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15084,7 +15084,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>SPVYWB4462LK10L</t>
+          <t>SPVYMB4462LK40M</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -15093,7 +15093,7 @@
         </is>
       </c>
       <c r="G201" s="1" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H201" t="inlineStr">
         <is>
@@ -15102,11 +15102,11 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>48#黑色/大号</t>
+          <t>284#卡其/小号</t>
         </is>
       </c>
       <c r="J201" s="1" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="K201" t="inlineStr">
         <is>
@@ -15114,7 +15114,7 @@
         </is>
       </c>
       <c r="L201" s="1" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="M201"/>
       <c r="N201"/>
@@ -15139,7 +15139,7 @@
     <row r="202" customHeight="true" ht="15">
       <c r="A202" t="inlineStr">
         <is>
-          <t>JDYPR261019115741B4462LK10M</t>
+          <t>JDYPR261019115741B4462LK41M</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15159,7 +15159,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>SPVYMB4462LK10M</t>
+          <t>SPVYWB4462LK41M</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -15168,7 +15168,7 @@
         </is>
       </c>
       <c r="G202" s="1" t="n">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="H202" t="inlineStr">
         <is>
@@ -15177,11 +15177,11 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>48#黑色/小号</t>
+          <t>110#咖色/小号</t>
         </is>
       </c>
       <c r="J202" s="1" t="n">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="K202" t="inlineStr">
         <is>
@@ -15189,7 +15189,7 @@
         </is>
       </c>
       <c r="L202" s="1" t="n">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="M202"/>
       <c r="N202"/>
@@ -15214,7 +15214,7 @@
     <row r="203" customHeight="true" ht="15">
       <c r="A203" t="inlineStr">
         <is>
-          <t>JDYPR261019115741B4462LK20M</t>
+          <t>JDYPR261019115741B4462LK90M</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -15234,7 +15234,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>SPVYMB4462LK20M</t>
+          <t>SPVYMB4462LK90M</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -15243,7 +15243,7 @@
         </is>
       </c>
       <c r="G203" s="1" t="n">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="H203" t="inlineStr">
         <is>
@@ -15252,11 +15252,11 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>115#米灰色/小号</t>
+          <t>231#灰绿色/小号</t>
         </is>
       </c>
       <c r="J203" s="1" t="n">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="K203" t="inlineStr">
         <is>
@@ -15264,7 +15264,7 @@
         </is>
       </c>
       <c r="L203" s="1" t="n">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="M203"/>
       <c r="N203"/>
@@ -15289,7 +15289,7 @@
     <row r="204" customHeight="true" ht="15">
       <c r="A204" t="inlineStr">
         <is>
-          <t>JDYPR261019115741B4462LK40M</t>
+          <t>JDYPR261020101559B6116LK10L</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -15309,49 +15309,49 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>SPVYMB4462LK40M</t>
+          <t>SPVYWB6116LK10L</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>时尚背包</t>
+          <t>女士挎包</t>
         </is>
       </c>
       <c r="G204" s="1" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>康会杰</t>
+          <t>周挥奇</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>284#卡其/小号</t>
+          <t>复古4001#黑色/大号</t>
         </is>
       </c>
       <c r="J204" s="1" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t>2026/11/12 00:00:00</t>
+          <t>2026/11/19 00:00:00</t>
         </is>
       </c>
       <c r="L204" s="1" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M204"/>
       <c r="N204"/>
       <c r="O204"/>
       <c r="P204" t="inlineStr">
         <is>
-          <t>丝棉包生产线</t>
+          <t>合成革高速线（计件）</t>
         </is>
       </c>
       <c r="Q204" t="inlineStr">
         <is>
-          <t>时尚包类目11、12月是旺季，根据去年同期预测日均销量会上涨</t>
+          <t>新品返单-第一批备货</t>
         </is>
       </c>
       <c r="R204"/>
@@ -15364,7 +15364,7 @@
     <row r="205" customHeight="true" ht="15">
       <c r="A205" t="inlineStr">
         <is>
-          <t>JDYPR261019115741B4462LK41M</t>
+          <t>JDYPR261020101559B6116LK10S</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -15384,49 +15384,49 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>SPVYWB4462LK41M</t>
+          <t>SPVYWB6116LK10S</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>时尚背包</t>
+          <t>女士挎包</t>
         </is>
       </c>
       <c r="G205" s="1" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>康会杰</t>
+          <t>周挥奇</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>110#咖色/小号</t>
+          <t>复古4001#黑色/小号</t>
         </is>
       </c>
       <c r="J205" s="1" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t>2026/11/12 00:00:00</t>
+          <t>2026/11/19 00:00:00</t>
         </is>
       </c>
       <c r="L205" s="1" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="M205"/>
       <c r="N205"/>
       <c r="O205"/>
       <c r="P205" t="inlineStr">
         <is>
-          <t>丝棉包生产线</t>
+          <t>合成革高速线（计件）</t>
         </is>
       </c>
       <c r="Q205" t="inlineStr">
         <is>
-          <t>时尚包类目11、12月是旺季，根据去年同期预测日均销量会上涨</t>
+          <t>新品返单-第一批备货</t>
         </is>
       </c>
       <c r="R205"/>
@@ -15439,7 +15439,7 @@
     <row r="206" customHeight="true" ht="15">
       <c r="A206" t="inlineStr">
         <is>
-          <t>JDYPR261019115741B4462LK90M</t>
+          <t>JDYPR261020101559B6116LK40S</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -15459,49 +15459,49 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>SPVYMB4462LK90M</t>
+          <t>SPVYWB6116LK40S</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>时尚背包</t>
+          <t>女士挎包</t>
         </is>
       </c>
       <c r="G206" s="1" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>康会杰</t>
+          <t>周挥奇</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>231#灰绿色/小号</t>
+          <t>复古8102#红棕啡色/小号</t>
         </is>
       </c>
       <c r="J206" s="1" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>2026/11/12 00:00:00</t>
+          <t>2026/11/19 00:00:00</t>
         </is>
       </c>
       <c r="L206" s="1" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="M206"/>
       <c r="N206"/>
       <c r="O206"/>
       <c r="P206" t="inlineStr">
         <is>
-          <t>丝棉包生产线</t>
+          <t>合成革高速线（计件）</t>
         </is>
       </c>
       <c r="Q206" t="inlineStr">
         <is>
-          <t>时尚包类目11、12月是旺季，根据去年同期预测日均销量会上涨</t>
+          <t>新品返单-第一批备货</t>
         </is>
       </c>
       <c r="R206"/>
@@ -15514,7 +15514,7 @@
     <row r="207" customHeight="true" ht="15">
       <c r="A207" t="inlineStr">
         <is>
-          <t>JDYPR261020101559B6116LK10L</t>
+          <t>JDYPR261020101559B6116LKP3L</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -15534,7 +15534,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>SPVYWB6116LK10L</t>
+          <t>SPVYWB6116LKP3L</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -15543,7 +15543,7 @@
         </is>
       </c>
       <c r="G207" s="1" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H207" t="inlineStr">
         <is>
@@ -15552,11 +15552,11 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>复古4001#黑色/大号</t>
+          <t>复古8102#红棕啡色/4001#黑色/9012#番木色/大号</t>
         </is>
       </c>
       <c r="J207" s="1" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="K207" t="inlineStr">
         <is>
@@ -15564,7 +15564,7 @@
         </is>
       </c>
       <c r="L207" s="1" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="M207"/>
       <c r="N207"/>
@@ -15589,7 +15589,7 @@
     <row r="208" customHeight="true" ht="15">
       <c r="A208" t="inlineStr">
         <is>
-          <t>JDYPR261020101559B6116LK10S</t>
+          <t>JDYPR261020101559B6116LKP3S</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -15609,7 +15609,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>SPVYWB6116LK10S</t>
+          <t>SPVYWB6116LKP3S</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -15618,7 +15618,7 @@
         </is>
       </c>
       <c r="G208" s="1" t="n">
-        <v>200</v>
+        <v>2000</v>
       </c>
       <c r="H208" t="inlineStr">
         <is>
@@ -15627,11 +15627,11 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>复古4001#黑色/小号</t>
+          <t>复古8102#红棕啡色/4001#黑色/9012#番木色/小号</t>
         </is>
       </c>
       <c r="J208" s="1" t="n">
-        <v>200</v>
+        <v>2000</v>
       </c>
       <c r="K208" t="inlineStr">
         <is>
@@ -15639,7 +15639,7 @@
         </is>
       </c>
       <c r="L208" s="1" t="n">
-        <v>200</v>
+        <v>2000</v>
       </c>
       <c r="M208"/>
       <c r="N208"/>
@@ -15664,7 +15664,7 @@
     <row r="209" customHeight="true" ht="15">
       <c r="A209" t="inlineStr">
         <is>
-          <t>JDYPR261020101559B6116LK40S</t>
+          <t>JDYPR26102010201116LK41S-C1</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -15684,7 +15684,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>SPVYWB6116LK40S</t>
+          <t>SPVYWB6116LK41S-C1</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -15693,7 +15693,7 @@
         </is>
       </c>
       <c r="G209" s="1" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H209" t="inlineStr">
         <is>
@@ -15702,11 +15702,11 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>复古8102#红棕啡色/小号</t>
+          <t>复古8089#黄棕色/8089#黄棕色（压花）/小号</t>
         </is>
       </c>
       <c r="J209" s="1" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K209" t="inlineStr">
         <is>
@@ -15714,7 +15714,7 @@
         </is>
       </c>
       <c r="L209" s="1" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="M209"/>
       <c r="N209"/>
@@ -15739,7 +15739,7 @@
     <row r="210" customHeight="true" ht="15">
       <c r="A210" t="inlineStr">
         <is>
-          <t>JDYPR261020101559B6116LKP3L</t>
+          <t>JDYPR26102010201116LK90S-C1</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -15759,7 +15759,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>SPVYWB6116LKP3L</t>
+          <t>SPVYWB6116LK90S-C1</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -15768,7 +15768,7 @@
         </is>
       </c>
       <c r="G210" s="1" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H210" t="inlineStr">
         <is>
@@ -15777,11 +15777,11 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>复古8102#红棕啡色/4001#黑色/9012#番木色/大号</t>
+          <t>复古7093#绿色/7093#绿色（压花）/小号</t>
         </is>
       </c>
       <c r="J210" s="1" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K210" t="inlineStr">
         <is>
@@ -15789,7 +15789,7 @@
         </is>
       </c>
       <c r="L210" s="1" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="M210"/>
       <c r="N210"/>
@@ -15814,7 +15814,7 @@
     <row r="211" customHeight="true" ht="15">
       <c r="A211" t="inlineStr">
         <is>
-          <t>JDYPR261020101559B6116LKP3S</t>
+          <t>JDYPR261020102011B6116LK40L</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -15834,7 +15834,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>SPVYWB6116LKP3S</t>
+          <t>SPVYWB6116LK40L</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
@@ -15843,7 +15843,7 @@
         </is>
       </c>
       <c r="G211" s="1" t="n">
-        <v>2000</v>
+        <v>100</v>
       </c>
       <c r="H211" t="inlineStr">
         <is>
@@ -15852,11 +15852,11 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>复古8102#红棕啡色/4001#黑色/9012#番木色/小号</t>
+          <t>复古8102#红棕啡色/大号</t>
         </is>
       </c>
       <c r="J211" s="1" t="n">
-        <v>2000</v>
+        <v>100</v>
       </c>
       <c r="K211" t="inlineStr">
         <is>
@@ -15864,7 +15864,7 @@
         </is>
       </c>
       <c r="L211" s="1" t="n">
-        <v>2000</v>
+        <v>100</v>
       </c>
       <c r="M211"/>
       <c r="N211"/>
@@ -15889,7 +15889,7 @@
     <row r="212" customHeight="true" ht="15">
       <c r="A212" t="inlineStr">
         <is>
-          <t>JDYPR26102010201116LK41S-C1</t>
+          <t>JDYPR261020102011B6116LK42S</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -15909,7 +15909,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>SPVYWB6116LK41S-C1</t>
+          <t>SPVYWB6116LK42S</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -15927,7 +15927,7 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>复古8089#黄棕色/8089#黄棕色（压花）/小号</t>
+          <t>复古207#红啡色/小号</t>
         </is>
       </c>
       <c r="J212" s="1" t="n">
@@ -15964,7 +15964,7 @@
     <row r="213" customHeight="true" ht="15">
       <c r="A213" t="inlineStr">
         <is>
-          <t>JDYPR26102010201116LK90S-C1</t>
+          <t>JDYPR261020102011B6116LKP1S</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -15984,7 +15984,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>SPVYWB6116LK90S-C1</t>
+          <t>SPVYWB6116LKP1S</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -16002,7 +16002,7 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>复古7093#绿色/7093#绿色（压花）/小号</t>
+          <t>复古8102#红棕啡色/9012#番木色/小号</t>
         </is>
       </c>
       <c r="J213" s="1" t="n">
@@ -16039,262 +16039,37 @@
     <row r="214" customHeight="true" ht="15">
       <c r="A214" t="inlineStr">
         <is>
-          <t>JDYPR261020102011B6116LK40L</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>创建</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>未关闭</t>
-        </is>
-      </c>
-      <c r="D214" t="inlineStr">
-        <is>
-          <t>2026/10/20</t>
-        </is>
-      </c>
-      <c r="E214" t="inlineStr">
-        <is>
-          <t>SPVYWB6116LK40L</t>
-        </is>
-      </c>
-      <c r="F214" t="inlineStr">
-        <is>
-          <t>女士挎包</t>
-        </is>
-      </c>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="B214"/>
+      <c r="C214"/>
+      <c r="D214"/>
+      <c r="E214"/>
+      <c r="F214"/>
       <c r="G214" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="H214" t="inlineStr">
-        <is>
-          <t>周挥奇</t>
-        </is>
-      </c>
-      <c r="I214" t="inlineStr">
-        <is>
-          <t>复古8102#红棕啡色/大号</t>
-        </is>
-      </c>
+        <v>36614</v>
+      </c>
+      <c r="H214"/>
+      <c r="I214"/>
       <c r="J214" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="K214" t="inlineStr">
-        <is>
-          <t>2026/11/19 00:00:00</t>
-        </is>
-      </c>
+        <v>36614</v>
+      </c>
+      <c r="K214"/>
       <c r="L214" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="M214"/>
+        <v>36614</v>
+      </c>
+      <c r="M214" s="1" t="n">
+        <v>0</v>
+      </c>
       <c r="N214"/>
-      <c r="O214"/>
-      <c r="P214" t="inlineStr">
-        <is>
-          <t>合成革高速线（计件）</t>
-        </is>
-      </c>
-      <c r="Q214" t="inlineStr">
-        <is>
-          <t>新品返单-第一批备货</t>
-        </is>
-      </c>
+      <c r="O214" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P214"/>
+      <c r="Q214"/>
       <c r="R214"/>
-      <c r="S214" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="215" customHeight="true" ht="15">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>JDYPR261020102011B6116LK42S</t>
-        </is>
-      </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>创建</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>未关闭</t>
-        </is>
-      </c>
-      <c r="D215" t="inlineStr">
-        <is>
-          <t>2026/10/20</t>
-        </is>
-      </c>
-      <c r="E215" t="inlineStr">
-        <is>
-          <t>SPVYWB6116LK42S</t>
-        </is>
-      </c>
-      <c r="F215" t="inlineStr">
-        <is>
-          <t>女士挎包</t>
-        </is>
-      </c>
-      <c r="G215" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="H215" t="inlineStr">
-        <is>
-          <t>周挥奇</t>
-        </is>
-      </c>
-      <c r="I215" t="inlineStr">
-        <is>
-          <t>复古207#红啡色/小号</t>
-        </is>
-      </c>
-      <c r="J215" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="K215" t="inlineStr">
-        <is>
-          <t>2026/11/19 00:00:00</t>
-        </is>
-      </c>
-      <c r="L215" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="M215"/>
-      <c r="N215"/>
-      <c r="O215"/>
-      <c r="P215" t="inlineStr">
-        <is>
-          <t>合成革高速线（计件）</t>
-        </is>
-      </c>
-      <c r="Q215" t="inlineStr">
-        <is>
-          <t>新品返单-第一批备货</t>
-        </is>
-      </c>
-      <c r="R215"/>
-      <c r="S215" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="216" customHeight="true" ht="15">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>JDYPR261020102011B6116LKP1S</t>
-        </is>
-      </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>创建</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>未关闭</t>
-        </is>
-      </c>
-      <c r="D216" t="inlineStr">
-        <is>
-          <t>2026/10/20</t>
-        </is>
-      </c>
-      <c r="E216" t="inlineStr">
-        <is>
-          <t>SPVYWB6116LKP1S</t>
-        </is>
-      </c>
-      <c r="F216" t="inlineStr">
-        <is>
-          <t>女士挎包</t>
-        </is>
-      </c>
-      <c r="G216" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="H216" t="inlineStr">
-        <is>
-          <t>周挥奇</t>
-        </is>
-      </c>
-      <c r="I216" t="inlineStr">
-        <is>
-          <t>复古8102#红棕啡色/9012#番木色/小号</t>
-        </is>
-      </c>
-      <c r="J216" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="K216" t="inlineStr">
-        <is>
-          <t>2026/11/19 00:00:00</t>
-        </is>
-      </c>
-      <c r="L216" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="M216"/>
-      <c r="N216"/>
-      <c r="O216"/>
-      <c r="P216" t="inlineStr">
-        <is>
-          <t>合成革高速线（计件）</t>
-        </is>
-      </c>
-      <c r="Q216" t="inlineStr">
-        <is>
-          <t>新品返单-第一批备货</t>
-        </is>
-      </c>
-      <c r="R216"/>
-      <c r="S216" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="217" customHeight="true" ht="15">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>合计</t>
-        </is>
-      </c>
-      <c r="B217"/>
-      <c r="C217"/>
-      <c r="D217"/>
-      <c r="E217"/>
-      <c r="F217"/>
-      <c r="G217" s="1" t="n">
-        <v>36914</v>
-      </c>
-      <c r="H217"/>
-      <c r="I217"/>
-      <c r="J217" s="1" t="n">
-        <v>36914</v>
-      </c>
-      <c r="K217"/>
-      <c r="L217" s="1" t="n">
-        <v>36914</v>
-      </c>
-      <c r="M217" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N217"/>
-      <c r="O217" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P217"/>
-      <c r="Q217"/>
-      <c r="R217"/>
-      <c r="S217"/>
+      <c r="S214"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/otd_apply.xlsx
+++ b/src/otd_apply.xlsx
@@ -15089,7 +15089,7 @@
         </is>
       </c>
       <c r="G201" s="1" t="n">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="H201" t="inlineStr">
         <is>
@@ -15102,7 +15102,7 @@
         </is>
       </c>
       <c r="J201" s="1" t="n">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="K201" t="inlineStr">
         <is>
@@ -15110,7 +15110,7 @@
         </is>
       </c>
       <c r="L201" s="1" t="n">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="M201"/>
       <c r="N201"/>
@@ -15122,7 +15122,7 @@
       </c>
       <c r="Q201" t="inlineStr">
         <is>
-          <t>常规补货</t>
+          <t>常规补货(SPVYWB1512LK01M平衡利库调拨，修改时间2026-10-21 10:56:47，调整前申请数量：200.0；调整后申请数量：176.0;)</t>
         </is>
       </c>
       <c r="R201"/>
@@ -15539,7 +15539,7 @@
         </is>
       </c>
       <c r="G207" s="1" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H207" t="inlineStr">
         <is>
@@ -15552,7 +15552,7 @@
         </is>
       </c>
       <c r="J207" s="1" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="K207" t="inlineStr">
         <is>
@@ -15560,7 +15560,7 @@
         </is>
       </c>
       <c r="L207" s="1" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M207"/>
       <c r="N207"/>
@@ -15572,7 +15572,7 @@
       </c>
       <c r="Q207" t="inlineStr">
         <is>
-          <t>常规补货</t>
+          <t>常规补货(SPVYWB1512LK29M平衡利库调拨，修改时间2026-10-21 10:58:04，调整前申请数量：100.0；调整后申请数量：98.0;)</t>
         </is>
       </c>
       <c r="R207"/>
@@ -17943,7 +17943,7 @@
         </is>
       </c>
       <c r="G239" s="1" t="n">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="H239" t="inlineStr">
         <is>
@@ -17956,7 +17956,7 @@
         </is>
       </c>
       <c r="J239" s="1" t="n">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="K239" t="inlineStr">
         <is>
@@ -17964,7 +17964,7 @@
         </is>
       </c>
       <c r="L239" s="1" t="n">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="M239"/>
       <c r="N239" t="inlineStr">
@@ -17980,7 +17980,7 @@
       </c>
       <c r="Q239" t="inlineStr">
         <is>
-          <t>旺季销量上涨</t>
+          <t>旺季销量上涨(SPVYMB4496LK10M-T4平衡利库调拨，修改时间2026-10-21 14:19:36，调整前申请数量：1250.0；调整后申请数量：1249.0;)</t>
         </is>
       </c>
       <c r="R239"/>
@@ -21421,7 +21421,7 @@
         </is>
       </c>
       <c r="G285" s="1" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="H285" t="inlineStr">
         <is>
@@ -21434,7 +21434,7 @@
         </is>
       </c>
       <c r="J285" s="1" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="K285" t="inlineStr">
         <is>
@@ -21442,7 +21442,7 @@
         </is>
       </c>
       <c r="L285" s="1" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="M285"/>
       <c r="N285"/>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="Q285" t="inlineStr">
         <is>
-          <t>时尚包类目11、12月是旺季，根据去年同期预测日均销量会上涨</t>
+          <t>时尚包类目11、12月是旺季，根据去年同期预测日均销量会上涨(SPVYWB4462LK10L平衡利库调拨，修改时间2026-10-21 11:00:44，调整前申请数量：100.0；调整后申请数量：90.0;)</t>
         </is>
       </c>
       <c r="R285"/>
@@ -21496,7 +21496,7 @@
         </is>
       </c>
       <c r="G286" s="1" t="n">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="H286" t="inlineStr">
         <is>
@@ -21509,7 +21509,7 @@
         </is>
       </c>
       <c r="J286" s="1" t="n">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="K286" t="inlineStr">
         <is>
@@ -21517,7 +21517,7 @@
         </is>
       </c>
       <c r="L286" s="1" t="n">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="M286"/>
       <c r="N286"/>
@@ -21529,7 +21529,7 @@
       </c>
       <c r="Q286" t="inlineStr">
         <is>
-          <t>时尚包类目11、12月是旺季，根据去年同期预测日均销量会上涨</t>
+          <t>时尚包类目11、12月是旺季，根据去年同期预测日均销量会上涨(SPVYMB4462LK10M平衡利库调拨，修改时间2026-10-21 10:59:35，调整前申请数量：300.0；调整后申请数量：297.0;)</t>
         </is>
       </c>
       <c r="R286"/>
@@ -21571,7 +21571,7 @@
         </is>
       </c>
       <c r="G287" s="1" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="H287" t="inlineStr">
         <is>
@@ -21584,7 +21584,7 @@
         </is>
       </c>
       <c r="J287" s="1" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="K287" t="inlineStr">
         <is>
@@ -21592,7 +21592,7 @@
         </is>
       </c>
       <c r="L287" s="1" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="M287"/>
       <c r="N287"/>
@@ -21604,7 +21604,7 @@
       </c>
       <c r="Q287" t="inlineStr">
         <is>
-          <t>时尚包类目11、12月是旺季，根据去年同期预测日均销量会上涨</t>
+          <t>时尚包类目11、12月是旺季，根据去年同期预测日均销量会上涨(SPVYMB4462LK20M平衡利库调拨，修改时间2026-10-21 10:59:42，调整前申请数量：50.0；调整后申请数量：45.0;)</t>
         </is>
       </c>
       <c r="R287"/>
@@ -21721,7 +21721,7 @@
         </is>
       </c>
       <c r="G289" s="1" t="n">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="H289" t="inlineStr">
         <is>
@@ -21734,7 +21734,7 @@
         </is>
       </c>
       <c r="J289" s="1" t="n">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="K289" t="inlineStr">
         <is>
@@ -21742,7 +21742,7 @@
         </is>
       </c>
       <c r="L289" s="1" t="n">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="M289"/>
       <c r="N289"/>
@@ -21754,7 +21754,7 @@
       </c>
       <c r="Q289" t="inlineStr">
         <is>
-          <t>时尚包类目11、12月是旺季，根据去年同期预测日均销量会上涨</t>
+          <t>时尚包类目11、12月是旺季，根据去年同期预测日均销量会上涨(SPVYWB4462LK41M平衡利库调拨，修改时间2026-10-21 11:00:50，调整前申请数量：150.0；调整后申请数量：147.0;)</t>
         </is>
       </c>
       <c r="R289"/>
@@ -21796,7 +21796,7 @@
         </is>
       </c>
       <c r="G290" s="1" t="n">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="H290" t="inlineStr">
         <is>
@@ -21809,7 +21809,7 @@
         </is>
       </c>
       <c r="J290" s="1" t="n">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="K290" t="inlineStr">
         <is>
@@ -21817,7 +21817,7 @@
         </is>
       </c>
       <c r="L290" s="1" t="n">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="M290"/>
       <c r="N290"/>
@@ -21829,7 +21829,7 @@
       </c>
       <c r="Q290" t="inlineStr">
         <is>
-          <t>时尚包类目11、12月是旺季，根据去年同期预测日均销量会上涨</t>
+          <t>时尚包类目11、12月是旺季，根据去年同期预测日均销量会上涨(SPVYMB4462LK90M平衡利库调拨，修改时间2026-10-21 10:59:52，调整前申请数量：150.0；调整后申请数量：147.0;)</t>
         </is>
       </c>
       <c r="R290"/>
@@ -22246,7 +22246,7 @@
         </is>
       </c>
       <c r="G296" s="1" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H296" t="inlineStr">
         <is>
@@ -22259,7 +22259,7 @@
         </is>
       </c>
       <c r="J296" s="1" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="K296" t="inlineStr">
         <is>
@@ -22267,7 +22267,7 @@
         </is>
       </c>
       <c r="L296" s="1" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="M296"/>
       <c r="N296"/>
@@ -22279,7 +22279,7 @@
       </c>
       <c r="Q296" t="inlineStr">
         <is>
-          <t>补采购单尾数</t>
+          <t>补采购单尾数(SPVYWB5049LK11L平衡利库调拨，修改时间2026-10-21 10:57:52，调整前申请数量：50.0；调整后申请数量：20.0;)</t>
         </is>
       </c>
       <c r="R296"/>
@@ -22621,7 +22621,7 @@
         </is>
       </c>
       <c r="G301" s="1" t="n">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="H301" t="inlineStr">
         <is>
@@ -22634,7 +22634,7 @@
         </is>
       </c>
       <c r="J301" s="1" t="n">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="K301" t="inlineStr">
         <is>
@@ -22642,7 +22642,7 @@
         </is>
       </c>
       <c r="L301" s="1" t="n">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="M301"/>
       <c r="N301"/>
@@ -22654,7 +22654,7 @@
       </c>
       <c r="Q301" t="inlineStr">
         <is>
-          <t>11 12月系统预测日均偏低</t>
+          <t>11 12月系统预测日均偏低 平衡利库</t>
         </is>
       </c>
       <c r="R301"/>
@@ -22996,7 +22996,7 @@
         </is>
       </c>
       <c r="G306" s="1" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="H306" t="inlineStr">
         <is>
@@ -23009,7 +23009,7 @@
         </is>
       </c>
       <c r="J306" s="1" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="K306" t="inlineStr">
         <is>
@@ -23017,7 +23017,7 @@
         </is>
       </c>
       <c r="L306" s="1" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="M306"/>
       <c r="N306"/>
@@ -23029,7 +23029,7 @@
       </c>
       <c r="Q306" t="inlineStr">
         <is>
-          <t>利润率达标，常规备货做利润</t>
+          <t>利润率达标，常规备货做利润(SPVYUB4149LK30L-T2平衡利库调拨，修改时间2026-10-21 10:56:53，调整前申请数量：100.0；调整后申请数量：92.0;)</t>
         </is>
       </c>
       <c r="R306"/>
@@ -23437,7 +23437,7 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>SPVYWB6116LK10L</t>
+          <t>VYWB6116LK10L</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
@@ -23463,7 +23463,7 @@
       </c>
       <c r="K312" t="inlineStr">
         <is>
-          <t>2026/11/19 00:00:00</t>
+          <t>2026/10/20 00:00:00</t>
         </is>
       </c>
       <c r="L312" s="1" t="n">
@@ -23512,7 +23512,7 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>SPVYWB6116LK10S</t>
+          <t>VYWB6116LK10S</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
@@ -23538,7 +23538,7 @@
       </c>
       <c r="K313" t="inlineStr">
         <is>
-          <t>2026/11/19 00:00:00</t>
+          <t>2026/10/20 00:00:00</t>
         </is>
       </c>
       <c r="L313" s="1" t="n">
@@ -23587,7 +23587,7 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>SPVYWB6116LK40S</t>
+          <t>VYWB6116LK40S</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
@@ -23613,7 +23613,7 @@
       </c>
       <c r="K314" t="inlineStr">
         <is>
-          <t>2026/11/19 00:00:00</t>
+          <t>2026/10/20 00:00:00</t>
         </is>
       </c>
       <c r="L314" s="1" t="n">
@@ -23662,7 +23662,7 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>SPVYWB6116LKP3L</t>
+          <t>VYWB6116LKP3L</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
@@ -23688,7 +23688,7 @@
       </c>
       <c r="K315" t="inlineStr">
         <is>
-          <t>2026/11/19 00:00:00</t>
+          <t>2026/10/20 00:00:00</t>
         </is>
       </c>
       <c r="L315" s="1" t="n">
@@ -23737,7 +23737,7 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>SPVYWB6116LKP3S</t>
+          <t>VYWB6116LKP3S</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
@@ -23763,7 +23763,7 @@
       </c>
       <c r="K316" t="inlineStr">
         <is>
-          <t>2026/11/19 00:00:00</t>
+          <t>2026/10/20 00:00:00</t>
         </is>
       </c>
       <c r="L316" s="1" t="n">
@@ -23812,7 +23812,7 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>SPVYWB6116LK41S-C1</t>
+          <t>VYWB6116LK41S-C1</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
@@ -23838,7 +23838,7 @@
       </c>
       <c r="K317" t="inlineStr">
         <is>
-          <t>2026/11/19 00:00:00</t>
+          <t>2026/10/20 00:00:00</t>
         </is>
       </c>
       <c r="L317" s="1" t="n">
@@ -23887,7 +23887,7 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>SPVYWB6116LK90S-C1</t>
+          <t>VYWB6116LK90S-C1</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
@@ -23913,7 +23913,7 @@
       </c>
       <c r="K318" t="inlineStr">
         <is>
-          <t>2026/11/19 00:00:00</t>
+          <t>2026/10/20 00:00:00</t>
         </is>
       </c>
       <c r="L318" s="1" t="n">
@@ -23962,7 +23962,7 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>SPVYWB6116LK40L</t>
+          <t>VYWB6116LK40L</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
@@ -23988,7 +23988,7 @@
       </c>
       <c r="K319" t="inlineStr">
         <is>
-          <t>2026/11/19 00:00:00</t>
+          <t>2026/10/20 00:00:00</t>
         </is>
       </c>
       <c r="L319" s="1" t="n">
@@ -24037,7 +24037,7 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>SPVYWB6116LK42S</t>
+          <t>VYWB6116LK42S</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
@@ -24063,7 +24063,7 @@
       </c>
       <c r="K320" t="inlineStr">
         <is>
-          <t>2026/11/19 00:00:00</t>
+          <t>2026/10/20 00:00:00</t>
         </is>
       </c>
       <c r="L320" s="1" t="n">
@@ -24112,7 +24112,7 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>SPVYWB6116LKP1S</t>
+          <t>VYWB6116LKP1S</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
@@ -24138,7 +24138,7 @@
       </c>
       <c r="K321" t="inlineStr">
         <is>
-          <t>2026/11/19 00:00:00</t>
+          <t>2026/10/20 00:00:00</t>
         </is>
       </c>
       <c r="L321" s="1" t="n">
@@ -24796,7 +24796,7 @@
         </is>
       </c>
       <c r="G330" s="1" t="n">
-        <v>600</v>
+        <v>591</v>
       </c>
       <c r="H330" t="inlineStr">
         <is>
@@ -24809,7 +24809,7 @@
         </is>
       </c>
       <c r="J330" s="1" t="n">
-        <v>600</v>
+        <v>591</v>
       </c>
       <c r="K330" t="inlineStr">
         <is>
@@ -24817,7 +24817,7 @@
         </is>
       </c>
       <c r="L330" s="1" t="n">
-        <v>600</v>
+        <v>591</v>
       </c>
       <c r="M330"/>
       <c r="N330"/>
@@ -24827,7 +24827,11 @@
           <t>丝棉包生产线</t>
         </is>
       </c>
-      <c r="Q330"/>
+      <c r="Q330" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> (SPVYWB4408LKP3M-T2平衡利库调拨，修改时间2026-10-21 10:59:58，调整前申请数量：600.0；调整后申请数量：591.0;)</t>
+        </is>
+      </c>
       <c r="R330" t="inlineStr">
         <is>
           <t>爆款</t>
@@ -25380,7 +25384,7 @@
         </is>
       </c>
       <c r="G338" s="1" t="n">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H338" t="inlineStr">
         <is>
@@ -25393,7 +25397,7 @@
         </is>
       </c>
       <c r="J338" s="1" t="n">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="K338" t="inlineStr">
         <is>
@@ -25401,7 +25405,7 @@
         </is>
       </c>
       <c r="L338" s="1" t="n">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="M338"/>
       <c r="N338"/>
@@ -25411,7 +25415,11 @@
           <t>合成革高速线（计件）</t>
         </is>
       </c>
-      <c r="Q338"/>
+      <c r="Q338" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> (SPVYWB4069LK10S-V1平衡利库调拨，修改时间2026-10-21 14:07:12，调整前申请数量：500.0；调整后申请数量：499.0;)</t>
+        </is>
+      </c>
       <c r="R338"/>
       <c r="S338" t="inlineStr">
         <is>
@@ -25735,7 +25743,7 @@
         </is>
       </c>
       <c r="G343" s="1" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H343" t="inlineStr">
         <is>
@@ -25748,7 +25756,7 @@
         </is>
       </c>
       <c r="J343" s="1" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="K343" t="inlineStr">
         <is>
@@ -25756,7 +25764,7 @@
         </is>
       </c>
       <c r="L343" s="1" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="M343"/>
       <c r="N343"/>
@@ -25766,7 +25774,11 @@
           <t>合成革高速线（计件）</t>
         </is>
       </c>
-      <c r="Q343"/>
+      <c r="Q343" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> (SPVYWB4069LK10M平衡利库调拨，修改时间2026-10-21 11:00:39，调整前申请数量：100.0；调整后申请数量：97.0;)</t>
+        </is>
+      </c>
       <c r="R343"/>
       <c r="S343" t="inlineStr">
         <is>
@@ -26303,7 +26315,7 @@
         </is>
       </c>
       <c r="G351" s="1" t="n">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="H351" t="inlineStr">
         <is>
@@ -26316,7 +26328,7 @@
         </is>
       </c>
       <c r="J351" s="1" t="n">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="K351" t="inlineStr">
         <is>
@@ -26324,7 +26336,7 @@
         </is>
       </c>
       <c r="L351" s="1" t="n">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="M351"/>
       <c r="N351"/>
@@ -26334,7 +26346,11 @@
           <t>丝棉包生产线</t>
         </is>
       </c>
-      <c r="Q351"/>
+      <c r="Q351" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> (SPVYUB5147LK10M-T2平衡利库调拨，修改时间2026-10-21 12:18:32，调整前申请数量：200.0；调整后申请数量：188.0;)</t>
+        </is>
+      </c>
       <c r="R351"/>
       <c r="S351" t="inlineStr">
         <is>
@@ -26729,7 +26745,7 @@
         </is>
       </c>
       <c r="G357" s="1" t="n">
-        <v>600</v>
+        <v>594</v>
       </c>
       <c r="H357" t="inlineStr">
         <is>
@@ -26742,7 +26758,7 @@
         </is>
       </c>
       <c r="J357" s="1" t="n">
-        <v>600</v>
+        <v>594</v>
       </c>
       <c r="K357" t="inlineStr">
         <is>
@@ -26750,7 +26766,7 @@
         </is>
       </c>
       <c r="L357" s="1" t="n">
-        <v>600</v>
+        <v>594</v>
       </c>
       <c r="M357"/>
       <c r="N357"/>
@@ -26760,7 +26776,11 @@
           <t>合成革高速线（计件）</t>
         </is>
       </c>
-      <c r="Q357"/>
+      <c r="Q357" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> (SPVYWBC0005LKP1L平衡利库调拨，修改时间2026-10-21 10:53:22，调整前申请数量：600.0；调整后申请数量：594.0;)</t>
+        </is>
+      </c>
       <c r="R357" t="inlineStr">
         <is>
           <t>品牌形象款</t>
@@ -26804,7 +26824,7 @@
         </is>
       </c>
       <c r="G358" s="1" t="n">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="H358" t="inlineStr">
         <is>
@@ -26817,7 +26837,7 @@
         </is>
       </c>
       <c r="J358" s="1" t="n">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="K358" t="inlineStr">
         <is>
@@ -26825,7 +26845,7 @@
         </is>
       </c>
       <c r="L358" s="1" t="n">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="M358"/>
       <c r="N358"/>
@@ -26835,7 +26855,11 @@
           <t>合成革高速线（计件）</t>
         </is>
       </c>
-      <c r="Q358"/>
+      <c r="Q358" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> (SPVYWBC0005LKP1M平衡利库调拨，修改时间2026-10-21 10:53:19，调整前申请数量：300.0；调整后申请数量：298.0;)</t>
+        </is>
+      </c>
       <c r="R358" t="inlineStr">
         <is>
           <t>品牌形象款</t>
@@ -26950,7 +26974,7 @@
         </is>
       </c>
       <c r="G360" s="1" t="n">
-        <v>200</v>
+        <v>104</v>
       </c>
       <c r="H360" t="inlineStr">
         <is>
@@ -26963,7 +26987,7 @@
         </is>
       </c>
       <c r="J360" s="1" t="n">
-        <v>200</v>
+        <v>104</v>
       </c>
       <c r="K360" t="inlineStr">
         <is>
@@ -26971,7 +26995,7 @@
         </is>
       </c>
       <c r="L360" s="1" t="n">
-        <v>200</v>
+        <v>104</v>
       </c>
       <c r="M360"/>
       <c r="N360"/>
@@ -26981,7 +27005,11 @@
           <t>合成革高速线（计件）</t>
         </is>
       </c>
-      <c r="Q360"/>
+      <c r="Q360" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> (SPVYWB2224LK13L平衡利库调拨，修改时间2026-10-21 12:23:23，调整前申请数量：200.0；调整后申请数量：104.0;)</t>
+        </is>
+      </c>
       <c r="R360"/>
       <c r="S360" t="inlineStr">
         <is>
@@ -27096,7 +27124,7 @@
         </is>
       </c>
       <c r="G362" s="1" t="n">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="H362" t="inlineStr">
         <is>
@@ -27109,7 +27137,7 @@
         </is>
       </c>
       <c r="J362" s="1" t="n">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="K362" t="inlineStr">
         <is>
@@ -27117,7 +27145,7 @@
         </is>
       </c>
       <c r="L362" s="1" t="n">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="M362"/>
       <c r="N362"/>
@@ -27127,7 +27155,11 @@
           <t>合成革高速线（计件）</t>
         </is>
       </c>
-      <c r="Q362"/>
+      <c r="Q362" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> (SPVYUB5214LK50M-M1平衡利库调拨，修改时间2026-10-21 12:18:55，调整前申请数量：200.0；调整后申请数量：198.0;)</t>
+        </is>
+      </c>
       <c r="R362" t="inlineStr">
         <is>
           <t>爆款</t>
@@ -29893,7 +29925,7 @@
         </is>
       </c>
       <c r="G401" s="1" t="n">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="H401" t="inlineStr">
         <is>
@@ -29906,7 +29938,7 @@
         </is>
       </c>
       <c r="J401" s="1" t="n">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="K401" t="inlineStr">
         <is>
@@ -29914,7 +29946,7 @@
         </is>
       </c>
       <c r="L401" s="1" t="n">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="M401"/>
       <c r="N401"/>
@@ -29924,7 +29956,11 @@
           <t>丝棉包生产线</t>
         </is>
       </c>
-      <c r="Q401"/>
+      <c r="Q401" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> (SPVYWB6204LK50L平衡利库调拨，修改时间2026-10-21 12:19:37，调整前申请数量：100.0；调整后申请数量：93.0;)</t>
+        </is>
+      </c>
       <c r="R401"/>
       <c r="S401" t="inlineStr">
         <is>
@@ -29964,7 +30000,7 @@
         </is>
       </c>
       <c r="G402" s="1" t="n">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="H402" t="inlineStr">
         <is>
@@ -29977,7 +30013,7 @@
         </is>
       </c>
       <c r="J402" s="1" t="n">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="K402" t="inlineStr">
         <is>
@@ -29985,7 +30021,7 @@
         </is>
       </c>
       <c r="L402" s="1" t="n">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="M402"/>
       <c r="N402"/>
@@ -29995,7 +30031,11 @@
           <t>合成革高速线（计件）</t>
         </is>
       </c>
-      <c r="Q402"/>
+      <c r="Q402" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> (SPVYWB2208LK23L平衡利库调拨，修改时间2026-10-21 12:05:06，调整前申请数量：350.0；调整后申请数量：345.0;)</t>
+        </is>
+      </c>
       <c r="R402"/>
       <c r="S402" t="inlineStr">
         <is>
@@ -30248,7 +30288,7 @@
         </is>
       </c>
       <c r="G406" s="1" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H406" t="inlineStr">
         <is>
@@ -30261,7 +30301,7 @@
         </is>
       </c>
       <c r="J406" s="1" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="K406" t="inlineStr">
         <is>
@@ -30269,7 +30309,7 @@
         </is>
       </c>
       <c r="L406" s="1" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M406"/>
       <c r="N406"/>
@@ -30279,7 +30319,11 @@
           <t>合成革高速线（计件）</t>
         </is>
       </c>
-      <c r="Q406"/>
+      <c r="Q406" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> (SPVYWB2038LK22M平衡利库调拨，修改时间2026-10-21 11:05:37，调整前申请数量：100.0；调整后申请数量：98.0;)</t>
+        </is>
+      </c>
       <c r="R406"/>
       <c r="S406" t="inlineStr">
         <is>
@@ -30319,7 +30363,7 @@
         </is>
       </c>
       <c r="G407" s="1" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H407" t="inlineStr">
         <is>
@@ -30332,7 +30376,7 @@
         </is>
       </c>
       <c r="J407" s="1" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K407" t="inlineStr">
         <is>
@@ -30340,7 +30384,7 @@
         </is>
       </c>
       <c r="L407" s="1" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="M407"/>
       <c r="N407"/>
@@ -30350,7 +30394,11 @@
           <t>合成革高速线（计件）</t>
         </is>
       </c>
-      <c r="Q407"/>
+      <c r="Q407" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> (SPVYWB2038LK23M平衡利库调拨，修改时间2026-10-21 11:59:45，调整前申请数量：100.0；调整后申请数量：99.0;)</t>
+        </is>
+      </c>
       <c r="R407"/>
       <c r="S407" t="inlineStr">
         <is>
@@ -31195,7 +31243,7 @@
         </is>
       </c>
       <c r="G419" s="1" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="H419" t="inlineStr">
         <is>
@@ -31208,7 +31256,7 @@
         </is>
       </c>
       <c r="J419" s="1" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="K419" t="inlineStr">
         <is>
@@ -31216,7 +31264,7 @@
         </is>
       </c>
       <c r="L419" s="1" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="M419"/>
       <c r="N419"/>
@@ -31226,7 +31274,11 @@
           <t>合成革高速线（计件）</t>
         </is>
       </c>
-      <c r="Q419"/>
+      <c r="Q419" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> (SPVYWB2035LK40M-Q2平衡利库调拨，修改时间2026-10-21 11:33:33，调整前申请数量：100.0；调整后申请数量：90.0;)</t>
+        </is>
+      </c>
       <c r="R419"/>
       <c r="S419" t="inlineStr">
         <is>
@@ -31905,7 +31957,7 @@
         </is>
       </c>
       <c r="G429" s="1" t="n">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="H429" t="inlineStr">
         <is>
@@ -31918,7 +31970,7 @@
         </is>
       </c>
       <c r="J429" s="1" t="n">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="K429" t="inlineStr">
         <is>
@@ -31926,7 +31978,7 @@
         </is>
       </c>
       <c r="L429" s="1" t="n">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="M429"/>
       <c r="N429"/>
@@ -31936,7 +31988,11 @@
           <t>布类高速线（计件）</t>
         </is>
       </c>
-      <c r="Q429"/>
+      <c r="Q429" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> (SPVYMB2023LK03S平衡利库调拨，修改时间2026-10-21 10:56:35，调整前申请数量：150.0；调整后申请数量：125;)</t>
+        </is>
+      </c>
       <c r="R429"/>
       <c r="S429" t="inlineStr">
         <is>
@@ -32047,7 +32103,7 @@
         </is>
       </c>
       <c r="G431" s="1" t="n">
-        <v>100</v>
+        <v>36</v>
       </c>
       <c r="H431" t="inlineStr">
         <is>
@@ -32060,7 +32116,7 @@
         </is>
       </c>
       <c r="J431" s="1" t="n">
-        <v>100</v>
+        <v>36</v>
       </c>
       <c r="K431" t="inlineStr">
         <is>
@@ -32068,7 +32124,7 @@
         </is>
       </c>
       <c r="L431" s="1" t="n">
-        <v>100</v>
+        <v>36</v>
       </c>
       <c r="M431"/>
       <c r="N431"/>
@@ -32078,7 +32134,11 @@
           <t>午餐包生产线</t>
         </is>
       </c>
-      <c r="Q431"/>
+      <c r="Q431" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> (SPVYMB5705LKP5L平衡利库调拨，修改时间2026-10-21 10:53:38，调整前申请数量：100.0；调整后申请数量：36.0;)</t>
+        </is>
+      </c>
       <c r="R431" t="inlineStr">
         <is>
           <t>大爆款</t>
@@ -32093,7 +32153,7 @@
     <row r="432" customHeight="true" ht="15">
       <c r="A432" t="inlineStr">
         <is>
-          <t>LXPP261020106</t>
+          <t>LXPP261020107</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
@@ -32113,16 +32173,16 @@
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>SPVYMB5705LKP4M</t>
+          <t>SPVYMB4230LK71L</t>
         </is>
       </c>
       <c r="F432" t="inlineStr">
         <is>
-          <t>午餐电脑背包</t>
+          <t>电脑背包</t>
         </is>
       </c>
       <c r="G432" s="1" t="n">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="H432" t="inlineStr">
         <is>
@@ -32131,11 +32191,11 @@
       </c>
       <c r="I432" t="inlineStr">
         <is>
-          <t>86#米黄/88#豆绿色/7235D#暗铜绿/15.6寸</t>
+          <t>20#灰紫/17寸</t>
         </is>
       </c>
       <c r="J432" s="1" t="n">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="K432" t="inlineStr">
         <is>
@@ -32143,17 +32203,25 @@
         </is>
       </c>
       <c r="L432" s="1" t="n">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="M432"/>
-      <c r="N432"/>
+      <c r="N432" t="inlineStr">
+        <is>
+          <t>补单</t>
+        </is>
+      </c>
       <c r="O432"/>
       <c r="P432" t="inlineStr">
         <is>
-          <t>午餐包生产线</t>
-        </is>
-      </c>
-      <c r="Q432"/>
+          <t>布类高速线（计件）</t>
+        </is>
+      </c>
+      <c r="Q432" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> (SPVYMB4230LK71L平衡利库调拨，修改时间2026-10-21 10:53:52，调整前申请数量：34.0；调整后申请数量：30.0;)</t>
+        </is>
+      </c>
       <c r="R432" t="inlineStr">
         <is>
           <t>大爆款</t>
@@ -32168,7 +32236,7 @@
     <row r="433" customHeight="true" ht="15">
       <c r="A433" t="inlineStr">
         <is>
-          <t>LXPP261020107</t>
+          <t>LXPP261020108</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
@@ -32188,16 +32256,16 @@
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>SPVYMB4230LK71L</t>
+          <t>SPVYMB2023LK01S</t>
         </is>
       </c>
       <c r="F433" t="inlineStr">
         <is>
-          <t>电脑背包</t>
+          <t>搭盖时尚背包</t>
         </is>
       </c>
       <c r="G433" s="1" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="H433" t="inlineStr">
         <is>
@@ -32206,11 +32274,11 @@
       </c>
       <c r="I433" t="inlineStr">
         <is>
-          <t>20#灰紫/17寸</t>
+          <t>23#黑色/4001#黑色/14寸</t>
         </is>
       </c>
       <c r="J433" s="1" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="K433" t="inlineStr">
         <is>
@@ -32218,7 +32286,7 @@
         </is>
       </c>
       <c r="L433" s="1" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="M433"/>
       <c r="N433" t="inlineStr">
@@ -32233,11 +32301,7 @@
         </is>
       </c>
       <c r="Q433"/>
-      <c r="R433" t="inlineStr">
-        <is>
-          <t>大爆款</t>
-        </is>
-      </c>
+      <c r="R433"/>
       <c r="S433" t="inlineStr">
         <is>
           <t>否</t>
@@ -32247,112 +32311,37 @@
     <row r="434" customHeight="true" ht="15">
       <c r="A434" t="inlineStr">
         <is>
-          <t>LXPP261020108</t>
-        </is>
-      </c>
-      <c r="B434" t="inlineStr">
-        <is>
-          <t>创建</t>
-        </is>
-      </c>
-      <c r="C434" t="inlineStr">
-        <is>
-          <t>未关闭</t>
-        </is>
-      </c>
-      <c r="D434" t="inlineStr">
-        <is>
-          <t>2026/10/20</t>
-        </is>
-      </c>
-      <c r="E434" t="inlineStr">
-        <is>
-          <t>SPVYMB2023LK01S</t>
-        </is>
-      </c>
-      <c r="F434" t="inlineStr">
-        <is>
-          <t>搭盖时尚背包</t>
-        </is>
-      </c>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="B434"/>
+      <c r="C434"/>
+      <c r="D434"/>
+      <c r="E434"/>
+      <c r="F434"/>
       <c r="G434" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="H434" t="inlineStr">
-        <is>
-          <t>吴冠烨</t>
-        </is>
-      </c>
-      <c r="I434" t="inlineStr">
-        <is>
-          <t>23#黑色/4001#黑色/14寸</t>
-        </is>
-      </c>
+        <v>81258</v>
+      </c>
+      <c r="H434"/>
+      <c r="I434"/>
       <c r="J434" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="K434" t="inlineStr">
-        <is>
-          <t>2026/10/20 00:00:00</t>
-        </is>
-      </c>
+        <v>81258</v>
+      </c>
+      <c r="K434"/>
       <c r="L434" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="M434"/>
-      <c r="N434" t="inlineStr">
-        <is>
-          <t>补单</t>
-        </is>
-      </c>
-      <c r="O434"/>
-      <c r="P434" t="inlineStr">
-        <is>
-          <t>布类高速线（计件）</t>
-        </is>
-      </c>
+        <v>81258</v>
+      </c>
+      <c r="M434" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N434"/>
+      <c r="O434" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P434"/>
       <c r="Q434"/>
       <c r="R434"/>
-      <c r="S434" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="435" customHeight="true" ht="15">
-      <c r="A435" t="inlineStr">
-        <is>
-          <t>合计</t>
-        </is>
-      </c>
-      <c r="B435"/>
-      <c r="C435"/>
-      <c r="D435"/>
-      <c r="E435"/>
-      <c r="F435"/>
-      <c r="G435" s="1" t="n">
-        <v>81698</v>
-      </c>
-      <c r="H435"/>
-      <c r="I435"/>
-      <c r="J435" s="1" t="n">
-        <v>81698</v>
-      </c>
-      <c r="K435"/>
-      <c r="L435" s="1" t="n">
-        <v>81698</v>
-      </c>
-      <c r="M435" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N435"/>
-      <c r="O435" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P435"/>
-      <c r="Q435"/>
-      <c r="R435"/>
-      <c r="S435"/>
+      <c r="S434"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/otd_apply.xlsx
+++ b/src/otd_apply.xlsx
@@ -9488,7 +9488,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>审核中</t>
+          <t>已审核</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -9563,7 +9563,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>审核中</t>
+          <t>已审核</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -9638,7 +9638,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>审核中</t>
+          <t>已审核</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -20466,7 +20466,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>创建</t>
+          <t>审核中</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -20545,7 +20545,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>创建</t>
+          <t>审核中</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -20569,7 +20569,7 @@
         </is>
       </c>
       <c r="G274" s="1" t="n">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="H274" t="inlineStr">
         <is>
@@ -20582,7 +20582,7 @@
         </is>
       </c>
       <c r="J274" s="1" t="n">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="K274" t="inlineStr">
         <is>
@@ -20590,7 +20590,7 @@
         </is>
       </c>
       <c r="L274" s="1" t="n">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="M274"/>
       <c r="N274" t="inlineStr">
@@ -20624,7 +20624,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>创建</t>
+          <t>审核中</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -20703,7 +20703,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>创建</t>
+          <t>审核中</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -20778,7 +20778,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>创建</t>
+          <t>审核中</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -20857,7 +20857,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>创建</t>
+          <t>审核中</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -20936,7 +20936,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>创建</t>
+          <t>审核中</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -21015,7 +21015,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>创建</t>
+          <t>审核中</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -21094,7 +21094,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>创建</t>
+          <t>审核中</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -21398,7 +21398,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>审核中</t>
+          <t>已审核</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -21473,7 +21473,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>审核中</t>
+          <t>已审核</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -22523,7 +22523,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>审核中</t>
+          <t>已审核</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -22598,7 +22598,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>审核中</t>
+          <t>已审核</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -22748,7 +22748,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>审核中</t>
+          <t>已审核</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -22823,7 +22823,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>审核中</t>
+          <t>已审核</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -22898,7 +22898,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>审核中</t>
+          <t>已审核</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -22973,7 +22973,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>审核中</t>
+          <t>已审核</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -23048,7 +23048,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>审核中</t>
+          <t>已审核</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -23123,7 +23123,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>审核中</t>
+          <t>已审核</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -23198,7 +23198,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>审核中</t>
+          <t>已审核</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -23273,7 +23273,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>审核中</t>
+          <t>已审核</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -23348,7 +23348,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>审核中</t>
+          <t>已审核</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -23423,7 +23423,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>审核中</t>
+          <t>已审核</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -23498,7 +23498,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>审核中</t>
+          <t>已审核</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -23573,7 +23573,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>审核中</t>
+          <t>已审核</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -23648,7 +23648,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>审核中</t>
+          <t>已审核</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -23723,7 +23723,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>审核中</t>
+          <t>已审核</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -24848,7 +24848,7 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>审核中</t>
+          <t>已审核</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -24923,7 +24923,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>审核中</t>
+          <t>已审核</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -24998,7 +24998,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>审核中</t>
+          <t>已审核</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -25073,7 +25073,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>审核中</t>
+          <t>已审核</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -25148,7 +25148,7 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>审核中</t>
+          <t>已审核</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -25223,7 +25223,7 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>审核中</t>
+          <t>已审核</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -25298,7 +25298,7 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>审核中</t>
+          <t>已审核</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -27776,7 +27776,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>审核中</t>
+          <t>已审核</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -28222,7 +28222,7 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>创建</t>
+          <t>审核中</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -28293,7 +28293,7 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>创建</t>
+          <t>审核中</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -28364,7 +28364,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>创建</t>
+          <t>审核中</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -28435,7 +28435,7 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>创建</t>
+          <t>审核中</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -28506,7 +28506,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>创建</t>
+          <t>审核中</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -28577,7 +28577,7 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>创建</t>
+          <t>审核中</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -28648,7 +28648,7 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>创建</t>
+          <t>审核中</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -28719,7 +28719,7 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>创建</t>
+          <t>审核中</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -28790,7 +28790,7 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>创建</t>
+          <t>审核中</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -29353,12 +29353,12 @@
     <row r="393" customHeight="true" ht="15">
       <c r="A393" t="inlineStr">
         <is>
-          <t>LXPP261020054</t>
+          <t>LXPP261020056</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>创建</t>
+          <t>已审核</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -29373,16 +29373,16 @@
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>SPVYWB3004LK17M-T2</t>
+          <t>SPVYWB5200LKP1M</t>
         </is>
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>手提电脑包</t>
+          <t>午餐托特包</t>
         </is>
       </c>
       <c r="G393" s="1" t="n">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="H393" t="inlineStr">
         <is>
@@ -29391,11 +29391,11 @@
       </c>
       <c r="I393" t="inlineStr">
         <is>
-          <t>927#浅沙色/两件套</t>
+          <t>1#黑色/77#米白色/8123D板栗粽/15.6寸</t>
         </is>
       </c>
       <c r="J393" s="1" t="n">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="K393" t="inlineStr">
         <is>
@@ -29403,18 +29403,22 @@
         </is>
       </c>
       <c r="L393" s="1" t="n">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="M393"/>
       <c r="N393"/>
       <c r="O393"/>
       <c r="P393" t="inlineStr">
         <is>
-          <t>合成革高速线（计件）</t>
+          <t>午餐包生产线</t>
         </is>
       </c>
       <c r="Q393"/>
-      <c r="R393"/>
+      <c r="R393" t="inlineStr">
+        <is>
+          <t>爆款</t>
+        </is>
+      </c>
       <c r="S393" t="inlineStr">
         <is>
           <t>否</t>
@@ -29424,12 +29428,12 @@
     <row r="394" customHeight="true" ht="15">
       <c r="A394" t="inlineStr">
         <is>
-          <t>LXPP261020055</t>
+          <t>LXPP261020057</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>创建</t>
+          <t>已审核</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -29444,16 +29448,16 @@
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>SPVYWB3004LK50M-T2</t>
+          <t>SPVYWB5200LKPCL-X1</t>
         </is>
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>手提电脑包</t>
+          <t>午餐托特包</t>
         </is>
       </c>
       <c r="G394" s="1" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="H394" t="inlineStr">
         <is>
@@ -29462,11 +29466,11 @@
       </c>
       <c r="I394" t="inlineStr">
         <is>
-          <t>1629#暗红色/15.6寸/两件套</t>
+          <t>2508342豹纹/8176#深咖啡色/17.3寸（无绣线）</t>
         </is>
       </c>
       <c r="J394" s="1" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="K394" t="inlineStr">
         <is>
@@ -29474,18 +29478,22 @@
         </is>
       </c>
       <c r="L394" s="1" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="M394"/>
       <c r="N394"/>
       <c r="O394"/>
       <c r="P394" t="inlineStr">
         <is>
-          <t>合成革高速线（计件）</t>
+          <t>午餐包生产线</t>
         </is>
       </c>
       <c r="Q394"/>
-      <c r="R394"/>
+      <c r="R394" t="inlineStr">
+        <is>
+          <t>爆款</t>
+        </is>
+      </c>
       <c r="S394" t="inlineStr">
         <is>
           <t>否</t>
@@ -29495,7 +29503,7 @@
     <row r="395" customHeight="true" ht="15">
       <c r="A395" t="inlineStr">
         <is>
-          <t>LXPP261020056</t>
+          <t>LXPP261020058</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -29515,7 +29523,7 @@
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>SPVYWB5200LKP1M</t>
+          <t>SPVYWB5200LKPCM-X1</t>
         </is>
       </c>
       <c r="F395" t="inlineStr">
@@ -29533,7 +29541,7 @@
       </c>
       <c r="I395" t="inlineStr">
         <is>
-          <t>1#黑色/77#米白色/8123D板栗粽/15.6寸</t>
+          <t>2508342豹纹/8176#深咖啡色/15.6寸（无绣线）</t>
         </is>
       </c>
       <c r="J395" s="1" t="n">
@@ -29570,12 +29578,12 @@
     <row r="396" customHeight="true" ht="15">
       <c r="A396" t="inlineStr">
         <is>
-          <t>LXPP261020057</t>
+          <t>LXPP261020059</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>已审核</t>
+          <t>创建</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -29590,16 +29598,16 @@
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>SPVYWB5200LKPCL-X1</t>
+          <t>SPVYWB5368LK41L</t>
         </is>
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>午餐托特包</t>
+          <t>电脑手提包</t>
         </is>
       </c>
       <c r="G396" s="1" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="H396" t="inlineStr">
         <is>
@@ -29608,11 +29616,11 @@
       </c>
       <c r="I396" t="inlineStr">
         <is>
-          <t>2508342豹纹/8176#深咖啡色/17.3寸（无绣线）</t>
+          <t>27#焦糖棕/17.3寸</t>
         </is>
       </c>
       <c r="J396" s="1" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="K396" t="inlineStr">
         <is>
@@ -29620,22 +29628,18 @@
         </is>
       </c>
       <c r="L396" s="1" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="M396"/>
       <c r="N396"/>
       <c r="O396"/>
       <c r="P396" t="inlineStr">
         <is>
-          <t>午餐包生产线</t>
+          <t>合成革高速线（计件）</t>
         </is>
       </c>
       <c r="Q396"/>
-      <c r="R396" t="inlineStr">
-        <is>
-          <t>爆款</t>
-        </is>
-      </c>
+      <c r="R396"/>
       <c r="S396" t="inlineStr">
         <is>
           <t>否</t>
@@ -29645,12 +29649,12 @@
     <row r="397" customHeight="true" ht="15">
       <c r="A397" t="inlineStr">
         <is>
-          <t>LXPP261020058</t>
+          <t>LXPP261020060</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>已审核</t>
+          <t>创建</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -29665,16 +29669,16 @@
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>SPVYWB5200LKPCM-X1</t>
+          <t>SPVYWB5368LK40M</t>
         </is>
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>午餐托特包</t>
+          <t>电脑手提包</t>
         </is>
       </c>
       <c r="G397" s="1" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="H397" t="inlineStr">
         <is>
@@ -29683,11 +29687,11 @@
       </c>
       <c r="I397" t="inlineStr">
         <is>
-          <t>2508342豹纹/8176#深咖啡色/15.6寸（无绣线）</t>
+          <t>121#饼干色/15.6寸</t>
         </is>
       </c>
       <c r="J397" s="1" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="K397" t="inlineStr">
         <is>
@@ -29695,22 +29699,18 @@
         </is>
       </c>
       <c r="L397" s="1" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="M397"/>
       <c r="N397"/>
       <c r="O397"/>
       <c r="P397" t="inlineStr">
         <is>
-          <t>午餐包生产线</t>
+          <t>合成革高速线（计件）</t>
         </is>
       </c>
       <c r="Q397"/>
-      <c r="R397" t="inlineStr">
-        <is>
-          <t>爆款</t>
-        </is>
-      </c>
+      <c r="R397"/>
       <c r="S397" t="inlineStr">
         <is>
           <t>否</t>
@@ -29720,7 +29720,7 @@
     <row r="398" customHeight="true" ht="15">
       <c r="A398" t="inlineStr">
         <is>
-          <t>LXPP261020059</t>
+          <t>LXPP261020061</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -29740,16 +29740,16 @@
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>SPVYWB5368LK41L</t>
+          <t>SPVYUB5012LKPLM</t>
         </is>
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>电脑手提包</t>
+          <t>午餐包</t>
         </is>
       </c>
       <c r="G398" s="1" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H398" t="inlineStr">
         <is>
@@ -29758,11 +29758,11 @@
       </c>
       <c r="I398" t="inlineStr">
         <is>
-          <t>27#焦糖棕/17.3寸</t>
+          <t>2508342豹纹/4001#黑色/小号</t>
         </is>
       </c>
       <c r="J398" s="1" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="K398" t="inlineStr">
         <is>
@@ -29770,14 +29770,14 @@
         </is>
       </c>
       <c r="L398" s="1" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="M398"/>
       <c r="N398"/>
       <c r="O398"/>
       <c r="P398" t="inlineStr">
         <is>
-          <t>合成革高速线（计件）</t>
+          <t>午餐包生产线</t>
         </is>
       </c>
       <c r="Q398"/>
@@ -29791,7 +29791,7 @@
     <row r="399" customHeight="true" ht="15">
       <c r="A399" t="inlineStr">
         <is>
-          <t>LXPP261020060</t>
+          <t>LXPP261020062</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -29811,12 +29811,12 @@
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>SPVYWB5368LK40M</t>
+          <t>SPVYUB5559LK10S-T2</t>
         </is>
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>电脑手提包</t>
+          <t>健身包</t>
         </is>
       </c>
       <c r="G399" s="1" t="n">
@@ -29829,7 +29829,7 @@
       </c>
       <c r="I399" t="inlineStr">
         <is>
-          <t>121#饼干色/15.6寸</t>
+          <t>25#黑色/11寸/两件套</t>
         </is>
       </c>
       <c r="J399" s="1" t="n">
@@ -29848,7 +29848,7 @@
       <c r="O399"/>
       <c r="P399" t="inlineStr">
         <is>
-          <t>合成革高速线（计件）</t>
+          <t>布类高速线（计件）</t>
         </is>
       </c>
       <c r="Q399"/>
@@ -29862,7 +29862,7 @@
     <row r="400" customHeight="true" ht="15">
       <c r="A400" t="inlineStr">
         <is>
-          <t>LXPP261020061</t>
+          <t>LXPP261020063</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -29882,16 +29882,16 @@
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>SPVYUB5012LKPLM</t>
+          <t>SPVYUB5559LK30M-T2</t>
         </is>
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>午餐包</t>
+          <t>健身包</t>
         </is>
       </c>
       <c r="G400" s="1" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H400" t="inlineStr">
         <is>
@@ -29900,11 +29900,11 @@
       </c>
       <c r="I400" t="inlineStr">
         <is>
-          <t>2508342豹纹/4001#黑色/小号</t>
+          <t>22#蓝色/158#淡蓝色/14.2寸/两件套</t>
         </is>
       </c>
       <c r="J400" s="1" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K400" t="inlineStr">
         <is>
@@ -29912,14 +29912,14 @@
         </is>
       </c>
       <c r="L400" s="1" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="M400"/>
       <c r="N400"/>
       <c r="O400"/>
       <c r="P400" t="inlineStr">
         <is>
-          <t>午餐包生产线</t>
+          <t>布类高速线（计件）</t>
         </is>
       </c>
       <c r="Q400"/>
@@ -29933,7 +29933,7 @@
     <row r="401" customHeight="true" ht="15">
       <c r="A401" t="inlineStr">
         <is>
-          <t>LXPP261020062</t>
+          <t>LXPP261020064</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -29953,7 +29953,7 @@
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>SPVYUB5559LK10S-T2</t>
+          <t>SPVYUB5559LK50S-T2</t>
         </is>
       </c>
       <c r="F401" t="inlineStr">
@@ -29971,7 +29971,7 @@
       </c>
       <c r="I401" t="inlineStr">
         <is>
-          <t>25#黑色/11寸/两件套</t>
+          <t>04#浅粉色/205#粉色/11寸/两件套</t>
         </is>
       </c>
       <c r="J401" s="1" t="n">
@@ -30004,7 +30004,7 @@
     <row r="402" customHeight="true" ht="15">
       <c r="A402" t="inlineStr">
         <is>
-          <t>LXPP261020063</t>
+          <t>LXPP261020065</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -30024,7 +30024,7 @@
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>SPVYUB5559LK30M-T2</t>
+          <t>SPVYUB5559LKP1M-T2</t>
         </is>
       </c>
       <c r="F402" t="inlineStr">
@@ -30042,7 +30042,7 @@
       </c>
       <c r="I402" t="inlineStr">
         <is>
-          <t>22#蓝色/158#淡蓝色/14.2寸/两件套</t>
+          <t>15#玫红色/36#黑色14.2寸/两件套</t>
         </is>
       </c>
       <c r="J402" s="1" t="n">
@@ -30075,7 +30075,7 @@
     <row r="403" customHeight="true" ht="15">
       <c r="A403" t="inlineStr">
         <is>
-          <t>LXPP261020064</t>
+          <t>LXPP261020066</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -30095,7 +30095,7 @@
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>SPVYUB5559LK50S-T2</t>
+          <t>SPVYUB5559LKP1S-T2</t>
         </is>
       </c>
       <c r="F403" t="inlineStr">
@@ -30113,7 +30113,7 @@
       </c>
       <c r="I403" t="inlineStr">
         <is>
-          <t>04#浅粉色/205#粉色/11寸/两件套</t>
+          <t>15#玫红色/36#黑色11寸/两件套</t>
         </is>
       </c>
       <c r="J403" s="1" t="n">
@@ -30146,7 +30146,7 @@
     <row r="404" customHeight="true" ht="15">
       <c r="A404" t="inlineStr">
         <is>
-          <t>LXPP261020065</t>
+          <t>LXPP261020067</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -30166,12 +30166,12 @@
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>SPVYUB5559LKP1M-T2</t>
+          <t>SPVYWB5023LK41S</t>
         </is>
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>健身包</t>
+          <t>托特手提包</t>
         </is>
       </c>
       <c r="G404" s="1" t="n">
@@ -30184,7 +30184,7 @@
       </c>
       <c r="I404" t="inlineStr">
         <is>
-          <t>15#玫红色/36#黑色14.2寸/两件套</t>
+          <t>8089#棕色/11.5寸</t>
         </is>
       </c>
       <c r="J404" s="1" t="n">
@@ -30203,7 +30203,7 @@
       <c r="O404"/>
       <c r="P404" t="inlineStr">
         <is>
-          <t>布类高速线（计件）</t>
+          <t>合成革高速线（计件）</t>
         </is>
       </c>
       <c r="Q404"/>
@@ -30217,7 +30217,7 @@
     <row r="405" customHeight="true" ht="15">
       <c r="A405" t="inlineStr">
         <is>
-          <t>LXPP261020066</t>
+          <t>LXPP261020068</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -30237,12 +30237,12 @@
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>SPVYUB5559LKP1S-T2</t>
+          <t>SPVYWB5023LK10S</t>
         </is>
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>健身包</t>
+          <t>托特手提包</t>
         </is>
       </c>
       <c r="G405" s="1" t="n">
@@ -30255,7 +30255,7 @@
       </c>
       <c r="I405" t="inlineStr">
         <is>
-          <t>15#玫红色/36#黑色11寸/两件套</t>
+          <t>4001#黑色/11.5寸</t>
         </is>
       </c>
       <c r="J405" s="1" t="n">
@@ -30274,7 +30274,7 @@
       <c r="O405"/>
       <c r="P405" t="inlineStr">
         <is>
-          <t>布类高速线（计件）</t>
+          <t>合成革高速线（计件）</t>
         </is>
       </c>
       <c r="Q405"/>
@@ -30288,12 +30288,12 @@
     <row r="406" customHeight="true" ht="15">
       <c r="A406" t="inlineStr">
         <is>
-          <t>LXPP261020067</t>
+          <t>LXPP261020069</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>创建</t>
+          <t>审核中</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
@@ -30308,16 +30308,16 @@
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>SPVYWB5023LK41S</t>
+          <t>VYWB6210LK42L-C1</t>
         </is>
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>托特手提包</t>
+          <t>午餐托特包</t>
         </is>
       </c>
       <c r="G406" s="1" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="H406" t="inlineStr">
         <is>
@@ -30326,11 +30326,11 @@
       </c>
       <c r="I406" t="inlineStr">
         <is>
-          <t>8089#棕色/11.5寸</t>
+          <t>#8089黄棕色(压花）/#8089黄棕色羊巴皮/17.3寸</t>
         </is>
       </c>
       <c r="J406" s="1" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="K406" t="inlineStr">
         <is>
@@ -30338,14 +30338,14 @@
         </is>
       </c>
       <c r="L406" s="1" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="M406"/>
       <c r="N406"/>
       <c r="O406"/>
       <c r="P406" t="inlineStr">
         <is>
-          <t>合成革高速线（计件）</t>
+          <t>午餐包生产线</t>
         </is>
       </c>
       <c r="Q406"/>
@@ -30359,7 +30359,7 @@
     <row r="407" customHeight="true" ht="15">
       <c r="A407" t="inlineStr">
         <is>
-          <t>LXPP261020068</t>
+          <t>LXPP261020072</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -30379,16 +30379,16 @@
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>SPVYWB5023LK10S</t>
+          <t>SPVYUB4488LKP2L-T2</t>
         </is>
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>托特手提包</t>
+          <t>化妆包</t>
         </is>
       </c>
       <c r="G407" s="1" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H407" t="inlineStr">
         <is>
@@ -30397,11 +30397,11 @@
       </c>
       <c r="I407" t="inlineStr">
         <is>
-          <t>4001#黑色/11.5寸</t>
+          <t>11#小卡其格/大号/两件套</t>
         </is>
       </c>
       <c r="J407" s="1" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="K407" t="inlineStr">
         <is>
@@ -30409,18 +30409,22 @@
         </is>
       </c>
       <c r="L407" s="1" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="M407"/>
       <c r="N407"/>
       <c r="O407"/>
       <c r="P407" t="inlineStr">
         <is>
-          <t>合成革高速线（计件）</t>
+          <t>丝棉包生产线</t>
         </is>
       </c>
       <c r="Q407"/>
-      <c r="R407"/>
+      <c r="R407" t="inlineStr">
+        <is>
+          <t>爆款</t>
+        </is>
+      </c>
       <c r="S407" t="inlineStr">
         <is>
           <t>否</t>
@@ -30430,7 +30434,7 @@
     <row r="408" customHeight="true" ht="15">
       <c r="A408" t="inlineStr">
         <is>
-          <t>LXPP261020069</t>
+          <t>LXPP261020073</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -30450,16 +30454,16 @@
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>SPVYWB6210LK42L-C1</t>
+          <t>SPVYUB4488LKP1L-T2</t>
         </is>
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>午餐托特包</t>
+          <t>化妆包</t>
         </is>
       </c>
       <c r="G408" s="1" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="H408" t="inlineStr">
         <is>
@@ -30468,11 +30472,11 @@
       </c>
       <c r="I408" t="inlineStr">
         <is>
-          <t>#8089黄棕色(压花）/#8089黄棕色羊巴皮/17.3寸</t>
+          <t>27#蓝白条/大号/两件套</t>
         </is>
       </c>
       <c r="J408" s="1" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="K408" t="inlineStr">
         <is>
@@ -30480,18 +30484,22 @@
         </is>
       </c>
       <c r="L408" s="1" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="M408"/>
       <c r="N408"/>
       <c r="O408"/>
       <c r="P408" t="inlineStr">
         <is>
-          <t>午餐包生产线</t>
+          <t>丝棉包生产线</t>
         </is>
       </c>
       <c r="Q408"/>
-      <c r="R408"/>
+      <c r="R408" t="inlineStr">
+        <is>
+          <t>爆款</t>
+        </is>
+      </c>
       <c r="S408" t="inlineStr">
         <is>
           <t>否</t>
@@ -30501,7 +30509,7 @@
     <row r="409" customHeight="true" ht="15">
       <c r="A409" t="inlineStr">
         <is>
-          <t>LXPP261020072</t>
+          <t>LXPP261020074</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -30521,7 +30529,7 @@
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>SPVYUB4488LKP2L-T2</t>
+          <t>SPVYWB6204LK90S</t>
         </is>
       </c>
       <c r="F409" t="inlineStr">
@@ -30530,7 +30538,7 @@
         </is>
       </c>
       <c r="G409" s="1" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H409" t="inlineStr">
         <is>
@@ -30539,11 +30547,11 @@
       </c>
       <c r="I409" t="inlineStr">
         <is>
-          <t>11#小卡其格/大号/两件套</t>
+          <t>170#灰绿色/小号</t>
         </is>
       </c>
       <c r="J409" s="1" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K409" t="inlineStr">
         <is>
@@ -30551,7 +30559,7 @@
         </is>
       </c>
       <c r="L409" s="1" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M409"/>
       <c r="N409"/>
@@ -30562,11 +30570,7 @@
         </is>
       </c>
       <c r="Q409"/>
-      <c r="R409" t="inlineStr">
-        <is>
-          <t>爆款</t>
-        </is>
-      </c>
+      <c r="R409"/>
       <c r="S409" t="inlineStr">
         <is>
           <t>否</t>
@@ -30576,7 +30580,7 @@
     <row r="410" customHeight="true" ht="15">
       <c r="A410" t="inlineStr">
         <is>
-          <t>LXPP261020073</t>
+          <t>LXPP261020075</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -30596,7 +30600,7 @@
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>SPVYUB4488LKP1L-T2</t>
+          <t>SPVYWB6204LK50L</t>
         </is>
       </c>
       <c r="F410" t="inlineStr">
@@ -30605,7 +30609,7 @@
         </is>
       </c>
       <c r="G410" s="1" t="n">
-        <v>50</v>
+        <v>93</v>
       </c>
       <c r="H410" t="inlineStr">
         <is>
@@ -30614,11 +30618,11 @@
       </c>
       <c r="I410" t="inlineStr">
         <is>
-          <t>27#蓝白条/大号/两件套</t>
+          <t>127#粉色/大号</t>
         </is>
       </c>
       <c r="J410" s="1" t="n">
-        <v>50</v>
+        <v>93</v>
       </c>
       <c r="K410" t="inlineStr">
         <is>
@@ -30626,7 +30630,7 @@
         </is>
       </c>
       <c r="L410" s="1" t="n">
-        <v>50</v>
+        <v>93</v>
       </c>
       <c r="M410"/>
       <c r="N410"/>
@@ -30636,12 +30640,12 @@
           <t>丝棉包生产线</t>
         </is>
       </c>
-      <c r="Q410"/>
-      <c r="R410" t="inlineStr">
-        <is>
-          <t>爆款</t>
-        </is>
-      </c>
+      <c r="Q410" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> (SPVYWB6204LK50L平衡利库调拨，修改时间2026-10-21 12:19:37，调整前申请数量：100.0；调整后申请数量：93.0;)</t>
+        </is>
+      </c>
+      <c r="R410"/>
       <c r="S410" t="inlineStr">
         <is>
           <t>否</t>
@@ -30651,7 +30655,7 @@
     <row r="411" customHeight="true" ht="15">
       <c r="A411" t="inlineStr">
         <is>
-          <t>LXPP261020074</t>
+          <t>LXPP261020079</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -30671,12 +30675,12 @@
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>SPVYWB6204LK90S</t>
+          <t>SPVYWB2038LK19M</t>
         </is>
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>化妆包</t>
+          <t>帆布托特包</t>
         </is>
       </c>
       <c r="G411" s="1" t="n">
@@ -30684,12 +30688,12 @@
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>李杰</t>
+          <t>吴冠烨</t>
         </is>
       </c>
       <c r="I411" t="inlineStr">
         <is>
-          <t>170#灰绿色/小号</t>
+          <t>902#粉泥</t>
         </is>
       </c>
       <c r="J411" s="1" t="n">
@@ -30708,7 +30712,7 @@
       <c r="O411"/>
       <c r="P411" t="inlineStr">
         <is>
-          <t>丝棉包生产线</t>
+          <t>合成革高速线（计件）</t>
         </is>
       </c>
       <c r="Q411"/>
@@ -30722,7 +30726,7 @@
     <row r="412" customHeight="true" ht="15">
       <c r="A412" t="inlineStr">
         <is>
-          <t>LXPP261020075</t>
+          <t>LXPP261020080</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -30742,29 +30746,29 @@
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>SPVYWB6204LK50L</t>
+          <t>SPVYWB2038LK22M</t>
         </is>
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>化妆包</t>
+          <t>帆布托特包</t>
         </is>
       </c>
       <c r="G412" s="1" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>李杰</t>
+          <t>吴冠烨</t>
         </is>
       </c>
       <c r="I412" t="inlineStr">
         <is>
-          <t>127#粉色/大号</t>
+          <t>171#橄榄绿</t>
         </is>
       </c>
       <c r="J412" s="1" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="K412" t="inlineStr">
         <is>
@@ -30772,19 +30776,19 @@
         </is>
       </c>
       <c r="L412" s="1" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="M412"/>
       <c r="N412"/>
       <c r="O412"/>
       <c r="P412" t="inlineStr">
         <is>
-          <t>丝棉包生产线</t>
+          <t>合成革高速线（计件）</t>
         </is>
       </c>
       <c r="Q412" t="inlineStr">
         <is>
-          <t xml:space="preserve"> (SPVYWB6204LK50L平衡利库调拨，修改时间2026-10-21 12:19:37，调整前申请数量：100.0；调整后申请数量：93.0;)</t>
+          <t xml:space="preserve"> (SPVYWB2038LK22M平衡利库调拨，修改时间2026-10-21 11:05:37，调整前申请数量：100.0；调整后申请数量：98.0;)</t>
         </is>
       </c>
       <c r="R412"/>
@@ -30797,7 +30801,7 @@
     <row r="413" customHeight="true" ht="15">
       <c r="A413" t="inlineStr">
         <is>
-          <t>LXPP261020079</t>
+          <t>LXPP261020081</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -30817,7 +30821,7 @@
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>SPVYWB2038LK19M</t>
+          <t>SPVYWB2038LK23M</t>
         </is>
       </c>
       <c r="F413" t="inlineStr">
@@ -30826,7 +30830,7 @@
         </is>
       </c>
       <c r="G413" s="1" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H413" t="inlineStr">
         <is>
@@ -30835,11 +30839,11 @@
       </c>
       <c r="I413" t="inlineStr">
         <is>
-          <t>902#粉泥</t>
+          <t>131#森林绿/01#黑色</t>
         </is>
       </c>
       <c r="J413" s="1" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K413" t="inlineStr">
         <is>
@@ -30847,7 +30851,7 @@
         </is>
       </c>
       <c r="L413" s="1" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="M413"/>
       <c r="N413"/>
@@ -30857,7 +30861,11 @@
           <t>合成革高速线（计件）</t>
         </is>
       </c>
-      <c r="Q413"/>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> (SPVYWB2038LK23M平衡利库调拨，修改时间2026-10-21 11:59:45，调整前申请数量：100.0；调整后申请数量：99.0;)</t>
+        </is>
+      </c>
       <c r="R413"/>
       <c r="S413" t="inlineStr">
         <is>
@@ -30868,12 +30876,12 @@
     <row r="414" customHeight="true" ht="15">
       <c r="A414" t="inlineStr">
         <is>
-          <t>LXPP261020080</t>
+          <t>LXPP261020082</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>创建</t>
+          <t>已审核</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -30888,16 +30896,16 @@
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>SPVYWB2038LK22M</t>
+          <t>SPVYUB2062LK28T</t>
         </is>
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>帆布托特包</t>
+          <t>鞋仓旅行包</t>
         </is>
       </c>
       <c r="G414" s="1" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H414" t="inlineStr">
         <is>
@@ -30906,11 +30914,11 @@
       </c>
       <c r="I414" t="inlineStr">
         <is>
-          <t>171#橄榄绿</t>
+          <t>24#裸色/两件套</t>
         </is>
       </c>
       <c r="J414" s="1" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="K414" t="inlineStr">
         <is>
@@ -30918,22 +30926,22 @@
         </is>
       </c>
       <c r="L414" s="1" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M414"/>
       <c r="N414"/>
       <c r="O414"/>
       <c r="P414" t="inlineStr">
         <is>
-          <t>合成革高速线（计件）</t>
-        </is>
-      </c>
-      <c r="Q414" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> (SPVYWB2038LK22M平衡利库调拨，修改时间2026-10-21 11:05:37，调整前申请数量：100.0；调整后申请数量：98.0;)</t>
-        </is>
-      </c>
-      <c r="R414"/>
+          <t>布类高速线（计件）</t>
+        </is>
+      </c>
+      <c r="Q414"/>
+      <c r="R414" t="inlineStr">
+        <is>
+          <t>大爆款</t>
+        </is>
+      </c>
       <c r="S414" t="inlineStr">
         <is>
           <t>否</t>
@@ -30943,12 +30951,12 @@
     <row r="415" customHeight="true" ht="15">
       <c r="A415" t="inlineStr">
         <is>
-          <t>LXPP261020081</t>
+          <t>LXPP261020083</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>创建</t>
+          <t>已审核</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
@@ -30963,16 +30971,16 @@
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>SPVYWB2038LK23M</t>
+          <t>SPVYUB2062LK14T</t>
         </is>
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>帆布托特包</t>
+          <t>鞋仓旅行包</t>
         </is>
       </c>
       <c r="G415" s="1" t="n">
-        <v>99</v>
+        <v>150</v>
       </c>
       <c r="H415" t="inlineStr">
         <is>
@@ -30981,11 +30989,11 @@
       </c>
       <c r="I415" t="inlineStr">
         <is>
-          <t>131#森林绿/01#黑色</t>
+          <t>24#深紫色/两件套</t>
         </is>
       </c>
       <c r="J415" s="1" t="n">
-        <v>99</v>
+        <v>150</v>
       </c>
       <c r="K415" t="inlineStr">
         <is>
@@ -30993,22 +31001,22 @@
         </is>
       </c>
       <c r="L415" s="1" t="n">
-        <v>99</v>
+        <v>150</v>
       </c>
       <c r="M415"/>
       <c r="N415"/>
       <c r="O415"/>
       <c r="P415" t="inlineStr">
         <is>
-          <t>合成革高速线（计件）</t>
-        </is>
-      </c>
-      <c r="Q415" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> (SPVYWB2038LK23M平衡利库调拨，修改时间2026-10-21 11:59:45，调整前申请数量：100.0；调整后申请数量：99.0;)</t>
-        </is>
-      </c>
-      <c r="R415"/>
+          <t>布类高速线（计件）</t>
+        </is>
+      </c>
+      <c r="Q415"/>
+      <c r="R415" t="inlineStr">
+        <is>
+          <t>大爆款</t>
+        </is>
+      </c>
       <c r="S415" t="inlineStr">
         <is>
           <t>否</t>
@@ -31018,7 +31026,7 @@
     <row r="416" customHeight="true" ht="15">
       <c r="A416" t="inlineStr">
         <is>
-          <t>LXPP261020082</t>
+          <t>LXPP261020084</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -31038,7 +31046,7 @@
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>SPVYUB2062LK28T</t>
+          <t>SPVYUB2062LK12T-SND</t>
         </is>
       </c>
       <c r="F416" t="inlineStr">
@@ -31056,7 +31064,7 @@
       </c>
       <c r="I416" t="inlineStr">
         <is>
-          <t>24#裸色/两件套</t>
+          <t>15#粉色/三件套</t>
         </is>
       </c>
       <c r="J416" s="1" t="n">
@@ -31093,7 +31101,7 @@
     <row r="417" customHeight="true" ht="15">
       <c r="A417" t="inlineStr">
         <is>
-          <t>LXPP261020083</t>
+          <t>LXPP261020085</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -31113,7 +31121,7 @@
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>SPVYUB2062LK14T</t>
+          <t>SPVYUB2062LK01T-L</t>
         </is>
       </c>
       <c r="F417" t="inlineStr">
@@ -31122,7 +31130,7 @@
         </is>
       </c>
       <c r="G417" s="1" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="H417" t="inlineStr">
         <is>
@@ -31131,11 +31139,11 @@
       </c>
       <c r="I417" t="inlineStr">
         <is>
-          <t>24#深紫色/两件套</t>
+          <t>34#黑色/两件套/大号</t>
         </is>
       </c>
       <c r="J417" s="1" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="K417" t="inlineStr">
         <is>
@@ -31143,7 +31151,7 @@
         </is>
       </c>
       <c r="L417" s="1" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="M417"/>
       <c r="N417"/>
@@ -31168,7 +31176,7 @@
     <row r="418" customHeight="true" ht="15">
       <c r="A418" t="inlineStr">
         <is>
-          <t>LXPP261020084</t>
+          <t>LXPP261020086</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
@@ -31188,7 +31196,7 @@
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>SPVYUB2062LK12T-SND</t>
+          <t>SPVYUB2062LK12T-L</t>
         </is>
       </c>
       <c r="F418" t="inlineStr">
@@ -31197,7 +31205,7 @@
         </is>
       </c>
       <c r="G418" s="1" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H418" t="inlineStr">
         <is>
@@ -31206,11 +31214,11 @@
       </c>
       <c r="I418" t="inlineStr">
         <is>
-          <t>15#粉色/三件套</t>
+          <t>15#粉色/两件套/大号</t>
         </is>
       </c>
       <c r="J418" s="1" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="K418" t="inlineStr">
         <is>
@@ -31218,7 +31226,7 @@
         </is>
       </c>
       <c r="L418" s="1" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M418"/>
       <c r="N418"/>
@@ -31228,7 +31236,11 @@
           <t>布类高速线（计件）</t>
         </is>
       </c>
-      <c r="Q418"/>
+      <c r="Q418" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> (SPVYUB2062LK12T-L平衡利库调拨，修改时间2026-10-21 14:50:23，调整前申请数量：100.0；调整后申请数量：98.0;)</t>
+        </is>
+      </c>
       <c r="R418" t="inlineStr">
         <is>
           <t>大爆款</t>
@@ -31243,7 +31255,7 @@
     <row r="419" customHeight="true" ht="15">
       <c r="A419" t="inlineStr">
         <is>
-          <t>LXPP261020085</t>
+          <t>LXPP261020087</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -31263,7 +31275,7 @@
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>SPVYUB2062LK01T-L</t>
+          <t>SPVYUB2062LK02T-1-L</t>
         </is>
       </c>
       <c r="F419" t="inlineStr">
@@ -31272,7 +31284,7 @@
         </is>
       </c>
       <c r="G419" s="1" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H419" t="inlineStr">
         <is>
@@ -31281,11 +31293,11 @@
       </c>
       <c r="I419" t="inlineStr">
         <is>
-          <t>34#黑色/两件套/大号</t>
+          <t>142#米白色/两件套/棕色织带/大号</t>
         </is>
       </c>
       <c r="J419" s="1" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K419" t="inlineStr">
         <is>
@@ -31293,7 +31305,7 @@
         </is>
       </c>
       <c r="L419" s="1" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="M419"/>
       <c r="N419"/>
@@ -31303,7 +31315,11 @@
           <t>布类高速线（计件）</t>
         </is>
       </c>
-      <c r="Q419"/>
+      <c r="Q419" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> (SPVYUB2062LK02T-1-L平衡利库调拨，修改时间2026-10-21 14:49:46，调整前申请数量：100.0；调整后申请数量：99.0;)</t>
+        </is>
+      </c>
       <c r="R419" t="inlineStr">
         <is>
           <t>大爆款</t>
@@ -31318,12 +31334,12 @@
     <row r="420" customHeight="true" ht="15">
       <c r="A420" t="inlineStr">
         <is>
-          <t>LXPP261020086</t>
+          <t>LXPP261020094</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>已审核</t>
+          <t>创建</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
@@ -31338,16 +31354,16 @@
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>SPVYUB2062LK12T-L</t>
+          <t>SPVYWB4235LKP1M-T2</t>
         </is>
       </c>
       <c r="F420" t="inlineStr">
         <is>
-          <t>鞋仓旅行包</t>
+          <t>电脑手提包</t>
         </is>
       </c>
       <c r="G420" s="1" t="n">
-        <v>98</v>
+        <v>450</v>
       </c>
       <c r="H420" t="inlineStr">
         <is>
@@ -31356,11 +31372,11 @@
       </c>
       <c r="I420" t="inlineStr">
         <is>
-          <t>15#粉色/两件套/大号</t>
+          <t>001#黑色/180#米色/138#棕色/15.6寸/两件套</t>
         </is>
       </c>
       <c r="J420" s="1" t="n">
-        <v>98</v>
+        <v>450</v>
       </c>
       <c r="K420" t="inlineStr">
         <is>
@@ -31368,26 +31384,18 @@
         </is>
       </c>
       <c r="L420" s="1" t="n">
-        <v>98</v>
+        <v>450</v>
       </c>
       <c r="M420"/>
       <c r="N420"/>
       <c r="O420"/>
       <c r="P420" t="inlineStr">
         <is>
-          <t>布类高速线（计件）</t>
-        </is>
-      </c>
-      <c r="Q420" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> (SPVYUB2062LK12T-L平衡利库调拨，修改时间2026-10-21 14:50:23，调整前申请数量：100.0；调整后申请数量：98.0;)</t>
-        </is>
-      </c>
-      <c r="R420" t="inlineStr">
-        <is>
-          <t>大爆款</t>
-        </is>
-      </c>
+          <t>合成革高速线（计件）</t>
+        </is>
+      </c>
+      <c r="Q420"/>
+      <c r="R420"/>
       <c r="S420" t="inlineStr">
         <is>
           <t>否</t>
@@ -31397,12 +31405,12 @@
     <row r="421" customHeight="true" ht="15">
       <c r="A421" t="inlineStr">
         <is>
-          <t>LXPP261020087</t>
+          <t>LXPP261020095</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>已审核</t>
+          <t>创建</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
@@ -31417,16 +31425,16 @@
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>SPVYUB2062LK02T-1-L</t>
+          <t>SPVYWB4235LKP1L-T2</t>
         </is>
       </c>
       <c r="F421" t="inlineStr">
         <is>
-          <t>鞋仓旅行包</t>
+          <t>电脑手提包</t>
         </is>
       </c>
       <c r="G421" s="1" t="n">
-        <v>99</v>
+        <v>350</v>
       </c>
       <c r="H421" t="inlineStr">
         <is>
@@ -31435,11 +31443,11 @@
       </c>
       <c r="I421" t="inlineStr">
         <is>
-          <t>142#米白色/两件套/棕色织带/大号</t>
+          <t>1010D米色/4001#黑色/8119#棕色/17.3寸/两件套</t>
         </is>
       </c>
       <c r="J421" s="1" t="n">
-        <v>99</v>
+        <v>350</v>
       </c>
       <c r="K421" t="inlineStr">
         <is>
@@ -31447,26 +31455,18 @@
         </is>
       </c>
       <c r="L421" s="1" t="n">
-        <v>99</v>
+        <v>350</v>
       </c>
       <c r="M421"/>
       <c r="N421"/>
       <c r="O421"/>
       <c r="P421" t="inlineStr">
         <is>
-          <t>布类高速线（计件）</t>
-        </is>
-      </c>
-      <c r="Q421" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> (SPVYUB2062LK02T-1-L平衡利库调拨，修改时间2026-10-21 14:49:46，调整前申请数量：100.0；调整后申请数量：99.0;)</t>
-        </is>
-      </c>
-      <c r="R421" t="inlineStr">
-        <is>
-          <t>大爆款</t>
-        </is>
-      </c>
+          <t>合成革高速线（计件）</t>
+        </is>
+      </c>
+      <c r="Q421"/>
+      <c r="R421"/>
       <c r="S421" t="inlineStr">
         <is>
           <t>否</t>
@@ -31476,7 +31476,7 @@
     <row r="422" customHeight="true" ht="15">
       <c r="A422" t="inlineStr">
         <is>
-          <t>LXPP261020094</t>
+          <t>LXPP261020096</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
@@ -31496,7 +31496,7 @@
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>SPVYWB4235LKP1M-T2</t>
+          <t>SPVYWB4235LK90M-T2</t>
         </is>
       </c>
       <c r="F422" t="inlineStr">
@@ -31505,7 +31505,7 @@
         </is>
       </c>
       <c r="G422" s="1" t="n">
-        <v>450</v>
+        <v>100</v>
       </c>
       <c r="H422" t="inlineStr">
         <is>
@@ -31514,11 +31514,11 @@
       </c>
       <c r="I422" t="inlineStr">
         <is>
-          <t>001#黑色/180#米色/138#棕色/15.6寸/两件套</t>
+          <t>7093#绿色/15.6寸/两件套</t>
         </is>
       </c>
       <c r="J422" s="1" t="n">
-        <v>450</v>
+        <v>100</v>
       </c>
       <c r="K422" t="inlineStr">
         <is>
@@ -31526,7 +31526,7 @@
         </is>
       </c>
       <c r="L422" s="1" t="n">
-        <v>450</v>
+        <v>100</v>
       </c>
       <c r="M422"/>
       <c r="N422"/>
@@ -31547,7 +31547,7 @@
     <row r="423" customHeight="true" ht="15">
       <c r="A423" t="inlineStr">
         <is>
-          <t>LXPP261020095</t>
+          <t>LXPP261020097</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
@@ -31567,7 +31567,7 @@
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>SPVYWB4235LKP1L-T2</t>
+          <t>SPVYWB4235LKP8M-T2</t>
         </is>
       </c>
       <c r="F423" t="inlineStr">
@@ -31576,7 +31576,7 @@
         </is>
       </c>
       <c r="G423" s="1" t="n">
-        <v>350</v>
+        <v>200</v>
       </c>
       <c r="H423" t="inlineStr">
         <is>
@@ -31585,11 +31585,11 @@
       </c>
       <c r="I423" t="inlineStr">
         <is>
-          <t>1010D米色/4001#黑色/8119#棕色/17.3寸/两件套</t>
+          <t>1010D米色/929#浅沙色/890#深咖色/15.6寸/两件套</t>
         </is>
       </c>
       <c r="J423" s="1" t="n">
-        <v>350</v>
+        <v>200</v>
       </c>
       <c r="K423" t="inlineStr">
         <is>
@@ -31597,7 +31597,7 @@
         </is>
       </c>
       <c r="L423" s="1" t="n">
-        <v>350</v>
+        <v>200</v>
       </c>
       <c r="M423"/>
       <c r="N423"/>
@@ -31618,7 +31618,7 @@
     <row r="424" customHeight="true" ht="15">
       <c r="A424" t="inlineStr">
         <is>
-          <t>LXPP261020096</t>
+          <t>LXPP261020098</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
@@ -31638,7 +31638,7 @@
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>SPVYWB4235LK90M-T2</t>
+          <t>SPVYWB4235LKP5M-T2</t>
         </is>
       </c>
       <c r="F424" t="inlineStr">
@@ -31656,7 +31656,7 @@
       </c>
       <c r="I424" t="inlineStr">
         <is>
-          <t>7093#绿色/15.6寸/两件套</t>
+          <t>1010D米色/7166#墨绿色/4001#黑色/15.6寸/两件套</t>
         </is>
       </c>
       <c r="J424" s="1" t="n">
@@ -31689,7 +31689,7 @@
     <row r="425" customHeight="true" ht="15">
       <c r="A425" t="inlineStr">
         <is>
-          <t>LXPP261020097</t>
+          <t>LXPP261020099</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -31709,7 +31709,7 @@
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>SPVYWB4235LKP8M-T2</t>
+          <t>SPVYWB4235LK20M-M1</t>
         </is>
       </c>
       <c r="F425" t="inlineStr">
@@ -31718,7 +31718,7 @@
         </is>
       </c>
       <c r="G425" s="1" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="H425" t="inlineStr">
         <is>
@@ -31727,11 +31727,11 @@
       </c>
       <c r="I425" t="inlineStr">
         <is>
-          <t>1010D米色/929#浅沙色/890#深咖色/15.6寸/两件套</t>
+          <t>4076#浅灰色/4076#浅灰色（压花）/15.6寸/两件套</t>
         </is>
       </c>
       <c r="J425" s="1" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="K425" t="inlineStr">
         <is>
@@ -31739,7 +31739,7 @@
         </is>
       </c>
       <c r="L425" s="1" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="M425"/>
       <c r="N425"/>
@@ -31760,7 +31760,7 @@
     <row r="426" customHeight="true" ht="15">
       <c r="A426" t="inlineStr">
         <is>
-          <t>LXPP261020098</t>
+          <t>LXPP261020100</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -31780,7 +31780,7 @@
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>SPVYWB4235LKP5M-T2</t>
+          <t>SPVYWB4235LK10M-M1</t>
         </is>
       </c>
       <c r="F426" t="inlineStr">
@@ -31789,7 +31789,7 @@
         </is>
       </c>
       <c r="G426" s="1" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="H426" t="inlineStr">
         <is>
@@ -31798,11 +31798,11 @@
       </c>
       <c r="I426" t="inlineStr">
         <is>
-          <t>1010D米色/7166#墨绿色/4001#黑色/15.6寸/两件套</t>
+          <t>4001#黑色/4001#黑色（压花）/15.6寸/两件套</t>
         </is>
       </c>
       <c r="J426" s="1" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="K426" t="inlineStr">
         <is>
@@ -31810,7 +31810,7 @@
         </is>
       </c>
       <c r="L426" s="1" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="M426"/>
       <c r="N426"/>
@@ -31831,7 +31831,7 @@
     <row r="427" customHeight="true" ht="15">
       <c r="A427" t="inlineStr">
         <is>
-          <t>LXPP261020099</t>
+          <t>LXPP261020101</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
@@ -31851,7 +31851,7 @@
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>SPVYWB4235LK20M-M1</t>
+          <t>SPVYWB4235LK90L-T2</t>
         </is>
       </c>
       <c r="F427" t="inlineStr">
@@ -31860,7 +31860,7 @@
         </is>
       </c>
       <c r="G427" s="1" t="n">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="H427" t="inlineStr">
         <is>
@@ -31869,11 +31869,11 @@
       </c>
       <c r="I427" t="inlineStr">
         <is>
-          <t>4076#浅灰色/4076#浅灰色（压花）/15.6寸/两件套</t>
+          <t>7093绿色/7093绿色（压花）/17.3寸/两件套</t>
         </is>
       </c>
       <c r="J427" s="1" t="n">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="K427" t="inlineStr">
         <is>
@@ -31881,7 +31881,7 @@
         </is>
       </c>
       <c r="L427" s="1" t="n">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="M427"/>
       <c r="N427"/>
@@ -31902,12 +31902,12 @@
     <row r="428" customHeight="true" ht="15">
       <c r="A428" t="inlineStr">
         <is>
-          <t>LXPP261020100</t>
+          <t>LXPP261020102</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>创建</t>
+          <t>已审核</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
@@ -31922,16 +31922,16 @@
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>SPVYWB4235LK10M-M1</t>
+          <t>SPVYMB2023LK01S</t>
         </is>
       </c>
       <c r="F428" t="inlineStr">
         <is>
-          <t>电脑手提包</t>
+          <t>搭盖时尚背包</t>
         </is>
       </c>
       <c r="G428" s="1" t="n">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="H428" t="inlineStr">
         <is>
@@ -31940,11 +31940,11 @@
       </c>
       <c r="I428" t="inlineStr">
         <is>
-          <t>4001#黑色/4001#黑色（压花）/15.6寸/两件套</t>
+          <t>23#黑色/4001#黑色/14寸</t>
         </is>
       </c>
       <c r="J428" s="1" t="n">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="K428" t="inlineStr">
         <is>
@@ -31952,14 +31952,14 @@
         </is>
       </c>
       <c r="L428" s="1" t="n">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="M428"/>
       <c r="N428"/>
       <c r="O428"/>
       <c r="P428" t="inlineStr">
         <is>
-          <t>合成革高速线（计件）</t>
+          <t>布类高速线（计件）</t>
         </is>
       </c>
       <c r="Q428"/>
@@ -31973,12 +31973,12 @@
     <row r="429" customHeight="true" ht="15">
       <c r="A429" t="inlineStr">
         <is>
-          <t>LXPP261020101</t>
+          <t>LXPP261020103</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>创建</t>
+          <t>已审核</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
@@ -31993,16 +31993,16 @@
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>SPVYWB4235LK90L-T2</t>
+          <t>SPVYMB2023LK03S</t>
         </is>
       </c>
       <c r="F429" t="inlineStr">
         <is>
-          <t>电脑手提包</t>
+          <t>搭盖时尚背包</t>
         </is>
       </c>
       <c r="G429" s="1" t="n">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="H429" t="inlineStr">
         <is>
@@ -32011,11 +32011,11 @@
       </c>
       <c r="I429" t="inlineStr">
         <is>
-          <t>7093绿色/7093绿色（压花）/17.3寸/两件套</t>
+          <t>23#黑色/211#红棕色/14寸</t>
         </is>
       </c>
       <c r="J429" s="1" t="n">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="K429" t="inlineStr">
         <is>
@@ -32023,17 +32023,21 @@
         </is>
       </c>
       <c r="L429" s="1" t="n">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="M429"/>
       <c r="N429"/>
       <c r="O429"/>
       <c r="P429" t="inlineStr">
         <is>
-          <t>合成革高速线（计件）</t>
-        </is>
-      </c>
-      <c r="Q429"/>
+          <t>布类高速线（计件）</t>
+        </is>
+      </c>
+      <c r="Q429" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> (SPVYMB2023LK03S平衡利库调拨，修改时间2026-10-21 10:56:35，调整前申请数量：150.0；调整后申请数量：125;)</t>
+        </is>
+      </c>
       <c r="R429"/>
       <c r="S429" t="inlineStr">
         <is>
@@ -32044,7 +32048,7 @@
     <row r="430" customHeight="true" ht="15">
       <c r="A430" t="inlineStr">
         <is>
-          <t>LXPP261020102</t>
+          <t>LXPP261020104</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -32064,7 +32068,7 @@
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>SPVYMB2023LK01S</t>
+          <t>SPVYMB2023LK23S</t>
         </is>
       </c>
       <c r="F430" t="inlineStr">
@@ -32073,7 +32077,7 @@
         </is>
       </c>
       <c r="G430" s="1" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="H430" t="inlineStr">
         <is>
@@ -32082,11 +32086,11 @@
       </c>
       <c r="I430" t="inlineStr">
         <is>
-          <t>23#黑色/4001#黑色/14寸</t>
+          <t>44#绿色/62#米白色/黑色皮革/14寸</t>
         </is>
       </c>
       <c r="J430" s="1" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="K430" t="inlineStr">
         <is>
@@ -32094,7 +32098,7 @@
         </is>
       </c>
       <c r="L430" s="1" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="M430"/>
       <c r="N430"/>
@@ -32115,12 +32119,12 @@
     <row r="431" customHeight="true" ht="15">
       <c r="A431" t="inlineStr">
         <is>
-          <t>LXPP261020103</t>
+          <t>LXPP261020105</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>已审核</t>
+          <t>创建</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
@@ -32135,16 +32139,16 @@
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>SPVYMB2023LK03S</t>
+          <t>SPVYMB5705LKP5L</t>
         </is>
       </c>
       <c r="F431" t="inlineStr">
         <is>
-          <t>搭盖时尚背包</t>
+          <t>午餐电脑背包</t>
         </is>
       </c>
       <c r="G431" s="1" t="n">
-        <v>125</v>
+        <v>36</v>
       </c>
       <c r="H431" t="inlineStr">
         <is>
@@ -32153,11 +32157,11 @@
       </c>
       <c r="I431" t="inlineStr">
         <is>
-          <t>23#黑色/211#红棕色/14寸</t>
+          <t>86#米黄/13#粉色/8094#赤棕色/17.3寸</t>
         </is>
       </c>
       <c r="J431" s="1" t="n">
-        <v>125</v>
+        <v>36</v>
       </c>
       <c r="K431" t="inlineStr">
         <is>
@@ -32165,22 +32169,26 @@
         </is>
       </c>
       <c r="L431" s="1" t="n">
-        <v>125</v>
+        <v>36</v>
       </c>
       <c r="M431"/>
       <c r="N431"/>
       <c r="O431"/>
       <c r="P431" t="inlineStr">
         <is>
-          <t>布类高速线（计件）</t>
+          <t>午餐包生产线</t>
         </is>
       </c>
       <c r="Q431" t="inlineStr">
         <is>
-          <t xml:space="preserve"> (SPVYMB2023LK03S平衡利库调拨，修改时间2026-10-21 10:56:35，调整前申请数量：150.0；调整后申请数量：125;)</t>
-        </is>
-      </c>
-      <c r="R431"/>
+          <t xml:space="preserve"> (SPVYMB5705LKP5L平衡利库调拨，修改时间2026-10-21 10:53:38，调整前申请数量：100.0；调整后申请数量：36.0;)</t>
+        </is>
+      </c>
+      <c r="R431" t="inlineStr">
+        <is>
+          <t>大爆款</t>
+        </is>
+      </c>
       <c r="S431" t="inlineStr">
         <is>
           <t>否</t>
@@ -32190,7 +32198,7 @@
     <row r="432" customHeight="true" ht="15">
       <c r="A432" t="inlineStr">
         <is>
-          <t>LXPP261020104</t>
+          <t>LXPP261020107</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
@@ -32210,16 +32218,16 @@
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>SPVYMB2023LK23S</t>
+          <t>SPVYMB4230LK71L</t>
         </is>
       </c>
       <c r="F432" t="inlineStr">
         <is>
-          <t>搭盖时尚背包</t>
+          <t>电脑背包</t>
         </is>
       </c>
       <c r="G432" s="1" t="n">
-        <v>150</v>
+        <v>30</v>
       </c>
       <c r="H432" t="inlineStr">
         <is>
@@ -32228,11 +32236,11 @@
       </c>
       <c r="I432" t="inlineStr">
         <is>
-          <t>44#绿色/62#米白色/黑色皮革/14寸</t>
+          <t>20#灰紫/17寸</t>
         </is>
       </c>
       <c r="J432" s="1" t="n">
-        <v>150</v>
+        <v>30</v>
       </c>
       <c r="K432" t="inlineStr">
         <is>
@@ -32240,18 +32248,30 @@
         </is>
       </c>
       <c r="L432" s="1" t="n">
-        <v>150</v>
+        <v>30</v>
       </c>
       <c r="M432"/>
-      <c r="N432"/>
+      <c r="N432" t="inlineStr">
+        <is>
+          <t>补单</t>
+        </is>
+      </c>
       <c r="O432"/>
       <c r="P432" t="inlineStr">
         <is>
           <t>布类高速线（计件）</t>
         </is>
       </c>
-      <c r="Q432"/>
-      <c r="R432"/>
+      <c r="Q432" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> (SPVYMB4230LK71L平衡利库调拨，修改时间2026-10-21 10:53:52，调整前申请数量：34.0；调整后申请数量：30.0;)</t>
+        </is>
+      </c>
+      <c r="R432" t="inlineStr">
+        <is>
+          <t>大爆款</t>
+        </is>
+      </c>
       <c r="S432" t="inlineStr">
         <is>
           <t>否</t>
@@ -32261,12 +32281,12 @@
     <row r="433" customHeight="true" ht="15">
       <c r="A433" t="inlineStr">
         <is>
-          <t>LXPP261020105</t>
+          <t>LXPP261020108</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>创建</t>
+          <t>已审核</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
@@ -32281,16 +32301,16 @@
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>SPVYMB5705LKP5L</t>
+          <t>SPVYMB2023LK01S</t>
         </is>
       </c>
       <c r="F433" t="inlineStr">
         <is>
-          <t>午餐电脑背包</t>
+          <t>搭盖时尚背包</t>
         </is>
       </c>
       <c r="G433" s="1" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="H433" t="inlineStr">
         <is>
@@ -32299,11 +32319,11 @@
       </c>
       <c r="I433" t="inlineStr">
         <is>
-          <t>86#米黄/13#粉色/8094#赤棕色/17.3寸</t>
+          <t>23#黑色/4001#黑色/14寸</t>
         </is>
       </c>
       <c r="J433" s="1" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="K433" t="inlineStr">
         <is>
@@ -32311,26 +32331,22 @@
         </is>
       </c>
       <c r="L433" s="1" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="M433"/>
-      <c r="N433"/>
+      <c r="N433" t="inlineStr">
+        <is>
+          <t>补单</t>
+        </is>
+      </c>
       <c r="O433"/>
       <c r="P433" t="inlineStr">
         <is>
-          <t>午餐包生产线</t>
-        </is>
-      </c>
-      <c r="Q433" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> (SPVYMB5705LKP5L平衡利库调拨，修改时间2026-10-21 10:53:38，调整前申请数量：100.0；调整后申请数量：36.0;)</t>
-        </is>
-      </c>
-      <c r="R433" t="inlineStr">
-        <is>
-          <t>大爆款</t>
-        </is>
-      </c>
+          <t>布类高速线（计件）</t>
+        </is>
+      </c>
+      <c r="Q433"/>
+      <c r="R433"/>
       <c r="S433" t="inlineStr">
         <is>
           <t>否</t>
@@ -32340,195 +32356,37 @@
     <row r="434" customHeight="true" ht="15">
       <c r="A434" t="inlineStr">
         <is>
-          <t>LXPP261020107</t>
-        </is>
-      </c>
-      <c r="B434" t="inlineStr">
-        <is>
-          <t>已审核</t>
-        </is>
-      </c>
-      <c r="C434" t="inlineStr">
-        <is>
-          <t>未关闭</t>
-        </is>
-      </c>
-      <c r="D434" t="inlineStr">
-        <is>
-          <t>2026/10/20</t>
-        </is>
-      </c>
-      <c r="E434" t="inlineStr">
-        <is>
-          <t>SPVYMB4230LK71L</t>
-        </is>
-      </c>
-      <c r="F434" t="inlineStr">
-        <is>
-          <t>电脑背包</t>
-        </is>
-      </c>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="B434"/>
+      <c r="C434"/>
+      <c r="D434"/>
+      <c r="E434"/>
+      <c r="F434"/>
       <c r="G434" s="1" t="n">
-        <v>30</v>
-      </c>
-      <c r="H434" t="inlineStr">
-        <is>
-          <t>吴冠烨</t>
-        </is>
-      </c>
-      <c r="I434" t="inlineStr">
-        <is>
-          <t>20#灰紫/17寸</t>
-        </is>
-      </c>
+        <v>76591</v>
+      </c>
+      <c r="H434"/>
+      <c r="I434"/>
       <c r="J434" s="1" t="n">
-        <v>30</v>
-      </c>
-      <c r="K434" t="inlineStr">
-        <is>
-          <t>2026/10/20 00:00:00</t>
-        </is>
-      </c>
+        <v>76591</v>
+      </c>
+      <c r="K434"/>
       <c r="L434" s="1" t="n">
-        <v>30</v>
-      </c>
-      <c r="M434"/>
-      <c r="N434" t="inlineStr">
-        <is>
-          <t>补单</t>
-        </is>
-      </c>
-      <c r="O434"/>
-      <c r="P434" t="inlineStr">
-        <is>
-          <t>布类高速线（计件）</t>
-        </is>
-      </c>
-      <c r="Q434" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> (SPVYMB4230LK71L平衡利库调拨，修改时间2026-10-21 10:53:52，调整前申请数量：34.0；调整后申请数量：30.0;)</t>
-        </is>
-      </c>
-      <c r="R434" t="inlineStr">
-        <is>
-          <t>大爆款</t>
-        </is>
-      </c>
-      <c r="S434" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="435" customHeight="true" ht="15">
-      <c r="A435" t="inlineStr">
-        <is>
-          <t>LXPP261020108</t>
-        </is>
-      </c>
-      <c r="B435" t="inlineStr">
-        <is>
-          <t>已审核</t>
-        </is>
-      </c>
-      <c r="C435" t="inlineStr">
-        <is>
-          <t>未关闭</t>
-        </is>
-      </c>
-      <c r="D435" t="inlineStr">
-        <is>
-          <t>2026/10/20</t>
-        </is>
-      </c>
-      <c r="E435" t="inlineStr">
-        <is>
-          <t>SPVYMB2023LK01S</t>
-        </is>
-      </c>
-      <c r="F435" t="inlineStr">
-        <is>
-          <t>搭盖时尚背包</t>
-        </is>
-      </c>
-      <c r="G435" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="H435" t="inlineStr">
-        <is>
-          <t>吴冠烨</t>
-        </is>
-      </c>
-      <c r="I435" t="inlineStr">
-        <is>
-          <t>23#黑色/4001#黑色/14寸</t>
-        </is>
-      </c>
-      <c r="J435" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="K435" t="inlineStr">
-        <is>
-          <t>2026/10/20 00:00:00</t>
-        </is>
-      </c>
-      <c r="L435" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="M435"/>
-      <c r="N435" t="inlineStr">
-        <is>
-          <t>补单</t>
-        </is>
-      </c>
-      <c r="O435"/>
-      <c r="P435" t="inlineStr">
-        <is>
-          <t>布类高速线（计件）</t>
-        </is>
-      </c>
-      <c r="Q435"/>
-      <c r="R435"/>
-      <c r="S435" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="436" customHeight="true" ht="15">
-      <c r="A436" t="inlineStr">
-        <is>
-          <t>合计</t>
-        </is>
-      </c>
-      <c r="B436"/>
-      <c r="C436"/>
-      <c r="D436"/>
-      <c r="E436"/>
-      <c r="F436"/>
-      <c r="G436" s="1" t="n">
-        <v>77190</v>
-      </c>
-      <c r="H436"/>
-      <c r="I436"/>
-      <c r="J436" s="1" t="n">
-        <v>77190</v>
-      </c>
-      <c r="K436"/>
-      <c r="L436" s="1" t="n">
-        <v>77190</v>
-      </c>
-      <c r="M436" s="1" t="n">
+        <v>76591</v>
+      </c>
+      <c r="M434" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="N436"/>
-      <c r="O436" s="1" t="n">
+      <c r="N434"/>
+      <c r="O434" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="P436"/>
-      <c r="Q436"/>
-      <c r="R436"/>
-      <c r="S436"/>
+      <c r="P434"/>
+      <c r="Q434"/>
+      <c r="R434"/>
+      <c r="S434"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/otd_apply.xlsx
+++ b/src/otd_apply.xlsx
@@ -1049,7 +1049,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>审核中</t>
+          <t>已审核</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>审核中</t>
+          <t>已审核</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -17297,7 +17297,7 @@
     <row r="231" customHeight="true" ht="15">
       <c r="A231" t="inlineStr">
         <is>
-          <t>JDYPR261020021433B5049LK41M</t>
+          <t>JDYPR2610200415213LK10XL-T4</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -17312,34 +17312,34 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>2026/10/20</t>
+          <t>2026/10/21</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>VYWB5049LK41M</t>
+          <t>SPVYMB4343LK10XL-T4</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>女士斜挎包</t>
+          <t>旅行背包</t>
         </is>
       </c>
       <c r="G231" s="1" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>唐海阳</t>
+          <t>何思琴</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>8094#赤棕色/小号/配两条肩带</t>
+          <t>33#黑色/4001黑色/18寸/四件套</t>
         </is>
       </c>
       <c r="J231" s="1" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K231" t="inlineStr">
         <is>
@@ -17347,19 +17347,19 @@
         </is>
       </c>
       <c r="L231" s="1" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M231"/>
       <c r="N231"/>
       <c r="O231"/>
       <c r="P231" t="inlineStr">
         <is>
-          <t>合成革高速线（计件）</t>
+          <t>布类高速线（计件）</t>
         </is>
       </c>
       <c r="Q231" t="inlineStr">
         <is>
-          <t>补采购单尾数</t>
+          <t>11 12月系统预测日均偏低</t>
         </is>
       </c>
       <c r="R231"/>
@@ -17372,7 +17372,7 @@
     <row r="232" customHeight="true" ht="15">
       <c r="A232" t="inlineStr">
         <is>
-          <t>JDYPR261020021543B5049LK11L</t>
+          <t>JDYPR26102004152143LKP2L-T4</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -17387,34 +17387,34 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>2026/10/20</t>
+          <t>2026/10/21</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>SPVYWB5049LK11L</t>
+          <t>SPVYMB4343LKP2L-T4</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>女士斜挎包</t>
+          <t>旅行背包</t>
         </is>
       </c>
       <c r="G232" s="1" t="n">
-        <v>20</v>
+        <v>698</v>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>唐海阳</t>
+          <t>何思琴</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>复古401#黑色/大号/配两条肩带</t>
+          <t>88#豆绿/86#米白色/171#深橄榄绿/17.3寸/四件套</t>
         </is>
       </c>
       <c r="J232" s="1" t="n">
-        <v>20</v>
+        <v>698</v>
       </c>
       <c r="K232" t="inlineStr">
         <is>
@@ -17422,19 +17422,19 @@
         </is>
       </c>
       <c r="L232" s="1" t="n">
-        <v>20</v>
+        <v>698</v>
       </c>
       <c r="M232"/>
       <c r="N232"/>
       <c r="O232"/>
       <c r="P232" t="inlineStr">
         <is>
-          <t>合成革高速线（计件）</t>
+          <t>布类高速线（计件）</t>
         </is>
       </c>
       <c r="Q232" t="inlineStr">
         <is>
-          <t>补采购单尾数(SPVYWB5049LK11L平衡利库调拨，修改时间2026-10-21 10:57:52，调整前申请数量：50.0；调整后申请数量：20.0;)</t>
+          <t>11 12月系统预测日均偏低 平衡利库</t>
         </is>
       </c>
       <c r="R232"/>
@@ -17447,7 +17447,7 @@
     <row r="233" customHeight="true" ht="15">
       <c r="A233" t="inlineStr">
         <is>
-          <t>JDYPR2610200415213LK10XL-T4</t>
+          <t>JDYPR26102004152143LKP4L-T4</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -17467,7 +17467,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>SPVYMB4343LK10XL-T4</t>
+          <t>SPVYMB4343LKP4L-T4</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -17476,7 +17476,7 @@
         </is>
       </c>
       <c r="G233" s="1" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="H233" t="inlineStr">
         <is>
@@ -17485,11 +17485,11 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>33#黑色/4001黑色/18寸/四件套</t>
+          <t>23#蓝紫色/4001#黑色/17.3寸/四件套</t>
         </is>
       </c>
       <c r="J233" s="1" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="K233" t="inlineStr">
         <is>
@@ -17497,7 +17497,7 @@
         </is>
       </c>
       <c r="L233" s="1" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="M233"/>
       <c r="N233"/>
@@ -17522,7 +17522,7 @@
     <row r="234" customHeight="true" ht="15">
       <c r="A234" t="inlineStr">
         <is>
-          <t>JDYPR26102004152143LKP2L-T4</t>
+          <t>JDYPR26102004152143LKP9L-T4</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -17542,7 +17542,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>SPVYMB4343LKP2L-T4</t>
+          <t>SPVYMB4343LKP9L-T4</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -17551,7 +17551,7 @@
         </is>
       </c>
       <c r="G234" s="1" t="n">
-        <v>698</v>
+        <v>100</v>
       </c>
       <c r="H234" t="inlineStr">
         <is>
@@ -17560,11 +17560,11 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>88#豆绿/86#米白色/171#深橄榄绿/17.3寸/四件套</t>
+          <t>38#墨蓝/27#灰蓝色/4001#黑色/17.3寸/四件套</t>
         </is>
       </c>
       <c r="J234" s="1" t="n">
-        <v>698</v>
+        <v>100</v>
       </c>
       <c r="K234" t="inlineStr">
         <is>
@@ -17572,7 +17572,7 @@
         </is>
       </c>
       <c r="L234" s="1" t="n">
-        <v>698</v>
+        <v>100</v>
       </c>
       <c r="M234"/>
       <c r="N234"/>
@@ -17584,7 +17584,7 @@
       </c>
       <c r="Q234" t="inlineStr">
         <is>
-          <t>11 12月系统预测日均偏低 平衡利库</t>
+          <t>11 12月系统预测日均偏低</t>
         </is>
       </c>
       <c r="R234"/>
@@ -17597,7 +17597,7 @@
     <row r="235" customHeight="true" ht="15">
       <c r="A235" t="inlineStr">
         <is>
-          <t>JDYPR26102004152143LKP4L-T4</t>
+          <t>JDYPR26102004152143LKPFL-T4</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -17617,7 +17617,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>SPVYMB4343LKP4L-T4</t>
+          <t>SPVYMB4343LKPFL-T4</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
@@ -17626,7 +17626,7 @@
         </is>
       </c>
       <c r="G235" s="1" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="H235" t="inlineStr">
         <is>
@@ -17635,11 +17635,11 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>23#蓝紫色/4001#黑色/17.3寸/四件套</t>
+          <t>34A黄棕色/62#米白色/4001黑色/17.3寸/四件套</t>
         </is>
       </c>
       <c r="J235" s="1" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="K235" t="inlineStr">
         <is>
@@ -17647,7 +17647,7 @@
         </is>
       </c>
       <c r="L235" s="1" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="M235"/>
       <c r="N235"/>
@@ -17672,12 +17672,12 @@
     <row r="236" customHeight="true" ht="15">
       <c r="A236" t="inlineStr">
         <is>
-          <t>JDYPR26102004152143LKP9L-T4</t>
+          <t>JDYPR26102012103361LK90L-C1</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>创建</t>
+          <t>已审核</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -17687,17 +17687,17 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>2026/10/21</t>
+          <t>2026/10/20</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>SPVYMB4343LKP9L-T4</t>
+          <t>VYWB5561LK90L-C1</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>旅行背包</t>
+          <t>电脑手提包</t>
         </is>
       </c>
       <c r="G236" s="1" t="n">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>何思琴</t>
+          <t>姚鲜珍</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>38#墨蓝/27#灰蓝色/4001#黑色/17.3寸/四件套</t>
+          <t>7093墨绿/7093墨绿（压花）/大号</t>
         </is>
       </c>
       <c r="J236" s="1" t="n">
@@ -17718,7 +17718,7 @@
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t>2026/11/19 00:00:00</t>
+          <t>2026/10/20 00:00:00</t>
         </is>
       </c>
       <c r="L236" s="1" t="n">
@@ -17729,12 +17729,12 @@
       <c r="O236"/>
       <c r="P236" t="inlineStr">
         <is>
-          <t>布类高速线（计件）</t>
+          <t>合成革高速线（计件）</t>
         </is>
       </c>
       <c r="Q236" t="inlineStr">
         <is>
-          <t>11 12月系统预测日均偏低</t>
+          <t>5561系列部分变体补单，近2个月一直缺货，无法提报活动；当前9100库存中只有7500是5561的，其余是小的时尚包；佳俊出货较慢</t>
         </is>
       </c>
       <c r="R236"/>
@@ -17747,12 +17747,12 @@
     <row r="237" customHeight="true" ht="15">
       <c r="A237" t="inlineStr">
         <is>
-          <t>JDYPR26102004152143LKPFL-T4</t>
+          <t>JDYPR26102012103361LK90M-C1</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>创建</t>
+          <t>已审核</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -17762,54 +17762,54 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>2026/10/21</t>
+          <t>2026/10/20</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>SPVYMB4343LKPFL-T4</t>
+          <t>VYWB5561LK90M-C1</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>旅行背包</t>
+          <t>电脑手提包</t>
         </is>
       </c>
       <c r="G237" s="1" t="n">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>何思琴</t>
+          <t>姚鲜珍</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>34A黄棕色/62#米白色/4001黑色/17.3寸/四件套</t>
+          <t>7093墨绿/7093墨绿（压花）/中号</t>
         </is>
       </c>
       <c r="J237" s="1" t="n">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t>2026/11/19 00:00:00</t>
+          <t>2026/10/20 00:00:00</t>
         </is>
       </c>
       <c r="L237" s="1" t="n">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="M237"/>
       <c r="N237"/>
       <c r="O237"/>
       <c r="P237" t="inlineStr">
         <is>
-          <t>布类高速线（计件）</t>
+          <t>合成革高速线（计件）</t>
         </is>
       </c>
       <c r="Q237" t="inlineStr">
         <is>
-          <t>11 12月系统预测日均偏低</t>
+          <t>5561系列部分变体补单，近2个月一直缺货，无法提报活动；当前9100库存中只有7500是5561的，其余是小的时尚包；佳俊出货较慢</t>
         </is>
       </c>
       <c r="R237"/>
@@ -17822,7 +17822,7 @@
     <row r="238" customHeight="true" ht="15">
       <c r="A238" t="inlineStr">
         <is>
-          <t>JDYPR26102012103361LK90L-C1</t>
+          <t>JDYPR261020121033B5561LK20M</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -17842,7 +17842,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>VYWB5561LK90L-C1</t>
+          <t>VYWB5561LK20M</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -17860,7 +17860,7 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>7093墨绿/7093墨绿（压花）/大号</t>
+          <t>4050D古堡灰/中号</t>
         </is>
       </c>
       <c r="J238" s="1" t="n">
@@ -17897,7 +17897,7 @@
     <row r="239" customHeight="true" ht="15">
       <c r="A239" t="inlineStr">
         <is>
-          <t>JDYPR26102012103361LK90M-C1</t>
+          <t>JDYPR261020121033B5561LK40L</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -17917,7 +17917,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>VYWB5561LK90M-C1</t>
+          <t>VYWB5561LK40L</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
@@ -17926,7 +17926,7 @@
         </is>
       </c>
       <c r="G239" s="1" t="n">
-        <v>700</v>
+        <v>200</v>
       </c>
       <c r="H239" t="inlineStr">
         <is>
@@ -17935,11 +17935,11 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>7093墨绿/7093墨绿（压花）/中号</t>
+          <t>复古8102红咖啡棕/大号</t>
         </is>
       </c>
       <c r="J239" s="1" t="n">
-        <v>700</v>
+        <v>200</v>
       </c>
       <c r="K239" t="inlineStr">
         <is>
@@ -17947,7 +17947,7 @@
         </is>
       </c>
       <c r="L239" s="1" t="n">
-        <v>700</v>
+        <v>200</v>
       </c>
       <c r="M239"/>
       <c r="N239"/>
@@ -17972,7 +17972,7 @@
     <row r="240" customHeight="true" ht="15">
       <c r="A240" t="inlineStr">
         <is>
-          <t>JDYPR261020121033B5561LK20M</t>
+          <t>JDYPR261020121033B5561LK40M</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -17992,7 +17992,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>VYWB5561LK20M</t>
+          <t>VYWB5561LK40M</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
@@ -18010,7 +18010,7 @@
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>4050D古堡灰/中号</t>
+          <t>复古8102红咖啡棕/中号</t>
         </is>
       </c>
       <c r="J240" s="1" t="n">
@@ -18047,7 +18047,7 @@
     <row r="241" customHeight="true" ht="15">
       <c r="A241" t="inlineStr">
         <is>
-          <t>JDYPR261020121033B5561LK40L</t>
+          <t>JDYPR261020121033B5561LKP1M</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -18067,7 +18067,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>VYWB5561LK40L</t>
+          <t>VYWB5561LKP1M</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -18085,7 +18085,7 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>复古8102红咖啡棕/大号</t>
+          <t>4001黑色/1007白杏色/8132D肉桂色/中号</t>
         </is>
       </c>
       <c r="J241" s="1" t="n">
@@ -18122,12 +18122,12 @@
     <row r="242" customHeight="true" ht="15">
       <c r="A242" t="inlineStr">
         <is>
-          <t>JDYPR261020121033B5561LK40M</t>
+          <t>JDYPR261022103431B4561LKP6M</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>已审核</t>
+          <t>创建</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -18137,54 +18137,54 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>2026/10/20</t>
+          <t>2026/10/22</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>VYWB5561LK40M</t>
+          <t>SPVYMB4561LKP6M</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>电脑手提包</t>
+          <t>电脑背包</t>
         </is>
       </c>
       <c r="G242" s="1" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>姚鲜珍</t>
+          <t>李晓玲</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>复古8102红咖啡棕/中号</t>
+          <t>48#绿色/77#米白色/7429D深绿灰/15.6寸</t>
         </is>
       </c>
       <c r="J242" s="1" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="K242" t="inlineStr">
         <is>
-          <t>2026/10/20 00:00:00</t>
+          <t>2026/11/21 00:00:00</t>
         </is>
       </c>
       <c r="L242" s="1" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="M242"/>
       <c r="N242"/>
       <c r="O242"/>
       <c r="P242" t="inlineStr">
         <is>
-          <t>合成革高速线（计件）</t>
+          <t>布类高速线（计件）</t>
         </is>
       </c>
       <c r="Q242" t="inlineStr">
         <is>
-          <t>5561系列部分变体补单，近2个月一直缺货，无法提报活动；当前9100库存中只有7500是5561的，其余是小的时尚包；佳俊出货较慢</t>
+          <t>新变体原下单100，平衡利库50个，剩50个无法下单，补交50个凑100下单</t>
         </is>
       </c>
       <c r="R242"/>
@@ -18197,7 +18197,7 @@
     <row r="243" customHeight="true" ht="15">
       <c r="A243" t="inlineStr">
         <is>
-          <t>JDYPR261020121033B5561LKP1M</t>
+          <t>LXPP261020002</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -18217,12 +18217,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>VYWB5561LKP1M</t>
+          <t>SPVYWB4408LKP3L-T2</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>电脑手提包</t>
+          <t>旅行托特包</t>
         </is>
       </c>
       <c r="G243" s="1" t="n">
@@ -18230,12 +18230,12 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>姚鲜珍</t>
+          <t>邹娇</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>4001黑色/1007白杏色/8132D肉桂色/中号</t>
+          <t>213#米白色/18#深绿色/156#豆绿/17.3寸/两件套</t>
         </is>
       </c>
       <c r="J243" s="1" t="n">
@@ -18254,15 +18254,15 @@
       <c r="O243"/>
       <c r="P243" t="inlineStr">
         <is>
-          <t>合成革高速线（计件）</t>
-        </is>
-      </c>
-      <c r="Q243" t="inlineStr">
-        <is>
-          <t>5561系列部分变体补单，近2个月一直缺货，无法提报活动；当前9100库存中只有7500是5561的，其余是小的时尚包；佳俊出货较慢</t>
-        </is>
-      </c>
-      <c r="R243"/>
+          <t>丝棉包生产线</t>
+        </is>
+      </c>
+      <c r="Q243"/>
+      <c r="R243" t="inlineStr">
+        <is>
+          <t>爆款</t>
+        </is>
+      </c>
       <c r="S243" t="inlineStr">
         <is>
           <t>否</t>
@@ -18272,12 +18272,12 @@
     <row r="244" customHeight="true" ht="15">
       <c r="A244" t="inlineStr">
         <is>
-          <t>JDYPR261022103431B4561LKP6M</t>
+          <t>LXPP261020003</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>创建</t>
+          <t>已审核</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -18287,57 +18287,57 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>2026/10/22</t>
+          <t>2026/10/20</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>SPVYMB4561LKP6M</t>
+          <t>SPVYWB4408LKP1M-T2</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>电脑背包</t>
+          <t>旅行托特包</t>
         </is>
       </c>
       <c r="G244" s="1" t="n">
-        <v>50</v>
+        <v>300</v>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>李晓玲</t>
+          <t>邹娇</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>48#绿色/77#米白色/7429D深绿灰/15.6寸</t>
+          <t>213#米白色/48#黑色/122#棕色/15.6寸/两件套</t>
         </is>
       </c>
       <c r="J244" s="1" t="n">
-        <v>50</v>
+        <v>300</v>
       </c>
       <c r="K244" t="inlineStr">
         <is>
-          <t>2026/11/21 00:00:00</t>
+          <t>2026/10/20 00:00:00</t>
         </is>
       </c>
       <c r="L244" s="1" t="n">
-        <v>50</v>
+        <v>300</v>
       </c>
       <c r="M244"/>
       <c r="N244"/>
       <c r="O244"/>
       <c r="P244" t="inlineStr">
         <is>
-          <t>布类高速线（计件）</t>
-        </is>
-      </c>
-      <c r="Q244" t="inlineStr">
-        <is>
-          <t>新变体原下单100，平衡利库50个，剩50个无法下单，补交50个凑100下单</t>
-        </is>
-      </c>
-      <c r="R244"/>
+          <t>丝棉包生产线</t>
+        </is>
+      </c>
+      <c r="Q244"/>
+      <c r="R244" t="inlineStr">
+        <is>
+          <t>爆款</t>
+        </is>
+      </c>
       <c r="S244" t="inlineStr">
         <is>
           <t>否</t>
@@ -18347,7 +18347,7 @@
     <row r="245" customHeight="true" ht="15">
       <c r="A245" t="inlineStr">
         <is>
-          <t>LXPP261020002</t>
+          <t>LXPP261020004</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -18367,7 +18367,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>SPVYWB4408LKP3L-T2</t>
+          <t>SPVYWB4408LKP3M-T2</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -18376,7 +18376,7 @@
         </is>
       </c>
       <c r="G245" s="1" t="n">
-        <v>200</v>
+        <v>591</v>
       </c>
       <c r="H245" t="inlineStr">
         <is>
@@ -18385,11 +18385,11 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>213#米白色/18#深绿色/156#豆绿/17.3寸/两件套</t>
+          <t>213#米白色/18#深绿色/156#豆绿/15.6寸/两件套</t>
         </is>
       </c>
       <c r="J245" s="1" t="n">
-        <v>200</v>
+        <v>591</v>
       </c>
       <c r="K245" t="inlineStr">
         <is>
@@ -18397,7 +18397,7 @@
         </is>
       </c>
       <c r="L245" s="1" t="n">
-        <v>200</v>
+        <v>591</v>
       </c>
       <c r="M245"/>
       <c r="N245"/>
@@ -18407,7 +18407,11 @@
           <t>丝棉包生产线</t>
         </is>
       </c>
-      <c r="Q245"/>
+      <c r="Q245" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> (SPVYWB4408LKP3M-T2平衡利库调拨，修改时间2026-10-21 10:59:58，调整前申请数量：600.0；调整后申请数量：591.0;)</t>
+        </is>
+      </c>
       <c r="R245" t="inlineStr">
         <is>
           <t>爆款</t>
@@ -18422,7 +18426,7 @@
     <row r="246" customHeight="true" ht="15">
       <c r="A246" t="inlineStr">
         <is>
-          <t>LXPP261020003</t>
+          <t>LXPP261020005</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -18442,7 +18446,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>SPVYWB4408LKP1M-T2</t>
+          <t>SPVYWB4408LKP1L-T2</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
@@ -18451,7 +18455,7 @@
         </is>
       </c>
       <c r="G246" s="1" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="H246" t="inlineStr">
         <is>
@@ -18460,11 +18464,11 @@
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>213#米白色/48#黑色/122#棕色/15.6寸/两件套</t>
+          <t>213#米白色/48#黑色/122#棕色/17.3寸/两件套</t>
         </is>
       </c>
       <c r="J246" s="1" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="K246" t="inlineStr">
         <is>
@@ -18472,7 +18476,7 @@
         </is>
       </c>
       <c r="L246" s="1" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="M246"/>
       <c r="N246"/>
@@ -18497,7 +18501,7 @@
     <row r="247" customHeight="true" ht="15">
       <c r="A247" t="inlineStr">
         <is>
-          <t>LXPP261020004</t>
+          <t>LXPP261020006</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -18517,7 +18521,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>SPVYWB4408LKP3M-T2</t>
+          <t>SPVYWB4408LKP7M-T2</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
@@ -18526,7 +18530,7 @@
         </is>
       </c>
       <c r="G247" s="1" t="n">
-        <v>591</v>
+        <v>100</v>
       </c>
       <c r="H247" t="inlineStr">
         <is>
@@ -18535,11 +18539,11 @@
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>213#米白色/18#深绿色/156#豆绿/15.6寸/两件套</t>
+          <t>206#米白色/202#深紫色/15.6寸/两件套</t>
         </is>
       </c>
       <c r="J247" s="1" t="n">
-        <v>591</v>
+        <v>100</v>
       </c>
       <c r="K247" t="inlineStr">
         <is>
@@ -18547,7 +18551,7 @@
         </is>
       </c>
       <c r="L247" s="1" t="n">
-        <v>591</v>
+        <v>100</v>
       </c>
       <c r="M247"/>
       <c r="N247"/>
@@ -18557,11 +18561,7 @@
           <t>丝棉包生产线</t>
         </is>
       </c>
-      <c r="Q247" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> (SPVYWB4408LKP3M-T2平衡利库调拨，修改时间2026-10-21 10:59:58，调整前申请数量：600.0；调整后申请数量：591.0;)</t>
-        </is>
-      </c>
+      <c r="Q247"/>
       <c r="R247" t="inlineStr">
         <is>
           <t>爆款</t>
@@ -18576,7 +18576,7 @@
     <row r="248" customHeight="true" ht="15">
       <c r="A248" t="inlineStr">
         <is>
-          <t>LXPP261020005</t>
+          <t>LXPP261020008</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -18596,16 +18596,16 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>SPVYWB4408LKP1L-T2</t>
+          <t>VYWB3013LKD7M-T2</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>旅行托特包</t>
+          <t>手提电脑包</t>
         </is>
       </c>
       <c r="G248" s="1" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="H248" t="inlineStr">
         <is>
@@ -18614,11 +18614,11 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>213#米白色/48#黑色/122#棕色/17.3寸/两件套</t>
+          <t>167#淡樱花粉/3060#珊瑚粉/两件套</t>
         </is>
       </c>
       <c r="J248" s="1" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="K248" t="inlineStr">
         <is>
@@ -18626,22 +18626,18 @@
         </is>
       </c>
       <c r="L248" s="1" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="M248"/>
       <c r="N248"/>
       <c r="O248"/>
       <c r="P248" t="inlineStr">
         <is>
-          <t>丝棉包生产线</t>
+          <t>合成革高速线（计件）</t>
         </is>
       </c>
       <c r="Q248"/>
-      <c r="R248" t="inlineStr">
-        <is>
-          <t>爆款</t>
-        </is>
-      </c>
+      <c r="R248"/>
       <c r="S248" t="inlineStr">
         <is>
           <t>否</t>
@@ -18651,7 +18647,7 @@
     <row r="249" customHeight="true" ht="15">
       <c r="A249" t="inlineStr">
         <is>
-          <t>LXPP261020006</t>
+          <t>LXPP261020009</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -18671,12 +18667,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>SPVYWB4408LKP7M-T2</t>
+          <t>VYWB3013LKD4M-T2</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>旅行托特包</t>
+          <t>手提电脑包</t>
         </is>
       </c>
       <c r="G249" s="1" t="n">
@@ -18689,7 +18685,7 @@
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>206#米白色/202#深紫色/15.6寸/两件套</t>
+          <t>5#米白/01#黑色/34#板栗粽/两件套</t>
         </is>
       </c>
       <c r="J249" s="1" t="n">
@@ -18708,15 +18704,11 @@
       <c r="O249"/>
       <c r="P249" t="inlineStr">
         <is>
-          <t>丝棉包生产线</t>
+          <t>合成革高速线（计件）</t>
         </is>
       </c>
       <c r="Q249"/>
-      <c r="R249" t="inlineStr">
-        <is>
-          <t>爆款</t>
-        </is>
-      </c>
+      <c r="R249"/>
       <c r="S249" t="inlineStr">
         <is>
           <t>否</t>
@@ -18726,7 +18718,7 @@
     <row r="250" customHeight="true" ht="15">
       <c r="A250" t="inlineStr">
         <is>
-          <t>LXPP261020008</t>
+          <t>LXPP261020010</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -18746,7 +18738,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>VYWB3013LKD7M-T2</t>
+          <t>VYWB3013LK11M-M1</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
@@ -18764,7 +18756,7 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>167#淡樱花粉/3060#珊瑚粉/两件套</t>
+          <t>4001#黑色（压花）/4001#黑色羊巴/15.6寸/两件套</t>
         </is>
       </c>
       <c r="J250" s="1" t="n">
@@ -18797,7 +18789,7 @@
     <row r="251" customHeight="true" ht="15">
       <c r="A251" t="inlineStr">
         <is>
-          <t>LXPP261020009</t>
+          <t>LXPP261020011</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -18817,16 +18809,16 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>VYWB3013LKD4M-T2</t>
+          <t>VYWB4069LK40S-V1</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>手提电脑包</t>
+          <t>女式挎包</t>
         </is>
       </c>
       <c r="G251" s="1" t="n">
-        <v>100</v>
+        <v>1500</v>
       </c>
       <c r="H251" t="inlineStr">
         <is>
@@ -18835,11 +18827,11 @@
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>5#米白/01#黑色/34#板栗粽/两件套</t>
+          <t>8102#浅棕色 /11寸/(更换挂饰)</t>
         </is>
       </c>
       <c r="J251" s="1" t="n">
-        <v>100</v>
+        <v>1500</v>
       </c>
       <c r="K251" t="inlineStr">
         <is>
@@ -18847,7 +18839,7 @@
         </is>
       </c>
       <c r="L251" s="1" t="n">
-        <v>100</v>
+        <v>1500</v>
       </c>
       <c r="M251"/>
       <c r="N251"/>
@@ -18868,7 +18860,7 @@
     <row r="252" customHeight="true" ht="15">
       <c r="A252" t="inlineStr">
         <is>
-          <t>LXPP261020010</t>
+          <t>LXPP261020012</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -18888,16 +18880,16 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>VYWB3013LK11M-M1</t>
+          <t>VYWB4069LK10S-V1</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>手提电脑包</t>
+          <t>女式挎包</t>
         </is>
       </c>
       <c r="G252" s="1" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="H252" t="inlineStr">
         <is>
@@ -18906,11 +18898,11 @@
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>4001#黑色（压花）/4001#黑色羊巴/15.6寸/两件套</t>
+          <t>4001#黑色/11寸/(更换挂饰)</t>
         </is>
       </c>
       <c r="J252" s="1" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="K252" t="inlineStr">
         <is>
@@ -18918,7 +18910,7 @@
         </is>
       </c>
       <c r="L252" s="1" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="M252"/>
       <c r="N252"/>
@@ -18928,7 +18920,11 @@
           <t>合成革高速线（计件）</t>
         </is>
       </c>
-      <c r="Q252"/>
+      <c r="Q252" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> (SPVYWB4069LK10S-V1平衡利库调拨，修改时间2026-10-21 14:07:12，调整前申请数量：500.0；调整后申请数量：499.0;)</t>
+        </is>
+      </c>
       <c r="R252"/>
       <c r="S252" t="inlineStr">
         <is>
@@ -18939,7 +18935,7 @@
     <row r="253" customHeight="true" ht="15">
       <c r="A253" t="inlineStr">
         <is>
-          <t>LXPP261020011</t>
+          <t>LXPP261020013</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -18959,7 +18955,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>VYWB4069LK40S-V1</t>
+          <t>VYWB4069LK41S-V1</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
@@ -18968,7 +18964,7 @@
         </is>
       </c>
       <c r="G253" s="1" t="n">
-        <v>1500</v>
+        <v>450</v>
       </c>
       <c r="H253" t="inlineStr">
         <is>
@@ -18977,11 +18973,11 @@
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>8102#浅棕色 /11寸/(更换挂饰)</t>
+          <t>2300#黑红色/11寸/(更换挂饰)</t>
         </is>
       </c>
       <c r="J253" s="1" t="n">
-        <v>1500</v>
+        <v>450</v>
       </c>
       <c r="K253" t="inlineStr">
         <is>
@@ -18989,7 +18985,7 @@
         </is>
       </c>
       <c r="L253" s="1" t="n">
-        <v>1500</v>
+        <v>450</v>
       </c>
       <c r="M253"/>
       <c r="N253"/>
@@ -19010,7 +19006,7 @@
     <row r="254" customHeight="true" ht="15">
       <c r="A254" t="inlineStr">
         <is>
-          <t>LXPP261020012</t>
+          <t>LXPP261020014</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -19030,7 +19026,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>VYWB4069LK10S-V1</t>
+          <t>VYWB4069LK01S-V1</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
@@ -19039,7 +19035,7 @@
         </is>
       </c>
       <c r="G254" s="1" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="H254" t="inlineStr">
         <is>
@@ -19048,11 +19044,11 @@
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>4001#黑色/11寸/(更换挂饰)</t>
+          <t>9071#裸色/11寸/(更换挂饰)</t>
         </is>
       </c>
       <c r="J254" s="1" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="K254" t="inlineStr">
         <is>
@@ -19060,7 +19056,7 @@
         </is>
       </c>
       <c r="L254" s="1" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="M254"/>
       <c r="N254"/>
@@ -19070,11 +19066,7 @@
           <t>合成革高速线（计件）</t>
         </is>
       </c>
-      <c r="Q254" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> (SPVYWB4069LK10S-V1平衡利库调拨，修改时间2026-10-21 14:07:12，调整前申请数量：500.0；调整后申请数量：499.0;)</t>
-        </is>
-      </c>
+      <c r="Q254"/>
       <c r="R254"/>
       <c r="S254" t="inlineStr">
         <is>
@@ -19085,7 +19077,7 @@
     <row r="255" customHeight="true" ht="15">
       <c r="A255" t="inlineStr">
         <is>
-          <t>LXPP261020013</t>
+          <t>LXPP261020015</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -19105,7 +19097,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>VYWB4069LK41S-V1</t>
+          <t>VYWB4069LK30S-V1</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
@@ -19114,7 +19106,7 @@
         </is>
       </c>
       <c r="G255" s="1" t="n">
-        <v>450</v>
+        <v>100</v>
       </c>
       <c r="H255" t="inlineStr">
         <is>
@@ -19123,11 +19115,11 @@
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>2300#黑红色/11寸/(更换挂饰)</t>
+          <t>52#湛蓝/11寸/(更换挂饰)</t>
         </is>
       </c>
       <c r="J255" s="1" t="n">
-        <v>450</v>
+        <v>100</v>
       </c>
       <c r="K255" t="inlineStr">
         <is>
@@ -19135,7 +19127,7 @@
         </is>
       </c>
       <c r="L255" s="1" t="n">
-        <v>450</v>
+        <v>100</v>
       </c>
       <c r="M255"/>
       <c r="N255"/>
@@ -19156,7 +19148,7 @@
     <row r="256" customHeight="true" ht="15">
       <c r="A256" t="inlineStr">
         <is>
-          <t>LXPP261020014</t>
+          <t>LXPP261020016</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -19176,7 +19168,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>VYWB4069LK01S-V1</t>
+          <t>VYWB4069LK44S-C1</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
@@ -19185,7 +19177,7 @@
         </is>
       </c>
       <c r="G256" s="1" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="H256" t="inlineStr">
         <is>
@@ -19194,19 +19186,19 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>9071#裸色/11寸/(更换挂饰)</t>
+          <t>复古8101D#红棕色（压花）/8101D#红棕色/11寸（双面压花）</t>
         </is>
       </c>
       <c r="J256" s="1" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="K256" t="inlineStr">
         <is>
-          <t>2026/10/20 00:00:00</t>
+          <t>2026/10/22 00:00:00</t>
         </is>
       </c>
       <c r="L256" s="1" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="M256"/>
       <c r="N256"/>
@@ -19227,7 +19219,7 @@
     <row r="257" customHeight="true" ht="15">
       <c r="A257" t="inlineStr">
         <is>
-          <t>LXPP261020015</t>
+          <t>LXPP261020017</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -19247,7 +19239,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>VYWB4069LK30S-V1</t>
+          <t>VYWB4069LK10M</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
@@ -19265,7 +19257,7 @@
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>52#湛蓝/11寸/(更换挂饰)</t>
+          <t>复古4001#黑色/12.5寸</t>
         </is>
       </c>
       <c r="J257" s="1" t="n">
@@ -19287,7 +19279,11 @@
           <t>合成革高速线（计件）</t>
         </is>
       </c>
-      <c r="Q257"/>
+      <c r="Q257" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> (SPVYWB4069LK10M平衡利库调拨，修改时间2026-10-21 11:00:39，调整前申请数量：100.0；调整后申请数量：97.0;)</t>
+        </is>
+      </c>
       <c r="R257"/>
       <c r="S257" t="inlineStr">
         <is>
@@ -19298,7 +19294,7 @@
     <row r="258" customHeight="true" ht="15">
       <c r="A258" t="inlineStr">
         <is>
-          <t>LXPP261020016</t>
+          <t>LXPP261020018</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -19318,16 +19314,16 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>VYWB4069LK44S-C1</t>
+          <t>SPVYWB4233LK10M</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>女式挎包</t>
+          <t>电脑手提包</t>
         </is>
       </c>
       <c r="G258" s="1" t="n">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="H258" t="inlineStr">
         <is>
@@ -19336,26 +19332,26 @@
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>复古8101D#红棕色（压花）/8101D#红棕色/11寸（双面压花）</t>
+          <t>48#黑色/15.6寸</t>
         </is>
       </c>
       <c r="J258" s="1" t="n">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="K258" t="inlineStr">
         <is>
-          <t>2026/10/22 00:00:00</t>
+          <t>2026/10/20 00:00:00</t>
         </is>
       </c>
       <c r="L258" s="1" t="n">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="M258"/>
       <c r="N258"/>
       <c r="O258"/>
       <c r="P258" t="inlineStr">
         <is>
-          <t>合成革高速线（计件）</t>
+          <t>丝棉包生产线</t>
         </is>
       </c>
       <c r="Q258"/>
@@ -19369,7 +19365,7 @@
     <row r="259" customHeight="true" ht="15">
       <c r="A259" t="inlineStr">
         <is>
-          <t>LXPP261020017</t>
+          <t>LXPP261020019</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -19389,16 +19385,16 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>VYWB4069LK10M</t>
+          <t>SPVYWB4233LK10M-T2</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>女式挎包</t>
+          <t>电脑手提包</t>
         </is>
       </c>
       <c r="G259" s="1" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="H259" t="inlineStr">
         <is>
@@ -19407,11 +19403,11 @@
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>复古4001#黑色/12.5寸</t>
+          <t>48#黑色/15.6寸/两件套</t>
         </is>
       </c>
       <c r="J259" s="1" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="K259" t="inlineStr">
         <is>
@@ -19419,21 +19415,17 @@
         </is>
       </c>
       <c r="L259" s="1" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="M259"/>
       <c r="N259"/>
       <c r="O259"/>
       <c r="P259" t="inlineStr">
         <is>
-          <t>合成革高速线（计件）</t>
-        </is>
-      </c>
-      <c r="Q259" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> (SPVYWB4069LK10M平衡利库调拨，修改时间2026-10-21 11:00:39，调整前申请数量：100.0；调整后申请数量：97.0;)</t>
-        </is>
-      </c>
+          <t>丝棉包生产线</t>
+        </is>
+      </c>
+      <c r="Q259"/>
       <c r="R259"/>
       <c r="S259" t="inlineStr">
         <is>
@@ -19444,7 +19436,7 @@
     <row r="260" customHeight="true" ht="15">
       <c r="A260" t="inlineStr">
         <is>
-          <t>LXPP261020018</t>
+          <t>LXPP261020020</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -19464,7 +19456,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>SPVYWB4233LK10M</t>
+          <t>SPVYWB4233LK10L-T2</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
@@ -19482,7 +19474,7 @@
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>48#黑色/15.6寸</t>
+          <t>48#黑色/17寸/两件套</t>
         </is>
       </c>
       <c r="J260" s="1" t="n">
@@ -19515,7 +19507,7 @@
     <row r="261" customHeight="true" ht="15">
       <c r="A261" t="inlineStr">
         <is>
-          <t>LXPP261020019</t>
+          <t>LXPP261020021</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -19535,7 +19527,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>SPVYWB4233LK10M-T2</t>
+          <t>SPVYWB4233LK50L-T2</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
@@ -19544,7 +19536,7 @@
         </is>
       </c>
       <c r="G261" s="1" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="H261" t="inlineStr">
         <is>
@@ -19553,11 +19545,11 @@
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>48#黑色/15.6寸/两件套</t>
+          <t>127#粉色/17.3寸/两件套</t>
         </is>
       </c>
       <c r="J261" s="1" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="K261" t="inlineStr">
         <is>
@@ -19565,7 +19557,7 @@
         </is>
       </c>
       <c r="L261" s="1" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="M261"/>
       <c r="N261"/>
@@ -19586,7 +19578,7 @@
     <row r="262" customHeight="true" ht="15">
       <c r="A262" t="inlineStr">
         <is>
-          <t>LXPP261020020</t>
+          <t>LXPP261020022</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -19606,7 +19598,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>SPVYWB4233LK10L-T2</t>
+          <t>SPVYWB4233LK50M</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
@@ -19615,7 +19607,7 @@
         </is>
       </c>
       <c r="G262" s="1" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="H262" t="inlineStr">
         <is>
@@ -19624,11 +19616,11 @@
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>48#黑色/17寸/两件套</t>
+          <t>127#粉色/15.6寸</t>
         </is>
       </c>
       <c r="J262" s="1" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="K262" t="inlineStr">
         <is>
@@ -19636,7 +19628,7 @@
         </is>
       </c>
       <c r="L262" s="1" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="M262"/>
       <c r="N262"/>
@@ -19657,7 +19649,7 @@
     <row r="263" customHeight="true" ht="15">
       <c r="A263" t="inlineStr">
         <is>
-          <t>LXPP261020021</t>
+          <t>LXPP261020023</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -19677,16 +19669,16 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>SPVYWB4233LK50L-T2</t>
+          <t>SPVYUB5147LK50M-T2</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>电脑手提包</t>
+          <t>健身包</t>
         </is>
       </c>
       <c r="G263" s="1" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="H263" t="inlineStr">
         <is>
@@ -19695,11 +19687,11 @@
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>127#粉色/17.3寸/两件套</t>
+          <t>127#淡粉色/14.2寸/两件套</t>
         </is>
       </c>
       <c r="J263" s="1" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="K263" t="inlineStr">
         <is>
@@ -19707,7 +19699,7 @@
         </is>
       </c>
       <c r="L263" s="1" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="M263"/>
       <c r="N263"/>
@@ -19728,7 +19720,7 @@
     <row r="264" customHeight="true" ht="15">
       <c r="A264" t="inlineStr">
         <is>
-          <t>LXPP261020022</t>
+          <t>LXPP261020024</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -19748,16 +19740,16 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>SPVYWB4233LK50M</t>
+          <t>SPVYUB5147LK50L-T2</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>电脑手提包</t>
+          <t>健身包</t>
         </is>
       </c>
       <c r="G264" s="1" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="H264" t="inlineStr">
         <is>
@@ -19766,11 +19758,11 @@
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>127#粉色/15.6寸</t>
+          <t>127#淡粉色/16.5寸/两件套</t>
         </is>
       </c>
       <c r="J264" s="1" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="K264" t="inlineStr">
         <is>
@@ -19778,7 +19770,7 @@
         </is>
       </c>
       <c r="L264" s="1" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="M264"/>
       <c r="N264"/>
@@ -19799,7 +19791,7 @@
     <row r="265" customHeight="true" ht="15">
       <c r="A265" t="inlineStr">
         <is>
-          <t>LXPP261020023</t>
+          <t>LXPP261020025</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -19819,7 +19811,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>SPVYUB5147LK50M-T2</t>
+          <t>SPVYUB5147LK10M-T2</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
@@ -19828,7 +19820,7 @@
         </is>
       </c>
       <c r="G265" s="1" t="n">
-        <v>400</v>
+        <v>188</v>
       </c>
       <c r="H265" t="inlineStr">
         <is>
@@ -19837,11 +19829,11 @@
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>127#淡粉色/14.2寸/两件套</t>
+          <t>48#黑色/14.2寸/两件套</t>
         </is>
       </c>
       <c r="J265" s="1" t="n">
-        <v>400</v>
+        <v>188</v>
       </c>
       <c r="K265" t="inlineStr">
         <is>
@@ -19849,7 +19841,7 @@
         </is>
       </c>
       <c r="L265" s="1" t="n">
-        <v>400</v>
+        <v>188</v>
       </c>
       <c r="M265"/>
       <c r="N265"/>
@@ -19859,7 +19851,11 @@
           <t>丝棉包生产线</t>
         </is>
       </c>
-      <c r="Q265"/>
+      <c r="Q265" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> (SPVYUB5147LK10M-T2平衡利库调拨，修改时间2026-10-21 12:18:32，调整前申请数量：200.0；调整后申请数量：188.0;)</t>
+        </is>
+      </c>
       <c r="R265"/>
       <c r="S265" t="inlineStr">
         <is>
@@ -19870,7 +19866,7 @@
     <row r="266" customHeight="true" ht="15">
       <c r="A266" t="inlineStr">
         <is>
-          <t>LXPP261020024</t>
+          <t>LXPP261020026</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -19890,7 +19886,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>SPVYUB5147LK50L-T2</t>
+          <t>SPVYUB5147LK51M-T2</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
@@ -19899,7 +19895,7 @@
         </is>
       </c>
       <c r="G266" s="1" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="H266" t="inlineStr">
         <is>
@@ -19908,11 +19904,11 @@
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>127#淡粉色/16.5寸/两件套</t>
+          <t>04#浅粉色/205#粉色/14.2寸/两件套</t>
         </is>
       </c>
       <c r="J266" s="1" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="K266" t="inlineStr">
         <is>
@@ -19920,7 +19916,7 @@
         </is>
       </c>
       <c r="L266" s="1" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="M266"/>
       <c r="N266"/>
@@ -19941,7 +19937,7 @@
     <row r="267" customHeight="true" ht="15">
       <c r="A267" t="inlineStr">
         <is>
-          <t>LXPP261020025</t>
+          <t>LXPP261020027</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -19961,7 +19957,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>SPVYUB5147LK10M-T2</t>
+          <t>SPVYUB5147LK30M-T2</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
@@ -19970,7 +19966,7 @@
         </is>
       </c>
       <c r="G267" s="1" t="n">
-        <v>188</v>
+        <v>100</v>
       </c>
       <c r="H267" t="inlineStr">
         <is>
@@ -19979,11 +19975,11 @@
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>48#黑色/14.2寸/两件套</t>
+          <t>18#蓝色/158#淡蓝色/14.2寸/两件套</t>
         </is>
       </c>
       <c r="J267" s="1" t="n">
-        <v>188</v>
+        <v>100</v>
       </c>
       <c r="K267" t="inlineStr">
         <is>
@@ -19991,7 +19987,7 @@
         </is>
       </c>
       <c r="L267" s="1" t="n">
-        <v>188</v>
+        <v>100</v>
       </c>
       <c r="M267"/>
       <c r="N267"/>
@@ -20001,11 +19997,7 @@
           <t>丝棉包生产线</t>
         </is>
       </c>
-      <c r="Q267" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> (SPVYUB5147LK10M-T2平衡利库调拨，修改时间2026-10-21 12:18:32，调整前申请数量：200.0；调整后申请数量：188.0;)</t>
-        </is>
-      </c>
+      <c r="Q267"/>
       <c r="R267"/>
       <c r="S267" t="inlineStr">
         <is>
@@ -20016,7 +20008,7 @@
     <row r="268" customHeight="true" ht="15">
       <c r="A268" t="inlineStr">
         <is>
-          <t>LXPP261020026</t>
+          <t>LXPP261020028</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -20036,7 +20028,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>SPVYUB5147LK51M-T2</t>
+          <t>SPVYUB5147LK40M-T2</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
@@ -20045,7 +20037,7 @@
         </is>
       </c>
       <c r="G268" s="1" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H268" t="inlineStr">
         <is>
@@ -20054,11 +20046,11 @@
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>04#浅粉色/205#粉色/14.2寸/两件套</t>
+          <t>138#驼色/14.2寸/两件套</t>
         </is>
       </c>
       <c r="J268" s="1" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K268" t="inlineStr">
         <is>
@@ -20066,7 +20058,7 @@
         </is>
       </c>
       <c r="L268" s="1" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="M268"/>
       <c r="N268"/>
@@ -20087,7 +20079,7 @@
     <row r="269" customHeight="true" ht="15">
       <c r="A269" t="inlineStr">
         <is>
-          <t>LXPP261020027</t>
+          <t>LXPP261020029</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -20107,12 +20099,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>SPVYUB5147LK30M-T2</t>
+          <t>VYWB3218LKP6M</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>健身包</t>
+          <t>电脑公文包</t>
         </is>
       </c>
       <c r="G269" s="1" t="n">
@@ -20125,7 +20117,7 @@
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>18#蓝色/158#淡蓝色/14.2寸/两件套</t>
+          <t>213#米白/170#豆绿/18#深绿色/15.6寸</t>
         </is>
       </c>
       <c r="J269" s="1" t="n">
@@ -20144,7 +20136,7 @@
       <c r="O269"/>
       <c r="P269" t="inlineStr">
         <is>
-          <t>丝棉包生产线</t>
+          <t>拉杆箱组装线</t>
         </is>
       </c>
       <c r="Q269"/>
@@ -20158,7 +20150,7 @@
     <row r="270" customHeight="true" ht="15">
       <c r="A270" t="inlineStr">
         <is>
-          <t>LXPP261020028</t>
+          <t>LXPP261020033</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -20178,12 +20170,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>SPVYUB5147LK40M-T2</t>
+          <t>SPVYMB4260LKP1L-T4</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>健身包</t>
+          <t>拉杆箱</t>
         </is>
       </c>
       <c r="G270" s="1" t="n">
@@ -20196,7 +20188,7 @@
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>138#驼色/14.2寸/两件套</t>
+          <t>13#黑色/62#米白/34#板栗棕/20寸/四件套</t>
         </is>
       </c>
       <c r="J270" s="1" t="n">
@@ -20215,7 +20207,7 @@
       <c r="O270"/>
       <c r="P270" t="inlineStr">
         <is>
-          <t>丝棉包生产线</t>
+          <t>拉杆箱组装线</t>
         </is>
       </c>
       <c r="Q270"/>
@@ -20229,7 +20221,7 @@
     <row r="271" customHeight="true" ht="15">
       <c r="A271" t="inlineStr">
         <is>
-          <t>LXPP261020029</t>
+          <t>LXPP261020035</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -20249,29 +20241,29 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>VYWB3218LKP6M</t>
+          <t>SPVYUB5214LK41M-M1</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>电脑公文包</t>
+          <t>洗漱包</t>
         </is>
       </c>
       <c r="G271" s="1" t="n">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>邹娇</t>
+          <t>李杰</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>213#米白/170#豆绿/18#深绿色/15.6寸</t>
+          <t>8089#黄棕（压花）/小号/两件套</t>
         </is>
       </c>
       <c r="J271" s="1" t="n">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="K271" t="inlineStr">
         <is>
@@ -20279,18 +20271,22 @@
         </is>
       </c>
       <c r="L271" s="1" t="n">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="M271"/>
       <c r="N271"/>
       <c r="O271"/>
       <c r="P271" t="inlineStr">
         <is>
-          <t>拉杆箱组装线</t>
+          <t>合成革高速线（计件）</t>
         </is>
       </c>
       <c r="Q271"/>
-      <c r="R271"/>
+      <c r="R271" t="inlineStr">
+        <is>
+          <t>爆款</t>
+        </is>
+      </c>
       <c r="S271" t="inlineStr">
         <is>
           <t>否</t>
@@ -20300,7 +20296,7 @@
     <row r="272" customHeight="true" ht="15">
       <c r="A272" t="inlineStr">
         <is>
-          <t>LXPP261020033</t>
+          <t>LXPP261020036</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -20320,29 +20316,29 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>SPVYMB4260LKP1L-T4</t>
+          <t>SPVYUB5214LK50M-M1</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>拉杆箱</t>
+          <t>洗漱包</t>
         </is>
       </c>
       <c r="G272" s="1" t="n">
-        <v>100</v>
+        <v>198</v>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>邹娇</t>
+          <t>李杰</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>13#黑色/62#米白/34#板栗棕/20寸/四件套</t>
+          <t>97#娇媚粉（压花）/小号/两件套</t>
         </is>
       </c>
       <c r="J272" s="1" t="n">
-        <v>100</v>
+        <v>198</v>
       </c>
       <c r="K272" t="inlineStr">
         <is>
@@ -20350,18 +20346,26 @@
         </is>
       </c>
       <c r="L272" s="1" t="n">
-        <v>100</v>
+        <v>198</v>
       </c>
       <c r="M272"/>
       <c r="N272"/>
       <c r="O272"/>
       <c r="P272" t="inlineStr">
         <is>
-          <t>拉杆箱组装线</t>
-        </is>
-      </c>
-      <c r="Q272"/>
-      <c r="R272"/>
+          <t>合成革高速线（计件）</t>
+        </is>
+      </c>
+      <c r="Q272" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> (SPVYUB5214LK50M-M1平衡利库调拨，修改时间2026-10-21 12:18:55，调整前申请数量：200.0；调整后申请数量：198.0;)</t>
+        </is>
+      </c>
+      <c r="R272" t="inlineStr">
+        <is>
+          <t>爆款</t>
+        </is>
+      </c>
       <c r="S272" t="inlineStr">
         <is>
           <t>否</t>
@@ -20371,7 +20375,7 @@
     <row r="273" customHeight="true" ht="15">
       <c r="A273" t="inlineStr">
         <is>
-          <t>LXPP261020035</t>
+          <t>LXPP261020037</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -20391,16 +20395,16 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>SPVYUB5214LK41M-M1</t>
+          <t>SPVYUB4488LK70S-T2</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>洗漱包</t>
+          <t>化妆包</t>
         </is>
       </c>
       <c r="G273" s="1" t="n">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="H273" t="inlineStr">
         <is>
@@ -20409,11 +20413,11 @@
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>8089#黄棕（压花）/小号/两件套</t>
+          <t>49#浅紫/小号/两件套</t>
         </is>
       </c>
       <c r="J273" s="1" t="n">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="K273" t="inlineStr">
         <is>
@@ -20421,14 +20425,14 @@
         </is>
       </c>
       <c r="L273" s="1" t="n">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="M273"/>
       <c r="N273"/>
       <c r="O273"/>
       <c r="P273" t="inlineStr">
         <is>
-          <t>合成革高速线（计件）</t>
+          <t>丝棉包生产线</t>
         </is>
       </c>
       <c r="Q273"/>
@@ -20446,7 +20450,7 @@
     <row r="274" customHeight="true" ht="15">
       <c r="A274" t="inlineStr">
         <is>
-          <t>LXPP261020036</t>
+          <t>LXPP261020045</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -20466,16 +20470,16 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>SPVYUB5214LK50M-M1</t>
+          <t>SPVYMB4496LKP3L-T4</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>洗漱包</t>
+          <t>旅行背包</t>
         </is>
       </c>
       <c r="G274" s="1" t="n">
-        <v>198</v>
+        <v>500</v>
       </c>
       <c r="H274" t="inlineStr">
         <is>
@@ -20484,11 +20488,11 @@
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>97#娇媚粉（压花）/小号/两件套</t>
+          <t>2508342豹纹/246#米黄色/大号/四件套</t>
         </is>
       </c>
       <c r="J274" s="1" t="n">
-        <v>198</v>
+        <v>500</v>
       </c>
       <c r="K274" t="inlineStr">
         <is>
@@ -20496,26 +20500,18 @@
         </is>
       </c>
       <c r="L274" s="1" t="n">
-        <v>198</v>
+        <v>500</v>
       </c>
       <c r="M274"/>
       <c r="N274"/>
       <c r="O274"/>
       <c r="P274" t="inlineStr">
         <is>
-          <t>合成革高速线（计件）</t>
-        </is>
-      </c>
-      <c r="Q274" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> (SPVYUB5214LK50M-M1平衡利库调拨，修改时间2026-10-21 12:18:55，调整前申请数量：200.0；调整后申请数量：198.0;)</t>
-        </is>
-      </c>
-      <c r="R274" t="inlineStr">
-        <is>
-          <t>爆款</t>
-        </is>
-      </c>
+          <t>布类高速线（计件）</t>
+        </is>
+      </c>
+      <c r="Q274"/>
+      <c r="R274"/>
       <c r="S274" t="inlineStr">
         <is>
           <t>否</t>
@@ -20525,7 +20521,7 @@
     <row r="275" customHeight="true" ht="15">
       <c r="A275" t="inlineStr">
         <is>
-          <t>LXPP261020037</t>
+          <t>LXPP261020046</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -20545,16 +20541,16 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>SPVYUB4488LK70S-T2</t>
+          <t>SPVYMB4496LKP3M-T4</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>化妆包</t>
+          <t>旅行背包</t>
         </is>
       </c>
       <c r="G275" s="1" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="H275" t="inlineStr">
         <is>
@@ -20563,11 +20559,11 @@
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>49#浅紫/小号/两件套</t>
+          <t>2508342豹纹/246#米黄色/中号/四件套</t>
         </is>
       </c>
       <c r="J275" s="1" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="K275" t="inlineStr">
         <is>
@@ -20575,22 +20571,18 @@
         </is>
       </c>
       <c r="L275" s="1" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="M275"/>
       <c r="N275"/>
       <c r="O275"/>
       <c r="P275" t="inlineStr">
         <is>
-          <t>丝棉包生产线</t>
+          <t>布类高速线（计件）</t>
         </is>
       </c>
       <c r="Q275"/>
-      <c r="R275" t="inlineStr">
-        <is>
-          <t>爆款</t>
-        </is>
-      </c>
+      <c r="R275"/>
       <c r="S275" t="inlineStr">
         <is>
           <t>否</t>
@@ -20600,7 +20592,7 @@
     <row r="276" customHeight="true" ht="15">
       <c r="A276" t="inlineStr">
         <is>
-          <t>LXPP261020045</t>
+          <t>LXPP261020052</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -20620,16 +20612,16 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>SPVYMB4496LKP3L-T4</t>
+          <t>VYWB3058LK58M</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>旅行背包</t>
+          <t>手提电脑包</t>
         </is>
       </c>
       <c r="G276" s="1" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="H276" t="inlineStr">
         <is>
@@ -20638,11 +20630,11 @@
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t>2508342豹纹/246#米黄色/大号/四件套</t>
+          <t>16安棕色豹纹/1#黑色/15.6寸</t>
         </is>
       </c>
       <c r="J276" s="1" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="K276" t="inlineStr">
         <is>
@@ -20650,14 +20642,14 @@
         </is>
       </c>
       <c r="L276" s="1" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="M276"/>
       <c r="N276"/>
       <c r="O276"/>
       <c r="P276" t="inlineStr">
         <is>
-          <t>布类高速线（计件）</t>
+          <t>合成革高速线（计件）</t>
         </is>
       </c>
       <c r="Q276"/>
@@ -20671,7 +20663,7 @@
     <row r="277" customHeight="true" ht="15">
       <c r="A277" t="inlineStr">
         <is>
-          <t>LXPP261020046</t>
+          <t>LXPP261020053</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -20691,16 +20683,16 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>SPVYMB4496LKP3M-T4</t>
+          <t>VYWB3058LK58L</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>旅行背包</t>
+          <t>手提电脑包</t>
         </is>
       </c>
       <c r="G277" s="1" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="H277" t="inlineStr">
         <is>
@@ -20709,11 +20701,11 @@
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t>2508342豹纹/246#米黄色/中号/四件套</t>
+          <t>16安棕色豹纹/4001#黑色/17寸</t>
         </is>
       </c>
       <c r="J277" s="1" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="K277" t="inlineStr">
         <is>
@@ -20721,14 +20713,14 @@
         </is>
       </c>
       <c r="L277" s="1" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="M277"/>
       <c r="N277"/>
       <c r="O277"/>
       <c r="P277" t="inlineStr">
         <is>
-          <t>布类高速线（计件）</t>
+          <t>合成革高速线（计件）</t>
         </is>
       </c>
       <c r="Q277"/>
@@ -20742,7 +20734,7 @@
     <row r="278" customHeight="true" ht="15">
       <c r="A278" t="inlineStr">
         <is>
-          <t>LXPP261020052</t>
+          <t>LXPP261020061</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -20762,12 +20754,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>VYWB3058LK58M</t>
+          <t>SPVYUB5012LKPLM</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>手提电脑包</t>
+          <t>午餐包</t>
         </is>
       </c>
       <c r="G278" s="1" t="n">
@@ -20780,7 +20772,7 @@
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t>16安棕色豹纹/1#黑色/15.6寸</t>
+          <t>2508342豹纹/4001#黑色/小号</t>
         </is>
       </c>
       <c r="J278" s="1" t="n">
@@ -20799,7 +20791,7 @@
       <c r="O278"/>
       <c r="P278" t="inlineStr">
         <is>
-          <t>合成革高速线（计件）</t>
+          <t>午餐包生产线</t>
         </is>
       </c>
       <c r="Q278"/>
@@ -20813,7 +20805,7 @@
     <row r="279" customHeight="true" ht="15">
       <c r="A279" t="inlineStr">
         <is>
-          <t>LXPP261020053</t>
+          <t>LXPP261020072</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -20833,16 +20825,16 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>VYWB3058LK58L</t>
+          <t>SPVYUB4488LKP2L-T2</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>手提电脑包</t>
+          <t>化妆包</t>
         </is>
       </c>
       <c r="G279" s="1" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="H279" t="inlineStr">
         <is>
@@ -20851,11 +20843,11 @@
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>16安棕色豹纹/4001#黑色/17寸</t>
+          <t>11#小卡其格/大号/两件套</t>
         </is>
       </c>
       <c r="J279" s="1" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="K279" t="inlineStr">
         <is>
@@ -20863,18 +20855,22 @@
         </is>
       </c>
       <c r="L279" s="1" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="M279"/>
       <c r="N279"/>
       <c r="O279"/>
       <c r="P279" t="inlineStr">
         <is>
-          <t>合成革高速线（计件）</t>
+          <t>丝棉包生产线</t>
         </is>
       </c>
       <c r="Q279"/>
-      <c r="R279"/>
+      <c r="R279" t="inlineStr">
+        <is>
+          <t>爆款</t>
+        </is>
+      </c>
       <c r="S279" t="inlineStr">
         <is>
           <t>否</t>
@@ -20884,7 +20880,7 @@
     <row r="280" customHeight="true" ht="15">
       <c r="A280" t="inlineStr">
         <is>
-          <t>LXPP261020061</t>
+          <t>LXPP261020073</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -20904,16 +20900,16 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>SPVYUB5012LKPLM</t>
+          <t>SPVYUB4488LKP1L-T2</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>午餐包</t>
+          <t>化妆包</t>
         </is>
       </c>
       <c r="G280" s="1" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="H280" t="inlineStr">
         <is>
@@ -20922,11 +20918,11 @@
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>2508342豹纹/4001#黑色/小号</t>
+          <t>27#蓝白条/大号/两件套</t>
         </is>
       </c>
       <c r="J280" s="1" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="K280" t="inlineStr">
         <is>
@@ -20934,18 +20930,22 @@
         </is>
       </c>
       <c r="L280" s="1" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="M280"/>
       <c r="N280"/>
       <c r="O280"/>
       <c r="P280" t="inlineStr">
         <is>
-          <t>午餐包生产线</t>
+          <t>丝棉包生产线</t>
         </is>
       </c>
       <c r="Q280"/>
-      <c r="R280"/>
+      <c r="R280" t="inlineStr">
+        <is>
+          <t>爆款</t>
+        </is>
+      </c>
       <c r="S280" t="inlineStr">
         <is>
           <t>否</t>
@@ -20955,12 +20955,12 @@
     <row r="281" customHeight="true" ht="15">
       <c r="A281" t="inlineStr">
         <is>
-          <t>LXPP261020072</t>
+          <t>LXPP261020074</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>已审核</t>
+          <t>创建</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -20975,7 +20975,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>SPVYUB4488LKP2L-T2</t>
+          <t>SPVYWB6204LK90S</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
@@ -20984,7 +20984,7 @@
         </is>
       </c>
       <c r="G281" s="1" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H281" t="inlineStr">
         <is>
@@ -20993,11 +20993,11 @@
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>11#小卡其格/大号/两件套</t>
+          <t>170#灰绿色/小号</t>
         </is>
       </c>
       <c r="J281" s="1" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K281" t="inlineStr">
         <is>
@@ -21005,7 +21005,7 @@
         </is>
       </c>
       <c r="L281" s="1" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M281"/>
       <c r="N281"/>
@@ -21016,11 +21016,7 @@
         </is>
       </c>
       <c r="Q281"/>
-      <c r="R281" t="inlineStr">
-        <is>
-          <t>爆款</t>
-        </is>
-      </c>
+      <c r="R281"/>
       <c r="S281" t="inlineStr">
         <is>
           <t>否</t>
@@ -21030,12 +21026,12 @@
     <row r="282" customHeight="true" ht="15">
       <c r="A282" t="inlineStr">
         <is>
-          <t>LXPP261020073</t>
+          <t>LXPP261020075</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>已审核</t>
+          <t>创建</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -21050,7 +21046,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>SPVYUB4488LKP1L-T2</t>
+          <t>SPVYWB6204LK50L</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
@@ -21059,7 +21055,7 @@
         </is>
       </c>
       <c r="G282" s="1" t="n">
-        <v>50</v>
+        <v>93</v>
       </c>
       <c r="H282" t="inlineStr">
         <is>
@@ -21068,11 +21064,11 @@
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>27#蓝白条/大号/两件套</t>
+          <t>127#粉色/大号</t>
         </is>
       </c>
       <c r="J282" s="1" t="n">
-        <v>50</v>
+        <v>93</v>
       </c>
       <c r="K282" t="inlineStr">
         <is>
@@ -21080,7 +21076,7 @@
         </is>
       </c>
       <c r="L282" s="1" t="n">
-        <v>50</v>
+        <v>93</v>
       </c>
       <c r="M282"/>
       <c r="N282"/>
@@ -21090,12 +21086,12 @@
           <t>丝棉包生产线</t>
         </is>
       </c>
-      <c r="Q282"/>
-      <c r="R282" t="inlineStr">
-        <is>
-          <t>爆款</t>
-        </is>
-      </c>
+      <c r="Q282" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> (SPVYWB6204LK50L平衡利库调拨，修改时间2026-10-21 12:19:37，调整前申请数量：100.0；调整后申请数量：93.0;)</t>
+        </is>
+      </c>
+      <c r="R282"/>
       <c r="S282" t="inlineStr">
         <is>
           <t>否</t>
@@ -21105,7 +21101,7 @@
     <row r="283" customHeight="true" ht="15">
       <c r="A283" t="inlineStr">
         <is>
-          <t>LXPP261020074</t>
+          <t>LXPP261020094</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -21125,29 +21121,29 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>SPVYWB6204LK90S</t>
+          <t>SPVYWB4235LKP1M-T2</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>化妆包</t>
+          <t>电脑手提包</t>
         </is>
       </c>
       <c r="G283" s="1" t="n">
-        <v>100</v>
+        <v>450</v>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>李杰</t>
+          <t>吴冠烨</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>170#灰绿色/小号</t>
+          <t>001#黑色/180#米色/138#棕色/15.6寸/两件套</t>
         </is>
       </c>
       <c r="J283" s="1" t="n">
-        <v>100</v>
+        <v>450</v>
       </c>
       <c r="K283" t="inlineStr">
         <is>
@@ -21155,14 +21151,14 @@
         </is>
       </c>
       <c r="L283" s="1" t="n">
-        <v>100</v>
+        <v>450</v>
       </c>
       <c r="M283"/>
       <c r="N283"/>
       <c r="O283"/>
       <c r="P283" t="inlineStr">
         <is>
-          <t>丝棉包生产线</t>
+          <t>合成革高速线（计件）</t>
         </is>
       </c>
       <c r="Q283"/>
@@ -21176,7 +21172,7 @@
     <row r="284" customHeight="true" ht="15">
       <c r="A284" t="inlineStr">
         <is>
-          <t>LXPP261020075</t>
+          <t>LXPP261020095</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -21196,29 +21192,29 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>SPVYWB6204LK50L</t>
+          <t>SPVYWB4235LKP1L-T2</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>化妆包</t>
+          <t>电脑手提包</t>
         </is>
       </c>
       <c r="G284" s="1" t="n">
-        <v>93</v>
+        <v>350</v>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>李杰</t>
+          <t>吴冠烨</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>127#粉色/大号</t>
+          <t>1010D米色/4001#黑色/8119#棕色/17.3寸/两件套</t>
         </is>
       </c>
       <c r="J284" s="1" t="n">
-        <v>93</v>
+        <v>350</v>
       </c>
       <c r="K284" t="inlineStr">
         <is>
@@ -21226,21 +21222,17 @@
         </is>
       </c>
       <c r="L284" s="1" t="n">
-        <v>93</v>
+        <v>350</v>
       </c>
       <c r="M284"/>
       <c r="N284"/>
       <c r="O284"/>
       <c r="P284" t="inlineStr">
         <is>
-          <t>丝棉包生产线</t>
-        </is>
-      </c>
-      <c r="Q284" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> (SPVYWB6204LK50L平衡利库调拨，修改时间2026-10-21 12:19:37，调整前申请数量：100.0；调整后申请数量：93.0;)</t>
-        </is>
-      </c>
+          <t>合成革高速线（计件）</t>
+        </is>
+      </c>
+      <c r="Q284"/>
       <c r="R284"/>
       <c r="S284" t="inlineStr">
         <is>
@@ -21251,7 +21243,7 @@
     <row r="285" customHeight="true" ht="15">
       <c r="A285" t="inlineStr">
         <is>
-          <t>LXPP261020094</t>
+          <t>LXPP261020096</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -21271,7 +21263,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>SPVYWB4235LKP1M-T2</t>
+          <t>SPVYWB4235LK90M-T2</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
@@ -21280,7 +21272,7 @@
         </is>
       </c>
       <c r="G285" s="1" t="n">
-        <v>450</v>
+        <v>100</v>
       </c>
       <c r="H285" t="inlineStr">
         <is>
@@ -21289,11 +21281,11 @@
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>001#黑色/180#米色/138#棕色/15.6寸/两件套</t>
+          <t>7093#绿色/15.6寸/两件套</t>
         </is>
       </c>
       <c r="J285" s="1" t="n">
-        <v>450</v>
+        <v>100</v>
       </c>
       <c r="K285" t="inlineStr">
         <is>
@@ -21301,7 +21293,7 @@
         </is>
       </c>
       <c r="L285" s="1" t="n">
-        <v>450</v>
+        <v>100</v>
       </c>
       <c r="M285"/>
       <c r="N285"/>
@@ -21322,7 +21314,7 @@
     <row r="286" customHeight="true" ht="15">
       <c r="A286" t="inlineStr">
         <is>
-          <t>LXPP261020095</t>
+          <t>LXPP261020097</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -21342,7 +21334,7 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>SPVYWB4235LKP1L-T2</t>
+          <t>SPVYWB4235LKP8M-T2</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
@@ -21351,7 +21343,7 @@
         </is>
       </c>
       <c r="G286" s="1" t="n">
-        <v>350</v>
+        <v>200</v>
       </c>
       <c r="H286" t="inlineStr">
         <is>
@@ -21360,11 +21352,11 @@
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>1010D米色/4001#黑色/8119#棕色/17.3寸/两件套</t>
+          <t>1010D米色/929#浅沙色/890#深咖色/15.6寸/两件套</t>
         </is>
       </c>
       <c r="J286" s="1" t="n">
-        <v>350</v>
+        <v>200</v>
       </c>
       <c r="K286" t="inlineStr">
         <is>
@@ -21372,7 +21364,7 @@
         </is>
       </c>
       <c r="L286" s="1" t="n">
-        <v>350</v>
+        <v>200</v>
       </c>
       <c r="M286"/>
       <c r="N286"/>
@@ -21393,7 +21385,7 @@
     <row r="287" customHeight="true" ht="15">
       <c r="A287" t="inlineStr">
         <is>
-          <t>LXPP261020096</t>
+          <t>LXPP261020098</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -21413,7 +21405,7 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>SPVYWB4235LK90M-T2</t>
+          <t>SPVYWB4235LKP5M-T2</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
@@ -21431,7 +21423,7 @@
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t>7093#绿色/15.6寸/两件套</t>
+          <t>1010D米色/7166#墨绿色/4001#黑色/15.6寸/两件套</t>
         </is>
       </c>
       <c r="J287" s="1" t="n">
@@ -21464,7 +21456,7 @@
     <row r="288" customHeight="true" ht="15">
       <c r="A288" t="inlineStr">
         <is>
-          <t>LXPP261020097</t>
+          <t>LXPP261020099</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -21484,7 +21476,7 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>SPVYWB4235LKP8M-T2</t>
+          <t>SPVYWB4235LK20M-M1</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
@@ -21493,7 +21485,7 @@
         </is>
       </c>
       <c r="G288" s="1" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="H288" t="inlineStr">
         <is>
@@ -21502,11 +21494,11 @@
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t>1010D米色/929#浅沙色/890#深咖色/15.6寸/两件套</t>
+          <t>4076#浅灰色/4076#浅灰色（压花）/15.6寸/两件套</t>
         </is>
       </c>
       <c r="J288" s="1" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="K288" t="inlineStr">
         <is>
@@ -21514,7 +21506,7 @@
         </is>
       </c>
       <c r="L288" s="1" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="M288"/>
       <c r="N288"/>
@@ -21535,7 +21527,7 @@
     <row r="289" customHeight="true" ht="15">
       <c r="A289" t="inlineStr">
         <is>
-          <t>LXPP261020098</t>
+          <t>LXPP261020100</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -21555,7 +21547,7 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>SPVYWB4235LKP5M-T2</t>
+          <t>SPVYWB4235LK10M-M1</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
@@ -21564,7 +21556,7 @@
         </is>
       </c>
       <c r="G289" s="1" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="H289" t="inlineStr">
         <is>
@@ -21573,11 +21565,11 @@
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>1010D米色/7166#墨绿色/4001#黑色/15.6寸/两件套</t>
+          <t>4001#黑色/4001#黑色（压花）/15.6寸/两件套</t>
         </is>
       </c>
       <c r="J289" s="1" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="K289" t="inlineStr">
         <is>
@@ -21585,7 +21577,7 @@
         </is>
       </c>
       <c r="L289" s="1" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="M289"/>
       <c r="N289"/>
@@ -21606,7 +21598,7 @@
     <row r="290" customHeight="true" ht="15">
       <c r="A290" t="inlineStr">
         <is>
-          <t>LXPP261020099</t>
+          <t>LXPP261020101</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -21626,7 +21618,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>SPVYWB4235LK20M-M1</t>
+          <t>SPVYWB4235LK90L-T2</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
@@ -21635,7 +21627,7 @@
         </is>
       </c>
       <c r="G290" s="1" t="n">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="H290" t="inlineStr">
         <is>
@@ -21644,11 +21636,11 @@
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t>4076#浅灰色/4076#浅灰色（压花）/15.6寸/两件套</t>
+          <t>7093绿色/7093绿色（压花）/17.3寸/两件套</t>
         </is>
       </c>
       <c r="J290" s="1" t="n">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="K290" t="inlineStr">
         <is>
@@ -21656,7 +21648,7 @@
         </is>
       </c>
       <c r="L290" s="1" t="n">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="M290"/>
       <c r="N290"/>
@@ -21677,7 +21669,7 @@
     <row r="291" customHeight="true" ht="15">
       <c r="A291" t="inlineStr">
         <is>
-          <t>LXPP261020100</t>
+          <t>LXPP261020105</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -21697,16 +21689,16 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>SPVYWB4235LK10M-M1</t>
+          <t>SPVYMB5705LKP5L</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>电脑手提包</t>
+          <t>午餐电脑背包</t>
         </is>
       </c>
       <c r="G291" s="1" t="n">
-        <v>250</v>
+        <v>36</v>
       </c>
       <c r="H291" t="inlineStr">
         <is>
@@ -21715,11 +21707,11 @@
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t>4001#黑色/4001#黑色（压花）/15.6寸/两件套</t>
+          <t>86#米黄/13#粉色/8094#赤棕色/17.3寸</t>
         </is>
       </c>
       <c r="J291" s="1" t="n">
-        <v>250</v>
+        <v>36</v>
       </c>
       <c r="K291" t="inlineStr">
         <is>
@@ -21727,18 +21719,26 @@
         </is>
       </c>
       <c r="L291" s="1" t="n">
-        <v>250</v>
+        <v>36</v>
       </c>
       <c r="M291"/>
       <c r="N291"/>
       <c r="O291"/>
       <c r="P291" t="inlineStr">
         <is>
-          <t>合成革高速线（计件）</t>
-        </is>
-      </c>
-      <c r="Q291"/>
-      <c r="R291"/>
+          <t>午餐包生产线</t>
+        </is>
+      </c>
+      <c r="Q291" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> (SPVYMB5705LKP5L平衡利库调拨，修改时间2026-10-21 10:53:38，调整前申请数量：100.0；调整后申请数量：36.0;)</t>
+        </is>
+      </c>
+      <c r="R291" t="inlineStr">
+        <is>
+          <t>大爆款</t>
+        </is>
+      </c>
       <c r="S291" t="inlineStr">
         <is>
           <t>否</t>
@@ -21748,7 +21748,7 @@
     <row r="292" customHeight="true" ht="15">
       <c r="A292" t="inlineStr">
         <is>
-          <t>LXPP261020101</t>
+          <t>LXPP261021001</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -21763,45 +21763,49 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>2026/10/20</t>
+          <t>2026/10/22</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>SPVYWB4235LK90L-T2</t>
+          <t>SPVYWB2208LK41M</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>电脑手提包</t>
+          <t>复古托特包</t>
         </is>
       </c>
       <c r="G292" s="1" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>吴冠烨</t>
+          <t>庞新会</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t>7093绿色/7093绿色（压花）/17.3寸/两件套</t>
+          <t>16#B土棕/15.6寸</t>
         </is>
       </c>
       <c r="J292" s="1" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="K292" t="inlineStr">
         <is>
-          <t>2026/10/20 00:00:00</t>
+          <t>2026/11/20 00:00:00</t>
         </is>
       </c>
       <c r="L292" s="1" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="M292"/>
-      <c r="N292"/>
+      <c r="N292" t="inlineStr">
+        <is>
+          <t>请工厂安排发货到前进仓</t>
+        </is>
+      </c>
       <c r="O292"/>
       <c r="P292" t="inlineStr">
         <is>
@@ -21819,7 +21823,7 @@
     <row r="293" customHeight="true" ht="15">
       <c r="A293" t="inlineStr">
         <is>
-          <t>LXPP261020105</t>
+          <t>LXPP261021002</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -21834,61 +21838,57 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>2026/10/20</t>
+          <t>2026/10/22</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>SPVYMB5705LKP5L</t>
+          <t>SPVYWB2208LK01M</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>午餐电脑背包</t>
+          <t>复古托特包</t>
         </is>
       </c>
       <c r="G293" s="1" t="n">
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>吴冠烨</t>
+          <t>庞新会</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>86#米黄/13#粉色/8094#赤棕色/17.3寸</t>
+          <t>4141#黑色</t>
         </is>
       </c>
       <c r="J293" s="1" t="n">
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="K293" t="inlineStr">
         <is>
-          <t>2026/10/20 00:00:00</t>
+          <t>2026/11/20 00:00:00</t>
         </is>
       </c>
       <c r="L293" s="1" t="n">
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="M293"/>
-      <c r="N293"/>
+      <c r="N293" t="inlineStr">
+        <is>
+          <t>请工厂安排发货到前进仓</t>
+        </is>
+      </c>
       <c r="O293"/>
       <c r="P293" t="inlineStr">
         <is>
-          <t>午餐包生产线</t>
-        </is>
-      </c>
-      <c r="Q293" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> (SPVYMB5705LKP5L平衡利库调拨，修改时间2026-10-21 10:53:38，调整前申请数量：100.0；调整后申请数量：36.0;)</t>
-        </is>
-      </c>
-      <c r="R293" t="inlineStr">
-        <is>
-          <t>大爆款</t>
-        </is>
-      </c>
+          <t>合成革高速线（计件）</t>
+        </is>
+      </c>
+      <c r="Q293"/>
+      <c r="R293"/>
       <c r="S293" t="inlineStr">
         <is>
           <t>否</t>
@@ -21898,7 +21898,7 @@
     <row r="294" customHeight="true" ht="15">
       <c r="A294" t="inlineStr">
         <is>
-          <t>LXPP261021001</t>
+          <t>LXPP261021003</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -21918,7 +21918,7 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>SPVYWB2208LK41M</t>
+          <t>SPVYWB2208LK23M</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
@@ -21927,7 +21927,7 @@
         </is>
       </c>
       <c r="G294" s="1" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="H294" t="inlineStr">
         <is>
@@ -21936,11 +21936,11 @@
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>16#B土棕/15.6寸</t>
+          <t>3#绿色</t>
         </is>
       </c>
       <c r="J294" s="1" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="K294" t="inlineStr">
         <is>
@@ -21948,7 +21948,7 @@
         </is>
       </c>
       <c r="L294" s="1" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="M294"/>
       <c r="N294" t="inlineStr">
@@ -21973,7 +21973,7 @@
     <row r="295" customHeight="true" ht="15">
       <c r="A295" t="inlineStr">
         <is>
-          <t>LXPP261021002</t>
+          <t>LXPP261021004</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -21993,7 +21993,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>SPVYWB2208LK01M</t>
+          <t>SPVYWB2208LK23L</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
@@ -22011,7 +22011,7 @@
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t>4141#黑色</t>
+          <t>3#绿色/17.3寸</t>
         </is>
       </c>
       <c r="J295" s="1" t="n">
@@ -22048,7 +22048,7 @@
     <row r="296" customHeight="true" ht="15">
       <c r="A296" t="inlineStr">
         <is>
-          <t>LXPP261021003</t>
+          <t>LXPP261021005</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -22068,7 +22068,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>SPVYWB2208LK23M</t>
+          <t>SPVYWB2208LK16M</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
@@ -22077,7 +22077,7 @@
         </is>
       </c>
       <c r="G296" s="1" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="H296" t="inlineStr">
         <is>
@@ -22086,11 +22086,11 @@
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t>3#绿色</t>
+          <t>8102#红棕啡色</t>
         </is>
       </c>
       <c r="J296" s="1" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="K296" t="inlineStr">
         <is>
@@ -22098,7 +22098,7 @@
         </is>
       </c>
       <c r="L296" s="1" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="M296"/>
       <c r="N296" t="inlineStr">
@@ -22123,7 +22123,7 @@
     <row r="297" customHeight="true" ht="15">
       <c r="A297" t="inlineStr">
         <is>
-          <t>LXPP261021004</t>
+          <t>LXPP261021006</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -22143,7 +22143,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>SPVYWB2208LK23L</t>
+          <t>SPVYWB2208LK10M</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
@@ -22161,7 +22161,7 @@
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t>3#绿色/17.3寸</t>
+          <t>1#黑色压纹</t>
         </is>
       </c>
       <c r="J297" s="1" t="n">
@@ -22198,7 +22198,7 @@
     <row r="298" customHeight="true" ht="15">
       <c r="A298" t="inlineStr">
         <is>
-          <t>LXPP261021005</t>
+          <t>LXPP261021007</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -22218,7 +22218,7 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>SPVYWB2208LK16M</t>
+          <t>SPVYWB2208LK10L</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
@@ -22236,7 +22236,7 @@
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t>8102#红棕啡色</t>
+          <t>1#黑色(压花)/17.3寸</t>
         </is>
       </c>
       <c r="J298" s="1" t="n">
@@ -22273,7 +22273,7 @@
     <row r="299" customHeight="true" ht="15">
       <c r="A299" t="inlineStr">
         <is>
-          <t>LXPP261021006</t>
+          <t>LXPP261021008</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -22293,7 +22293,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>SPVYWB2208LK10M</t>
+          <t>SPVYWB2208LK32M</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
@@ -22311,7 +22311,7 @@
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t>1#黑色压纹</t>
+          <t>压纹04#蓝色/069#绀蓝色/15.6寸</t>
         </is>
       </c>
       <c r="J299" s="1" t="n">
@@ -22348,7 +22348,7 @@
     <row r="300" customHeight="true" ht="15">
       <c r="A300" t="inlineStr">
         <is>
-          <t>LXPP261021007</t>
+          <t>LXPP261021009</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -22368,12 +22368,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>SPVYWB2208LK10L</t>
+          <t>SPVYWB5368LK10L</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>复古托特包</t>
+          <t>电脑手提包</t>
         </is>
       </c>
       <c r="G300" s="1" t="n">
@@ -22386,7 +22386,7 @@
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>1#黑色(压花)/17.3寸</t>
+          <t>01#黑色/17.3寸</t>
         </is>
       </c>
       <c r="J300" s="1" t="n">
@@ -22423,7 +22423,7 @@
     <row r="301" customHeight="true" ht="15">
       <c r="A301" t="inlineStr">
         <is>
-          <t>LXPP261021008</t>
+          <t>LXPP261021010</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -22443,12 +22443,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>SPVYWB2208LK32M</t>
+          <t>SPVYWB5368LK41L</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>复古托特包</t>
+          <t>电脑手提包</t>
         </is>
       </c>
       <c r="G301" s="1" t="n">
@@ -22461,7 +22461,7 @@
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t>压纹04#蓝色/069#绀蓝色/15.6寸</t>
+          <t>27#焦糖棕/17.3寸</t>
         </is>
       </c>
       <c r="J301" s="1" t="n">
@@ -22498,187 +22498,37 @@
     <row r="302" customHeight="true" ht="15">
       <c r="A302" t="inlineStr">
         <is>
-          <t>LXPP261021009</t>
-        </is>
-      </c>
-      <c r="B302" t="inlineStr">
-        <is>
-          <t>创建</t>
-        </is>
-      </c>
-      <c r="C302" t="inlineStr">
-        <is>
-          <t>未关闭</t>
-        </is>
-      </c>
-      <c r="D302" t="inlineStr">
-        <is>
-          <t>2026/10/22</t>
-        </is>
-      </c>
-      <c r="E302" t="inlineStr">
-        <is>
-          <t>SPVYWB5368LK10L</t>
-        </is>
-      </c>
-      <c r="F302" t="inlineStr">
-        <is>
-          <t>电脑手提包</t>
-        </is>
-      </c>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="B302"/>
+      <c r="C302"/>
+      <c r="D302"/>
+      <c r="E302"/>
+      <c r="F302"/>
       <c r="G302" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="H302" t="inlineStr">
-        <is>
-          <t>庞新会</t>
-        </is>
-      </c>
-      <c r="I302" t="inlineStr">
-        <is>
-          <t>01#黑色/17.3寸</t>
-        </is>
-      </c>
+        <v>51501</v>
+      </c>
+      <c r="H302"/>
+      <c r="I302"/>
       <c r="J302" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="K302" t="inlineStr">
-        <is>
-          <t>2026/11/20 00:00:00</t>
-        </is>
-      </c>
+        <v>51501</v>
+      </c>
+      <c r="K302"/>
       <c r="L302" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="M302"/>
-      <c r="N302" t="inlineStr">
-        <is>
-          <t>请工厂安排发货到前进仓</t>
-        </is>
-      </c>
-      <c r="O302"/>
-      <c r="P302" t="inlineStr">
-        <is>
-          <t>合成革高速线（计件）</t>
-        </is>
-      </c>
+        <v>51301</v>
+      </c>
+      <c r="M302" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N302"/>
+      <c r="O302" s="1" t="n">
+        <v>200</v>
+      </c>
+      <c r="P302"/>
       <c r="Q302"/>
       <c r="R302"/>
-      <c r="S302" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="303" customHeight="true" ht="15">
-      <c r="A303" t="inlineStr">
-        <is>
-          <t>LXPP261021010</t>
-        </is>
-      </c>
-      <c r="B303" t="inlineStr">
-        <is>
-          <t>创建</t>
-        </is>
-      </c>
-      <c r="C303" t="inlineStr">
-        <is>
-          <t>未关闭</t>
-        </is>
-      </c>
-      <c r="D303" t="inlineStr">
-        <is>
-          <t>2026/10/22</t>
-        </is>
-      </c>
-      <c r="E303" t="inlineStr">
-        <is>
-          <t>SPVYWB5368LK41L</t>
-        </is>
-      </c>
-      <c r="F303" t="inlineStr">
-        <is>
-          <t>电脑手提包</t>
-        </is>
-      </c>
-      <c r="G303" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="H303" t="inlineStr">
-        <is>
-          <t>庞新会</t>
-        </is>
-      </c>
-      <c r="I303" t="inlineStr">
-        <is>
-          <t>27#焦糖棕/17.3寸</t>
-        </is>
-      </c>
-      <c r="J303" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="K303" t="inlineStr">
-        <is>
-          <t>2026/11/20 00:00:00</t>
-        </is>
-      </c>
-      <c r="L303" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="M303"/>
-      <c r="N303" t="inlineStr">
-        <is>
-          <t>请工厂安排发货到前进仓</t>
-        </is>
-      </c>
-      <c r="O303"/>
-      <c r="P303" t="inlineStr">
-        <is>
-          <t>合成革高速线（计件）</t>
-        </is>
-      </c>
-      <c r="Q303"/>
-      <c r="R303"/>
-      <c r="S303" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="304" customHeight="true" ht="15">
-      <c r="A304" t="inlineStr">
-        <is>
-          <t>合计</t>
-        </is>
-      </c>
-      <c r="B304"/>
-      <c r="C304"/>
-      <c r="D304"/>
-      <c r="E304"/>
-      <c r="F304"/>
-      <c r="G304" s="1" t="n">
-        <v>51571</v>
-      </c>
-      <c r="H304"/>
-      <c r="I304"/>
-      <c r="J304" s="1" t="n">
-        <v>51571</v>
-      </c>
-      <c r="K304"/>
-      <c r="L304" s="1" t="n">
-        <v>51371</v>
-      </c>
-      <c r="M304" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N304"/>
-      <c r="O304" s="1" t="n">
-        <v>200</v>
-      </c>
-      <c r="P304"/>
-      <c r="Q304"/>
-      <c r="R304"/>
-      <c r="S304"/>
+      <c r="S302"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/otd_apply.xlsx
+++ b/src/otd_apply.xlsx
@@ -524,7 +524,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>创建</t>
+          <t>审核中</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>创建</t>
+          <t>审核中</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>创建</t>
+          <t>审核中</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>创建</t>
+          <t>审核中</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -812,7 +812,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>创建</t>
+          <t>审核中</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2420,7 +2420,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>创建</t>
+          <t>审核中</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>创建</t>
+          <t>审核中</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2564,7 +2564,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>创建</t>
+          <t>审核中</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>创建</t>
+          <t>审核中</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">

--- a/src/otd_apply.xlsx
+++ b/src/otd_apply.xlsx
@@ -172,7 +172,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>审核中</t>
+          <t>已审核</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -244,7 +244,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>审核中</t>
+          <t>已审核</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -316,7 +316,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>审核中</t>
+          <t>已审核</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -388,7 +388,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>审核中</t>
+          <t>已审核</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -460,7 +460,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>审核中</t>
+          <t>已审核</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -532,7 +532,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>审核中</t>
+          <t>已审核</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -604,7 +604,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>审核中</t>
+          <t>已审核</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>审核中</t>
+          <t>已审核</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>审核中</t>
+          <t>已审核</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>审核中</t>
+          <t>已审核</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>审核中</t>
+          <t>已审核</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>审核中</t>
+          <t>已审核</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>审核中</t>
+          <t>已审核</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>审核中</t>
+          <t>已审核</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>审核中</t>
+          <t>已审核</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>审核中</t>
+          <t>已审核</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>JDYPR261026100154B6235LK90M</t>
+          <t>JDYPR261023115047B5089LK41L</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1339,47 +1339,47 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026/10/26</t>
+          <t>2026/10/23</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>SPVYWB6235LK90M</t>
+          <t>SPVYWB5089LK41L</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>午餐电脑手提包</t>
+          <t>电脑手提包</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>复古7093#绿色/中号</t>
+          <t>8105#秋叶棕色/17.3寸</t>
         </is>
       </c>
       <c r="J18" s="1" t="n">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="K18" s="1" t="n">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026/11/25 00:00:00</t>
+          <t>2026/11/20 00:00:00</t>
         </is>
       </c>
       <c r="M18" s="1" t="n">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="N18"/>
       <c r="O18" t="inlineStr">
         <is>
-          <t>鲜明波</t>
+          <t>王琦</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>提需求收新品尾货</t>
+          <t>新增大号变体，运营何思琴</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>JDYPR261026100154B6235LK40M</t>
+          <t>JDYPR261023115047B5089LK20L</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1411,47 +1411,47 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026/10/26</t>
+          <t>2026/10/23</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>SPVYWB6235LK40M</t>
+          <t>SPVYWB5089LK20L</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>午餐电脑手提包</t>
+          <t>电脑手提包</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>复古8102#红棕啡色/中号</t>
+          <t>4012#驼灰色/17.3寸</t>
         </is>
       </c>
       <c r="J19" s="1" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="K19" s="1" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026/11/25 00:00:00</t>
+          <t>2026/11/20 00:00:00</t>
         </is>
       </c>
       <c r="M19" s="1" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="N19"/>
       <c r="O19" t="inlineStr">
         <is>
-          <t>鲜明波</t>
+          <t>王琦</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>提需求收新品尾货</t>
+          <t>新增大号变体，运营何思琴</t>
         </is>
       </c>
     </row>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>JDYPR261026100154B6235LK10M</t>
+          <t>JDYPR261023115047B5089LK00L</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1483,47 +1483,47 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026/10/26</t>
+          <t>2026/10/23</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>SPVYWB6235LK10M</t>
+          <t>SPVYWB5089LK00L</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>午餐电脑手提包</t>
+          <t>电脑手提包</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>复古#101黑色/中号</t>
+          <t>9006#米杏色/17.3寸</t>
         </is>
       </c>
       <c r="J20" s="1" t="n">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="K20" s="1" t="n">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026/11/25 00:00:00</t>
+          <t>2026/11/20 00:00:00</t>
         </is>
       </c>
       <c r="M20" s="1" t="n">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="N20"/>
       <c r="O20" t="inlineStr">
         <is>
-          <t>鲜明波</t>
+          <t>王琦</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>提需求收新品尾货</t>
+          <t>新增大号变体，运营何思琴</t>
         </is>
       </c>
     </row>
@@ -1535,7 +1535,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>JDYPR261023115047B5089LK41L</t>
+          <t>LXPP261023001</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026/10/26</t>
+          <t>2026/10/23</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1560,44 +1560,40 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>SPVYWB5089LK41L</t>
+          <t>SPVYMB2023LK03S</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>电脑手提包</t>
+          <t>搭盖时尚背包</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>8105#秋叶棕色/17.3寸</t>
+          <t>23#黑色/211#红棕色/14寸</t>
         </is>
       </c>
       <c r="J21" s="1" t="n">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="K21" s="1" t="n">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026/11/20 00:00:00</t>
+          <t>2026/10/23 00:00:00</t>
         </is>
       </c>
       <c r="M21" s="1" t="n">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="N21"/>
       <c r="O21" t="inlineStr">
         <is>
-          <t>王琦</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>新增大号变体，运营何思琴</t>
-        </is>
-      </c>
+          <t>吴冠烨</t>
+        </is>
+      </c>
+      <c r="P21"/>
     </row>
     <row r="22" customHeight="true" ht="15">
       <c r="A22" t="inlineStr">
@@ -1607,7 +1603,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>JDYPR261023115047B5089LK20L</t>
+          <t>LXPP261023002</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1617,7 +1613,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026/10/26</t>
+          <t>2026/10/23</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1632,44 +1628,40 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>SPVYWB5089LK20L</t>
+          <t>SPVYTK000701</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>电脑手提包</t>
+          <t>绑包丝带</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>4012#驼灰色/17.3寸</t>
+          <t>随机色混发3pcs</t>
         </is>
       </c>
       <c r="J22" s="1" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="K22" s="1" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026/11/20 00:00:00</t>
+          <t>2026/10/23 00:00:00</t>
         </is>
       </c>
       <c r="M22" s="1" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="N22"/>
       <c r="O22" t="inlineStr">
         <is>
-          <t>王琦</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>新增大号变体，运营何思琴</t>
-        </is>
-      </c>
+          <t>吴冠烨</t>
+        </is>
+      </c>
+      <c r="P22"/>
     </row>
     <row r="23" customHeight="true" ht="15">
       <c r="A23" t="inlineStr">
@@ -1679,7 +1671,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>JDYPR261023115047B5089LK00L</t>
+          <t>LXPP261021002</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1689,7 +1681,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026/10/26</t>
+          <t>2026/10/22</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1699,29 +1691,29 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026/10/23</t>
+          <t>2026/10/21</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>SPVYWB5089LK00L</t>
+          <t>SPVYWB2208LK01M</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>电脑手提包</t>
+          <t>复古托特包</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>9006#米杏色/17.3寸</t>
+          <t>4141#黑色</t>
         </is>
       </c>
       <c r="J23" s="1" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="K23" s="1" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1729,19 +1721,15 @@
         </is>
       </c>
       <c r="M23" s="1" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="N23"/>
       <c r="O23" t="inlineStr">
         <is>
-          <t>王琦</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>新增大号变体，运营何思琴</t>
-        </is>
-      </c>
+          <t>庞新会</t>
+        </is>
+      </c>
+      <c r="P23"/>
     </row>
     <row r="24" customHeight="true" ht="15">
       <c r="A24" t="inlineStr">
@@ -1751,7 +1739,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>LXPP261023001</t>
+          <t>LXPP261021003</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1761,7 +1749,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026/10/23</t>
+          <t>2026/10/22</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1771,42 +1759,42 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026/10/23</t>
+          <t>2026/10/21</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>SPVYMB2023LK03S</t>
+          <t>SPVYWB2208LK23M</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>搭盖时尚背包</t>
+          <t>复古托特包</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>23#黑色/211#红棕色/14寸</t>
+          <t>3#绿色</t>
         </is>
       </c>
       <c r="J24" s="1" t="n">
-        <v>25</v>
+        <v>300</v>
       </c>
       <c r="K24" s="1" t="n">
-        <v>25</v>
+        <v>300</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026/10/23 00:00:00</t>
+          <t>2026/11/20 00:00:00</t>
         </is>
       </c>
       <c r="M24" s="1" t="n">
-        <v>25</v>
+        <v>300</v>
       </c>
       <c r="N24"/>
       <c r="O24" t="inlineStr">
         <is>
-          <t>吴冠烨</t>
+          <t>庞新会</t>
         </is>
       </c>
       <c r="P24"/>
@@ -1819,7 +1807,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>LXPP261023002</t>
+          <t>LXPP261021005</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1829,7 +1817,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026/10/23</t>
+          <t>2026/10/22</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1839,42 +1827,42 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026/10/23</t>
+          <t>2026/10/21</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>SPVYTK000701</t>
+          <t>SPVYWB2208LK16M</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>绑包丝带</t>
+          <t>复古托特包</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>随机色混发3pcs</t>
+          <t>8102#红棕啡色</t>
         </is>
       </c>
       <c r="J25" s="1" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="K25" s="1" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026/10/23 00:00:00</t>
+          <t>2026/11/20 00:00:00</t>
         </is>
       </c>
       <c r="M25" s="1" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="N25"/>
       <c r="O25" t="inlineStr">
         <is>
-          <t>吴冠烨</t>
+          <t>庞新会</t>
         </is>
       </c>
       <c r="P25"/>
@@ -1887,7 +1875,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>LXPP261021002</t>
+          <t>LXPP261021006</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1912,7 +1900,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>SPVYWB2208LK01M</t>
+          <t>SPVYWB2208LK10M</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1922,7 +1910,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>4141#黑色</t>
+          <t>1#黑色压纹</t>
         </is>
       </c>
       <c r="J26" s="1" t="n">
@@ -1955,7 +1943,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>LXPP261021003</t>
+          <t>LXPP261021008</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1980,7 +1968,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>SPVYWB2208LK23M</t>
+          <t>SPVYWB2208LK32M</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1990,14 +1978,14 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>3#绿色</t>
+          <t>压纹04#蓝色/069#绀蓝色/15.6寸</t>
         </is>
       </c>
       <c r="J27" s="1" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="K27" s="1" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -2005,7 +1993,7 @@
         </is>
       </c>
       <c r="M27" s="1" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="N27"/>
       <c r="O27" t="inlineStr">
@@ -2023,7 +2011,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>LXPP261021005</t>
+          <t>LXPP261021001</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2048,7 +2036,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>SPVYWB2208LK16M</t>
+          <t>SPVYWB2208LK41M</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2058,14 +2046,14 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>8102#红棕啡色</t>
+          <t>16#B土棕/15.6寸</t>
         </is>
       </c>
       <c r="J28" s="1" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="K28" s="1" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -2073,7 +2061,7 @@
         </is>
       </c>
       <c r="M28" s="1" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N28"/>
       <c r="O28" t="inlineStr">
@@ -2091,7 +2079,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>LXPP261021006</t>
+          <t>LXPP261021009</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2116,17 +2104,17 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>SPVYWB2208LK10M</t>
+          <t>SPVYWB5368LK10L</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>复古托特包</t>
+          <t>电脑手提包</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1#黑色压纹</t>
+          <t>01#黑色/17.3寸</t>
         </is>
       </c>
       <c r="J29" s="1" t="n">
@@ -2159,7 +2147,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>LXPP261021008</t>
+          <t>LXPP261021004</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2184,7 +2172,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>SPVYWB2208LK32M</t>
+          <t>SPVYWB2208LK23L</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2194,7 +2182,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>压纹04#蓝色/069#绀蓝色/15.6寸</t>
+          <t>3#绿色/17.3寸</t>
         </is>
       </c>
       <c r="J30" s="1" t="n">
@@ -2227,7 +2215,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>LXPP261021001</t>
+          <t>LXPP261021007</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2252,7 +2240,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>SPVYWB2208LK41M</t>
+          <t>SPVYWB2208LK10L</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2262,14 +2250,14 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>16#B土棕/15.6寸</t>
+          <t>1#黑色(压花)/17.3寸</t>
         </is>
       </c>
       <c r="J31" s="1" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K31" s="1" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2277,7 +2265,7 @@
         </is>
       </c>
       <c r="M31" s="1" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="N31"/>
       <c r="O31" t="inlineStr">
@@ -2295,7 +2283,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>LXPP261021009</t>
+          <t>LXPP261021010</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2320,7 +2308,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>SPVYWB5368LK10L</t>
+          <t>SPVYWB5368LK41L</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2330,7 +2318,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>01#黑色/17.3寸</t>
+          <t>27#焦糖棕/17.3寸</t>
         </is>
       </c>
       <c r="J32" s="1" t="n">
@@ -2363,12 +2351,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>LXPP261021004</t>
+          <t>JDYPP20261022081615935</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>创建</t>
+          <t>已审核</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2383,22 +2371,22 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026/10/21</t>
+          <t>2026/10/22</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SPVYWB2208LK23L</t>
+          <t>LK6546M-BLK</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>复古托特包</t>
+          <t>女士单肩包</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>3#绿色/17.3寸</t>
+          <t>4006#黑色/12.5寸</t>
         </is>
       </c>
       <c r="J33" s="1" t="n">
@@ -2409,7 +2397,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2026/11/20 00:00:00</t>
+          <t>2026/12/1 00:00:00</t>
         </is>
       </c>
       <c r="M33" s="1" t="n">
@@ -2418,10 +2406,14 @@
       <c r="N33"/>
       <c r="O33" t="inlineStr">
         <is>
-          <t>庞新会</t>
-        </is>
-      </c>
-      <c r="P33"/>
+          <t>李子遥</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>新品</t>
+        </is>
+      </c>
     </row>
     <row r="34" customHeight="true" ht="15">
       <c r="A34" t="inlineStr">
@@ -2431,12 +2423,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>LXPP261021007</t>
+          <t>JDYPP20261022081615556</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>创建</t>
+          <t>已审核</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2451,45 +2443,49 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026/10/21</t>
+          <t>2026/10/22</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>SPVYWB2208LK10L</t>
+          <t>LK6546M-BRN</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>复古托特包</t>
+          <t>女士单肩包</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1#黑色(压花)/17.3寸</t>
+          <t>1012#深咖啡色/12.5寸</t>
         </is>
       </c>
       <c r="J34" s="1" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="K34" s="1" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2026/11/20 00:00:00</t>
+          <t>2026/12/1 00:00:00</t>
         </is>
       </c>
       <c r="M34" s="1" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N34"/>
       <c r="O34" t="inlineStr">
         <is>
-          <t>庞新会</t>
-        </is>
-      </c>
-      <c r="P34"/>
+          <t>李子遥</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>新品</t>
+        </is>
+      </c>
     </row>
     <row r="35" customHeight="true" ht="15">
       <c r="A35" t="inlineStr">
@@ -2499,12 +2495,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>LXPP261021010</t>
+          <t>JDYPP20261022081615162</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>创建</t>
+          <t>已审核</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2519,22 +2515,22 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026/10/21</t>
+          <t>2026/10/22</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>SPVYWB5368LK41L</t>
+          <t>LK6546S-BE</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>电脑手提包</t>
+          <t>女士单肩包</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>27#焦糖棕/17.3寸</t>
+          <t>16#米黄色/11寸</t>
         </is>
       </c>
       <c r="J35" s="1" t="n">
@@ -2545,7 +2541,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2026/11/20 00:00:00</t>
+          <t>2026/12/1 00:00:00</t>
         </is>
       </c>
       <c r="M35" s="1" t="n">
@@ -2554,10 +2550,14 @@
       <c r="N35"/>
       <c r="O35" t="inlineStr">
         <is>
-          <t>庞新会</t>
-        </is>
-      </c>
-      <c r="P35"/>
+          <t>李子遥</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>新品</t>
+        </is>
+      </c>
     </row>
     <row r="36" customHeight="true" ht="15">
       <c r="A36" t="inlineStr">
@@ -2567,7 +2567,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>JDYPP20261022081615935</t>
+          <t>JDYPP20261022081614770</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>LK6546M-BLK</t>
+          <t>LK6546S-BRN</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2602,14 +2602,14 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>4006#黑色/12.5寸</t>
+          <t>1012#深咖啡色/11寸</t>
         </is>
       </c>
       <c r="J36" s="1" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="K36" s="1" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
         </is>
       </c>
       <c r="M36" s="1" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="N36"/>
       <c r="O36" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>JDYPP20261022081615556</t>
+          <t>JDYPP20261022081614379</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>LK6546M-BRN</t>
+          <t>LK6546S-BLU</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2674,14 +2674,14 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1012#深咖啡色/12.5寸</t>
+          <t>58#浅蓝色/11寸</t>
         </is>
       </c>
       <c r="J37" s="1" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K37" s="1" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         </is>
       </c>
       <c r="M37" s="1" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="N37"/>
       <c r="O37" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>JDYPP20261022081615162</t>
+          <t>JDYPP20261022081613994</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>LK6546S-BE</t>
+          <t>LK6546S-GN01</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2746,14 +2746,14 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>16#米黄色/11寸</t>
+          <t>178#绿色/11寸</t>
         </is>
       </c>
       <c r="J38" s="1" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="K38" s="1" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         </is>
       </c>
       <c r="M38" s="1" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N38"/>
       <c r="O38" t="inlineStr">
@@ -2783,7 +2783,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>JDYPP20261022081614770</t>
+          <t>JDYPP20261022081613617</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>LK6546S-BRN</t>
+          <t>LK6546S-AP</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2818,14 +2818,14 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1012#深咖啡色/11寸</t>
+          <t>02#豹纹/11寸</t>
         </is>
       </c>
       <c r="J39" s="1" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="K39" s="1" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         </is>
       </c>
       <c r="M39" s="1" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="N39"/>
       <c r="O39" t="inlineStr">
@@ -2855,7 +2855,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>JDYPP20261022081614379</t>
+          <t>JDYPP20261022081613239</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>LK6546S-BLU</t>
+          <t>LK6546S-BLK</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2890,14 +2890,14 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>58#浅蓝色/11寸</t>
+          <t>4006#黑色/11寸</t>
         </is>
       </c>
       <c r="J40" s="1" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="K40" s="1" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
         </is>
       </c>
       <c r="M40" s="1" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="N40"/>
       <c r="O40" t="inlineStr">
@@ -2927,7 +2927,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>JDYPP20261022081613994</t>
+          <t>JDYPP20261022081612858</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2952,7 +2952,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>LK6546S-GN01</t>
+          <t>LK6546S-GN</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2962,14 +2962,14 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>178#绿色/11寸</t>
+          <t>298#浅绿色/11寸</t>
         </is>
       </c>
       <c r="J41" s="1" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K41" s="1" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2977,7 +2977,7 @@
         </is>
       </c>
       <c r="M41" s="1" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="N41"/>
       <c r="O41" t="inlineStr">
@@ -2999,7 +2999,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>JDYPP20261022081613617</t>
+          <t>JDYPP20261022081612475</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>LK6546S-AP</t>
+          <t>LK6546S-WHT</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>02#豹纹/11寸</t>
+          <t>0104#天光白色/11寸</t>
         </is>
       </c>
       <c r="J42" s="1" t="n">
@@ -3066,12 +3066,12 @@
     <row r="43" customHeight="true" ht="15">
       <c r="A43" t="inlineStr">
         <is>
-          <t>kd</t>
+          <t>江海霞</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>JDYPP20261022081613239</t>
+          <t>CGSQ005483</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3096,54 +3096,50 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>LK6546S-BLK</t>
+          <t>VYWB5128LK10M-T2</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>女士单肩包</t>
+          <t>电脑手提包</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>4006#黑色/11寸</t>
+          <t>01#黑色/15.6寸/两件套</t>
         </is>
       </c>
       <c r="J43" s="1" t="n">
-        <v>300</v>
+        <v>1</v>
       </c>
       <c r="K43" s="1" t="n">
-        <v>300</v>
+        <v>1</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>2026/12/1 00:00:00</t>
+          <t>2026/10/22 00:00:00</t>
         </is>
       </c>
       <c r="M43" s="1" t="n">
-        <v>300</v>
+        <v>1</v>
       </c>
       <c r="N43"/>
       <c r="O43" t="inlineStr">
         <is>
-          <t>李子遥</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>新品</t>
-        </is>
-      </c>
+          <t>国际站</t>
+        </is>
+      </c>
+      <c r="P43"/>
     </row>
     <row r="44" customHeight="true" ht="15">
       <c r="A44" t="inlineStr">
         <is>
-          <t>kd</t>
+          <t>江海霞</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>JDYPP20261022081612858</t>
+          <t>CGSQ005483</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3168,44 +3164,40 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>LK6546S-GN</t>
+          <t>VYWB5128LK40M-T2</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>女士单肩包</t>
+          <t>电脑手提包</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>298#浅绿色/11寸</t>
+          <t>202#土棕色/15.6寸/两件套</t>
         </is>
       </c>
       <c r="J44" s="1" t="n">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="K44" s="1" t="n">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2026/12/1 00:00:00</t>
+          <t>2026/10/22 00:00:00</t>
         </is>
       </c>
       <c r="M44" s="1" t="n">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="N44"/>
       <c r="O44" t="inlineStr">
         <is>
-          <t>李子遥</t>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>新品</t>
-        </is>
-      </c>
+          <t>国际站</t>
+        </is>
+      </c>
+      <c r="P44"/>
     </row>
     <row r="45" customHeight="true" ht="15">
       <c r="A45" t="inlineStr">
@@ -3215,7 +3207,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>JDYPP20261022081612475</t>
+          <t>JDYPP20261022063217462</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3240,54 +3232,54 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>LK6546S-WHT</t>
+          <t>VYWB5031LKP4M</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>女士单肩包</t>
+          <t>电脑手提包</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0104#天光白色/11寸</t>
+          <t>4001#黑色/8022#咖啡色/豹纹/15.6寸</t>
         </is>
       </c>
       <c r="J45" s="1" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="K45" s="1" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2026/12/1 00:00:00</t>
+          <t>2026/11/25 00:00:00</t>
         </is>
       </c>
       <c r="M45" s="1" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="N45"/>
       <c r="O45" t="inlineStr">
         <is>
-          <t>李子遥</t>
+          <t>梁庭威</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>新品</t>
+          <t>新变体</t>
         </is>
       </c>
     </row>
     <row r="46" customHeight="true" ht="15">
       <c r="A46" t="inlineStr">
         <is>
-          <t>江海霞</t>
+          <t>kd</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CGSQ005483</t>
+          <t>JDYPP20261022063217106</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3312,7 +3304,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>VYWB5128LK10M-T2</t>
+          <t>VYWB5031LK11M-C1</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3322,40 +3314,44 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>01#黑色/15.6寸/两件套</t>
+          <t>复古4001#黑色（压花）/4001#黑色/15.6寸</t>
         </is>
       </c>
       <c r="J46" s="1" t="n">
-        <v>1</v>
+        <v>150</v>
       </c>
       <c r="K46" s="1" t="n">
-        <v>1</v>
+        <v>150</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2026/10/22 00:00:00</t>
+          <t>2026/11/25 00:00:00</t>
         </is>
       </c>
       <c r="M46" s="1" t="n">
-        <v>1</v>
+        <v>150</v>
       </c>
       <c r="N46"/>
       <c r="O46" t="inlineStr">
         <is>
-          <t>国际站</t>
-        </is>
-      </c>
-      <c r="P46"/>
+          <t>梁庭威</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>新变体</t>
+        </is>
+      </c>
     </row>
     <row r="47" customHeight="true" ht="15">
       <c r="A47" t="inlineStr">
         <is>
-          <t>江海霞</t>
+          <t>kd</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CGSQ005483</t>
+          <t>JDYPP20261022063216751</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3380,7 +3376,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>VYWB5128LK40M-T2</t>
+          <t>VYWB5031LK30M-C1</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3390,30 +3386,34 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>202#土棕色/15.6寸/两件套</t>
+          <t>复古6159#蓝色（压花）/6159#蓝色/15.6寸</t>
         </is>
       </c>
       <c r="J47" s="1" t="n">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="K47" s="1" t="n">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2026/10/22 00:00:00</t>
+          <t>2026/11/25 00:00:00</t>
         </is>
       </c>
       <c r="M47" s="1" t="n">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="N47"/>
       <c r="O47" t="inlineStr">
         <is>
-          <t>国际站</t>
-        </is>
-      </c>
-      <c r="P47"/>
+          <t>梁庭威</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>新变体</t>
+        </is>
+      </c>
     </row>
     <row r="48" customHeight="true" ht="15">
       <c r="A48" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>JDYPP20261022063217462</t>
+          <t>JDYPP20261022063216397</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>VYWB5031LKP4M</t>
+          <t>VYWB5031LK42L-C1</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3458,7 +3458,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>4001#黑色/8022#咖啡色/豹纹/15.6寸</t>
+          <t>复古8089#黄棕色(压花)/8089#黄棕色/17.3寸</t>
         </is>
       </c>
       <c r="J48" s="1" t="n">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>JDYPP20261022063217106</t>
+          <t>JDYPR261022103431B4561LKP6M</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>已审核</t>
+          <t>创建</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3520,42 +3520,42 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>VYWB5031LK11M-C1</t>
+          <t>SPVYMB4561LKP6M</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>电脑手提包</t>
+          <t>电脑背包</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>复古4001#黑色（压花）/4001#黑色/15.6寸</t>
+          <t>48#绿色/77#米白色/7429D深绿灰/15.6寸</t>
         </is>
       </c>
       <c r="J49" s="1" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="K49" s="1" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2026/11/25 00:00:00</t>
+          <t>2026/11/21 00:00:00</t>
         </is>
       </c>
       <c r="M49" s="1" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="N49"/>
       <c r="O49" t="inlineStr">
         <is>
-          <t>梁庭威</t>
+          <t>李晓玲</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>新变体</t>
+          <t>新变体原下单100，平衡利库50个，剩50个无法下单，补交50个凑100下单</t>
         </is>
       </c>
     </row>
@@ -3567,17 +3567,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>JDYPP20261022063216751</t>
+          <t>JDYPP20261021091400998</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>已审核</t>
+          <t>创建</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026/10/22</t>
+          <t>2026/10/21</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3587,47 +3587,47 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026/10/22</t>
+          <t>2026/10/21</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>VYWB5031LK30M-C1</t>
+          <t>LKC0011M-BLK</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>电脑手提包</t>
+          <t>女士单肩包</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>复古6159#蓝色（压花）/6159#蓝色/15.6寸</t>
+          <t>复古01#黑色/中号</t>
         </is>
       </c>
       <c r="J50" s="1" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="K50" s="1" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>2026/11/25 00:00:00</t>
+          <t>2026/11/15 00:00:00</t>
         </is>
       </c>
       <c r="M50" s="1" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="N50"/>
       <c r="O50" t="inlineStr">
         <is>
-          <t>梁庭威</t>
+          <t>庞新会</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>新变体</t>
+          <t>新品</t>
         </is>
       </c>
     </row>
@@ -3639,17 +3639,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>JDYPP20261022063216397</t>
+          <t>JDYPP20261021091400581</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>已审核</t>
+          <t>创建</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026/10/22</t>
+          <t>2026/10/21</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3659,47 +3659,47 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026/10/22</t>
+          <t>2026/10/21</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>VYWB5031LK42L-C1</t>
+          <t>LKC0011M-BLK</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>电脑手提包</t>
+          <t>女士单肩包</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>复古8089#黄棕色(压花)/8089#黄棕色/17.3寸</t>
+          <t>复古01#黑色/中号</t>
         </is>
       </c>
       <c r="J51" s="1" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="K51" s="1" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2026/11/25 00:00:00</t>
+          <t>2026/11/16 00:00:00</t>
         </is>
       </c>
       <c r="M51" s="1" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="N51"/>
       <c r="O51" t="inlineStr">
         <is>
-          <t>梁庭威</t>
+          <t>姚鲜珍</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>新变体</t>
+          <t>新品</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>JDYPR261022103431B4561LKP6M</t>
+          <t>JDYPP20261021091400183</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026/10/22</t>
+          <t>2026/10/21</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3731,47 +3731,47 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026/10/22</t>
+          <t>2026/10/21</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>SPVYMB4561LKP6M</t>
+          <t>LKC0011S-BLK</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>电脑背包</t>
+          <t>女士单肩包</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>48#绿色/77#米白色/7429D深绿灰/15.6寸</t>
+          <t>复古01#黑色/小号</t>
         </is>
       </c>
       <c r="J52" s="1" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="K52" s="1" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>2026/11/21 00:00:00</t>
+          <t>2026/11/15 00:00:00</t>
         </is>
       </c>
       <c r="M52" s="1" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="N52"/>
       <c r="O52" t="inlineStr">
         <is>
-          <t>李晓玲</t>
+          <t>庞新会</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>新变体原下单100，平衡利库50个，剩50个无法下单，补交50个凑100下单</t>
+          <t>新品</t>
         </is>
       </c>
     </row>
@@ -3783,7 +3783,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>JDYPP20261021091400998</t>
+          <t>JDYPP20261021091359782</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>LKC0011M-BLK</t>
+          <t>LKC0011S-BLK</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3818,27 +3818,27 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>复古01#黑色/中号</t>
+          <t>复古01#黑色/小号</t>
         </is>
       </c>
       <c r="J53" s="1" t="n">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="K53" s="1" t="n">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>2026/11/15 00:00:00</t>
+          <t>2026/11/16 00:00:00</t>
         </is>
       </c>
       <c r="M53" s="1" t="n">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="N53"/>
       <c r="O53" t="inlineStr">
         <is>
-          <t>庞新会</t>
+          <t>姚鲜珍</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -3855,7 +3855,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>JDYPP20261021091400581</t>
+          <t>JDYPP20261021091359398</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3880,7 +3880,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>LKC0011M-BLK</t>
+          <t>LKC0011M-AP02</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3890,14 +3890,14 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>复古01#黑色/中号</t>
+          <t>07#豹纹/41#深咖色/中号</t>
         </is>
       </c>
       <c r="J54" s="1" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K54" s="1" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         </is>
       </c>
       <c r="M54" s="1" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N54"/>
       <c r="O54" t="inlineStr">
@@ -3927,7 +3927,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>JDYPP20261021091400183</t>
+          <t>JDYPP20261021091359013</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3952,7 +3952,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>LKC0011S-BLK</t>
+          <t>LKC0011M-PA</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3960,29 +3960,29 @@
           <t>女士单肩包</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>复古01#黑色/小号</t>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>=8021D#咖色老花/220#深棕色/中号</t>
         </is>
       </c>
       <c r="J55" s="1" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="K55" s="1" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>2026/11/15 00:00:00</t>
+          <t>2026/11/16 00:00:00</t>
         </is>
       </c>
       <c r="M55" s="1" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="N55"/>
       <c r="O55" t="inlineStr">
         <is>
-          <t>庞新会</t>
+          <t>姚鲜珍</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -3999,7 +3999,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>JDYPP20261021091359782</t>
+          <t>JDYPP20261021091358613</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4024,7 +4024,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>LKC0011S-BLK</t>
+          <t>LKC0011S-PA</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4034,14 +4034,14 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>复古01#黑色/小号</t>
+          <t>8021D#咖色老花/220#深棕色/小号</t>
         </is>
       </c>
       <c r="J56" s="1" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="K56" s="1" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
@@ -4049,7 +4049,7 @@
         </is>
       </c>
       <c r="M56" s="1" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="N56"/>
       <c r="O56" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>JDYPP20261021091359398</t>
+          <t>JDYPP20261021091358212</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>LKC0011M-AP02</t>
+          <t>LKC0011M-GN01-C1</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4106,27 +4106,27 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>07#豹纹/41#深咖色/中号</t>
+          <t>复古7093#绿色（压花）/7093#绿色/中号</t>
         </is>
       </c>
       <c r="J57" s="1" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="K57" s="1" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>2026/11/16 00:00:00</t>
+          <t>2026/11/15 00:00:00</t>
         </is>
       </c>
       <c r="M57" s="1" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="N57"/>
       <c r="O57" t="inlineStr">
         <is>
-          <t>姚鲜珍</t>
+          <t>庞新会</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>JDYPP20261021091359013</t>
+          <t>JDYPP20261021091357775</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -4168,7 +4168,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>LKC0011M-PA</t>
+          <t>LKC0011M-GN01-C1</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4176,16 +4176,16 @@
           <t>女士单肩包</t>
         </is>
       </c>
-      <c r="I58" s="2" t="inlineStr">
-        <is>
-          <t>=8021D#咖色老花/220#深棕色/中号</t>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>复古7093#绿色（压花）/7093#绿色/中号</t>
         </is>
       </c>
       <c r="J58" s="1" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="K58" s="1" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
@@ -4193,12 +4193,12 @@
         </is>
       </c>
       <c r="M58" s="1" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="N58"/>
       <c r="O58" t="inlineStr">
         <is>
-          <t>姚鲜珍</t>
+          <t>洪佳佩</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -4215,7 +4215,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>JDYPP20261021091358613</t>
+          <t>JDYPP20261021091357381</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4240,7 +4240,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>LKC0011S-PA</t>
+          <t>LKC0011M-BRN03-C1</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4250,27 +4250,27 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>8021D#咖色老花/220#深棕色/小号</t>
+          <t>复古8089#黄棕色（压花）/8089#黄棕色/中号</t>
         </is>
       </c>
       <c r="J59" s="1" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="K59" s="1" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>2026/11/16 00:00:00</t>
+          <t>2026/11/15 00:00:00</t>
         </is>
       </c>
       <c r="M59" s="1" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="N59"/>
       <c r="O59" t="inlineStr">
         <is>
-          <t>姚鲜珍</t>
+          <t>庞新会</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -4287,7 +4287,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>JDYPP20261021091358212</t>
+          <t>JDYPP20261021091356941</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>LKC0011M-GN01-C1</t>
+          <t>LKC0011M-BRN03-C1</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4322,7 +4322,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>复古7093#绿色（压花）/7093#绿色/中号</t>
+          <t>复古8089#黄棕色（压花）/8089#黄棕色/中号</t>
         </is>
       </c>
       <c r="J60" s="1" t="n">
@@ -4333,7 +4333,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>2026/11/15 00:00:00</t>
+          <t>2026/11/16 00:00:00</t>
         </is>
       </c>
       <c r="M60" s="1" t="n">
@@ -4342,7 +4342,7 @@
       <c r="N60"/>
       <c r="O60" t="inlineStr">
         <is>
-          <t>庞新会</t>
+          <t>洪佳佩</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>JDYPP20261021091357775</t>
+          <t>JDYPP20261021091356515</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4384,7 +4384,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>LKC0011M-GN01-C1</t>
+          <t>LKC0011M-AP01</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4394,7 +4394,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>复古7093#绿色（压花）/7093#绿色/中号</t>
+          <t>9065#河狸毛皮色/中号</t>
         </is>
       </c>
       <c r="J61" s="1" t="n">
@@ -4414,7 +4414,7 @@
       <c r="N61"/>
       <c r="O61" t="inlineStr">
         <is>
-          <t>洪佳佩</t>
+          <t>姚鲜珍</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>JDYPP20261021091357381</t>
+          <t>JDYPP20261021091355678</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4456,7 +4456,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>LKC0011M-BRN03-C1</t>
+          <t>LKC0011M-AP</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4466,14 +4466,14 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>复古8089#黄棕色（压花）/8089#黄棕色/中号</t>
+          <t>8014#冰咖啡色（豹纹）/8050#深棕色/中号</t>
         </is>
       </c>
       <c r="J62" s="1" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="K62" s="1" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
         </is>
       </c>
       <c r="M62" s="1" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="N62"/>
       <c r="O62" t="inlineStr">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>JDYPP20261021091356941</t>
+          <t>JDYPP20261021091355266</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4528,7 +4528,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>LKC0011M-BRN03-C1</t>
+          <t>LKC0011M-AP</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4538,14 +4538,14 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>复古8089#黄棕色（压花）/8089#黄棕色/中号</t>
+          <t>8014#冰咖啡色（豹纹）/8050#深棕色/中号</t>
         </is>
       </c>
       <c r="J63" s="1" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K63" s="1" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
@@ -4553,7 +4553,7 @@
         </is>
       </c>
       <c r="M63" s="1" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N63"/>
       <c r="O63" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>JDYPP20261021091356515</t>
+          <t>JDYPP20261021091354825</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4600,7 +4600,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>LKC0011M-AP01</t>
+          <t>LKC0011M-AP</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4610,7 +4610,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>9065#河狸毛皮色/中号</t>
+          <t>8014#冰咖啡色（豹纹）/8050#深棕色/中号</t>
         </is>
       </c>
       <c r="J64" s="1" t="n">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>JDYPP20261021091355678</t>
+          <t>JDYPP20261021091354415</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4672,7 +4672,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>LKC0011M-AP</t>
+          <t>LKC0011S-AP</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>8014#冰咖啡色（豹纹）/8050#深棕色/中号</t>
+          <t>8014#冰咖啡色（豹纹）/8050#深棕色/小号</t>
         </is>
       </c>
       <c r="J65" s="1" t="n">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>JDYPP20261021091355266</t>
+          <t>JDYPP20261021091354006</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4744,7 +4744,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>LKC0011M-AP</t>
+          <t>LKC0011S-AP</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4754,14 +4754,14 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>8014#冰咖啡色（豹纹）/8050#深棕色/中号</t>
+          <t>8014#冰咖啡色（豹纹）/8050#深棕色/小号</t>
         </is>
       </c>
       <c r="J66" s="1" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="K66" s="1" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="M66" s="1" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="N66"/>
       <c r="O66" t="inlineStr">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>JDYPP20261021091354825</t>
+          <t>JDYPP20261021091353562</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4816,7 +4816,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>LKC0011M-AP</t>
+          <t>LKC0011S-AP</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>8014#冰咖啡色（豹纹）/8050#深棕色/中号</t>
+          <t>8014#冰咖啡色（豹纹）/8050#深棕色/小号</t>
         </is>
       </c>
       <c r="J67" s="1" t="n">
@@ -4863,7 +4863,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>JDYPP20261021091354415</t>
+          <t>JDYPP20261021091353155</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>LKC0011S-AP</t>
+          <t>LKC0011M-BRN02</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4898,27 +4898,27 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>8014#冰咖啡色（豹纹）/8050#深棕色/小号</t>
+          <t>复古09#栗棕色/中号</t>
         </is>
       </c>
       <c r="J68" s="1" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="K68" s="1" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>2026/11/15 00:00:00</t>
+          <t>2026/11/16 00:00:00</t>
         </is>
       </c>
       <c r="M68" s="1" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="N68"/>
       <c r="O68" t="inlineStr">
         <is>
-          <t>庞新会</t>
+          <t>洪佳佩</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -4935,7 +4935,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>JDYPP20261021091354006</t>
+          <t>JDYPP20261021091352720</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>LKC0011S-AP</t>
+          <t>LKC0011M-BRN02</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4970,7 +4970,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>8014#冰咖啡色（豹纹）/8050#深棕色/小号</t>
+          <t>复古09#栗棕色/中号</t>
         </is>
       </c>
       <c r="J69" s="1" t="n">
@@ -4990,7 +4990,7 @@
       <c r="N69"/>
       <c r="O69" t="inlineStr">
         <is>
-          <t>洪佳佩</t>
+          <t>姚鲜珍</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -5007,7 +5007,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>JDYPP20261021091353562</t>
+          <t>JDYPP20261021091352285</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -5032,7 +5032,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>LKC0011S-AP</t>
+          <t>LKC0011S-BRN02</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -5042,14 +5042,14 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>8014#冰咖啡色（豹纹）/8050#深棕色/小号</t>
+          <t>复古09#栗棕色/小号</t>
         </is>
       </c>
       <c r="J70" s="1" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K70" s="1" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L70" t="inlineStr">
         <is>
@@ -5057,7 +5057,7 @@
         </is>
       </c>
       <c r="M70" s="1" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N70"/>
       <c r="O70" t="inlineStr">
@@ -5079,7 +5079,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>JDYPP20261021091353155</t>
+          <t>JDYPP20261021091351857</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>LKC0011M-BRN02</t>
+          <t>LKC0011M-GN-CT</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -5114,14 +5114,14 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>复古09#栗棕色/中号</t>
+          <t>复古22#军绿色/7935#深绿色/210#巧克力棕色/中号</t>
         </is>
       </c>
       <c r="J71" s="1" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K71" s="1" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L71" t="inlineStr">
         <is>
@@ -5129,12 +5129,12 @@
         </is>
       </c>
       <c r="M71" s="1" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N71"/>
       <c r="O71" t="inlineStr">
         <is>
-          <t>洪佳佩</t>
+          <t>姚鲜珍</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>JDYPP20261021091352720</t>
+          <t>JDYPP20261021091351431</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>LKC0011M-BRN02</t>
+          <t>LKC0011S-GN-CT</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -5186,14 +5186,14 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>复古09#栗棕色/中号</t>
+          <t>复古22#军绿色/7935#深绿色/210#巧克力棕色/小号</t>
         </is>
       </c>
       <c r="J72" s="1" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K72" s="1" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L72" t="inlineStr">
         <is>
@@ -5201,7 +5201,7 @@
         </is>
       </c>
       <c r="M72" s="1" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N72"/>
       <c r="O72" t="inlineStr">
@@ -5223,7 +5223,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>JDYPP20261021091352285</t>
+          <t>JDYPP20261021091351005</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -5248,7 +5248,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>LKC0011S-BRN02</t>
+          <t>LKC0011M-RD-CT</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -5258,14 +5258,14 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>复古09#栗棕色/小号</t>
+          <t>复古2435#安道尔红色/2387#红壁色/402P珠光酒红色/中号</t>
         </is>
       </c>
       <c r="J73" s="1" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="K73" s="1" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="L73" t="inlineStr">
         <is>
@@ -5273,7 +5273,7 @@
         </is>
       </c>
       <c r="M73" s="1" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="N73"/>
       <c r="O73" t="inlineStr">
@@ -5295,7 +5295,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>JDYPP20261021091351857</t>
+          <t>JDYPP20261021091350580</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -5320,7 +5320,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>LKC0011M-GN-CT</t>
+          <t>LKC0011S-RD-CT</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5330,7 +5330,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>复古22#军绿色/7935#深绿色/210#巧克力棕色/中号</t>
+          <t>复古2435#安道尔红色/2387#红壁色/402P珠光酒红色/小号</t>
         </is>
       </c>
       <c r="J74" s="1" t="n">
@@ -5367,7 +5367,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>JDYPP20261021091351431</t>
+          <t>JDYPP20261021091350183</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5392,7 +5392,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>LKC0011S-GN-CT</t>
+          <t>LKC0011M-BRN01-CT</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5402,14 +5402,14 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>复古22#军绿色/7935#深绿色/210#巧克力棕色/小号</t>
+          <t>复古8025#红土陶色/8027D#玳瑁色/203#浅咖色/中号</t>
         </is>
       </c>
       <c r="J75" s="1" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="K75" s="1" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="L75" t="inlineStr">
         <is>
@@ -5417,12 +5417,12 @@
         </is>
       </c>
       <c r="M75" s="1" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="N75"/>
       <c r="O75" t="inlineStr">
         <is>
-          <t>姚鲜珍</t>
+          <t>洪佳佩</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -5439,7 +5439,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>JDYPP20261021091351005</t>
+          <t>JDYPP20261021091349752</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>LKC0011M-RD-CT</t>
+          <t>LKC0011M-BRN01-CT</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>复古2435#安道尔红色/2387#红壁色/402P珠光酒红色/中号</t>
+          <t>复古8025#红土陶色/8027D#玳瑁色/203#浅咖色/中号</t>
         </is>
       </c>
       <c r="J76" s="1" t="n">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>JDYPP20261021091350580</t>
+          <t>JDYPP20261021091349376</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>LKC0011S-RD-CT</t>
+          <t>LKC0011S-BRN01-CT</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5546,14 +5546,14 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>复古2435#安道尔红色/2387#红壁色/402P珠光酒红色/小号</t>
+          <t>复古8025#红土陶色/8027D#玳瑁色/203#浅咖色/小号</t>
         </is>
       </c>
       <c r="J77" s="1" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="K77" s="1" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="L77" t="inlineStr">
         <is>
@@ -5561,12 +5561,12 @@
         </is>
       </c>
       <c r="M77" s="1" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="N77"/>
       <c r="O77" t="inlineStr">
         <is>
-          <t>姚鲜珍</t>
+          <t>洪佳佩</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -5583,7 +5583,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>JDYPP20261021091350183</t>
+          <t>JDYPP20261021091348935</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5608,7 +5608,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>LKC0011M-BRN01-CT</t>
+          <t>LKC0011S-BRN01-CT</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5618,7 +5618,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>复古8025#红土陶色/8027D#玳瑁色/203#浅咖色/中号</t>
+          <t>复古8025#红土陶色/8027D#玳瑁色/203#浅咖色/小号</t>
         </is>
       </c>
       <c r="J78" s="1" t="n">
@@ -5638,7 +5638,7 @@
       <c r="N78"/>
       <c r="O78" t="inlineStr">
         <is>
-          <t>洪佳佩</t>
+          <t>姚鲜珍</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -5655,7 +5655,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>JDYPP20261021091349752</t>
+          <t>JDYPP20261021091348524</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5680,7 +5680,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>LKC0011M-BRN01-CT</t>
+          <t>LKC0011M-BRN-CT</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5690,27 +5690,27 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>复古8025#红土陶色/8027D#玳瑁色/203#浅咖色/中号</t>
+          <t>复古8056D#黑糖棕色/8050#欧洲蕨棕色/210#巧克力棕色/中号</t>
         </is>
       </c>
       <c r="J79" s="1" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="K79" s="1" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>2026/11/16 00:00:00</t>
+          <t>2026/11/15 00:00:00</t>
         </is>
       </c>
       <c r="M79" s="1" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="N79"/>
       <c r="O79" t="inlineStr">
         <is>
-          <t>姚鲜珍</t>
+          <t>庞新会</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -5727,7 +5727,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>JDYPP20261021091349376</t>
+          <t>JDYPP20261021091348170</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5752,7 +5752,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>LKC0011S-BRN01-CT</t>
+          <t>LKC0011M-BRN-CT</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5762,7 +5762,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>复古8025#红土陶色/8027D#玳瑁色/203#浅咖色/小号</t>
+          <t>复古8056D#黑糖棕色/8050#欧洲蕨棕色/210#巧克力棕色/中号</t>
         </is>
       </c>
       <c r="J80" s="1" t="n">
@@ -5799,7 +5799,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>JDYPP20261021091348935</t>
+          <t>JDYPP20261021091347784</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>LKC0011S-BRN01-CT</t>
+          <t>LKC0011M-BRN-CT</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5834,14 +5834,14 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>复古8025#红土陶色/8027D#玳瑁色/203#浅咖色/小号</t>
+          <t>复古8056D#黑糖棕色/8050#欧洲蕨棕色/210#巧克力棕色/中号</t>
         </is>
       </c>
       <c r="J81" s="1" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="K81" s="1" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="L81" t="inlineStr">
         <is>
@@ -5849,7 +5849,7 @@
         </is>
       </c>
       <c r="M81" s="1" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="N81"/>
       <c r="O81" t="inlineStr">
@@ -5871,7 +5871,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>JDYPP20261021091348524</t>
+          <t>JDYPP20261021091347429</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5896,7 +5896,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>LKC0011M-BRN-CT</t>
+          <t>LKC0011S-BRN-CT</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5906,7 +5906,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>复古8056D#黑糖棕色/8050#欧洲蕨棕色/210#巧克力棕色/中号</t>
+          <t>复古8056D#黑糖棕色/8050#欧洲蕨棕色/210#巧克力棕色/小号</t>
         </is>
       </c>
       <c r="J82" s="1" t="n">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>JDYPP20261021091348170</t>
+          <t>JDYPP20261021091347035</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>LKC0011M-BRN-CT</t>
+          <t>LKC0011S-BRN-CT</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5978,14 +5978,14 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>复古8056D#黑糖棕色/8050#欧洲蕨棕色/210#巧克力棕色/中号</t>
+          <t>复古8056D#黑糖棕色/8050#欧洲蕨棕色/210#巧克力棕色/小号</t>
         </is>
       </c>
       <c r="J83" s="1" t="n">
-        <v>50</v>
+        <v>400</v>
       </c>
       <c r="K83" s="1" t="n">
-        <v>50</v>
+        <v>400</v>
       </c>
       <c r="L83" t="inlineStr">
         <is>
@@ -5993,12 +5993,12 @@
         </is>
       </c>
       <c r="M83" s="1" t="n">
-        <v>50</v>
+        <v>400</v>
       </c>
       <c r="N83"/>
       <c r="O83" t="inlineStr">
         <is>
-          <t>洪佳佩</t>
+          <t>姚鲜珍</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>JDYPP20261021091347784</t>
+          <t>JDYPR261019112819B5781LKP1L</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>创建</t>
+          <t>已审核</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -6035,47 +6035,47 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026/10/21</t>
+          <t>2026/10/19</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>LKC0011M-BRN-CT</t>
+          <t>SPVYUB5781LKP1L</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>女士单肩包</t>
+          <t>午餐包</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>复古8056D#黑糖棕色/8050#欧洲蕨棕色/210#巧克力棕色/中号</t>
+          <t>127#浅粉色/126#酱红色/大号</t>
         </is>
       </c>
       <c r="J84" s="1" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K84" s="1" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>2026/11/16 00:00:00</t>
+          <t>2026/11/18 00:00:00</t>
         </is>
       </c>
       <c r="M84" s="1" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="N84"/>
       <c r="O84" t="inlineStr">
         <is>
-          <t>姚鲜珍</t>
+          <t>黄格格</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>新品</t>
+          <t>10月8号开始二推，备货至1月，1月日均49单备货，现在备货引流大小号</t>
         </is>
       </c>
     </row>
@@ -6087,12 +6087,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>JDYPP20261021091347429</t>
+          <t>JDYPR261019112819B5781LKP1M</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>创建</t>
+          <t>已审核</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -6107,47 +6107,47 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026/10/21</t>
+          <t>2026/10/19</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>LKC0011S-BRN-CT</t>
+          <t>SPVYUB5781LKP1M</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>女士单肩包</t>
+          <t>午餐包</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>复古8056D#黑糖棕色/8050#欧洲蕨棕色/210#巧克力棕色/小号</t>
+          <t>127#浅粉色/126#酱红色/中号</t>
         </is>
       </c>
       <c r="J85" s="1" t="n">
-        <v>30</v>
+        <v>800</v>
       </c>
       <c r="K85" s="1" t="n">
-        <v>30</v>
+        <v>800</v>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>2026/11/15 00:00:00</t>
+          <t>2026/11/18 00:00:00</t>
         </is>
       </c>
       <c r="M85" s="1" t="n">
-        <v>30</v>
+        <v>800</v>
       </c>
       <c r="N85"/>
       <c r="O85" t="inlineStr">
         <is>
-          <t>庞新会</t>
+          <t>黄格格</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>新品</t>
+          <t>10月8号开始二推，备货至1月，1月日均49单备货，现在备货引流大小号</t>
         </is>
       </c>
     </row>
@@ -6159,7 +6159,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>JDYPP20261021091347035</t>
+          <t>JDYPR26102004152143LKP2L-T4</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -6179,47 +6179,47 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026/10/21</t>
+          <t>2026/10/20</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>LKC0011S-BRN-CT</t>
+          <t>SPVYMB4343LKP2L-T4</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>女士单肩包</t>
+          <t>旅行背包</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>复古8056D#黑糖棕色/8050#欧洲蕨棕色/210#巧克力棕色/小号</t>
+          <t>88#豆绿/86#米白色/171#深橄榄绿/17.3寸/四件套</t>
         </is>
       </c>
       <c r="J86" s="1" t="n">
-        <v>400</v>
+        <v>698</v>
       </c>
       <c r="K86" s="1" t="n">
-        <v>400</v>
+        <v>698</v>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>2026/11/16 00:00:00</t>
+          <t>2026/11/19 00:00:00</t>
         </is>
       </c>
       <c r="M86" s="1" t="n">
-        <v>400</v>
+        <v>698</v>
       </c>
       <c r="N86"/>
       <c r="O86" t="inlineStr">
         <is>
-          <t>姚鲜珍</t>
+          <t>何思琴</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>新品</t>
+          <t>11 12月系统预测日均偏低 平衡利库</t>
         </is>
       </c>
     </row>
@@ -6231,12 +6231,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>JDYPR261019112819B5781LKP1L</t>
+          <t>JDYPR2610200415213LK10XL-T4</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>已审核</t>
+          <t>创建</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -6251,22 +6251,22 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026/10/19</t>
+          <t>2026/10/20</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>SPVYUB5781LKP1L</t>
+          <t>SPVYMB4343LK10XL-T4</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>午餐包</t>
+          <t>旅行背包</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>127#浅粉色/126#酱红色/大号</t>
+          <t>33#黑色/4001黑色/18寸/四件套</t>
         </is>
       </c>
       <c r="J87" s="1" t="n">
@@ -6277,7 +6277,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>2026/11/18 00:00:00</t>
+          <t>2026/11/19 00:00:00</t>
         </is>
       </c>
       <c r="M87" s="1" t="n">
@@ -6286,12 +6286,12 @@
       <c r="N87"/>
       <c r="O87" t="inlineStr">
         <is>
-          <t>黄格格</t>
+          <t>何思琴</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>10月8号开始二推，备货至1月，1月日均49单备货，现在备货引流大小号</t>
+          <t>11 12月系统预测日均偏低</t>
         </is>
       </c>
     </row>
@@ -6303,12 +6303,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>JDYPR261019112819B5781LKP1M</t>
+          <t>JDYPR26102004152143LKP9L-T4</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>已审核</t>
+          <t>创建</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -6323,47 +6323,47 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026/10/19</t>
+          <t>2026/10/20</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>SPVYUB5781LKP1M</t>
+          <t>SPVYMB4343LKP9L-T4</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>午餐包</t>
+          <t>旅行背包</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>127#浅粉色/126#酱红色/中号</t>
+          <t>38#墨蓝/27#灰蓝色/4001#黑色/17.3寸/四件套</t>
         </is>
       </c>
       <c r="J88" s="1" t="n">
-        <v>800</v>
+        <v>100</v>
       </c>
       <c r="K88" s="1" t="n">
-        <v>800</v>
+        <v>100</v>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>2026/11/18 00:00:00</t>
+          <t>2026/11/19 00:00:00</t>
         </is>
       </c>
       <c r="M88" s="1" t="n">
-        <v>800</v>
+        <v>100</v>
       </c>
       <c r="N88"/>
       <c r="O88" t="inlineStr">
         <is>
-          <t>黄格格</t>
+          <t>何思琴</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>10月8号开始二推，备货至1月，1月日均49单备货，现在备货引流大小号</t>
+          <t>11 12月系统预测日均偏低</t>
         </is>
       </c>
     </row>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>JDYPR26102004152143LKP2L-T4</t>
+          <t>JDYPR26102004152143LKP4L-T4</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -6400,7 +6400,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>SPVYMB4343LKP2L-T4</t>
+          <t>SPVYMB4343LKP4L-T4</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -6410,14 +6410,14 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>88#豆绿/86#米白色/171#深橄榄绿/17.3寸/四件套</t>
+          <t>23#蓝紫色/4001#黑色/17.3寸/四件套</t>
         </is>
       </c>
       <c r="J89" s="1" t="n">
-        <v>698</v>
+        <v>150</v>
       </c>
       <c r="K89" s="1" t="n">
-        <v>698</v>
+        <v>150</v>
       </c>
       <c r="L89" t="inlineStr">
         <is>
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M89" s="1" t="n">
-        <v>698</v>
+        <v>150</v>
       </c>
       <c r="N89"/>
       <c r="O89" t="inlineStr">
@@ -6435,7 +6435,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>11 12月系统预测日均偏低 平衡利库</t>
+          <t>11 12月系统预测日均偏低</t>
         </is>
       </c>
     </row>
@@ -6447,7 +6447,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>JDYPR2610200415213LK10XL-T4</t>
+          <t>JDYPR26102004152143LKPFL-T4</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -6472,7 +6472,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>SPVYMB4343LK10XL-T4</t>
+          <t>SPVYMB4343LKPFL-T4</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -6482,7 +6482,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>33#黑色/4001黑色/18寸/四件套</t>
+          <t>34A黄棕色/62#米白色/4001黑色/17.3寸/四件套</t>
         </is>
       </c>
       <c r="J90" s="1" t="n">
@@ -6519,7 +6519,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>JDYPR26102004152143LKP9L-T4</t>
+          <t>JDYPR26102002082788LK40M-T2</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -6544,24 +6544,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>SPVYMB4343LKP9L-T4</t>
+          <t>SPVYMB5688LK40M-T2</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>旅行背包</t>
+          <t>妈咪包</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>38#墨蓝/27#灰蓝色/4001#黑色/17.3寸/四件套</t>
+          <t>250#驼绒棕/15.6寸/两件套</t>
         </is>
       </c>
       <c r="J91" s="1" t="n">
-        <v>100</v>
+        <v>800</v>
       </c>
       <c r="K91" s="1" t="n">
-        <v>100</v>
+        <v>800</v>
       </c>
       <c r="L91" t="inlineStr">
         <is>
@@ -6569,17 +6569,17 @@
         </is>
       </c>
       <c r="M91" s="1" t="n">
-        <v>100</v>
+        <v>800</v>
       </c>
       <c r="N91"/>
       <c r="O91" t="inlineStr">
         <is>
-          <t>何思琴</t>
+          <t>唐海阳</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>11 12月系统预测日均偏低</t>
+          <t>5688首批800单，日均最高能到40+，近一周毛利转正，均价能到40美金，再推广过程中棋盘格表现优秀，因此二推返单棋盘格做次卖色引流，并新增6个变体和2个大号变体，目前新增变体走变体流程下单</t>
         </is>
       </c>
     </row>
@@ -6591,7 +6591,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>JDYPR26102004152143LKP4L-T4</t>
+          <t>JDYPR26102002082788LK10M-T2</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6616,24 +6616,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>SPVYMB4343LKP4L-T4</t>
+          <t>SPVYMB5688LK10M-T2</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>旅行背包</t>
+          <t>妈咪包</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>23#蓝紫色/4001#黑色/17.3寸/四件套</t>
+          <t>1#黑色/15.6寸/两件套</t>
         </is>
       </c>
       <c r="J92" s="1" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="K92" s="1" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="L92" t="inlineStr">
         <is>
@@ -6641,17 +6641,17 @@
         </is>
       </c>
       <c r="M92" s="1" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="N92"/>
       <c r="O92" t="inlineStr">
         <is>
-          <t>何思琴</t>
+          <t>唐海阳</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>11 12月系统预测日均偏低</t>
+          <t>5688首批800单，日均最高能到40+，近一周毛利转正，均价能到40美金，再推广过程中棋盘格表现优秀，因此二推返单棋盘格做次卖色引流，并新增6个变体和2个大号变体，目前新增变体走变体流程下单</t>
         </is>
       </c>
     </row>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>JDYPR26102004152143LKPFL-T4</t>
+          <t>JDYPR26102002082788LK41M-T2</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6688,17 +6688,17 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>SPVYMB4343LKPFL-T4</t>
+          <t>SPVYMB5688LK41M-T2</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>旅行背包</t>
+          <t>妈咪包</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>34A黄棕色/62#米白色/4001黑色/17.3寸/四件套</t>
+          <t>120#苏丹棕/15.6寸/两件套</t>
         </is>
       </c>
       <c r="J93" s="1" t="n">
@@ -6718,12 +6718,12 @@
       <c r="N93"/>
       <c r="O93" t="inlineStr">
         <is>
-          <t>何思琴</t>
+          <t>唐海阳</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>11 12月系统预测日均偏低</t>
+          <t>5688首批800单，日均最高能到40+，近一周毛利转正，均价能到40美金，再推广过程中棋盘格表现优秀，因此二推返单棋盘格做次卖色引流，并新增6个变体和2个大号变体，目前新增变体走变体流程下单</t>
         </is>
       </c>
     </row>
@@ -6735,7 +6735,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>JDYPR26102002082788LK40M-T2</t>
+          <t>JDYPR26102002082788LKP1M-T2</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6760,7 +6760,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>SPVYMB5688LK40M-T2</t>
+          <t>SPVYMB5688LKP1M-T2</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6770,14 +6770,14 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>250#驼绒棕/15.6寸/两件套</t>
+          <t>白裸棋盘格/15.6寸/两件套</t>
         </is>
       </c>
       <c r="J94" s="1" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="K94" s="1" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="L94" t="inlineStr">
         <is>
@@ -6785,7 +6785,7 @@
         </is>
       </c>
       <c r="M94" s="1" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="N94"/>
       <c r="O94" t="inlineStr">
@@ -6807,17 +6807,17 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>JDYPR26102002082788LK10M-T2</t>
+          <t>LXPP261020076</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>创建</t>
+          <t>已审核</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026/10/21</t>
+          <t>2026/10/20</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -6832,42 +6832,42 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>SPVYMB5688LK10M-T2</t>
+          <t>VYWB2208LK23L</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>妈咪包</t>
+          <t>复古托特包</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>1#黑色/15.6寸/两件套</t>
+          <t>3#绿色/17.3寸</t>
         </is>
       </c>
       <c r="J95" s="1" t="n">
-        <v>200</v>
+        <v>350</v>
       </c>
       <c r="K95" s="1" t="n">
-        <v>200</v>
+        <v>350</v>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>2026/11/19 00:00:00</t>
+          <t>2026/10/20 00:00:00</t>
         </is>
       </c>
       <c r="M95" s="1" t="n">
-        <v>200</v>
+        <v>350</v>
       </c>
       <c r="N95"/>
       <c r="O95" t="inlineStr">
         <is>
-          <t>唐海阳</t>
+          <t>吴冠烨</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>5688首批800单，日均最高能到40+，近一周毛利转正，均价能到40美金，再推广过程中棋盘格表现优秀，因此二推返单棋盘格做次卖色引流，并新增6个变体和2个大号变体，目前新增变体走变体流程下单</t>
+          <t xml:space="preserve"> (SPVYWB2208LK23L平衡利库调拨，修改时间2026-10-21 12:05:06，调整前申请数量：350.0；调整后申请数量：345.0;)</t>
         </is>
       </c>
     </row>
@@ -6879,7 +6879,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>JDYPR26102002082788LK41M-T2</t>
+          <t>LXPP261020099</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026/10/21</t>
+          <t>2026/10/20</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -6904,44 +6904,40 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>SPVYMB5688LK41M-T2</t>
+          <t>SPVYWB4235LK20M-M1</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>妈咪包</t>
+          <t>电脑手提包</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>120#苏丹棕/15.6寸/两件套</t>
+          <t>4076#浅灰色/4076#浅灰色（压花）/15.6寸/两件套</t>
         </is>
       </c>
       <c r="J96" s="1" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="K96" s="1" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>2026/11/19 00:00:00</t>
+          <t>2026/10/20 00:00:00</t>
         </is>
       </c>
       <c r="M96" s="1" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="N96"/>
       <c r="O96" t="inlineStr">
         <is>
-          <t>唐海阳</t>
-        </is>
-      </c>
-      <c r="P96" t="inlineStr">
-        <is>
-          <t>5688首批800单，日均最高能到40+，近一周毛利转正，均价能到40美金，再推广过程中棋盘格表现优秀，因此二推返单棋盘格做次卖色引流，并新增6个变体和2个大号变体，目前新增变体走变体流程下单</t>
-        </is>
-      </c>
+          <t>吴冠烨</t>
+        </is>
+      </c>
+      <c r="P96"/>
     </row>
     <row r="97" customHeight="true" ht="15">
       <c r="A97" t="inlineStr">
@@ -6951,7 +6947,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>JDYPR26102002082788LKP1M-T2</t>
+          <t>LXPP261020100</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -6961,7 +6957,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026/10/21</t>
+          <t>2026/10/20</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -6976,44 +6972,40 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>SPVYMB5688LKP1M-T2</t>
+          <t>SPVYWB4235LK10M-M1</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>妈咪包</t>
+          <t>电脑手提包</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>白裸棋盘格/15.6寸/两件套</t>
+          <t>4001#黑色/4001#黑色（压花）/15.6寸/两件套</t>
         </is>
       </c>
       <c r="J97" s="1" t="n">
-        <v>600</v>
+        <v>250</v>
       </c>
       <c r="K97" s="1" t="n">
-        <v>600</v>
+        <v>250</v>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>2026/11/19 00:00:00</t>
+          <t>2026/10/20 00:00:00</t>
         </is>
       </c>
       <c r="M97" s="1" t="n">
-        <v>600</v>
+        <v>250</v>
       </c>
       <c r="N97"/>
       <c r="O97" t="inlineStr">
         <is>
-          <t>唐海阳</t>
-        </is>
-      </c>
-      <c r="P97" t="inlineStr">
-        <is>
-          <t>5688首批800单，日均最高能到40+，近一周毛利转正，均价能到40美金，再推广过程中棋盘格表现优秀，因此二推返单棋盘格做次卖色引流，并新增6个变体和2个大号变体，目前新增变体走变体流程下单</t>
-        </is>
-      </c>
+          <t>吴冠烨</t>
+        </is>
+      </c>
+      <c r="P97"/>
     </row>
     <row r="98" customHeight="true" ht="15">
       <c r="A98" t="inlineStr">
@@ -7023,7 +7015,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>LXPP261020099</t>
+          <t>LXPP261020096</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -7048,7 +7040,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>SPVYWB4235LK20M-M1</t>
+          <t>SPVYWB4235LK90M-T2</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -7058,14 +7050,14 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>4076#浅灰色/4076#浅灰色（压花）/15.6寸/两件套</t>
+          <t>7093#绿色/15.6寸/两件套</t>
         </is>
       </c>
       <c r="J98" s="1" t="n">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="K98" s="1" t="n">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="L98" t="inlineStr">
         <is>
@@ -7073,7 +7065,7 @@
         </is>
       </c>
       <c r="M98" s="1" t="n">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="N98"/>
       <c r="O98" t="inlineStr">
@@ -7091,7 +7083,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>LXPP261020100</t>
+          <t>LXPP261020097</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -7116,7 +7108,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>SPVYWB4235LK10M-M1</t>
+          <t>SPVYWB4235LKP8M-T2</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -7126,14 +7118,14 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>4001#黑色/4001#黑色（压花）/15.6寸/两件套</t>
+          <t>1010D米色/929#浅沙色/890#深咖色/15.6寸/两件套</t>
         </is>
       </c>
       <c r="J99" s="1" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="K99" s="1" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="L99" t="inlineStr">
         <is>
@@ -7141,7 +7133,7 @@
         </is>
       </c>
       <c r="M99" s="1" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="N99"/>
       <c r="O99" t="inlineStr">
@@ -7159,7 +7151,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>LXPP261020096</t>
+          <t>LXPP261020098</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -7184,7 +7176,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>SPVYWB4235LK90M-T2</t>
+          <t>SPVYWB4235LKP5M-T2</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -7194,7 +7186,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>7093#绿色/15.6寸/两件套</t>
+          <t>1010D米色/7166#墨绿色/4001#黑色/15.6寸/两件套</t>
         </is>
       </c>
       <c r="J100" s="1" t="n">
@@ -7227,7 +7219,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>LXPP261020097</t>
+          <t>LXPP261020094</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -7252,7 +7244,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>SPVYWB4235LKP8M-T2</t>
+          <t>SPVYWB4235LKP1M-T2</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -7262,14 +7254,14 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>1010D米色/929#浅沙色/890#深咖色/15.6寸/两件套</t>
+          <t>001#黑色/180#米色/138#棕色/15.6寸/两件套</t>
         </is>
       </c>
       <c r="J101" s="1" t="n">
-        <v>200</v>
+        <v>450</v>
       </c>
       <c r="K101" s="1" t="n">
-        <v>200</v>
+        <v>450</v>
       </c>
       <c r="L101" t="inlineStr">
         <is>
@@ -7277,7 +7269,7 @@
         </is>
       </c>
       <c r="M101" s="1" t="n">
-        <v>200</v>
+        <v>450</v>
       </c>
       <c r="N101"/>
       <c r="O101" t="inlineStr">
@@ -7295,7 +7287,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>LXPP261020098</t>
+          <t>LXPP261020105</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -7320,24 +7312,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>SPVYWB4235LKP5M-T2</t>
+          <t>SPVYMB5705LKP5L</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>电脑手提包</t>
+          <t>午餐电脑背包</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>1010D米色/7166#墨绿色/4001#黑色/15.6寸/两件套</t>
+          <t>86#米黄/13#粉色/8094#赤棕色/17.3寸</t>
         </is>
       </c>
       <c r="J102" s="1" t="n">
-        <v>100</v>
+        <v>36</v>
       </c>
       <c r="K102" s="1" t="n">
-        <v>100</v>
+        <v>36</v>
       </c>
       <c r="L102" t="inlineStr">
         <is>
@@ -7345,7 +7337,7 @@
         </is>
       </c>
       <c r="M102" s="1" t="n">
-        <v>100</v>
+        <v>36</v>
       </c>
       <c r="N102"/>
       <c r="O102" t="inlineStr">
@@ -7353,7 +7345,11 @@
           <t>吴冠烨</t>
         </is>
       </c>
-      <c r="P102"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> (SPVYMB5705LKP5L平衡利库调拨，修改时间2026-10-21 10:53:38，调整前申请数量：100.0；调整后申请数量：36.0;)</t>
+        </is>
+      </c>
     </row>
     <row r="103" customHeight="true" ht="15">
       <c r="A103" t="inlineStr">
@@ -7363,7 +7359,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>LXPP261020094</t>
+          <t>LXPP261020095</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -7388,7 +7384,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>SPVYWB4235LKP1M-T2</t>
+          <t>SPVYWB4235LKP1L-T2</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -7398,14 +7394,14 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>001#黑色/180#米色/138#棕色/15.6寸/两件套</t>
+          <t>1010D米色/4001#黑色/8119#棕色/17.3寸/两件套</t>
         </is>
       </c>
       <c r="J103" s="1" t="n">
-        <v>450</v>
+        <v>350</v>
       </c>
       <c r="K103" s="1" t="n">
-        <v>450</v>
+        <v>350</v>
       </c>
       <c r="L103" t="inlineStr">
         <is>
@@ -7413,7 +7409,7 @@
         </is>
       </c>
       <c r="M103" s="1" t="n">
-        <v>450</v>
+        <v>350</v>
       </c>
       <c r="N103"/>
       <c r="O103" t="inlineStr">
@@ -7431,7 +7427,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>LXPP261020105</t>
+          <t>LXPP261020101</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -7456,24 +7452,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>SPVYMB5705LKP5L</t>
+          <t>SPVYWB4235LK90L-T2</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>午餐电脑背包</t>
+          <t>电脑手提包</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>86#米黄/13#粉色/8094#赤棕色/17.3寸</t>
+          <t>7093绿色/7093绿色（压花）/17.3寸/两件套</t>
         </is>
       </c>
       <c r="J104" s="1" t="n">
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="K104" s="1" t="n">
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="L104" t="inlineStr">
         <is>
@@ -7481,7 +7477,7 @@
         </is>
       </c>
       <c r="M104" s="1" t="n">
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="N104"/>
       <c r="O104" t="inlineStr">
@@ -7489,11 +7485,7 @@
           <t>吴冠烨</t>
         </is>
       </c>
-      <c r="P104" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> (SPVYMB5705LKP5L平衡利库调拨，修改时间2026-10-21 10:53:38，调整前申请数量：100.0；调整后申请数量：36.0;)</t>
-        </is>
-      </c>
+      <c r="P104"/>
     </row>
     <row r="105" customHeight="true" ht="15">
       <c r="A105" t="inlineStr">
@@ -7503,12 +7495,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>LXPP261020095</t>
+          <t>LXPP261020077</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>创建</t>
+          <t>已审核</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -7528,24 +7520,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>SPVYWB4235LKP1L-T2</t>
+          <t>VYWB2208LK18L</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>电脑手提包</t>
+          <t>复古托特包</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>1010D米色/4001#黑色/8119#棕色/17.3寸/两件套</t>
+          <t>8#黄棕/17.3寸</t>
         </is>
       </c>
       <c r="J105" s="1" t="n">
-        <v>350</v>
+        <v>100</v>
       </c>
       <c r="K105" s="1" t="n">
-        <v>350</v>
+        <v>100</v>
       </c>
       <c r="L105" t="inlineStr">
         <is>
@@ -7553,7 +7545,7 @@
         </is>
       </c>
       <c r="M105" s="1" t="n">
-        <v>350</v>
+        <v>100</v>
       </c>
       <c r="N105"/>
       <c r="O105" t="inlineStr">
@@ -7571,12 +7563,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>LXPP261020101</t>
+          <t>LXPP261020078</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>创建</t>
+          <t>已审核</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -7596,24 +7588,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>SPVYWB4235LK90L-T2</t>
+          <t>VYWB2208LK10L</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>电脑手提包</t>
+          <t>复古托特包</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>7093绿色/7093绿色（压花）/17.3寸/两件套</t>
+          <t>1#黑色(压花)/17.3寸</t>
         </is>
       </c>
       <c r="J106" s="1" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="K106" s="1" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="L106" t="inlineStr">
         <is>
@@ -7621,7 +7613,7 @@
         </is>
       </c>
       <c r="M106" s="1" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="N106"/>
       <c r="O106" t="inlineStr">
@@ -13958,14 +13950,14 @@
       <c r="H195"/>
       <c r="I195"/>
       <c r="J195" s="1" t="n">
-        <v>32516</v>
+        <v>32916</v>
       </c>
       <c r="K195" s="1" t="n">
-        <v>32516</v>
+        <v>32916</v>
       </c>
       <c r="L195"/>
       <c r="M195" s="1" t="n">
-        <v>30616</v>
+        <v>31016</v>
       </c>
       <c r="N195" s="1" t="n">
         <v>1900</v>

--- a/src/otd_apply.xlsx
+++ b/src/otd_apply.xlsx
@@ -9839,17 +9839,17 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>JDYPR26101511293796LK90M-T4</t>
+          <t>JDYPR26101303340831LK42L-M1</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>已审核</t>
+          <t>创建</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026/10/15</t>
+          <t>2026/10/13</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -9859,49 +9859,47 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026/10/15</t>
+          <t>2026/10/13</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>SPVYMB4496LK90M-T4</t>
+          <t>SPVYUB5631LK42L-M1</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>旅行背包</t>
+          <t>午餐包</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>156#绿色/中号/四件套</t>
+          <t>复古8089#黄棕色（压花）/复古8089#黄棕色/大号/两件套</t>
         </is>
       </c>
       <c r="J138" s="1" t="n">
-        <v>194</v>
+        <v>100</v>
       </c>
       <c r="K138" s="1" t="n">
-        <v>194</v>
+        <v>100</v>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>2026/11/14 00:00:00</t>
+          <t>2026/11/12 00:00:00</t>
         </is>
       </c>
       <c r="M138" s="1" t="n">
-        <v>-6</v>
-      </c>
-      <c r="N138" s="1" t="n">
-        <v>200</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="N138"/>
       <c r="O138" t="inlineStr">
         <is>
-          <t>吴颖</t>
+          <t>唐海阳</t>
         </is>
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>旺季销量上涨(SPVYMB4496LK90M-T4平衡利库调拨，修改时间2026-10-21 17:16:45，调整前申请数量：200.0；调整后申请数量：194.0;)</t>
+          <t>5631近期2推表现符合预期，补充活动消耗的库存，避免年底大流量结束后库存缺失导致断货</t>
         </is>
       </c>
     </row>
@@ -9913,7 +9911,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>JDYPR26101303340831LK42L-M1</t>
+          <t>JDYPR26101303340831LK40L-T2</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -9938,7 +9936,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>SPVYUB5631LK42L-M1</t>
+          <t>SPVYUB5631LK40L-T2</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -9948,14 +9946,14 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>复古8089#黄棕色（压花）/复古8089#黄棕色/大号/两件套</t>
+          <t>12#焦糖棕/大号/两件套</t>
         </is>
       </c>
       <c r="J139" s="1" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="K139" s="1" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="L139" t="inlineStr">
         <is>
@@ -9963,7 +9961,7 @@
         </is>
       </c>
       <c r="M139" s="1" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="N139"/>
       <c r="O139" t="inlineStr">
@@ -9985,7 +9983,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>JDYPR26101303340831LK40L-T2</t>
+          <t>JDYPR26101303340831LK40M-T2</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -10010,7 +10008,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>SPVYUB5631LK40L-T2</t>
+          <t>SPVYUB5631LK40M-T2</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -10020,14 +10018,14 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>12#焦糖棕/大号/两件套</t>
+          <t>12#焦糖棕/中号/两件套</t>
         </is>
       </c>
       <c r="J140" s="1" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="K140" s="1" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="L140" t="inlineStr">
         <is>
@@ -10035,7 +10033,7 @@
         </is>
       </c>
       <c r="M140" s="1" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="N140"/>
       <c r="O140" t="inlineStr">
@@ -10057,7 +10055,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>JDYPR26101303340831LK40M-T2</t>
+          <t>JDYPR26101303323231LK42M-M1</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -10082,7 +10080,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>SPVYUB5631LK40M-T2</t>
+          <t>SPVYUB5631LK42M-M1</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -10092,7 +10090,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>12#焦糖棕/中号/两件套</t>
+          <t>复古8089#黄棕色（压花）/复古8089#黄棕色/中号/两件套</t>
         </is>
       </c>
       <c r="J141" s="1" t="n">
@@ -10129,12 +10127,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>JDYPR26101303323231LK42M-M1</t>
+          <t>JDYPR26101310142069LK30S-V1</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>创建</t>
+          <t>重新审核</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -10149,47 +10147,47 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026/10/13</t>
+          <t>2026/10/12</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>SPVYUB5631LK42M-M1</t>
+          <t>VYWB4069LK30S-V1</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>午餐包</t>
+          <t>女式挎包</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>复古8089#黄棕色（压花）/复古8089#黄棕色/中号/两件套</t>
+          <t>52#湛蓝/11寸/(更换挂饰)</t>
         </is>
       </c>
       <c r="J142" s="1" t="n">
-        <v>250</v>
+        <v>50</v>
       </c>
       <c r="K142" s="1" t="n">
-        <v>250</v>
+        <v>50</v>
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>2026/11/12 00:00:00</t>
+          <t>2026/10/15 00:00:00</t>
         </is>
       </c>
       <c r="M142" s="1" t="n">
-        <v>250</v>
+        <v>50</v>
       </c>
       <c r="N142"/>
       <c r="O142" t="inlineStr">
         <is>
-          <t>唐海阳</t>
+          <t>符琪</t>
         </is>
       </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>5631近期2推表现符合预期，补充活动消耗的库存，避免年底大流量结束后库存缺失导致断货</t>
+          <t>加急出货</t>
         </is>
       </c>
     </row>
@@ -10201,17 +10199,17 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>JDYPR26101310142069LK30S-V1</t>
+          <t>JDYPR261010074303B4416LK10M</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>重新审核</t>
+          <t>已审核</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026/10/13</t>
+          <t>2026/10/11</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -10221,47 +10219,47 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026/10/12</t>
+          <t>2026/10/10</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>VYWB4069LK30S-V1</t>
+          <t>SPVYUB4416LK10M</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>女式挎包</t>
+          <t>拉杆箱</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>52#湛蓝/11寸/(更换挂饰)</t>
+          <t>48#黑色/小号</t>
         </is>
       </c>
       <c r="J143" s="1" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="K143" s="1" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>2026/10/15 00:00:00</t>
+          <t>2026/11/9 00:00:00</t>
         </is>
       </c>
       <c r="M143" s="1" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="N143"/>
       <c r="O143" t="inlineStr">
         <is>
-          <t>符琪</t>
+          <t>姚鲜珍</t>
         </is>
       </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>加急出货</t>
+          <t>常规备货（做货周期长）</t>
         </is>
       </c>
     </row>
@@ -10273,7 +10271,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>JDYPR261010074303B4416LK10M</t>
+          <t>JDYPR261010074303B4416LKP5M</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -10298,7 +10296,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>SPVYUB4416LK10M</t>
+          <t>SPVYUB4416LKP5M</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -10308,14 +10306,14 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>48#黑色/小号</t>
+          <t>213#米白/284#卡其/小号</t>
         </is>
       </c>
       <c r="J144" s="1" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K144" s="1" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L144" t="inlineStr">
         <is>
@@ -10323,7 +10321,7 @@
         </is>
       </c>
       <c r="M144" s="1" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="N144"/>
       <c r="O144" t="inlineStr">
@@ -10345,7 +10343,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>JDYPR261010074303B4416LKP5M</t>
+          <t>JDYPR26101007430316LK90M-X1</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -10370,7 +10368,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>SPVYUB4416LKP5M</t>
+          <t>SPVYUB4416LK90M-X1</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -10380,14 +10378,14 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>213#米白/284#卡其/小号</t>
+          <t>72#深绿色(菱形格绣线)/小号</t>
         </is>
       </c>
       <c r="J145" s="1" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="K145" s="1" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="L145" t="inlineStr">
         <is>
@@ -10395,7 +10393,7 @@
         </is>
       </c>
       <c r="M145" s="1" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="N145"/>
       <c r="O145" t="inlineStr">
@@ -10417,7 +10415,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>JDYPR26101007430316LK90M-X1</t>
+          <t>JDYPR261010074303B4416LKP1M</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -10442,7 +10440,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>SPVYUB4416LK90M-X1</t>
+          <t>SPVYUB4416LKP1M</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -10452,14 +10450,14 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>72#深绿色(菱形格绣线)/小号</t>
+          <t>4125-pvc-黑色/73#米白/8123D#板栗棕/小号</t>
         </is>
       </c>
       <c r="J146" s="1" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="K146" s="1" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="L146" t="inlineStr">
         <is>
@@ -10467,7 +10465,7 @@
         </is>
       </c>
       <c r="M146" s="1" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="N146"/>
       <c r="O146" t="inlineStr">
@@ -10489,7 +10487,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>JDYPR261010074303B4416LKP1M</t>
+          <t>JDYPR261010074303B4416LKP2M</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -10514,7 +10512,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>SPVYUB4416LKP1M</t>
+          <t>SPVYUB4416LKP2M</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -10524,14 +10522,14 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>4125-pvc-黑色/73#米白/8123D#板栗棕/小号</t>
+          <t>4125-pvc-黑色/8123D#板栗棕/小号</t>
         </is>
       </c>
       <c r="J147" s="1" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="K147" s="1" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="L147" t="inlineStr">
         <is>
@@ -10539,7 +10537,7 @@
         </is>
       </c>
       <c r="M147" s="1" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="N147"/>
       <c r="O147" t="inlineStr">
@@ -10561,17 +10559,17 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>JDYPR261010074303B4416LKP2M</t>
+          <t>JDYPR26100904101312LK80M-C1</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>已审核</t>
+          <t>创建</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026/10/11</t>
+          <t>2026/10/9</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -10581,37 +10579,37 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>2026/10/10</t>
+          <t>2026/10/9</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>SPVYUB4416LKP2M</t>
+          <t>SPVYWB1512LK80M-C1</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>拉杆箱</t>
+          <t>圆顶贝壳包</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>4125-pvc-黑色/8123D#板栗棕/小号</t>
+          <t>8089#黄棕色（压花）/中号</t>
         </is>
       </c>
       <c r="J148" s="1" t="n">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="K148" s="1" t="n">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>2026/11/9 00:00:00</t>
+          <t>2026/11/8 00:00:00</t>
         </is>
       </c>
       <c r="M148" s="1" t="n">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="N148"/>
       <c r="O148" t="inlineStr">
@@ -10621,7 +10619,7 @@
       </c>
       <c r="P148" t="inlineStr">
         <is>
-          <t>常规备货（做货周期长）</t>
+          <t>常规补货</t>
         </is>
       </c>
     </row>
@@ -10633,7 +10631,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>JDYPR26100904101312LK80M-C1</t>
+          <t>JDYPR261009041013B1512LK29M</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -10658,7 +10656,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>SPVYWB1512LK80M-C1</t>
+          <t>SPVYWB1512LK29M</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -10668,14 +10666,14 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>8089#黄棕色（压花）/中号</t>
+          <t>186#裸色</t>
         </is>
       </c>
       <c r="J149" s="1" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="K149" s="1" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L149" t="inlineStr">
         <is>
@@ -10683,7 +10681,7 @@
         </is>
       </c>
       <c r="M149" s="1" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="N149"/>
       <c r="O149" t="inlineStr">
@@ -10693,7 +10691,7 @@
       </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>常规补货</t>
+          <t>常规补货(SPVYWB1512LK29M平衡利库调拨，修改时间2026-10-21 10:58:04，调整前申请数量：100.0；调整后申请数量：98.0;)</t>
         </is>
       </c>
     </row>
@@ -10705,7 +10703,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>JDYPR261009041013B1512LK29M</t>
+          <t>JDYPR261009041013B1512LK10L</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -10730,7 +10728,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>SPVYWB1512LK29M</t>
+          <t>SPVYWB1512LK10L</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -10740,14 +10738,14 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>186#裸色</t>
+          <t>11#大红色/大号</t>
         </is>
       </c>
       <c r="J150" s="1" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="K150" s="1" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L150" t="inlineStr">
         <is>
@@ -10755,7 +10753,7 @@
         </is>
       </c>
       <c r="M150" s="1" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="N150"/>
       <c r="O150" t="inlineStr">
@@ -10765,7 +10763,7 @@
       </c>
       <c r="P150" t="inlineStr">
         <is>
-          <t>常规补货(SPVYWB1512LK29M平衡利库调拨，修改时间2026-10-21 10:58:04，调整前申请数量：100.0；调整后申请数量：98.0;)</t>
+          <t>常规补货</t>
         </is>
       </c>
     </row>
@@ -10777,7 +10775,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>JDYPR261009041013B1512LK10L</t>
+          <t>JDYPR261009041013B1512LK18M</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -10802,7 +10800,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>SPVYWB1512LK10L</t>
+          <t>SPVYWB1512LK18M</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -10812,7 +10810,7 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>11#大红色/大号</t>
+          <t>棕色</t>
         </is>
       </c>
       <c r="J151" s="1" t="n">
@@ -10849,7 +10847,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>JDYPR261009041013B1512LK18M</t>
+          <t>JDYPR261009041013B1512LK06M</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -10874,7 +10872,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>SPVYWB1512LK18M</t>
+          <t>SPVYWB1512LK06M</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -10884,7 +10882,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>棕色</t>
+          <t>深蓝</t>
         </is>
       </c>
       <c r="J152" s="1" t="n">
@@ -10921,7 +10919,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>JDYPR261009041013B1512LK06M</t>
+          <t>JDYPR261009041013B1512LK04M</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -10946,7 +10944,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>SPVYWB1512LK06M</t>
+          <t>SPVYWB1512LK04M</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -10956,7 +10954,7 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>深蓝</t>
+          <t>米白配粉色</t>
         </is>
       </c>
       <c r="J153" s="1" t="n">
@@ -10993,7 +10991,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>JDYPR261009041013B1512LK04M</t>
+          <t>JDYPR261009041013B1512LK03M</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -11018,7 +11016,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>SPVYWB1512LK04M</t>
+          <t>SPVYWB1512LK03M</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -11028,7 +11026,7 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>米白配粉色</t>
+          <t>米色配黑色</t>
         </is>
       </c>
       <c r="J154" s="1" t="n">
@@ -11065,7 +11063,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>JDYPR261009041013B1512LK03M</t>
+          <t>JDYPR261009041013B1512LK01M</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -11090,7 +11088,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>SPVYWB1512LK03M</t>
+          <t>SPVYWB1512LK01M</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -11100,14 +11098,14 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>米色配黑色</t>
+          <t>黑色</t>
         </is>
       </c>
       <c r="J155" s="1" t="n">
-        <v>100</v>
+        <v>176</v>
       </c>
       <c r="K155" s="1" t="n">
-        <v>100</v>
+        <v>176</v>
       </c>
       <c r="L155" t="inlineStr">
         <is>
@@ -11115,7 +11113,7 @@
         </is>
       </c>
       <c r="M155" s="1" t="n">
-        <v>100</v>
+        <v>176</v>
       </c>
       <c r="N155"/>
       <c r="O155" t="inlineStr">
@@ -11125,29 +11123,29 @@
       </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t>常规补货</t>
+          <t>常规补货(SPVYWB1512LK01M平衡利库调拨，修改时间2026-10-21 10:56:47，调整前申请数量：200.0；调整后申请数量：176.0;)</t>
         </is>
       </c>
     </row>
     <row r="156" customHeight="true" ht="15">
       <c r="A156" t="inlineStr">
         <is>
-          <t>kd</t>
+          <t>江海霞</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>JDYPR261009041013B1512LK01M</t>
+          <t>CGSQ005274</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>创建</t>
+          <t>重新审核</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026/10/9</t>
+          <t>2026/9/10</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -11157,47 +11155,47 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026/10/9</t>
+          <t>2026/9/10</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>SPVYWB1512LK01M</t>
+          <t>VYGJZ011203</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>圆顶贝壳包</t>
+          <t>定制无纺布袋</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>黑色</t>
+          <t>定制无纺布袋</t>
         </is>
       </c>
       <c r="J156" s="1" t="n">
-        <v>176</v>
+        <v>70</v>
       </c>
       <c r="K156" s="1" t="n">
-        <v>176</v>
+        <v>70</v>
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>2026/11/8 00:00:00</t>
+          <t>2026/9/10 00:00:00</t>
         </is>
       </c>
       <c r="M156" s="1" t="n">
-        <v>176</v>
+        <v>70</v>
       </c>
       <c r="N156"/>
       <c r="O156" t="inlineStr">
         <is>
-          <t>姚鲜珍</t>
+          <t>江海霞</t>
         </is>
       </c>
       <c r="P156" t="inlineStr">
         <is>
-          <t>常规补货(SPVYWB1512LK01M平衡利库调拨，修改时间2026-10-21 10:56:47，调整前申请数量：200.0；调整后申请数量：176.0;)</t>
+          <t>国际站</t>
         </is>
       </c>
     </row>
@@ -11209,7 +11207,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>CGSQ005274</t>
+          <t>CGSQ005272</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -11248,10 +11246,10 @@
         </is>
       </c>
       <c r="J157" s="1" t="n">
-        <v>70</v>
+        <v>520</v>
       </c>
       <c r="K157" s="1" t="n">
-        <v>70</v>
+        <v>520</v>
       </c>
       <c r="L157" t="inlineStr">
         <is>
@@ -11259,7 +11257,7 @@
         </is>
       </c>
       <c r="M157" s="1" t="n">
-        <v>70</v>
+        <v>520</v>
       </c>
       <c r="N157"/>
       <c r="O157" t="inlineStr">
@@ -11276,104 +11274,32 @@
     <row r="158" customHeight="true" ht="15">
       <c r="A158" t="inlineStr">
         <is>
-          <t>江海霞</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>CGSQ005272</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>重新审核</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>2026/9/10</t>
-        </is>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>未关闭</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>2026/9/10</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>VYGJZ011203</t>
-        </is>
-      </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>定制无纺布袋</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>定制无纺布袋</t>
-        </is>
-      </c>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="B158"/>
+      <c r="C158"/>
+      <c r="D158"/>
+      <c r="E158"/>
+      <c r="F158"/>
+      <c r="G158"/>
+      <c r="H158"/>
+      <c r="I158"/>
       <c r="J158" s="1" t="n">
-        <v>520</v>
+        <v>25788</v>
       </c>
       <c r="K158" s="1" t="n">
-        <v>520</v>
-      </c>
-      <c r="L158" t="inlineStr">
-        <is>
-          <t>2026/9/10 00:00:00</t>
-        </is>
-      </c>
+        <v>25788</v>
+      </c>
+      <c r="L158"/>
       <c r="M158" s="1" t="n">
-        <v>520</v>
-      </c>
-      <c r="N158"/>
-      <c r="O158" t="inlineStr">
-        <is>
-          <t>江海霞</t>
-        </is>
-      </c>
-      <c r="P158" t="inlineStr">
-        <is>
-          <t>国际站</t>
-        </is>
-      </c>
-    </row>
-    <row r="159" customHeight="true" ht="15">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>合计</t>
-        </is>
-      </c>
-      <c r="B159"/>
-      <c r="C159"/>
-      <c r="D159"/>
-      <c r="E159"/>
-      <c r="F159"/>
-      <c r="G159"/>
-      <c r="H159"/>
-      <c r="I159"/>
-      <c r="J159" s="1" t="n">
-        <v>25982</v>
-      </c>
-      <c r="K159" s="1" t="n">
-        <v>25982</v>
-      </c>
-      <c r="L159"/>
-      <c r="M159" s="1" t="n">
-        <v>25782</v>
-      </c>
-      <c r="N159" s="1" t="n">
-        <v>200</v>
-      </c>
-      <c r="O159"/>
-      <c r="P159"/>
+        <v>25788</v>
+      </c>
+      <c r="N158" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O158"/>
+      <c r="P158"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/otd_apply.xlsx
+++ b/src/otd_apply.xlsx
@@ -5779,7 +5779,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>JDYPR261026122052B3033LK03M</t>
+          <t>JDYPP20261027075417616</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5799,22 +5799,22 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026/10/26</t>
+          <t>2026/10/27</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>SPVYUB3033LK03M</t>
+          <t>SPLK6135L-AP-T2</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>箱开式旅行包</t>
+          <t>旅行背包</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>73#白色/001#黑色</t>
+          <t>HYH02#豹纹/18寸/两件套</t>
         </is>
       </c>
       <c r="J82" s="1" t="n">
@@ -5825,7 +5825,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>2026/11/25 00:00:00</t>
+          <t>2026/11/30 00:00:00</t>
         </is>
       </c>
       <c r="M82" s="1" t="n">
@@ -5834,12 +5834,12 @@
       <c r="N82"/>
       <c r="O82" t="inlineStr">
         <is>
-          <t>李晓玲</t>
+          <t>陈剑军</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>利润变体少量补货(SPVYUB3033LK03M平衡利库调拨，修改时间2026-10-28 11:03:24，调整前申请数量：100.0；调整后申请数量：93.0;)</t>
+          <t>新品</t>
         </is>
       </c>
     </row>
@@ -5851,7 +5851,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>JDYPP20261027075417616</t>
+          <t>JDYPP20261027075417205</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>SPLK6135L-AP-T2</t>
+          <t>SPLK6135L-GN-T2</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>HYH02#豹纹/18寸/两件套</t>
+          <t>05#灰绿色/18寸/两件套</t>
         </is>
       </c>
       <c r="J83" s="1" t="n">
@@ -5923,7 +5923,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>JDYPP20261027075417205</t>
+          <t>JDYPP20261027075416792</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5948,7 +5948,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>SPLK6135L-GN-T2</t>
+          <t>SPLK6135L-BRN-T2</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5958,14 +5958,14 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>05#灰绿色/18寸/两件套</t>
+          <t>09#咖色/18寸/两件套</t>
         </is>
       </c>
       <c r="J84" s="1" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="K84" s="1" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L84" t="inlineStr">
         <is>
@@ -5973,7 +5973,7 @@
         </is>
       </c>
       <c r="M84" s="1" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N84"/>
       <c r="O84" t="inlineStr">
@@ -5995,7 +5995,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>JDYPP20261027075416792</t>
+          <t>JDYPP20261027075416382</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -6020,7 +6020,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>SPLK6135L-BRN-T2</t>
+          <t>SPLK6135L-BLK-T2</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -6030,7 +6030,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>09#咖色/18寸/两件套</t>
+          <t>01#黑色/18寸/两件套</t>
         </is>
       </c>
       <c r="J85" s="1" t="n">
@@ -6067,7 +6067,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>JDYPP20261027075416382</t>
+          <t>JDYPP20261027075415973</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -6092,7 +6092,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>SPLK6135L-BLK-T2</t>
+          <t>SPLK6135M-KH-T2</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -6102,14 +6102,14 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>01#黑色/18寸/两件套</t>
+          <t>08#裸色/17寸/两件套</t>
         </is>
       </c>
       <c r="J86" s="1" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K86" s="1" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L86" t="inlineStr">
         <is>
@@ -6117,7 +6117,7 @@
         </is>
       </c>
       <c r="M86" s="1" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="N86"/>
       <c r="O86" t="inlineStr">
@@ -6139,7 +6139,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>JDYPP20261027075415973</t>
+          <t>JDYPP20261027075415561</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -6164,7 +6164,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>SPLK6135M-KH-T2</t>
+          <t>SPLK6135M-BLU-T2</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>08#裸色/17寸/两件套</t>
+          <t>04#深蓝色/17寸/两件套</t>
         </is>
       </c>
       <c r="J87" s="1" t="n">
@@ -6211,7 +6211,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>JDYPP20261027075415561</t>
+          <t>JDYPP20261027075415151</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>SPLK6135M-BLU-T2</t>
+          <t>SPLK6135M-GN01-T2</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -6246,14 +6246,14 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>04#深蓝色/17寸/两件套</t>
+          <t>19#橄榄绿色/17寸/两件套</t>
         </is>
       </c>
       <c r="J88" s="1" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="K88" s="1" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L88" t="inlineStr">
         <is>
@@ -6261,7 +6261,7 @@
         </is>
       </c>
       <c r="M88" s="1" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N88"/>
       <c r="O88" t="inlineStr">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>JDYPP20261027075415151</t>
+          <t>JDYPP20261027075414740</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -6308,7 +6308,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>SPLK6135M-GN01-T2</t>
+          <t>SPLK6135M-GY-T2</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -6318,14 +6318,14 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>19#橄榄绿色/17寸/两件套</t>
+          <t>03#中灰色/17寸/两件套</t>
         </is>
       </c>
       <c r="J89" s="1" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K89" s="1" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L89" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="M89" s="1" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="N89"/>
       <c r="O89" t="inlineStr">
@@ -6355,7 +6355,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>JDYPP20261027075414740</t>
+          <t>JDYPP20261027075414330</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -6380,7 +6380,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>SPLK6135M-GY-T2</t>
+          <t>SPLK6135M-PK-T2</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -6390,7 +6390,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>03#中灰色/17寸/两件套</t>
+          <t>02#浅粉色/17寸/两件套</t>
         </is>
       </c>
       <c r="J90" s="1" t="n">
@@ -6427,7 +6427,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>JDYPP20261027075414330</t>
+          <t>JDYPP20261027075413919</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -6452,7 +6452,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>SPLK6135M-PK-T2</t>
+          <t>SPLK6135M-BLU-CT-T2</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -6462,14 +6462,14 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>02#浅粉色/17寸/两件套</t>
+          <t>17#浅蓝色/04#深蓝色/09#灰蓝色/17寸/两件套</t>
         </is>
       </c>
       <c r="J91" s="1" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="K91" s="1" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="L91" t="inlineStr">
         <is>
@@ -6477,7 +6477,7 @@
         </is>
       </c>
       <c r="M91" s="1" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="N91"/>
       <c r="O91" t="inlineStr">
@@ -6499,7 +6499,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>JDYPP20261027075413919</t>
+          <t>JDYPP20261027075413508</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>SPLK6135M-BLU-CT-T2</t>
+          <t>SPLK6135M-KH-CB-T2</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6534,14 +6534,14 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>17#浅蓝色/04#深蓝色/09#灰蓝色/17寸/两件套</t>
+          <t>21#米黄色/13#卡其色/17寸/两件套</t>
         </is>
       </c>
       <c r="J92" s="1" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="K92" s="1" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="L92" t="inlineStr">
         <is>
@@ -6549,7 +6549,7 @@
         </is>
       </c>
       <c r="M92" s="1" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="N92"/>
       <c r="O92" t="inlineStr">
@@ -6571,7 +6571,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>JDYPP20261027075413508</t>
+          <t>JDYPP20261027075413097</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6596,7 +6596,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>SPLK6135M-KH-CB-T2</t>
+          <t>SPLK6135M-AP-T2</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6606,14 +6606,14 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>21#米黄色/13#卡其色/17寸/两件套</t>
+          <t>HYH02#豹纹/17寸/两件套</t>
         </is>
       </c>
       <c r="J93" s="1" t="n">
-        <v>200</v>
+        <v>650</v>
       </c>
       <c r="K93" s="1" t="n">
-        <v>200</v>
+        <v>650</v>
       </c>
       <c r="L93" t="inlineStr">
         <is>
@@ -6621,7 +6621,7 @@
         </is>
       </c>
       <c r="M93" s="1" t="n">
-        <v>200</v>
+        <v>650</v>
       </c>
       <c r="N93"/>
       <c r="O93" t="inlineStr">
@@ -6643,7 +6643,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>JDYPP20261027075413097</t>
+          <t>JDYPP20261027075412687</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6668,7 +6668,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>SPLK6135M-AP-T2</t>
+          <t>SPLK6135M-GN-T2</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6678,14 +6678,14 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>HYH02#豹纹/17寸/两件套</t>
+          <t>05#灰绿色/17寸/两件套</t>
         </is>
       </c>
       <c r="J94" s="1" t="n">
-        <v>650</v>
+        <v>400</v>
       </c>
       <c r="K94" s="1" t="n">
-        <v>650</v>
+        <v>400</v>
       </c>
       <c r="L94" t="inlineStr">
         <is>
@@ -6693,7 +6693,7 @@
         </is>
       </c>
       <c r="M94" s="1" t="n">
-        <v>650</v>
+        <v>400</v>
       </c>
       <c r="N94"/>
       <c r="O94" t="inlineStr">
@@ -6715,7 +6715,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>JDYPP20261027075412687</t>
+          <t>JDYPP20261027075412276</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6740,7 +6740,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>SPLK6135M-GN-T2</t>
+          <t>SPLK6135M-BRN01-T2</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6750,14 +6750,14 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>05#灰绿色/17寸/两件套</t>
+          <t>16#咖色/17寸/两件套</t>
         </is>
       </c>
       <c r="J95" s="1" t="n">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="K95" s="1" t="n">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="L95" t="inlineStr">
         <is>
@@ -6765,7 +6765,7 @@
         </is>
       </c>
       <c r="M95" s="1" t="n">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="N95"/>
       <c r="O95" t="inlineStr">
@@ -6787,7 +6787,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>JDYPP20261027075412276</t>
+          <t>JDYPP20261027075411863</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -6812,7 +6812,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>SPLK6135M-BRN01-T2</t>
+          <t>SPLK6135M-BRN-T2</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6822,14 +6822,14 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>16#咖色/17寸/两件套</t>
+          <t>09#咖色/17寸/两件套</t>
         </is>
       </c>
       <c r="J96" s="1" t="n">
-        <v>100</v>
+        <v>1500</v>
       </c>
       <c r="K96" s="1" t="n">
-        <v>100</v>
+        <v>1500</v>
       </c>
       <c r="L96" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         </is>
       </c>
       <c r="M96" s="1" t="n">
-        <v>100</v>
+        <v>1500</v>
       </c>
       <c r="N96"/>
       <c r="O96" t="inlineStr">
@@ -6859,7 +6859,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>JDYPP20261027075411863</t>
+          <t>JDYPP20261027075411447</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>SPLK6135M-BRN-T2</t>
+          <t>SPLK6135M-BLK-T2</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6894,14 +6894,14 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>09#咖色/17寸/两件套</t>
+          <t>01#黑色/17寸/两件套</t>
         </is>
       </c>
       <c r="J97" s="1" t="n">
-        <v>1500</v>
+        <v>1800</v>
       </c>
       <c r="K97" s="1" t="n">
-        <v>1500</v>
+        <v>1800</v>
       </c>
       <c r="L97" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
         </is>
       </c>
       <c r="M97" s="1" t="n">
-        <v>1500</v>
+        <v>1800</v>
       </c>
       <c r="N97"/>
       <c r="O97" t="inlineStr">
@@ -6931,12 +6931,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>JDYPP20261027075411447</t>
+          <t>JDYPR261026122533B4191LK10M</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>已审核</t>
+          <t>审核中</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -6951,47 +6951,47 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026/10/27</t>
+          <t>2026/10/26</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>SPLK6135M-BLK-T2</t>
+          <t>SPVYWB4191LK10M</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>旅行背包</t>
+          <t>电脑手提包</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>01#黑色/17寸/两件套</t>
+          <t>4001#黑色/15.6寸</t>
         </is>
       </c>
       <c r="J98" s="1" t="n">
-        <v>1800</v>
+        <v>1500</v>
       </c>
       <c r="K98" s="1" t="n">
-        <v>1800</v>
+        <v>1500</v>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>2026/11/30 00:00:00</t>
+          <t>2026/11/25 00:00:00</t>
         </is>
       </c>
       <c r="M98" s="1" t="n">
-        <v>1800</v>
+        <v>1500</v>
       </c>
       <c r="N98"/>
       <c r="O98" t="inlineStr">
         <is>
-          <t>陈剑军</t>
+          <t>李晓玲</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>新品</t>
+          <t>9月断货，日均数据有误，目前日均100+，且11-12月旺季，销量会增长较多，目前引流变体日均50，库存不足，需要补货</t>
         </is>
       </c>
     </row>
@@ -7003,12 +7003,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>JDYPR261026122533B4191LK10M</t>
+          <t>JDYPR26102610482056LK01M-Q3</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>审核中</t>
+          <t>已审核</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -7028,24 +7028,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>SPVYWB4191LK10M</t>
+          <t>SPVYUB1856LK01M-Q3</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>电脑手提包</t>
+          <t>轻便旅行背包</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>4001#黑色/15.6寸</t>
+          <t>1#黑色/无密码锁/无USB</t>
         </is>
       </c>
       <c r="J99" s="1" t="n">
-        <v>1500</v>
+        <v>100</v>
       </c>
       <c r="K99" s="1" t="n">
-        <v>1500</v>
+        <v>100</v>
       </c>
       <c r="L99" t="inlineStr">
         <is>
@@ -7053,19 +7053,15 @@
         </is>
       </c>
       <c r="M99" s="1" t="n">
-        <v>1500</v>
+        <v>100</v>
       </c>
       <c r="N99"/>
       <c r="O99" t="inlineStr">
         <is>
-          <t>李晓玲</t>
-        </is>
-      </c>
-      <c r="P99" t="inlineStr">
-        <is>
-          <t>9月断货，日均数据有误，目前日均100+，且11-12月旺季，销量会增长较多，目前引流变体日均50，库存不足，需要补货</t>
-        </is>
-      </c>
+          <t>方思媛</t>
+        </is>
+      </c>
+      <c r="P99"/>
     </row>
     <row r="100" customHeight="true" ht="15">
       <c r="A100" t="inlineStr">
@@ -7075,7 +7071,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>JDYPR26102610482056LK01M-Q3</t>
+          <t>JDYPR26102610482056LK01S-Q3</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -7100,7 +7096,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>SPVYUB1856LK01M-Q3</t>
+          <t>SPVYUB1856LK01S-Q3</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -7110,7 +7106,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>1#黑色/无密码锁/无USB</t>
+          <t>1#黑色/15.6寸/无密码锁/无USB</t>
         </is>
       </c>
       <c r="J100" s="1" t="n">
@@ -7143,7 +7139,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>JDYPR26102610482056LK01S-Q3</t>
+          <t>JDYPR26102610482056LK09M-Q3</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -7168,7 +7164,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>SPVYUB1856LK01S-Q3</t>
+          <t>SPVYUB1856LK09M-Q3</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -7178,7 +7174,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>1#黑色/15.6寸/无密码锁/无USB</t>
+          <t>14#酒红色/无密码锁/无USB</t>
         </is>
       </c>
       <c r="J101" s="1" t="n">
@@ -7211,7 +7207,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>JDYPR26102610482056LK09M-Q3</t>
+          <t>JDYPR26102610431556LK31M-Q3</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -7236,7 +7232,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>SPVYUB1856LK09M-Q3</t>
+          <t>SPVYUB1856LK31M-Q3</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -7246,7 +7242,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>14#酒红色/无密码锁/无USB</t>
+          <t>24#灰色/无密码锁/无USB</t>
         </is>
       </c>
       <c r="J102" s="1" t="n">
@@ -7279,7 +7275,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>JDYPR26102610431556LK31M-Q3</t>
+          <t>JDYPR26102610431556LK05M-Q3</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -7304,7 +7300,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>SPVYUB1856LK31M-Q3</t>
+          <t>SPVYUB1856LK05M-Q3</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -7314,7 +7310,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>24#灰色/无密码锁/无USB</t>
+          <t>24#藏蓝色/无密码锁/无USB</t>
         </is>
       </c>
       <c r="J103" s="1" t="n">
@@ -7347,7 +7343,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>JDYPR26102610431556LK05M-Q3</t>
+          <t>JDYPR26102610431556LK01L-Q3</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -7372,7 +7368,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>SPVYUB1856LK05M-Q3</t>
+          <t>SPVYUB1856LK01L-Q3</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -7382,14 +7378,14 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>24#藏蓝色/无密码锁/无USB</t>
+          <t>1#黑色/18寸/无密码锁/无USB</t>
         </is>
       </c>
       <c r="J104" s="1" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="K104" s="1" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L104" t="inlineStr">
         <is>
@@ -7397,7 +7393,7 @@
         </is>
       </c>
       <c r="M104" s="1" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N104"/>
       <c r="O104" t="inlineStr">
@@ -7415,7 +7411,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>JDYPR26102610431556LK01L-Q3</t>
+          <t>JDYPP20261027034552928</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -7435,22 +7431,22 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026/10/26</t>
+          <t>2026/10/27</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>SPVYUB1856LK01L-Q3</t>
+          <t>SPVYWB6007LKP8M</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>轻便旅行背包</t>
+          <t>电脑公文包</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>1#黑色/18寸/无密码锁/无USB</t>
+          <t>HYH02#豹纹/8176#深咖啡色/大号</t>
         </is>
       </c>
       <c r="J105" s="1" t="n">
@@ -7461,7 +7457,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>2026/11/25 00:00:00</t>
+          <t>2026/11/26 00:00:00</t>
         </is>
       </c>
       <c r="M105" s="1" t="n">
@@ -7470,10 +7466,14 @@
       <c r="N105"/>
       <c r="O105" t="inlineStr">
         <is>
-          <t>方思媛</t>
-        </is>
-      </c>
-      <c r="P105"/>
+          <t>姚鲜珍</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>新变体</t>
+        </is>
+      </c>
     </row>
     <row r="106" customHeight="true" ht="15">
       <c r="A106" t="inlineStr">
@@ -7483,7 +7483,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>JDYPP20261027034552928</t>
+          <t>JDYPP20261027012840161</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -7508,42 +7508,42 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>SPVYWB6007LKP8M</t>
+          <t>SPLK6632L-BLK-T4</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>电脑公文包</t>
+          <t>旅行背包</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>HYH02#豹纹/8176#深咖啡色/大号</t>
+          <t>01#黑色/17.3寸/四件套</t>
         </is>
       </c>
       <c r="J106" s="1" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K106" s="1" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>2026/11/26 00:00:00</t>
+          <t>2026/12/13 00:00:00</t>
         </is>
       </c>
       <c r="M106" s="1" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="N106"/>
       <c r="O106" t="inlineStr">
         <is>
-          <t>姚鲜珍</t>
+          <t>李子遥</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>新变体</t>
+          <t>新品</t>
         </is>
       </c>
     </row>
@@ -7555,7 +7555,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>JDYPP20261027012840161</t>
+          <t>JDYPP20261027012839771</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -7580,7 +7580,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>SPLK6632L-BLK-T4</t>
+          <t>SPLK6632L-PL-CT-T4</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -7590,7 +7590,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>01#黑色/17.3寸/四件套</t>
+          <t>38#葡萄紫色/31#浅粉色/01#黑色/17.3寸/四件套</t>
         </is>
       </c>
       <c r="J107" s="1" t="n">
@@ -7627,7 +7627,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>JDYPP20261027012839771</t>
+          <t>JDYPP20261027012839353</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -7652,7 +7652,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>SPLK6632L-PL-CT-T4</t>
+          <t>SPLK6632L-GN-CT-T4</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7662,7 +7662,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>38#葡萄紫色/31#浅粉色/01#黑色/17.3寸/四件套</t>
+          <t>06#薄荷绿色/35#米白色/01#黑色/17.3寸/四件套</t>
         </is>
       </c>
       <c r="J108" s="1" t="n">
@@ -7699,7 +7699,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>JDYPP20261027012839353</t>
+          <t>JDYPP20261027012838945</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -7724,7 +7724,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>SPLK6632L-GN-CT-T4</t>
+          <t>SPLK6632L-BLU-CT-T4</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7734,14 +7734,14 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>06#薄荷绿色/35#米白色/01#黑色/17.3寸/四件套</t>
+          <t>85#湖蓝色/04#蓝灰色/01#黑色/17.3寸/四件套</t>
         </is>
       </c>
       <c r="J109" s="1" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="K109" s="1" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="L109" t="inlineStr">
         <is>
@@ -7749,7 +7749,7 @@
         </is>
       </c>
       <c r="M109" s="1" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="N109"/>
       <c r="O109" t="inlineStr">
@@ -7771,7 +7771,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>JDYPP20261027012838945</t>
+          <t>JDYPP20261027012838514</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -7796,7 +7796,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>SPLK6632L-BLU-CT-T4</t>
+          <t>SPLK6632M-PL-CT-T4</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7806,14 +7806,14 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>85#湖蓝色/04#蓝灰色/01#黑色/17.3寸/四件套</t>
+          <t>38#葡萄紫色/31#浅粉色/01#黑色/15.6寸/四件套</t>
         </is>
       </c>
       <c r="J110" s="1" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="K110" s="1" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="L110" t="inlineStr">
         <is>
@@ -7821,7 +7821,7 @@
         </is>
       </c>
       <c r="M110" s="1" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="N110"/>
       <c r="O110" t="inlineStr">
@@ -7843,7 +7843,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>JDYPP20261027012838514</t>
+          <t>JDYPP20261027012838021</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -7868,7 +7868,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>SPLK6632M-PL-CT-T4</t>
+          <t>SPLK6632M-GN-CT-T4</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7878,14 +7878,14 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>38#葡萄紫色/31#浅粉色/01#黑色/15.6寸/四件套</t>
+          <t>06#薄荷绿色/35#米白色/01#黑色/15.6寸/四件套</t>
         </is>
       </c>
       <c r="J111" s="1" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="K111" s="1" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="L111" t="inlineStr">
         <is>
@@ -7893,7 +7893,7 @@
         </is>
       </c>
       <c r="M111" s="1" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="N111"/>
       <c r="O111" t="inlineStr">
@@ -7915,7 +7915,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>JDYPP20261027012838021</t>
+          <t>JDYPP20261027012837623</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -7940,7 +7940,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>SPLK6632M-GN-CT-T4</t>
+          <t>SPLK6632M-BLU01-CT-T4</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7950,14 +7950,14 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>06#薄荷绿色/35#米白色/01#黑色/15.6寸/四件套</t>
+          <t>24#浅蓝色/35#米白色/29#灰色/15.6寸/四件套</t>
         </is>
       </c>
       <c r="J112" s="1" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="K112" s="1" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="L112" t="inlineStr">
         <is>
@@ -7965,7 +7965,7 @@
         </is>
       </c>
       <c r="M112" s="1" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="N112"/>
       <c r="O112" t="inlineStr">
@@ -7987,7 +7987,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>JDYPP20261027012837623</t>
+          <t>JDYPP20261027012837188</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -8012,7 +8012,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>SPLK6632M-BLU01-CT-T4</t>
+          <t>SPLK6632M-GN-CB-T4</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -8022,7 +8022,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>24#浅蓝色/35#米白色/29#灰色/15.6寸/四件套</t>
+          <t>86#浅绿色/30#深绿色/29#灰色/15.6寸/四件套</t>
         </is>
       </c>
       <c r="J113" s="1" t="n">
@@ -8059,7 +8059,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>JDYPP20261027012837188</t>
+          <t>JDYPP20261027012836761</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -8084,7 +8084,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>SPLK6632M-GN-CB-T4</t>
+          <t>SPLK6632M-KH-CT-T4</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -8094,7 +8094,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>86#浅绿色/30#深绿色/29#灰色/15.6寸/四件套</t>
+          <t>08#卡其色/67#浅卡其色/115#咖色/15.6寸/四件套</t>
         </is>
       </c>
       <c r="J114" s="1" t="n">
@@ -8131,7 +8131,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>JDYPP20261027012836761</t>
+          <t>JDYPP20261027012836295</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>SPLK6632M-KH-CT-T4</t>
+          <t>SPLK6632M-YW-CT-T4</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>08#卡其色/67#浅卡其色/115#咖色/15.6寸/四件套</t>
+          <t>62#淡黄色/03#米白色/116#绿色/15.6寸/四件套</t>
         </is>
       </c>
       <c r="J115" s="1" t="n">
@@ -8203,7 +8203,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>JDYPP20261027012836295</t>
+          <t>JDYPP20261027012835900</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>SPLK6632M-YW-CT-T4</t>
+          <t>SPLK6632M-BLK-T4</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -8238,14 +8238,14 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>62#淡黄色/03#米白色/116#绿色/15.6寸/四件套</t>
+          <t>01#黑色/15.6寸/四件套</t>
         </is>
       </c>
       <c r="J116" s="1" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="K116" s="1" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="L116" t="inlineStr">
         <is>
@@ -8253,7 +8253,7 @@
         </is>
       </c>
       <c r="M116" s="1" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="N116"/>
       <c r="O116" t="inlineStr">
@@ -8275,7 +8275,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>JDYPP20261027012835900</t>
+          <t>JDYPP20261027012835310</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -8300,7 +8300,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>SPLK6632M-BLK-T4</t>
+          <t>SPLK6632M-BLU-CT-T4</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -8310,14 +8310,14 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>01#黑色/15.6寸/四件套</t>
+          <t>85#湖蓝色/04#蓝灰色/01#黑色/15.6寸/四件套</t>
         </is>
       </c>
       <c r="J117" s="1" t="n">
-        <v>300</v>
+        <v>1700</v>
       </c>
       <c r="K117" s="1" t="n">
-        <v>300</v>
+        <v>1700</v>
       </c>
       <c r="L117" t="inlineStr">
         <is>
@@ -8325,7 +8325,7 @@
         </is>
       </c>
       <c r="M117" s="1" t="n">
-        <v>300</v>
+        <v>1700</v>
       </c>
       <c r="N117"/>
       <c r="O117" t="inlineStr">
@@ -8347,7 +8347,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>JDYPP20261027012835310</t>
+          <t>JDYPP20261026103848342</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -8357,7 +8357,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026/10/27</t>
+          <t>2026/10/26</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -8367,47 +8367,47 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026/10/27</t>
+          <t>2026/10/26</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>SPLK6632M-BLU-CT-T4</t>
+          <t>VYWB3013LK51M-T2</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>旅行背包</t>
+          <t>手提电脑包</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>85#湖蓝色/04#蓝灰色/01#黑色/15.6寸/四件套</t>
+          <t>2390#晚红色/15.6寸/两件套</t>
         </is>
       </c>
       <c r="J118" s="1" t="n">
-        <v>1700</v>
+        <v>100</v>
       </c>
       <c r="K118" s="1" t="n">
-        <v>1700</v>
+        <v>100</v>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>2026/12/13 00:00:00</t>
+          <t>2026/12/7 00:00:00</t>
         </is>
       </c>
       <c r="M118" s="1" t="n">
-        <v>1700</v>
+        <v>100</v>
       </c>
       <c r="N118"/>
       <c r="O118" t="inlineStr">
         <is>
-          <t>李子遥</t>
+          <t>邹娇</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>新品</t>
+          <t>新变体</t>
         </is>
       </c>
     </row>
@@ -8419,12 +8419,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>JDYPP20261026103848342</t>
+          <t>JDYPR261023115047B5089LK41L</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>已审核</t>
+          <t>审核中</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -8439,47 +8439,47 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026/10/26</t>
+          <t>2026/10/23</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>VYWB3013LK51M-T2</t>
+          <t>VYWB5089LK41L</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>手提电脑包</t>
+          <t>电脑手提包</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>2390#晚红色/15.6寸/两件套</t>
+          <t>8105#秋叶棕色/17.3寸</t>
         </is>
       </c>
       <c r="J119" s="1" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="K119" s="1" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>2026/12/7 00:00:00</t>
+          <t>2026/10/23 00:00:00</t>
         </is>
       </c>
       <c r="M119" s="1" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="N119"/>
       <c r="O119" t="inlineStr">
         <is>
-          <t>邹娇</t>
+          <t>王琦</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>新变体</t>
+          <t>新增大号变体，运营何思琴</t>
         </is>
       </c>
     </row>
@@ -8491,7 +8491,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>JDYPR261023115047B5089LK41L</t>
+          <t>JDYPR261023115047B5089LK20L</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -8516,7 +8516,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>VYWB5089LK41L</t>
+          <t>VYWB5089LK20L</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -8526,7 +8526,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>8105#秋叶棕色/17.3寸</t>
+          <t>4012#驼灰色/17.3寸</t>
         </is>
       </c>
       <c r="J120" s="1" t="n">
@@ -8563,7 +8563,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>JDYPR261023115047B5089LK20L</t>
+          <t>JDYPR261023115047B5089LK00L</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -8588,7 +8588,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>VYWB5089LK20L</t>
+          <t>VYWB5089LK00L</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -8598,7 +8598,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>4012#驼灰色/17.3寸</t>
+          <t>9006#米杏色/17.3寸</t>
         </is>
       </c>
       <c r="J121" s="1" t="n">
@@ -8635,17 +8635,17 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>JDYPR261023115047B5089LK00L</t>
+          <t>LXPP261023001</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>审核中</t>
+          <t>已审核</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026/10/26</t>
+          <t>2026/10/23</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -8660,24 +8660,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>VYWB5089LK00L</t>
+          <t>SPVYMB2023LK03S</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>电脑手提包</t>
+          <t>搭盖时尚背包</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>9006#米杏色/17.3寸</t>
+          <t>23#黑色/211#红棕色/14寸</t>
         </is>
       </c>
       <c r="J122" s="1" t="n">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="K122" s="1" t="n">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="L122" t="inlineStr">
         <is>
@@ -8685,19 +8685,15 @@
         </is>
       </c>
       <c r="M122" s="1" t="n">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="N122"/>
       <c r="O122" t="inlineStr">
         <is>
-          <t>王琦</t>
-        </is>
-      </c>
-      <c r="P122" t="inlineStr">
-        <is>
-          <t>新增大号变体，运营何思琴</t>
-        </is>
-      </c>
+          <t>吴冠烨</t>
+        </is>
+      </c>
+      <c r="P122"/>
     </row>
     <row r="123" customHeight="true" ht="15">
       <c r="A123" t="inlineStr">
@@ -8707,7 +8703,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>LXPP261023001</t>
+          <t>LXPP261021009</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -8717,7 +8713,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026/10/23</t>
+          <t>2026/10/22</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -8727,42 +8723,42 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026/10/23</t>
+          <t>2026/10/21</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>SPVYMB2023LK03S</t>
+          <t>SPVYWB5368LK10L</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>搭盖时尚背包</t>
+          <t>电脑手提包</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>23#黑色/211#红棕色/14寸</t>
+          <t>01#黑色/17.3寸</t>
         </is>
       </c>
       <c r="J123" s="1" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="K123" s="1" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>2026/10/23 00:00:00</t>
+          <t>2026/11/20 00:00:00</t>
         </is>
       </c>
       <c r="M123" s="1" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="N123"/>
       <c r="O123" t="inlineStr">
         <is>
-          <t>吴冠烨</t>
+          <t>庞新会</t>
         </is>
       </c>
       <c r="P123"/>
@@ -8775,7 +8771,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>LXPP261021009</t>
+          <t>LXPP261021010</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -8800,7 +8796,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>SPVYWB5368LK10L</t>
+          <t>SPVYWB5368LK41L</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -8810,7 +8806,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>01#黑色/17.3寸</t>
+          <t>27#焦糖棕/17.3寸</t>
         </is>
       </c>
       <c r="J124" s="1" t="n">
@@ -8843,17 +8839,17 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>LXPP261021010</t>
+          <t>JDYPP20261021091400998</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>已审核</t>
+          <t>创建</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026/10/22</t>
+          <t>2026/10/21</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -8868,32 +8864,32 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>SPVYWB5368LK41L</t>
+          <t>LKC0011M-BLK</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>电脑手提包</t>
+          <t>女士单肩包</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>27#焦糖棕/17.3寸</t>
+          <t>复古01#黑色/中号</t>
         </is>
       </c>
       <c r="J125" s="1" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="K125" s="1" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>2026/11/20 00:00:00</t>
+          <t>2026/11/15 00:00:00</t>
         </is>
       </c>
       <c r="M125" s="1" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="N125"/>
       <c r="O125" t="inlineStr">
@@ -8901,7 +8897,11 @@
           <t>庞新会</t>
         </is>
       </c>
-      <c r="P125"/>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>新品</t>
+        </is>
+      </c>
     </row>
     <row r="126" customHeight="true" ht="15">
       <c r="A126" t="inlineStr">
@@ -8911,7 +8911,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>JDYPP20261021091400998</t>
+          <t>JDYPP20261021091400581</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -8957,7 +8957,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>2026/11/15 00:00:00</t>
+          <t>2026/11/16 00:00:00</t>
         </is>
       </c>
       <c r="M126" s="1" t="n">
@@ -8966,7 +8966,7 @@
       <c r="N126"/>
       <c r="O126" t="inlineStr">
         <is>
-          <t>庞新会</t>
+          <t>姚鲜珍</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
@@ -8983,7 +8983,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>JDYPP20261021091400581</t>
+          <t>JDYPP20261021091400183</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -9008,7 +9008,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>LKC0011M-BLK</t>
+          <t>LKC0011S-BLK</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -9018,27 +9018,27 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>复古01#黑色/中号</t>
+          <t>复古01#黑色/小号</t>
         </is>
       </c>
       <c r="J127" s="1" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="K127" s="1" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>2026/11/16 00:00:00</t>
+          <t>2026/11/15 00:00:00</t>
         </is>
       </c>
       <c r="M127" s="1" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="N127"/>
       <c r="O127" t="inlineStr">
         <is>
-          <t>姚鲜珍</t>
+          <t>庞新会</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
@@ -9055,7 +9055,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>JDYPP20261021091400183</t>
+          <t>JDYPP20261021091359782</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -9094,23 +9094,23 @@
         </is>
       </c>
       <c r="J128" s="1" t="n">
-        <v>20</v>
+        <v>150</v>
       </c>
       <c r="K128" s="1" t="n">
-        <v>20</v>
+        <v>150</v>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>2026/11/15 00:00:00</t>
+          <t>2026/11/16 00:00:00</t>
         </is>
       </c>
       <c r="M128" s="1" t="n">
-        <v>20</v>
+        <v>150</v>
       </c>
       <c r="N128"/>
       <c r="O128" t="inlineStr">
         <is>
-          <t>庞新会</t>
+          <t>姚鲜珍</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
@@ -9127,7 +9127,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>JDYPP20261021091359782</t>
+          <t>JDYPP20261021091359398</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -9152,7 +9152,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>LKC0011S-BLK</t>
+          <t>LKC0011M-AP02</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -9162,14 +9162,14 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>复古01#黑色/小号</t>
+          <t>07#豹纹/41#深咖色/中号</t>
         </is>
       </c>
       <c r="J129" s="1" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="K129" s="1" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="L129" t="inlineStr">
         <is>
@@ -9177,7 +9177,7 @@
         </is>
       </c>
       <c r="M129" s="1" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="N129"/>
       <c r="O129" t="inlineStr">
@@ -9199,7 +9199,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>JDYPP20261021091359398</t>
+          <t>JDYPP20261021091359013</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>LKC0011M-AP02</t>
+          <t>LKC0011M-PA</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -9232,9 +9232,9 @@
           <t>女士单肩包</t>
         </is>
       </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>07#豹纹/41#深咖色/中号</t>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t>=8021D#咖色老花/220#深棕色/中号</t>
         </is>
       </c>
       <c r="J130" s="1" t="n">
@@ -9271,7 +9271,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>JDYPP20261021091359013</t>
+          <t>JDYPP20261021091358613</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -9296,7 +9296,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>LKC0011M-PA</t>
+          <t>LKC0011S-PA</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -9304,9 +9304,9 @@
           <t>女士单肩包</t>
         </is>
       </c>
-      <c r="I131" s="2" t="inlineStr">
-        <is>
-          <t>=8021D#咖色老花/220#深棕色/中号</t>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>8021D#咖色老花/220#深棕色/小号</t>
         </is>
       </c>
       <c r="J131" s="1" t="n">
@@ -9343,7 +9343,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>JDYPP20261021091358613</t>
+          <t>JDYPP20261021091358212</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -9368,7 +9368,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>LKC0011S-PA</t>
+          <t>LKC0011M-GN01-C1</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -9378,27 +9378,27 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>8021D#咖色老花/220#深棕色/小号</t>
+          <t>复古7093#绿色（压花）/7093#绿色/中号</t>
         </is>
       </c>
       <c r="J132" s="1" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="K132" s="1" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>2026/11/16 00:00:00</t>
+          <t>2026/11/15 00:00:00</t>
         </is>
       </c>
       <c r="M132" s="1" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="N132"/>
       <c r="O132" t="inlineStr">
         <is>
-          <t>姚鲜珍</t>
+          <t>庞新会</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
@@ -9415,7 +9415,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>JDYPP20261021091358212</t>
+          <t>JDYPP20261021091357775</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -9461,7 +9461,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>2026/11/15 00:00:00</t>
+          <t>2026/11/16 00:00:00</t>
         </is>
       </c>
       <c r="M133" s="1" t="n">
@@ -9470,7 +9470,7 @@
       <c r="N133"/>
       <c r="O133" t="inlineStr">
         <is>
-          <t>庞新会</t>
+          <t>洪佳佩</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
@@ -9487,7 +9487,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>JDYPP20261021091357775</t>
+          <t>JDYPP20261021091357381</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -9512,7 +9512,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>LKC0011M-GN01-C1</t>
+          <t>LKC0011M-BRN03-C1</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -9522,7 +9522,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>复古7093#绿色（压花）/7093#绿色/中号</t>
+          <t>复古8089#黄棕色（压花）/8089#黄棕色/中号</t>
         </is>
       </c>
       <c r="J134" s="1" t="n">
@@ -9533,7 +9533,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>2026/11/16 00:00:00</t>
+          <t>2026/11/15 00:00:00</t>
         </is>
       </c>
       <c r="M134" s="1" t="n">
@@ -9542,7 +9542,7 @@
       <c r="N134"/>
       <c r="O134" t="inlineStr">
         <is>
-          <t>洪佳佩</t>
+          <t>庞新会</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
@@ -9559,7 +9559,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>JDYPP20261021091357381</t>
+          <t>JDYPP20261021091356941</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -9605,7 +9605,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>2026/11/15 00:00:00</t>
+          <t>2026/11/16 00:00:00</t>
         </is>
       </c>
       <c r="M135" s="1" t="n">
@@ -9614,7 +9614,7 @@
       <c r="N135"/>
       <c r="O135" t="inlineStr">
         <is>
-          <t>庞新会</t>
+          <t>洪佳佩</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
@@ -9631,7 +9631,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>JDYPP20261021091356941</t>
+          <t>JDYPP20261021091356515</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -9656,7 +9656,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>LKC0011M-BRN03-C1</t>
+          <t>LKC0011M-AP01</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -9666,7 +9666,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>复古8089#黄棕色（压花）/8089#黄棕色/中号</t>
+          <t>9065#河狸毛皮色/中号</t>
         </is>
       </c>
       <c r="J136" s="1" t="n">
@@ -9686,7 +9686,7 @@
       <c r="N136"/>
       <c r="O136" t="inlineStr">
         <is>
-          <t>洪佳佩</t>
+          <t>姚鲜珍</t>
         </is>
       </c>
       <c r="P136" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>JDYPP20261021091356515</t>
+          <t>JDYPP20261021091355678</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -9728,7 +9728,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>LKC0011M-AP01</t>
+          <t>LKC0011M-AP</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -9738,27 +9738,27 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>9065#河狸毛皮色/中号</t>
+          <t>8014#冰咖啡色（豹纹）/8050#深棕色/中号</t>
         </is>
       </c>
       <c r="J137" s="1" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="K137" s="1" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>2026/11/16 00:00:00</t>
+          <t>2026/11/15 00:00:00</t>
         </is>
       </c>
       <c r="M137" s="1" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="N137"/>
       <c r="O137" t="inlineStr">
         <is>
-          <t>姚鲜珍</t>
+          <t>庞新会</t>
         </is>
       </c>
       <c r="P137" t="inlineStr">
@@ -9775,7 +9775,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>JDYPP20261021091355678</t>
+          <t>JDYPP20261021091355266</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -9814,23 +9814,23 @@
         </is>
       </c>
       <c r="J138" s="1" t="n">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="K138" s="1" t="n">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>2026/11/15 00:00:00</t>
+          <t>2026/11/16 00:00:00</t>
         </is>
       </c>
       <c r="M138" s="1" t="n">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="N138"/>
       <c r="O138" t="inlineStr">
         <is>
-          <t>庞新会</t>
+          <t>洪佳佩</t>
         </is>
       </c>
       <c r="P138" t="inlineStr">
@@ -9847,7 +9847,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>JDYPP20261021091355266</t>
+          <t>JDYPP20261021091354825</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -9886,10 +9886,10 @@
         </is>
       </c>
       <c r="J139" s="1" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="K139" s="1" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="L139" t="inlineStr">
         <is>
@@ -9897,12 +9897,12 @@
         </is>
       </c>
       <c r="M139" s="1" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="N139"/>
       <c r="O139" t="inlineStr">
         <is>
-          <t>洪佳佩</t>
+          <t>姚鲜珍</t>
         </is>
       </c>
       <c r="P139" t="inlineStr">
@@ -9919,7 +9919,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>JDYPP20261021091354825</t>
+          <t>JDYPP20261021091354415</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>LKC0011M-AP</t>
+          <t>LKC0011S-AP</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -9954,27 +9954,27 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>8014#冰咖啡色（豹纹）/8050#深棕色/中号</t>
+          <t>8014#冰咖啡色（豹纹）/8050#深棕色/小号</t>
         </is>
       </c>
       <c r="J140" s="1" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="K140" s="1" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>2026/11/16 00:00:00</t>
+          <t>2026/11/15 00:00:00</t>
         </is>
       </c>
       <c r="M140" s="1" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="N140"/>
       <c r="O140" t="inlineStr">
         <is>
-          <t>姚鲜珍</t>
+          <t>庞新会</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
@@ -9991,7 +9991,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>JDYPP20261021091354415</t>
+          <t>JDYPP20261021091354006</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -10030,23 +10030,23 @@
         </is>
       </c>
       <c r="J141" s="1" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="K141" s="1" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>2026/11/15 00:00:00</t>
+          <t>2026/11/16 00:00:00</t>
         </is>
       </c>
       <c r="M141" s="1" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="N141"/>
       <c r="O141" t="inlineStr">
         <is>
-          <t>庞新会</t>
+          <t>洪佳佩</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
@@ -10063,7 +10063,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>JDYPP20261021091354006</t>
+          <t>JDYPP20261021091353562</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -10118,7 +10118,7 @@
       <c r="N142"/>
       <c r="O142" t="inlineStr">
         <is>
-          <t>洪佳佩</t>
+          <t>姚鲜珍</t>
         </is>
       </c>
       <c r="P142" t="inlineStr">
@@ -10135,7 +10135,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>JDYPP20261021091353562</t>
+          <t>JDYPP20261021091353155</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -10160,7 +10160,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>LKC0011S-AP</t>
+          <t>LKC0011M-BRN02</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -10170,7 +10170,7 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>8014#冰咖啡色（豹纹）/8050#深棕色/小号</t>
+          <t>复古09#栗棕色/中号</t>
         </is>
       </c>
       <c r="J143" s="1" t="n">
@@ -10190,7 +10190,7 @@
       <c r="N143"/>
       <c r="O143" t="inlineStr">
         <is>
-          <t>姚鲜珍</t>
+          <t>洪佳佩</t>
         </is>
       </c>
       <c r="P143" t="inlineStr">
@@ -10207,7 +10207,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>JDYPP20261021091353155</t>
+          <t>JDYPP20261021091352720</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -10262,7 +10262,7 @@
       <c r="N144"/>
       <c r="O144" t="inlineStr">
         <is>
-          <t>洪佳佩</t>
+          <t>姚鲜珍</t>
         </is>
       </c>
       <c r="P144" t="inlineStr">
@@ -10279,7 +10279,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>JDYPP20261021091352720</t>
+          <t>JDYPP20261021091352285</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>LKC0011M-BRN02</t>
+          <t>LKC0011S-BRN02</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -10314,14 +10314,14 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>复古09#栗棕色/中号</t>
+          <t>复古09#栗棕色/小号</t>
         </is>
       </c>
       <c r="J145" s="1" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K145" s="1" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L145" t="inlineStr">
         <is>
@@ -10329,7 +10329,7 @@
         </is>
       </c>
       <c r="M145" s="1" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N145"/>
       <c r="O145" t="inlineStr">
@@ -10351,7 +10351,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>JDYPP20261021091352285</t>
+          <t>JDYPP20261021091351857</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -10376,7 +10376,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>LKC0011S-BRN02</t>
+          <t>LKC0011M-GN-CT</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -10386,7 +10386,7 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>复古09#栗棕色/小号</t>
+          <t>复古22#军绿色/7935#深绿色/210#巧克力棕色/中号</t>
         </is>
       </c>
       <c r="J146" s="1" t="n">
@@ -10423,7 +10423,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>JDYPP20261021091351857</t>
+          <t>JDYPP20261021091351431</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -10448,7 +10448,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>LKC0011M-GN-CT</t>
+          <t>LKC0011S-GN-CT</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -10458,7 +10458,7 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>复古22#军绿色/7935#深绿色/210#巧克力棕色/中号</t>
+          <t>复古22#军绿色/7935#深绿色/210#巧克力棕色/小号</t>
         </is>
       </c>
       <c r="J147" s="1" t="n">
@@ -10495,7 +10495,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>JDYPP20261021091351431</t>
+          <t>JDYPP20261021091351005</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -10520,7 +10520,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>LKC0011S-GN-CT</t>
+          <t>LKC0011M-RD-CT</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -10530,14 +10530,14 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>复古22#军绿色/7935#深绿色/210#巧克力棕色/小号</t>
+          <t>复古2435#安道尔红色/2387#红壁色/402P珠光酒红色/中号</t>
         </is>
       </c>
       <c r="J148" s="1" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="K148" s="1" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="L148" t="inlineStr">
         <is>
@@ -10545,7 +10545,7 @@
         </is>
       </c>
       <c r="M148" s="1" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="N148"/>
       <c r="O148" t="inlineStr">
@@ -10567,7 +10567,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>JDYPP20261021091351005</t>
+          <t>JDYPP20261021091350580</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -10592,7 +10592,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>LKC0011M-RD-CT</t>
+          <t>LKC0011S-RD-CT</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -10602,14 +10602,14 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>复古2435#安道尔红色/2387#红壁色/402P珠光酒红色/中号</t>
+          <t>复古2435#安道尔红色/2387#红壁色/402P珠光酒红色/小号</t>
         </is>
       </c>
       <c r="J149" s="1" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K149" s="1" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L149" t="inlineStr">
         <is>
@@ -10617,7 +10617,7 @@
         </is>
       </c>
       <c r="M149" s="1" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N149"/>
       <c r="O149" t="inlineStr">
@@ -10639,7 +10639,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>JDYPP20261021091350580</t>
+          <t>JDYPP20261021091350183</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -10664,7 +10664,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>LKC0011S-RD-CT</t>
+          <t>LKC0011M-BRN01-CT</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -10674,14 +10674,14 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>复古2435#安道尔红色/2387#红壁色/402P珠光酒红色/小号</t>
+          <t>复古8025#红土陶色/8027D#玳瑁色/203#浅咖色/中号</t>
         </is>
       </c>
       <c r="J150" s="1" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="K150" s="1" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="L150" t="inlineStr">
         <is>
@@ -10689,12 +10689,12 @@
         </is>
       </c>
       <c r="M150" s="1" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="N150"/>
       <c r="O150" t="inlineStr">
         <is>
-          <t>姚鲜珍</t>
+          <t>洪佳佩</t>
         </is>
       </c>
       <c r="P150" t="inlineStr">
@@ -10711,7 +10711,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>JDYPP20261021091350183</t>
+          <t>JDYPP20261021091349752</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -10766,7 +10766,7 @@
       <c r="N151"/>
       <c r="O151" t="inlineStr">
         <is>
-          <t>洪佳佩</t>
+          <t>姚鲜珍</t>
         </is>
       </c>
       <c r="P151" t="inlineStr">
@@ -10783,7 +10783,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>JDYPP20261021091349752</t>
+          <t>JDYPP20261021091349376</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -10808,7 +10808,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>LKC0011M-BRN01-CT</t>
+          <t>LKC0011S-BRN01-CT</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -10818,7 +10818,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>复古8025#红土陶色/8027D#玳瑁色/203#浅咖色/中号</t>
+          <t>复古8025#红土陶色/8027D#玳瑁色/203#浅咖色/小号</t>
         </is>
       </c>
       <c r="J152" s="1" t="n">
@@ -10838,7 +10838,7 @@
       <c r="N152"/>
       <c r="O152" t="inlineStr">
         <is>
-          <t>姚鲜珍</t>
+          <t>洪佳佩</t>
         </is>
       </c>
       <c r="P152" t="inlineStr">
@@ -10855,7 +10855,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>JDYPP20261021091349376</t>
+          <t>JDYPP20261021091348935</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -10910,7 +10910,7 @@
       <c r="N153"/>
       <c r="O153" t="inlineStr">
         <is>
-          <t>洪佳佩</t>
+          <t>姚鲜珍</t>
         </is>
       </c>
       <c r="P153" t="inlineStr">
@@ -10927,7 +10927,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>JDYPP20261021091348935</t>
+          <t>JDYPP20261021091348524</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -10952,7 +10952,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>LKC0011S-BRN01-CT</t>
+          <t>LKC0011M-BRN-CT</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -10962,27 +10962,27 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>复古8025#红土陶色/8027D#玳瑁色/203#浅咖色/小号</t>
+          <t>复古8056D#黑糖棕色/8050#欧洲蕨棕色/210#巧克力棕色/中号</t>
         </is>
       </c>
       <c r="J154" s="1" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="K154" s="1" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>2026/11/16 00:00:00</t>
+          <t>2026/11/15 00:00:00</t>
         </is>
       </c>
       <c r="M154" s="1" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="N154"/>
       <c r="O154" t="inlineStr">
         <is>
-          <t>姚鲜珍</t>
+          <t>庞新会</t>
         </is>
       </c>
       <c r="P154" t="inlineStr">
@@ -10999,7 +10999,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>JDYPP20261021091348524</t>
+          <t>JDYPP20261021091348170</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -11038,23 +11038,23 @@
         </is>
       </c>
       <c r="J155" s="1" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="K155" s="1" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>2026/11/15 00:00:00</t>
+          <t>2026/11/16 00:00:00</t>
         </is>
       </c>
       <c r="M155" s="1" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="N155"/>
       <c r="O155" t="inlineStr">
         <is>
-          <t>庞新会</t>
+          <t>洪佳佩</t>
         </is>
       </c>
       <c r="P155" t="inlineStr">
@@ -11071,7 +11071,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>JDYPP20261021091348170</t>
+          <t>JDYPP20261021091347784</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -11110,10 +11110,10 @@
         </is>
       </c>
       <c r="J156" s="1" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="K156" s="1" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="L156" t="inlineStr">
         <is>
@@ -11121,12 +11121,12 @@
         </is>
       </c>
       <c r="M156" s="1" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="N156"/>
       <c r="O156" t="inlineStr">
         <is>
-          <t>洪佳佩</t>
+          <t>姚鲜珍</t>
         </is>
       </c>
       <c r="P156" t="inlineStr">
@@ -11143,7 +11143,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>JDYPP20261021091347784</t>
+          <t>JDYPP20261021091347429</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -11168,7 +11168,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>LKC0011M-BRN-CT</t>
+          <t>LKC0011S-BRN-CT</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -11178,27 +11178,27 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>复古8056D#黑糖棕色/8050#欧洲蕨棕色/210#巧克力棕色/中号</t>
+          <t>复古8056D#黑糖棕色/8050#欧洲蕨棕色/210#巧克力棕色/小号</t>
         </is>
       </c>
       <c r="J157" s="1" t="n">
-        <v>200</v>
+        <v>30</v>
       </c>
       <c r="K157" s="1" t="n">
-        <v>200</v>
+        <v>30</v>
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>2026/11/16 00:00:00</t>
+          <t>2026/11/15 00:00:00</t>
         </is>
       </c>
       <c r="M157" s="1" t="n">
-        <v>200</v>
+        <v>30</v>
       </c>
       <c r="N157"/>
       <c r="O157" t="inlineStr">
         <is>
-          <t>姚鲜珍</t>
+          <t>庞新会</t>
         </is>
       </c>
       <c r="P157" t="inlineStr">
@@ -11215,7 +11215,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>JDYPP20261021091347429</t>
+          <t>JDYPP20261021091347035</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -11254,23 +11254,23 @@
         </is>
       </c>
       <c r="J158" s="1" t="n">
-        <v>30</v>
+        <v>400</v>
       </c>
       <c r="K158" s="1" t="n">
-        <v>30</v>
+        <v>400</v>
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>2026/11/15 00:00:00</t>
+          <t>2026/11/16 00:00:00</t>
         </is>
       </c>
       <c r="M158" s="1" t="n">
-        <v>30</v>
+        <v>400</v>
       </c>
       <c r="N158"/>
       <c r="O158" t="inlineStr">
         <is>
-          <t>庞新会</t>
+          <t>姚鲜珍</t>
         </is>
       </c>
       <c r="P158" t="inlineStr">
@@ -11287,12 +11287,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>JDYPP20261021091347035</t>
+          <t>JDYPR26102004152143LKP2L-T4</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>创建</t>
+          <t>已审核</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -11307,47 +11307,47 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>2026/10/21</t>
+          <t>2026/10/20</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>LKC0011S-BRN-CT</t>
+          <t>SPVYMB4343LKP2L-T4</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>女士单肩包</t>
+          <t>旅行背包</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>复古8056D#黑糖棕色/8050#欧洲蕨棕色/210#巧克力棕色/小号</t>
+          <t>88#豆绿/86#米白色/171#深橄榄绿/17.3寸/四件套</t>
         </is>
       </c>
       <c r="J159" s="1" t="n">
-        <v>400</v>
+        <v>698</v>
       </c>
       <c r="K159" s="1" t="n">
-        <v>400</v>
+        <v>698</v>
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>2026/11/16 00:00:00</t>
+          <t>2026/11/19 00:00:00</t>
         </is>
       </c>
       <c r="M159" s="1" t="n">
-        <v>400</v>
+        <v>698</v>
       </c>
       <c r="N159"/>
       <c r="O159" t="inlineStr">
         <is>
-          <t>姚鲜珍</t>
+          <t>何思琴</t>
         </is>
       </c>
       <c r="P159" t="inlineStr">
         <is>
-          <t>新品</t>
+          <t>11 12月系统预测日均偏低 平衡利库</t>
         </is>
       </c>
     </row>
@@ -11359,7 +11359,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>JDYPR26102004152143LKP2L-T4</t>
+          <t>JDYPR2610200415213LK10XL-T4</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -11384,7 +11384,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>SPVYMB4343LKP2L-T4</t>
+          <t>SPVYMB4343LK10XL-T4</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -11394,14 +11394,14 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>88#豆绿/86#米白色/171#深橄榄绿/17.3寸/四件套</t>
+          <t>33#黑色/4001黑色/18寸/四件套</t>
         </is>
       </c>
       <c r="J160" s="1" t="n">
-        <v>698</v>
+        <v>100</v>
       </c>
       <c r="K160" s="1" t="n">
-        <v>698</v>
+        <v>100</v>
       </c>
       <c r="L160" t="inlineStr">
         <is>
@@ -11409,7 +11409,7 @@
         </is>
       </c>
       <c r="M160" s="1" t="n">
-        <v>698</v>
+        <v>100</v>
       </c>
       <c r="N160"/>
       <c r="O160" t="inlineStr">
@@ -11419,7 +11419,7 @@
       </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>11 12月系统预测日均偏低 平衡利库</t>
+          <t>11 12月系统预测日均偏低</t>
         </is>
       </c>
     </row>
@@ -11431,7 +11431,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>JDYPR2610200415213LK10XL-T4</t>
+          <t>JDYPR26102004152143LKP9L-T4</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -11456,7 +11456,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>SPVYMB4343LK10XL-T4</t>
+          <t>SPVYMB4343LKP9L-T4</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -11466,7 +11466,7 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>33#黑色/4001黑色/18寸/四件套</t>
+          <t>38#墨蓝/27#灰蓝色/4001#黑色/17.3寸/四件套</t>
         </is>
       </c>
       <c r="J161" s="1" t="n">
@@ -11503,7 +11503,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>JDYPR26102004152143LKP9L-T4</t>
+          <t>JDYPR26102004152143LKP4L-T4</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -11528,7 +11528,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>SPVYMB4343LKP9L-T4</t>
+          <t>SPVYMB4343LKP4L-T4</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -11538,14 +11538,14 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>38#墨蓝/27#灰蓝色/4001#黑色/17.3寸/四件套</t>
+          <t>23#蓝紫色/4001#黑色/17.3寸/四件套</t>
         </is>
       </c>
       <c r="J162" s="1" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="K162" s="1" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="L162" t="inlineStr">
         <is>
@@ -11553,7 +11553,7 @@
         </is>
       </c>
       <c r="M162" s="1" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="N162"/>
       <c r="O162" t="inlineStr">
@@ -11575,7 +11575,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>JDYPR26102004152143LKP4L-T4</t>
+          <t>JDYPR26102004152143LKPFL-T4</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -11600,7 +11600,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>SPVYMB4343LKP4L-T4</t>
+          <t>SPVYMB4343LKPFL-T4</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -11610,14 +11610,14 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>23#蓝紫色/4001#黑色/17.3寸/四件套</t>
+          <t>34A黄棕色/62#米白色/4001黑色/17.3寸/四件套</t>
         </is>
       </c>
       <c r="J163" s="1" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="K163" s="1" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="L163" t="inlineStr">
         <is>
@@ -11625,7 +11625,7 @@
         </is>
       </c>
       <c r="M163" s="1" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="N163"/>
       <c r="O163" t="inlineStr">
@@ -11647,12 +11647,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>JDYPR26102004152143LKPFL-T4</t>
+          <t>JDYPR26102002082788LK40M-T2</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>已审核</t>
+          <t>创建</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -11672,24 +11672,24 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>SPVYMB4343LKPFL-T4</t>
+          <t>SPVYMB5688LK40M-T2</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>旅行背包</t>
+          <t>妈咪包</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>34A黄棕色/62#米白色/4001黑色/17.3寸/四件套</t>
+          <t>250#驼绒棕/15.6寸/两件套</t>
         </is>
       </c>
       <c r="J164" s="1" t="n">
-        <v>100</v>
+        <v>800</v>
       </c>
       <c r="K164" s="1" t="n">
-        <v>100</v>
+        <v>800</v>
       </c>
       <c r="L164" t="inlineStr">
         <is>
@@ -11697,17 +11697,17 @@
         </is>
       </c>
       <c r="M164" s="1" t="n">
-        <v>100</v>
+        <v>800</v>
       </c>
       <c r="N164"/>
       <c r="O164" t="inlineStr">
         <is>
-          <t>何思琴</t>
+          <t>唐海阳</t>
         </is>
       </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>11 12月系统预测日均偏低</t>
+          <t>5688首批800单，日均最高能到40+，近一周毛利转正，均价能到40美金，再推广过程中棋盘格表现优秀，因此二推返单棋盘格做次卖色引流，并新增6个变体和2个大号变体，目前新增变体走变体流程下单</t>
         </is>
       </c>
     </row>
@@ -11719,7 +11719,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>JDYPR26102002082788LK40M-T2</t>
+          <t>JDYPR26102002082788LK10M-T2</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -11744,7 +11744,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>SPVYMB5688LK40M-T2</t>
+          <t>SPVYMB5688LK10M-T2</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -11754,14 +11754,14 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>250#驼绒棕/15.6寸/两件套</t>
+          <t>1#黑色/15.6寸/两件套</t>
         </is>
       </c>
       <c r="J165" s="1" t="n">
-        <v>800</v>
+        <v>200</v>
       </c>
       <c r="K165" s="1" t="n">
-        <v>800</v>
+        <v>200</v>
       </c>
       <c r="L165" t="inlineStr">
         <is>
@@ -11769,7 +11769,7 @@
         </is>
       </c>
       <c r="M165" s="1" t="n">
-        <v>800</v>
+        <v>200</v>
       </c>
       <c r="N165"/>
       <c r="O165" t="inlineStr">
@@ -11791,7 +11791,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>JDYPR26102002082788LK10M-T2</t>
+          <t>JDYPR26102002082788LK41M-T2</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -11816,7 +11816,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>SPVYMB5688LK10M-T2</t>
+          <t>SPVYMB5688LK41M-T2</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -11826,14 +11826,14 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>1#黑色/15.6寸/两件套</t>
+          <t>120#苏丹棕/15.6寸/两件套</t>
         </is>
       </c>
       <c r="J166" s="1" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K166" s="1" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L166" t="inlineStr">
         <is>
@@ -11841,7 +11841,7 @@
         </is>
       </c>
       <c r="M166" s="1" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="N166"/>
       <c r="O166" t="inlineStr">
@@ -11863,7 +11863,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>JDYPR26102002082788LK41M-T2</t>
+          <t>JDYPR26102002082788LKP1M-T2</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -11888,7 +11888,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>SPVYMB5688LK41M-T2</t>
+          <t>SPVYMB5688LKP1M-T2</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -11898,14 +11898,14 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>120#苏丹棕/15.6寸/两件套</t>
+          <t>白裸棋盘格/15.6寸/两件套</t>
         </is>
       </c>
       <c r="J167" s="1" t="n">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="K167" s="1" t="n">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="L167" t="inlineStr">
         <is>
@@ -11913,7 +11913,7 @@
         </is>
       </c>
       <c r="M167" s="1" t="n">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="N167"/>
       <c r="O167" t="inlineStr">
@@ -11935,17 +11935,17 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>JDYPR26102002082788LKP1M-T2</t>
+          <t>JDYPR261019043927LKP4L-D-V1</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>创建</t>
+          <t>已审核</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026/10/21</t>
+          <t>2026/10/20</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -11955,47 +11955,47 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>2026/10/20</t>
+          <t>2026/10/19</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>SPVYMB5688LKP1M-T2</t>
+          <t>SPVYMB2237LKP4L-D-V1</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>妈咪包</t>
+          <t>绣线电脑背包</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>白裸棋盘格/15.6寸/两件套</t>
+          <t>44#米杏色/43#咖啡色/17.3寸/单层/加大水杯袋</t>
         </is>
       </c>
       <c r="J168" s="1" t="n">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="K168" s="1" t="n">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>2026/11/19 00:00:00</t>
+          <t>2026/11/18 00:00:00</t>
         </is>
       </c>
       <c r="M168" s="1" t="n">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="N168"/>
       <c r="O168" t="inlineStr">
         <is>
-          <t>唐海阳</t>
+          <t>柳干</t>
         </is>
       </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>5688首批800单，日均最高能到40+，近一周毛利转正，均价能到40美金，再推广过程中棋盘格表现优秀，因此二推返单棋盘格做次卖色引流，并新增6个变体和2个大号变体，目前新增变体走变体流程下单</t>
+          <t>大水杯变体正常备货，逐步淘汰无大水杯单层变体，近期毛利率有所回升</t>
         </is>
       </c>
     </row>
@@ -12007,7 +12007,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>JDYPR261019043927LKP4L-D-V1</t>
+          <t>JDYPR261019043927K13XL-D-V1</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -12032,7 +12032,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>SPVYMB2237LKP4L-D-V1</t>
+          <t>SPVYMB2237LK13XL-D-V1</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -12042,7 +12042,7 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>44#米杏色/43#咖啡色/17.3寸/单层/加大水杯袋</t>
+          <t>76#暗紫色/13#黑色/18寸/单层/加大水杯袋</t>
         </is>
       </c>
       <c r="J169" s="1" t="n">
@@ -12079,7 +12079,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>JDYPR261019043927K13XL-D-V1</t>
+          <t>JDYPR261019043927LKP6M-D-V1</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -12104,7 +12104,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>SPVYMB2237LK13XL-D-V1</t>
+          <t>SPVYMB2237LKP6M-D-V1</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>76#暗紫色/13#黑色/18寸/单层/加大水杯袋</t>
+          <t>22#藏蓝/50#淡粉/06#深蓝/15.6寸/单层/加大水杯袋</t>
         </is>
       </c>
       <c r="J170" s="1" t="n">
@@ -12151,7 +12151,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>JDYPR261019043927LKP6M-D-V1</t>
+          <t>JDYPR261019043927K32XL-D-V1</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -12176,7 +12176,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>SPVYMB2237LKP6M-D-V1</t>
+          <t>SPVYMB2237LK32XL-D-V1</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -12186,7 +12186,7 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>22#藏蓝/50#淡粉/06#深蓝/15.6寸/单层/加大水杯袋</t>
+          <t>68#灰色/13#黑色/18寸/单层/加大水杯袋</t>
         </is>
       </c>
       <c r="J171" s="1" t="n">
@@ -12223,7 +12223,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>JDYPR261019043927K32XL-D-V1</t>
+          <t>JDYPR261019043927K03XL-D-V1</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -12248,7 +12248,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>SPVYMB2237LK32XL-D-V1</t>
+          <t>SPVYMB2237LK03XL-D-V1</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -12258,7 +12258,7 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>68#灰色/13#黑色/18寸/单层/加大水杯袋</t>
+          <t>46#米白/13#黑色/18寸/单层/加大水杯袋</t>
         </is>
       </c>
       <c r="J172" s="1" t="n">
@@ -12295,7 +12295,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>JDYPR261019043927K03XL-D-V1</t>
+          <t>JDYPR261019043927LKP5L-D-V1</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -12320,7 +12320,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>SPVYMB2237LK03XL-D-V1</t>
+          <t>SPVYMB2237LKP5L-D-V1</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -12330,7 +12330,7 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>46#米白/13#黑色/18寸/单层/加大水杯袋</t>
+          <t>24#墨蓝/7#浅蓝/4001#黑色/17.3寸/单层/加大水杯袋</t>
         </is>
       </c>
       <c r="J173" s="1" t="n">
@@ -12367,7 +12367,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>JDYPR261019043927LKP5L-D-V1</t>
+          <t>JDYPR261019043927LK23L-D-V1</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -12392,7 +12392,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>SPVYMB2237LKP5L-D-V1</t>
+          <t>SPVYMB2237LK23L-D-V1</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -12402,7 +12402,7 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>24#墨蓝/7#浅蓝/4001#黑色/17.3寸/单层/加大水杯袋</t>
+          <t>44#绿色/13#黑色/17.3寸/单层/加大水杯袋</t>
         </is>
       </c>
       <c r="J174" s="1" t="n">
@@ -12439,7 +12439,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>JDYPR261019043927LK23L-D-V1</t>
+          <t>JDYPR261019043927LK27M-D-V1</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -12464,7 +12464,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>SPVYMB2237LK23L-D-V1</t>
+          <t>SPVYMB2237LK27M-D-V1</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -12474,7 +12474,7 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>44#绿色/13#黑色/17.3寸/单层/加大水杯袋</t>
+          <t>46#米白/15#原色/15.6寸/单层/加大水杯袋</t>
         </is>
       </c>
       <c r="J175" s="1" t="n">
@@ -12511,7 +12511,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>JDYPR261019043927LK27M-D-V1</t>
+          <t>JDYPR261019043927LK01M-D-V1</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -12536,7 +12536,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>SPVYMB2237LK27M-D-V1</t>
+          <t>SPVYMB2237LK01M-D-V1</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -12546,7 +12546,7 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>46#米白/15#原色/15.6寸/单层/加大水杯袋</t>
+          <t>13#黑色/34#板栗棕/15.6寸/单层/加大水杯袋</t>
         </is>
       </c>
       <c r="J176" s="1" t="n">
@@ -12583,7 +12583,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>JDYPR261019043927LK01M-D-V1</t>
+          <t>JDYPR261019043927LK13M-D-V1</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -12608,7 +12608,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>SPVYMB2237LK01M-D-V1</t>
+          <t>SPVYMB2237LK13M-D-V1</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -12618,7 +12618,7 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>13#黑色/34#板栗棕/15.6寸/单层/加大水杯袋</t>
+          <t>76#暗紫色/13#黑色/15.6寸/单层/加大水杯袋</t>
         </is>
       </c>
       <c r="J177" s="1" t="n">
@@ -12655,7 +12655,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>JDYPR261019043927LK13M-D-V1</t>
+          <t>JDYPR261019043927LKP5M-D-V1</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -12680,7 +12680,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>SPVYMB2237LK13M-D-V1</t>
+          <t>SPVYMB2237LKP5M-D-V1</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -12690,7 +12690,7 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>76#暗紫色/13#黑色/15.6寸/单层/加大水杯袋</t>
+          <t>24#墨蓝/7#浅蓝/4001#黑色/15.6寸/单层/加大水杯袋</t>
         </is>
       </c>
       <c r="J178" s="1" t="n">
@@ -12727,7 +12727,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>JDYPR261019043927LKP5M-D-V1</t>
+          <t>JDYPR261019043927LK32M-D-V1</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -12752,7 +12752,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>SPVYMB2237LKP5M-D-V1</t>
+          <t>SPVYMB2237LK32M-D-V1</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -12762,7 +12762,7 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>24#墨蓝/7#浅蓝/4001#黑色/15.6寸/单层/加大水杯袋</t>
+          <t>68#灰色/13#黑色/15.6寸/单层/加大水杯袋</t>
         </is>
       </c>
       <c r="J179" s="1" t="n">
@@ -12799,7 +12799,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>JDYPR261019043927LK32M-D-V1</t>
+          <t>JDYPR261019043927LK32L-D-V1</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>SPVYMB2237LK32M-D-V1</t>
+          <t>SPVYMB2237LK32L-D-V1</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -12834,7 +12834,7 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>68#灰色/13#黑色/15.6寸/单层/加大水杯袋</t>
+          <t>68#灰色/13#黑色/17.3寸/单层/加大水杯袋</t>
         </is>
       </c>
       <c r="J180" s="1" t="n">
@@ -12871,7 +12871,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>JDYPR261019043927LK32L-D-V1</t>
+          <t>JDYPP20261020085827777</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -12891,29 +12891,29 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>2026/10/19</t>
+          <t>2026/10/20</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>SPVYMB2237LK32L-D-V1</t>
+          <t>SPLK6622L-GN</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>绣线电脑背包</t>
+          <t>电脑背包</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>68#灰色/13#黑色/17.3寸/单层/加大水杯袋</t>
+          <t>15#豆绿色/17.3寸</t>
         </is>
       </c>
       <c r="J181" s="1" t="n">
-        <v>100</v>
+        <v>350</v>
       </c>
       <c r="K181" s="1" t="n">
-        <v>100</v>
+        <v>350</v>
       </c>
       <c r="L181" t="inlineStr">
         <is>
@@ -12921,17 +12921,17 @@
         </is>
       </c>
       <c r="M181" s="1" t="n">
-        <v>100</v>
+        <v>350</v>
       </c>
       <c r="N181"/>
       <c r="O181" t="inlineStr">
         <is>
-          <t>柳干</t>
+          <t>黄小凤</t>
         </is>
       </c>
       <c r="P181" t="inlineStr">
         <is>
-          <t>大水杯变体正常备货，逐步淘汰无大水杯单层变体，近期毛利率有所回升</t>
+          <t>新品</t>
         </is>
       </c>
     </row>
@@ -12943,7 +12943,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>JDYPP20261020085827777</t>
+          <t>JDYPP20261020085827325</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -12968,7 +12968,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>SPLK6622L-GN</t>
+          <t>SPLK6622L-BLU</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -12978,14 +12978,14 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>15#豆绿色/17.3寸</t>
+          <t>04#深蓝色/17.3寸</t>
         </is>
       </c>
       <c r="J182" s="1" t="n">
-        <v>350</v>
+        <v>100</v>
       </c>
       <c r="K182" s="1" t="n">
-        <v>350</v>
+        <v>100</v>
       </c>
       <c r="L182" t="inlineStr">
         <is>
@@ -12993,7 +12993,7 @@
         </is>
       </c>
       <c r="M182" s="1" t="n">
-        <v>350</v>
+        <v>100</v>
       </c>
       <c r="N182"/>
       <c r="O182" t="inlineStr">
@@ -13015,7 +13015,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>JDYPP20261020085827325</t>
+          <t>JDYPP20261020085826871</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -13040,7 +13040,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>SPLK6622L-BLU</t>
+          <t>SPLK6622L-AP</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -13050,14 +13050,14 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>04#深蓝色/17.3寸</t>
+          <t>2508342豹纹/17.3寸</t>
         </is>
       </c>
       <c r="J183" s="1" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="K183" s="1" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="L183" t="inlineStr">
         <is>
@@ -13065,7 +13065,7 @@
         </is>
       </c>
       <c r="M183" s="1" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="N183"/>
       <c r="O183" t="inlineStr">
@@ -13087,7 +13087,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>JDYPP20261020085826871</t>
+          <t>JDYPP20261020085826445</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -13112,7 +13112,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>SPLK6622L-AP</t>
+          <t>SPLK6622L-BLK</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -13122,27 +13122,27 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>2508342豹纹/17.3寸</t>
+          <t>01#黑色/17.3寸</t>
         </is>
       </c>
       <c r="J184" s="1" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="K184" s="1" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>2026/11/18 00:00:00</t>
+          <t>2026/11/1 00:00:00</t>
         </is>
       </c>
       <c r="M184" s="1" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="N184"/>
       <c r="O184" t="inlineStr">
         <is>
-          <t>黄小凤</t>
+          <t>郑梓东</t>
         </is>
       </c>
       <c r="P184" t="inlineStr">
@@ -13159,7 +13159,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>JDYPP20261020085826445</t>
+          <t>JDYPP20261020085825988</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -13198,23 +13198,23 @@
         </is>
       </c>
       <c r="J185" s="1" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K185" s="1" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>2026/11/1 00:00:00</t>
+          <t>2026/11/18 00:00:00</t>
         </is>
       </c>
       <c r="M185" s="1" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="N185"/>
       <c r="O185" t="inlineStr">
         <is>
-          <t>郑梓东</t>
+          <t>黄小凤</t>
         </is>
       </c>
       <c r="P185" t="inlineStr">
@@ -13231,7 +13231,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>JDYPP20261020085825988</t>
+          <t>JDYPP20261020085825574</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -13256,7 +13256,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>SPLK6622L-BLK</t>
+          <t>SPLK6622M-PL</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -13266,7 +13266,7 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>01#黑色/17.3寸</t>
+          <t>20#浅紫色/15.6寸</t>
         </is>
       </c>
       <c r="J186" s="1" t="n">
@@ -13303,7 +13303,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>JDYPP20261020085825574</t>
+          <t>JDYPP20261020085825185</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -13328,7 +13328,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>SPLK6622M-PL</t>
+          <t>SPLK6622M-PK</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -13338,7 +13338,7 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>20#浅紫色/15.6寸</t>
+          <t>02#浅粉色/15.6寸</t>
         </is>
       </c>
       <c r="J187" s="1" t="n">
@@ -13375,7 +13375,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>JDYPP20261020085825185</t>
+          <t>JDYPP20261020085824830</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -13400,7 +13400,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>SPLK6622M-PK</t>
+          <t>SPLK6622M-GN01</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -13410,27 +13410,27 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>02#浅粉色/15.6寸</t>
+          <t>19#橄榄绿色/15.6寸</t>
         </is>
       </c>
       <c r="J188" s="1" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="K188" s="1" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>2026/11/18 00:00:00</t>
+          <t>2026/11/1 00:00:00</t>
         </is>
       </c>
       <c r="M188" s="1" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="N188"/>
       <c r="O188" t="inlineStr">
         <is>
-          <t>黄小凤</t>
+          <t>郑梓东</t>
         </is>
       </c>
       <c r="P188" t="inlineStr">
@@ -13447,7 +13447,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>JDYPP20261020085824830</t>
+          <t>JDYPP20261020085824446</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -13486,23 +13486,23 @@
         </is>
       </c>
       <c r="J189" s="1" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K189" s="1" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>2026/11/1 00:00:00</t>
+          <t>2026/11/18 00:00:00</t>
         </is>
       </c>
       <c r="M189" s="1" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N189"/>
       <c r="O189" t="inlineStr">
         <is>
-          <t>郑梓东</t>
+          <t>黄小凤</t>
         </is>
       </c>
       <c r="P189" t="inlineStr">
@@ -13519,7 +13519,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>JDYPP20261020085824446</t>
+          <t>JDYPP20261020085824087</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -13544,7 +13544,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>SPLK6622M-GN01</t>
+          <t>SPLK6622M-BLK</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -13554,27 +13554,27 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>19#橄榄绿色/15.6寸</t>
+          <t>01#黑色/15.6寸</t>
         </is>
       </c>
       <c r="J190" s="1" t="n">
-        <v>100</v>
+        <v>450</v>
       </c>
       <c r="K190" s="1" t="n">
-        <v>100</v>
+        <v>450</v>
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>2026/11/18 00:00:00</t>
+          <t>2026/11/1 00:00:00</t>
         </is>
       </c>
       <c r="M190" s="1" t="n">
-        <v>100</v>
+        <v>450</v>
       </c>
       <c r="N190"/>
       <c r="O190" t="inlineStr">
         <is>
-          <t>黄小凤</t>
+          <t>郑梓东</t>
         </is>
       </c>
       <c r="P190" t="inlineStr">
@@ -13591,7 +13591,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>JDYPP20261020085824087</t>
+          <t>JDYPP20261020085823703</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -13630,23 +13630,23 @@
         </is>
       </c>
       <c r="J191" s="1" t="n">
-        <v>450</v>
+        <v>200</v>
       </c>
       <c r="K191" s="1" t="n">
-        <v>450</v>
+        <v>200</v>
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>2026/11/1 00:00:00</t>
+          <t>2026/11/18 00:00:00</t>
         </is>
       </c>
       <c r="M191" s="1" t="n">
-        <v>450</v>
+        <v>200</v>
       </c>
       <c r="N191"/>
       <c r="O191" t="inlineStr">
         <is>
-          <t>郑梓东</t>
+          <t>黄小凤</t>
         </is>
       </c>
       <c r="P191" t="inlineStr">
@@ -13663,7 +13663,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>JDYPP20261020085823703</t>
+          <t>JDYPP20261020085823347</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -13688,7 +13688,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>SPLK6622M-BLK</t>
+          <t>SPLK6622M-BLU</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -13698,27 +13698,27 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>01#黑色/15.6寸</t>
+          <t>04#深蓝色/15.6寸</t>
         </is>
       </c>
       <c r="J192" s="1" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="K192" s="1" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>2026/11/18 00:00:00</t>
+          <t>2026/11/1 00:00:00</t>
         </is>
       </c>
       <c r="M192" s="1" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="N192"/>
       <c r="O192" t="inlineStr">
         <is>
-          <t>黄小凤</t>
+          <t>郑梓东</t>
         </is>
       </c>
       <c r="P192" t="inlineStr">
@@ -13735,7 +13735,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>JDYPP20261020085823347</t>
+          <t>JDYPP20261020085822958</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -13774,23 +13774,23 @@
         </is>
       </c>
       <c r="J193" s="1" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="K193" s="1" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>2026/11/1 00:00:00</t>
+          <t>2026/11/18 00:00:00</t>
         </is>
       </c>
       <c r="M193" s="1" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="N193"/>
       <c r="O193" t="inlineStr">
         <is>
-          <t>郑梓东</t>
+          <t>黄小凤</t>
         </is>
       </c>
       <c r="P193" t="inlineStr">
@@ -13807,7 +13807,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>JDYPP20261020085822958</t>
+          <t>JDYPP20261020085822504</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -13832,7 +13832,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>SPLK6622M-BLU</t>
+          <t>SPLK6622M-AP01</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -13842,7 +13842,7 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>04#深蓝色/15.6寸</t>
+          <t>黑灰豹纹/15.6寸</t>
         </is>
       </c>
       <c r="J194" s="1" t="n">
@@ -13879,7 +13879,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>JDYPP20261020085822504</t>
+          <t>JDYPP20261020085822132</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -13904,7 +13904,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>SPLK6622M-AP01</t>
+          <t>SPLK6622M-AP</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -13914,27 +13914,27 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>黑灰豹纹/15.6寸</t>
+          <t>2508342豹纹/15.6寸</t>
         </is>
       </c>
       <c r="J195" s="1" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="K195" s="1" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>2026/11/18 00:00:00</t>
+          <t>2026/11/1 00:00:00</t>
         </is>
       </c>
       <c r="M195" s="1" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="N195"/>
       <c r="O195" t="inlineStr">
         <is>
-          <t>黄小凤</t>
+          <t>郑梓东</t>
         </is>
       </c>
       <c r="P195" t="inlineStr">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>JDYPP20261020085822132</t>
+          <t>JDYPP20261020085821714</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -13990,23 +13990,23 @@
         </is>
       </c>
       <c r="J196" s="1" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="K196" s="1" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>2026/11/1 00:00:00</t>
+          <t>2026/11/18 00:00:00</t>
         </is>
       </c>
       <c r="M196" s="1" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="N196"/>
       <c r="O196" t="inlineStr">
         <is>
-          <t>郑梓东</t>
+          <t>黄小凤</t>
         </is>
       </c>
       <c r="P196" t="inlineStr">
@@ -14023,7 +14023,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>JDYPP20261020085821714</t>
+          <t>JDYPP20261020085821293</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -14048,7 +14048,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>SPLK6622M-AP</t>
+          <t>SPLK6622M-GN</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -14058,27 +14058,27 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>2508342豹纹/15.6寸</t>
+          <t>15#豆绿色/15.6寸</t>
         </is>
       </c>
       <c r="J197" s="1" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="K197" s="1" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>2026/11/18 00:00:00</t>
+          <t>2026/11/1 00:00:00</t>
         </is>
       </c>
       <c r="M197" s="1" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="N197"/>
       <c r="O197" t="inlineStr">
         <is>
-          <t>黄小凤</t>
+          <t>郑梓东</t>
         </is>
       </c>
       <c r="P197" t="inlineStr">
@@ -14095,7 +14095,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>JDYPP20261020085821293</t>
+          <t>JDYPP20261020085820905</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -14134,23 +14134,23 @@
         </is>
       </c>
       <c r="J198" s="1" t="n">
-        <v>100</v>
+        <v>1400</v>
       </c>
       <c r="K198" s="1" t="n">
-        <v>100</v>
+        <v>1400</v>
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>2026/11/1 00:00:00</t>
+          <t>2026/11/18 00:00:00</t>
         </is>
       </c>
       <c r="M198" s="1" t="n">
-        <v>100</v>
+        <v>1400</v>
       </c>
       <c r="N198"/>
       <c r="O198" t="inlineStr">
         <is>
-          <t>郑梓东</t>
+          <t>黄小凤</t>
         </is>
       </c>
       <c r="P198" t="inlineStr">
@@ -14167,7 +14167,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>JDYPP20261020085820905</t>
+          <t>JDYPP20261015060042706</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -14177,7 +14177,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2026/10/20</t>
+          <t>2026/10/15</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -14187,47 +14187,47 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>2026/10/20</t>
+          <t>2026/10/15</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>SPLK6622M-GN</t>
+          <t>VYWB6115LKP2M</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>电脑背包</t>
+          <t>圆顶贝壳包</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>15#豆绿色/15.6寸</t>
+          <t>透明TPU/865#浅黄棕/中号</t>
         </is>
       </c>
       <c r="J199" s="1" t="n">
-        <v>1400</v>
+        <v>100</v>
       </c>
       <c r="K199" s="1" t="n">
-        <v>1400</v>
+        <v>100</v>
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>2026/11/18 00:00:00</t>
+          <t>2026/11/19 00:00:00</t>
         </is>
       </c>
       <c r="M199" s="1" t="n">
-        <v>1400</v>
+        <v>100</v>
       </c>
       <c r="N199"/>
       <c r="O199" t="inlineStr">
         <is>
-          <t>黄小凤</t>
+          <t>姚鲜珍</t>
         </is>
       </c>
       <c r="P199" t="inlineStr">
         <is>
-          <t>新品</t>
+          <t>新变体</t>
         </is>
       </c>
     </row>
@@ -14239,7 +14239,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>JDYPP20261015060042706</t>
+          <t>JDYPP20261015060041950</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -14264,7 +14264,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>VYWB6115LKP2M</t>
+          <t>VYWB6115LKP1M</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -14274,14 +14274,14 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>透明TPU/865#浅黄棕/中号</t>
+          <t>透明TPU/4001#黑色/中号</t>
         </is>
       </c>
       <c r="J200" s="1" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="K200" s="1" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="L200" t="inlineStr">
         <is>
@@ -14289,7 +14289,7 @@
         </is>
       </c>
       <c r="M200" s="1" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="N200"/>
       <c r="O200" t="inlineStr">
@@ -14311,17 +14311,17 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>JDYPP20261015060041950</t>
+          <t>JDYPR26101303340831LK42L-M1</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>已审核</t>
+          <t>创建</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>2026/10/15</t>
+          <t>2026/10/13</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -14331,47 +14331,47 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>2026/10/15</t>
+          <t>2026/10/13</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>VYWB6115LKP1M</t>
+          <t>SPVYUB5631LK42L-M1</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>圆顶贝壳包</t>
+          <t>午餐包</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>透明TPU/4001#黑色/中号</t>
+          <t>复古8089#黄棕色（压花）/复古8089#黄棕色/大号/两件套</t>
         </is>
       </c>
       <c r="J201" s="1" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="K201" s="1" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>2026/11/19 00:00:00</t>
+          <t>2026/11/12 00:00:00</t>
         </is>
       </c>
       <c r="M201" s="1" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="N201"/>
       <c r="O201" t="inlineStr">
         <is>
-          <t>姚鲜珍</t>
+          <t>唐海阳</t>
         </is>
       </c>
       <c r="P201" t="inlineStr">
         <is>
-          <t>新变体</t>
+          <t>5631近期2推表现符合预期，补充活动消耗的库存，避免年底大流量结束后库存缺失导致断货</t>
         </is>
       </c>
     </row>
@@ -14383,7 +14383,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>JDYPR26101303340831LK42L-M1</t>
+          <t>JDYPR26101303340831LK40L-T2</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -14408,7 +14408,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>SPVYUB5631LK42L-M1</t>
+          <t>SPVYUB5631LK40L-T2</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -14418,14 +14418,14 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>复古8089#黄棕色（压花）/复古8089#黄棕色/大号/两件套</t>
+          <t>12#焦糖棕/大号/两件套</t>
         </is>
       </c>
       <c r="J202" s="1" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="K202" s="1" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="L202" t="inlineStr">
         <is>
@@ -14433,7 +14433,7 @@
         </is>
       </c>
       <c r="M202" s="1" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="N202"/>
       <c r="O202" t="inlineStr">
@@ -14455,7 +14455,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>JDYPR26101303340831LK40L-T2</t>
+          <t>JDYPR26101303340831LK40M-T2</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -14480,7 +14480,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>SPVYUB5631LK40L-T2</t>
+          <t>SPVYUB5631LK40M-T2</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -14490,14 +14490,14 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>12#焦糖棕/大号/两件套</t>
+          <t>12#焦糖棕/中号/两件套</t>
         </is>
       </c>
       <c r="J203" s="1" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="K203" s="1" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="L203" t="inlineStr">
         <is>
@@ -14505,7 +14505,7 @@
         </is>
       </c>
       <c r="M203" s="1" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="N203"/>
       <c r="O203" t="inlineStr">
@@ -14527,7 +14527,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>JDYPR26101303340831LK40M-T2</t>
+          <t>JDYPR26101303323231LK42M-M1</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -14552,7 +14552,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>SPVYUB5631LK40M-T2</t>
+          <t>SPVYUB5631LK42M-M1</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -14562,7 +14562,7 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>12#焦糖棕/中号/两件套</t>
+          <t>复古8089#黄棕色（压花）/复古8089#黄棕色/中号/两件套</t>
         </is>
       </c>
       <c r="J204" s="1" t="n">
@@ -14599,12 +14599,12 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>JDYPR26101303323231LK42M-M1</t>
+          <t>JDYPR26101310142069LK30S-V1</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>创建</t>
+          <t>重新审核</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -14619,47 +14619,47 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>2026/10/13</t>
+          <t>2026/10/12</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>SPVYUB5631LK42M-M1</t>
+          <t>VYWB4069LK30S-V1</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>午餐包</t>
+          <t>女式挎包</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>复古8089#黄棕色（压花）/复古8089#黄棕色/中号/两件套</t>
+          <t>52#湛蓝/11寸/(更换挂饰)</t>
         </is>
       </c>
       <c r="J205" s="1" t="n">
-        <v>250</v>
+        <v>50</v>
       </c>
       <c r="K205" s="1" t="n">
-        <v>250</v>
+        <v>50</v>
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>2026/11/12 00:00:00</t>
+          <t>2026/10/15 00:00:00</t>
         </is>
       </c>
       <c r="M205" s="1" t="n">
-        <v>250</v>
+        <v>50</v>
       </c>
       <c r="N205"/>
       <c r="O205" t="inlineStr">
         <is>
-          <t>唐海阳</t>
+          <t>符琪</t>
         </is>
       </c>
       <c r="P205" t="inlineStr">
         <is>
-          <t>5631近期2推表现符合预期，补充活动消耗的库存，避免年底大流量结束后库存缺失导致断货</t>
+          <t>加急出货</t>
         </is>
       </c>
     </row>
@@ -14671,17 +14671,17 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>JDYPR26101310142069LK30S-V1</t>
+          <t>JDYPR26100904101312LK80M-C1</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>重新审核</t>
+          <t>创建</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2026/10/13</t>
+          <t>2026/10/9</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -14691,47 +14691,47 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>2026/10/12</t>
+          <t>2026/10/9</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>VYWB4069LK30S-V1</t>
+          <t>SPVYWB1512LK80M-C1</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>女式挎包</t>
+          <t>圆顶贝壳包</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>52#湛蓝/11寸/(更换挂饰)</t>
+          <t>8089#黄棕色（压花）/中号</t>
         </is>
       </c>
       <c r="J206" s="1" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K206" s="1" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>2026/10/15 00:00:00</t>
+          <t>2026/11/8 00:00:00</t>
         </is>
       </c>
       <c r="M206" s="1" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N206"/>
       <c r="O206" t="inlineStr">
         <is>
-          <t>符琪</t>
+          <t>姚鲜珍</t>
         </is>
       </c>
       <c r="P206" t="inlineStr">
         <is>
-          <t>加急出货</t>
+          <t>常规补货</t>
         </is>
       </c>
     </row>
@@ -14743,7 +14743,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>JDYPR26100904101312LK80M-C1</t>
+          <t>JDYPR261009041013B1512LK29M</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -14768,7 +14768,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>SPVYWB1512LK80M-C1</t>
+          <t>SPVYWB1512LK29M</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -14778,14 +14778,14 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>8089#黄棕色（压花）/中号</t>
+          <t>186#裸色</t>
         </is>
       </c>
       <c r="J207" s="1" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="K207" s="1" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L207" t="inlineStr">
         <is>
@@ -14793,7 +14793,7 @@
         </is>
       </c>
       <c r="M207" s="1" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="N207"/>
       <c r="O207" t="inlineStr">
@@ -14803,7 +14803,7 @@
       </c>
       <c r="P207" t="inlineStr">
         <is>
-          <t>常规补货</t>
+          <t>常规补货(SPVYWB1512LK29M平衡利库调拨，修改时间2026-10-21 10:58:04，调整前申请数量：100.0；调整后申请数量：98.0;)</t>
         </is>
       </c>
     </row>
@@ -14815,7 +14815,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>JDYPR261009041013B1512LK29M</t>
+          <t>JDYPR261009041013B1512LK10L</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -14840,7 +14840,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>SPVYWB1512LK29M</t>
+          <t>SPVYWB1512LK10L</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -14850,14 +14850,14 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>186#裸色</t>
+          <t>11#大红色/大号</t>
         </is>
       </c>
       <c r="J208" s="1" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="K208" s="1" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L208" t="inlineStr">
         <is>
@@ -14865,7 +14865,7 @@
         </is>
       </c>
       <c r="M208" s="1" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="N208"/>
       <c r="O208" t="inlineStr">
@@ -14875,7 +14875,7 @@
       </c>
       <c r="P208" t="inlineStr">
         <is>
-          <t>常规补货(SPVYWB1512LK29M平衡利库调拨，修改时间2026-10-21 10:58:04，调整前申请数量：100.0；调整后申请数量：98.0;)</t>
+          <t>常规补货</t>
         </is>
       </c>
     </row>
@@ -14887,7 +14887,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>JDYPR261009041013B1512LK10L</t>
+          <t>JDYPR261009041013B1512LK18M</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -14912,7 +14912,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>SPVYWB1512LK10L</t>
+          <t>SPVYWB1512LK18M</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -14922,7 +14922,7 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>11#大红色/大号</t>
+          <t>棕色</t>
         </is>
       </c>
       <c r="J209" s="1" t="n">
@@ -14959,7 +14959,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>JDYPR261009041013B1512LK18M</t>
+          <t>JDYPR261009041013B1512LK06M</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -14984,7 +14984,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>SPVYWB1512LK18M</t>
+          <t>SPVYWB1512LK06M</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>棕色</t>
+          <t>深蓝</t>
         </is>
       </c>
       <c r="J210" s="1" t="n">
@@ -15031,7 +15031,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>JDYPR261009041013B1512LK06M</t>
+          <t>JDYPR261009041013B1512LK04M</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -15056,7 +15056,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>SPVYWB1512LK06M</t>
+          <t>SPVYWB1512LK04M</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -15066,7 +15066,7 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>深蓝</t>
+          <t>米白配粉色</t>
         </is>
       </c>
       <c r="J211" s="1" t="n">
@@ -15103,7 +15103,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>JDYPR261009041013B1512LK04M</t>
+          <t>JDYPR261009041013B1512LK03M</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -15128,7 +15128,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>SPVYWB1512LK04M</t>
+          <t>SPVYWB1512LK03M</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -15138,7 +15138,7 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>米白配粉色</t>
+          <t>米色配黑色</t>
         </is>
       </c>
       <c r="J212" s="1" t="n">
@@ -15175,7 +15175,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>JDYPR261009041013B1512LK03M</t>
+          <t>JDYPR261009041013B1512LK01M</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -15200,7 +15200,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>SPVYWB1512LK03M</t>
+          <t>SPVYWB1512LK01M</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -15210,14 +15210,14 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>米色配黑色</t>
+          <t>黑色</t>
         </is>
       </c>
       <c r="J213" s="1" t="n">
-        <v>100</v>
+        <v>176</v>
       </c>
       <c r="K213" s="1" t="n">
-        <v>100</v>
+        <v>176</v>
       </c>
       <c r="L213" t="inlineStr">
         <is>
@@ -15225,7 +15225,7 @@
         </is>
       </c>
       <c r="M213" s="1" t="n">
-        <v>100</v>
+        <v>176</v>
       </c>
       <c r="N213"/>
       <c r="O213" t="inlineStr">
@@ -15235,29 +15235,29 @@
       </c>
       <c r="P213" t="inlineStr">
         <is>
-          <t>常规补货</t>
+          <t>常规补货(SPVYWB1512LK01M平衡利库调拨，修改时间2026-10-21 10:56:47，调整前申请数量：200.0；调整后申请数量：176.0;)</t>
         </is>
       </c>
     </row>
     <row r="214" customHeight="true" ht="15">
       <c r="A214" t="inlineStr">
         <is>
-          <t>kd</t>
+          <t>江海霞</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>JDYPR261009041013B1512LK01M</t>
+          <t>CGSQ005274</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>创建</t>
+          <t>重新审核</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>2026/10/9</t>
+          <t>2026/9/10</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -15267,47 +15267,47 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>2026/10/9</t>
+          <t>2026/9/10</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>SPVYWB1512LK01M</t>
+          <t>VYGJZ011203</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>圆顶贝壳包</t>
+          <t>定制无纺布袋</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>黑色</t>
+          <t>定制无纺布袋</t>
         </is>
       </c>
       <c r="J214" s="1" t="n">
-        <v>176</v>
+        <v>70</v>
       </c>
       <c r="K214" s="1" t="n">
-        <v>176</v>
+        <v>70</v>
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>2026/11/8 00:00:00</t>
+          <t>2026/9/10 00:00:00</t>
         </is>
       </c>
       <c r="M214" s="1" t="n">
-        <v>176</v>
+        <v>70</v>
       </c>
       <c r="N214"/>
       <c r="O214" t="inlineStr">
         <is>
-          <t>姚鲜珍</t>
+          <t>江海霞</t>
         </is>
       </c>
       <c r="P214" t="inlineStr">
         <is>
-          <t>常规补货(SPVYWB1512LK01M平衡利库调拨，修改时间2026-10-21 10:56:47，调整前申请数量：200.0；调整后申请数量：176.0;)</t>
+          <t>国际站</t>
         </is>
       </c>
     </row>
@@ -15319,7 +15319,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>CGSQ005274</t>
+          <t>CGSQ005272</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -15358,10 +15358,10 @@
         </is>
       </c>
       <c r="J215" s="1" t="n">
-        <v>70</v>
+        <v>520</v>
       </c>
       <c r="K215" s="1" t="n">
-        <v>70</v>
+        <v>520</v>
       </c>
       <c r="L215" t="inlineStr">
         <is>
@@ -15369,7 +15369,7 @@
         </is>
       </c>
       <c r="M215" s="1" t="n">
-        <v>70</v>
+        <v>520</v>
       </c>
       <c r="N215"/>
       <c r="O215" t="inlineStr">
@@ -15386,104 +15386,32 @@
     <row r="216" customHeight="true" ht="15">
       <c r="A216" t="inlineStr">
         <is>
-          <t>江海霞</t>
-        </is>
-      </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>CGSQ005272</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>重新审核</t>
-        </is>
-      </c>
-      <c r="D216" t="inlineStr">
-        <is>
-          <t>2026/9/10</t>
-        </is>
-      </c>
-      <c r="E216" t="inlineStr">
-        <is>
-          <t>未关闭</t>
-        </is>
-      </c>
-      <c r="F216" t="inlineStr">
-        <is>
-          <t>2026/9/10</t>
-        </is>
-      </c>
-      <c r="G216" t="inlineStr">
-        <is>
-          <t>VYGJZ011203</t>
-        </is>
-      </c>
-      <c r="H216" t="inlineStr">
-        <is>
-          <t>定制无纺布袋</t>
-        </is>
-      </c>
-      <c r="I216" t="inlineStr">
-        <is>
-          <t>定制无纺布袋</t>
-        </is>
-      </c>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="B216"/>
+      <c r="C216"/>
+      <c r="D216"/>
+      <c r="E216"/>
+      <c r="F216"/>
+      <c r="G216"/>
+      <c r="H216"/>
+      <c r="I216"/>
       <c r="J216" s="1" t="n">
-        <v>520</v>
+        <v>43324</v>
       </c>
       <c r="K216" s="1" t="n">
-        <v>520</v>
-      </c>
-      <c r="L216" t="inlineStr">
-        <is>
-          <t>2026/9/10 00:00:00</t>
-        </is>
-      </c>
+        <v>43324</v>
+      </c>
+      <c r="L216"/>
       <c r="M216" s="1" t="n">
-        <v>520</v>
-      </c>
-      <c r="N216"/>
-      <c r="O216" t="inlineStr">
-        <is>
-          <t>江海霞</t>
-        </is>
-      </c>
-      <c r="P216" t="inlineStr">
-        <is>
-          <t>国际站</t>
-        </is>
-      </c>
-    </row>
-    <row r="217" customHeight="true" ht="15">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>合计</t>
-        </is>
-      </c>
-      <c r="B217"/>
-      <c r="C217"/>
-      <c r="D217"/>
-      <c r="E217"/>
-      <c r="F217"/>
-      <c r="G217"/>
-      <c r="H217"/>
-      <c r="I217"/>
-      <c r="J217" s="1" t="n">
-        <v>43424</v>
-      </c>
-      <c r="K217" s="1" t="n">
-        <v>43424</v>
-      </c>
-      <c r="L217"/>
-      <c r="M217" s="1" t="n">
-        <v>43424</v>
-      </c>
-      <c r="N217" s="1" t="n">
+        <v>43324</v>
+      </c>
+      <c r="N216" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="O217"/>
-      <c r="P217"/>
+      <c r="O216"/>
+      <c r="P216"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
